--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -665,7 +665,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>CAS3 / CAS3+</t>
+          <t>CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -1077,7 +1077,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -1099,9 +1099,9 @@
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC</t>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>FEM(LCI 이전 생산) / BDC(LCI 이후 생산)</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
           <t>mk3.com, amazon(YGOHUF5662 F20/F21 2011-2017), transpondery.com(전환기 생산일자 확인 권고)</t>
         </is>
       </c>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>2015 LCI 전후 FEM → BDC 전환기 — 생산월·실물 모듈로 구분 필요</t>
         </is>
@@ -1973,7 +1973,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -1995,9 +1995,9 @@
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC</t>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>FEM(LCI 이전 생산) / BDC(LCI 이후 생산)</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2005,9 +2005,9 @@
           <t>bmwpartsdeal.com(2015 228i F22 Key Fob 부품목록), ebay(FEM/BDC F22 키등록)</t>
         </is>
       </c>
-      <c r="N24" s="6" t="inlineStr">
-        <is>
-          <t>FEM → BDC 전환기 — 생산월로 구분</t>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>FEM → BDC 전환기</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>ID46(PCF7945)</t>
         </is>
@@ -4835,9 +4835,9 @@
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="6" t="inlineStr">
-        <is>
-          <t>CAS3 / CAS3+</t>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -4845,9 +4845,9 @@
           <t>automodulelab.com(CAS3+는 2008 중기 변경 이후 모든 E섀시), key-programmer.org(CAS3 ISN)</t>
         </is>
       </c>
-      <c r="N71" s="6" t="inlineStr">
-        <is>
-          <t>2008 중반 CAS3 → CAS3+ 전환 — 생산월로 구분</t>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>2008 중반 CAS3 → CAS3+ 전환</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -5331,9 +5331,9 @@
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC</t>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>FEM(LCI 이전 생산) / BDC(LCI 이후 생산)</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
           <t>press.bmwgroup.com(F30 LCI 07/2015), transpondery.com(전환기 생산일자·모듈로 확인)</t>
         </is>
       </c>
-      <c r="N79" s="6" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr">
         <is>
           <t>F30 LCI 2015.7 — FEM → BDC 전환기</t>
         </is>
@@ -7049,7 +7049,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="6" t="inlineStr">
         <is>
-          <t>FEM / BDC</t>
+          <t>FEM(LCI 이전 생산) / BDC(LCI 이후 생산)</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -7111,9 +7111,9 @@
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC</t>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>FEM(LCI 이전 생산) / BDC(LCI 이후 생산)</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -7121,9 +7121,9 @@
           <t>rpmmotorsport.net(F32 LCI 05/2016~, F36 LCI 05/2016~), thegarageegy.com</t>
         </is>
       </c>
-      <c r="N108" s="6" t="inlineStr">
-        <is>
-          <t>2016.5 LCI 전후 — 생산월로 구분</t>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>2016.5 LCI 전후</t>
         </is>
       </c>
     </row>
@@ -8945,7 +8945,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F139" s="6" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>ID46(PCF7942)</t>
         </is>
@@ -8967,9 +8967,9 @@
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr"/>
-      <c r="L139" s="6" t="inlineStr">
-        <is>
-          <t>CAS2</t>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>CAS2(이전) / CAS3(이후)</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
           <t>amazon(CAS2 E60 2004-2006), scribd(E60 CAS2 ~2006)</t>
         </is>
       </c>
-      <c r="N139" s="6" t="inlineStr">
+      <c r="N139" s="2" t="inlineStr">
         <is>
           <t>CAS2 → CAS3 전환 시점(2006~2007) 원문 미확인</t>
         </is>
@@ -9073,7 +9073,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F141" s="6" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>ID46(PCF7945)</t>
         </is>
@@ -9095,9 +9095,9 @@
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr"/>
-      <c r="L141" s="6" t="inlineStr">
-        <is>
-          <t>CAS3 / CAS3+</t>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
@@ -9105,9 +9105,9 @@
           <t>bestkeysolution.com(5WK49124 = 컴포트액세스 미지원), ebay(KR55WK49147 PN 926886-02), mhhauto.com(2008~ CAS3+ 올키분실 시 ISN 필요)</t>
         </is>
       </c>
-      <c r="N141" s="6" t="inlineStr">
-        <is>
-          <t>2008년부터 암호화 CAS3+ — 생산월 구분</t>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>2008년부터 암호화 CAS3+</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F146" s="6" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953, Hitag Pro/EWS5)</t>
         </is>
@@ -9403,9 +9403,9 @@
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="6" t="inlineStr">
-        <is>
-          <t>CAS4 / CAS4+</t>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>CAS4(2012 중반 이전 생산) / CAS4+(2012 중반 이후 생산, 일부 자료는 2013~)</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
@@ -9413,7 +9413,7 @@
           <t>ebay(2012 F10 535i CAS 7317512), justanswer.com(F07 535i GT CAS4 복구), blog.xhorsetool.com(2012 F10 CAS4, CAS4+는 2013~), automodulelab.com(CAS4+ 2012 중반~2014 후기 생산)</t>
         </is>
       </c>
-      <c r="N146" s="6" t="inlineStr">
+      <c r="N146" s="2" t="inlineStr">
         <is>
           <t>CAS4+ 도입: automodulelab은 2012 중반 이후 생산분, xhorsetool은 2013 F10부터 — 생산월 확인</t>
         </is>
@@ -9873,7 +9873,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F154" s="6" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953, Hitag Pro/EWS5)</t>
         </is>
@@ -9895,9 +9895,9 @@
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="6" t="inlineStr">
-        <is>
-          <t>CAS4 / CAS4+</t>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>CAS4(2012 중반 이전 생산) / CAS4+(2012 중반 이후 생산, 일부 자료는 2013~)</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
@@ -9905,7 +9905,7 @@
           <t>blog.xhorsetool.com(2012 520d F10 CAS4 키추가, CAS4+는 2013~), keystation.co.uk, automodulelab.com(CAS4+ 2012 중반~2014 후기 생산)</t>
         </is>
       </c>
-      <c r="N154" s="6" t="inlineStr">
+      <c r="N154" s="2" t="inlineStr">
         <is>
           <t>CAS4+ 도입: automodulelab은 2012 중반 이후 생산분, xhorsetool은 2013 F10부터 — 생산월 확인</t>
         </is>
@@ -10433,7 +10433,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -10455,9 +10455,9 @@
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr"/>
-      <c r="L163" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3</t>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
@@ -10465,9 +10465,9 @@
           <t>autelscanner.org(BDC03 = G30/G31/G60 2020.7 이후 생산), abrites.com(BN020 BDC2)</t>
         </is>
       </c>
-      <c r="N163" s="6" t="inlineStr">
-        <is>
-          <t>2020.7 LCI부터 BDC3 — 생산월로 구분</t>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>2020.7 LCI부터 BDC3</t>
         </is>
       </c>
     </row>
@@ -10497,7 +10497,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F164" s="6" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -10515,9 +10515,9 @@
       <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="2" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="6" t="inlineStr">
-        <is>
-          <t>BDC3 (일부 BDC2)</t>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
           <t>autelscanner.org(G30 2020.7~ BDC03), go-parts.com(BDC2는 대략 2021년까지)</t>
         </is>
       </c>
-      <c r="N164" s="6" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -11485,7 +11485,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F180" s="6" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>ID46(PCF7942)</t>
         </is>
@@ -11507,9 +11507,9 @@
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="6" t="inlineStr">
-        <is>
-          <t>CAS2</t>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>CAS2(이전) / CAS3(이후)</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
@@ -11517,7 +11517,7 @@
           <t>keyecu.com(CAS2 E60/E63 2004-2006 HU92 KR55WK47)</t>
         </is>
       </c>
-      <c r="N180" s="6" t="inlineStr">
+      <c r="N180" s="2" t="inlineStr">
         <is>
           <t>CAS2 → CAS3 전환 시점 원문 미확인</t>
         </is>
@@ -11609,7 +11609,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F182" s="6" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>ID46(PCF7945A, Hitag2)</t>
         </is>
@@ -11631,9 +11631,9 @@
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="6" t="inlineStr">
-        <is>
-          <t>CAS3 / CAS3+</t>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
@@ -11641,9 +11641,9 @@
           <t>keyecu.com(5WK49145 2006-2011 PCF7945 키리스고), bestkeysolution.com</t>
         </is>
       </c>
-      <c r="N182" s="6" t="inlineStr">
-        <is>
-          <t>2008 CAS3 → CAS3+ 전환 — 생산월 구분</t>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>2008 CAS3 → CAS3+ 전환</t>
         </is>
       </c>
     </row>
@@ -11861,7 +11861,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953, Hitag Pro/EWS5)</t>
         </is>
@@ -11883,9 +11883,9 @@
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="6" t="inlineStr">
-        <is>
-          <t>CAS4 / CAS4+</t>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>CAS4(2012 중반 이전 생산) / CAS4+(2012 중반 이후 생산, 일부 자료는 2013~)</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
@@ -11893,7 +11893,7 @@
           <t>amazon(CAS4 F10 PCF7953 ID49 128bit), keyecu.com(PCF7953/49 CAS4/CAS4+), automodulelab.com(CAS4+ 2012 중반~2014 후기 생산)</t>
         </is>
       </c>
-      <c r="N186" s="6" t="inlineStr">
+      <c r="N186" s="2" t="inlineStr">
         <is>
           <t>CAS4+ 도입: automodulelab은 2012 중반 이후 생산분, xhorsetool은 2013 F10부터 — 생산월 확인</t>
         </is>
@@ -12345,7 +12345,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F194" s="6" t="inlineStr">
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -12367,9 +12367,9 @@
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3</t>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
@@ -12377,9 +12377,9 @@
           <t>bmwpartsdeal.com(2020 M5 F90 키), autelscanner.org(G30계열 2020.7~ BDC03)</t>
         </is>
       </c>
-      <c r="N194" s="6" t="inlineStr">
-        <is>
-          <t>2020.7 LCI 전후 — 생산월 구분</t>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>2020.7 LCI 전후</t>
         </is>
       </c>
     </row>
@@ -13013,7 +13013,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F205" s="6" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>ID46(PCF7942)</t>
         </is>
@@ -13035,9 +13035,9 @@
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
-      <c r="L205" s="6" t="inlineStr">
-        <is>
-          <t>CAS2</t>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>CAS2(이전) / CAS3(이후)</t>
         </is>
       </c>
       <c r="M205" s="2" t="inlineStr">
@@ -13045,7 +13045,7 @@
           <t>keyecu.com(CAS2 E63 2004-2006 HU92)</t>
         </is>
       </c>
-      <c r="N205" s="6" t="inlineStr">
+      <c r="N205" s="2" t="inlineStr">
         <is>
           <t>CAS2 → CAS3 전환기(2006~2007)</t>
         </is>
@@ -13141,7 +13141,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F207" s="6" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>ID46(PCF7945)</t>
         </is>
@@ -13163,9 +13163,9 @@
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr"/>
-      <c r="L207" s="6" t="inlineStr">
-        <is>
-          <t>CAS3 / CAS3+</t>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)</t>
         </is>
       </c>
       <c r="M207" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
           <t>diamondkeysupply.com(CAS3 컴포트/비컴포트), keyecu.com(5WK49145)</t>
         </is>
       </c>
-      <c r="N207" s="6" t="inlineStr">
+      <c r="N207" s="2" t="inlineStr">
         <is>
           <t>2008 CAS3 → CAS3+ 전환</t>
         </is>
@@ -13385,7 +13385,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F211" s="6" t="inlineStr">
+      <c r="F211" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953, Hitag Pro/EWS5)</t>
         </is>
@@ -13407,9 +13407,9 @@
         </is>
       </c>
       <c r="K211" s="2" t="inlineStr"/>
-      <c r="L211" s="6" t="inlineStr">
-        <is>
-          <t>CAS4 / CAS4+</t>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>CAS4(2012 중반 이전 생산) / CAS4+(2012 중반 이후 생산, 일부 자료는 2013~)</t>
         </is>
       </c>
       <c r="M211" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
           <t>amazon(PCF7953 CAS4 6시리즈/M6 F06/F12 2012-2017), abkeys.com(HUF5661), automodulelab.com(CAS4+ 2012 중반~2014 후기 생산)</t>
         </is>
       </c>
-      <c r="N211" s="6" t="inlineStr">
+      <c r="N211" s="2" t="inlineStr">
         <is>
           <t>CAS4+ 도입: automodulelab은 2012 중반 이후 생산분, xhorsetool은 2013 F10부터 — 생산월 확인</t>
         </is>
@@ -13993,7 +13993,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F221" s="6" t="inlineStr">
+      <c r="F221" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -14015,9 +14015,9 @@
         </is>
       </c>
       <c r="K221" s="2" t="inlineStr"/>
-      <c r="L221" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3</t>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M221" s="2" t="inlineStr">
@@ -14025,7 +14025,7 @@
           <t>autoevolution.com(G32 LCI 2020), autelscanner.org(G30계열 2020.7~ BDC03)</t>
         </is>
       </c>
-      <c r="N221" s="6" t="inlineStr">
+      <c r="N221" s="2" t="inlineStr">
         <is>
           <t>2020 LCI 전후 — G30과 같은 전환 추정</t>
         </is>
@@ -14301,7 +14301,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F226" s="6" t="inlineStr">
+      <c r="F226" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953, Hitag Pro/EWS5)</t>
         </is>
@@ -14323,9 +14323,9 @@
         </is>
       </c>
       <c r="K226" s="2" t="inlineStr"/>
-      <c r="L226" s="6" t="inlineStr">
-        <is>
-          <t>CAS4 / CAS4+</t>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>CAS4(2012 중반 이전 생산) / CAS4+(2012 중반 이후 생산, 일부 자료는 2013~)</t>
         </is>
       </c>
       <c r="M226" s="2" t="inlineStr">
@@ -14333,7 +14333,7 @@
           <t>keyecu.com(M6 F06/F12 2012-2017 PCF7953/49), automodulelab.com(2012 중반 이후 CAS4+)</t>
         </is>
       </c>
-      <c r="N226" s="6" t="inlineStr">
+      <c r="N226" s="2" t="inlineStr">
         <is>
           <t>CAS4+ 도입: automodulelab은 2012 중반 이후 생산분, xhorsetool은 2013 F10부터 — 생산월 확인</t>
         </is>
@@ -15465,7 +15465,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F245" s="6" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro/EWS5)</t>
         </is>
@@ -15487,9 +15487,9 @@
         </is>
       </c>
       <c r="K245" s="2" t="inlineStr"/>
-      <c r="L245" s="6" t="inlineStr">
-        <is>
-          <t>CAS4 / CAS4+</t>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>CAS4(2012 중반 이전 생산) / CAS4+(2012 중반 이후 생산, 일부 자료는 2013~)</t>
         </is>
       </c>
       <c r="M245" s="2" t="inlineStr">
@@ -15497,7 +15497,7 @@
           <t>automodulelab.com(CAS4+ 2012 중반~ F01/F02 후기 생산), rpmmotorsport.net(F01/F02/F04 CAS 탈거)</t>
         </is>
       </c>
-      <c r="N245" s="6" t="inlineStr">
+      <c r="N245" s="2" t="inlineStr">
         <is>
           <t>CAS4+ 도입: automodulelab은 2012 중반 이후 생산분, xhorsetool은 2013 F10부터 — 생산월 확인</t>
         </is>
@@ -16025,7 +16025,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F254" s="6" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -16047,9 +16047,9 @@
         </is>
       </c>
       <c r="K254" s="2" t="inlineStr"/>
-      <c r="L254" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3</t>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M254" s="2" t="inlineStr">
@@ -16057,7 +16057,7 @@
           <t>abrites.com(BDC2 대략 2021까지), autelscanner.org(BDC03 G시리즈 2020~)</t>
         </is>
       </c>
-      <c r="N254" s="6" t="inlineStr">
+      <c r="N254" s="2" t="inlineStr">
         <is>
           <t>G11 전용 BDC3 전환 원문 없음</t>
         </is>
@@ -16089,7 +16089,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F255" s="6" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -16111,9 +16111,9 @@
         </is>
       </c>
       <c r="K255" s="2" t="inlineStr"/>
-      <c r="L255" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3</t>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M255" s="2" t="inlineStr">
@@ -16121,7 +16121,7 @@
           <t>tlkeys.com(순정 N5F-ID21A 434MHz), remotefobcentre.com(G11/G12 2015-2022 키)</t>
         </is>
       </c>
-      <c r="N255" s="6" t="inlineStr">
+      <c r="N255" s="2" t="inlineStr">
         <is>
           <t>G11 전용 BDC3 전환 원문 없음</t>
         </is>
@@ -16153,7 +16153,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F256" s="6" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -16175,9 +16175,9 @@
         </is>
       </c>
       <c r="K256" s="2" t="inlineStr"/>
-      <c r="L256" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3</t>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M256" s="2" t="inlineStr">
@@ -16185,7 +16185,7 @@
           <t>ebay(740i 순정 디스플레이키), wikipedia(G11 2015-2022)</t>
         </is>
       </c>
-      <c r="N256" s="6" t="inlineStr">
+      <c r="N256" s="2" t="inlineStr">
         <is>
           <t>G70과 연식 겹침</t>
         </is>
@@ -16857,7 +16857,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F268" s="6" t="inlineStr">
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -16879,9 +16879,9 @@
         </is>
       </c>
       <c r="K268" s="2" t="inlineStr"/>
-      <c r="L268" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3</t>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M268" s="2" t="inlineStr">
@@ -16889,7 +16889,7 @@
           <t>ebay(2020 BMW N5F-ID21A 키), autelscanner.org(G시리즈 2020~ BDC03)</t>
         </is>
       </c>
-      <c r="N268" s="6" t="inlineStr"/>
+      <c r="N268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -17345,7 +17345,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F276" s="6" t="inlineStr">
+      <c r="F276" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -17367,9 +17367,9 @@
         </is>
       </c>
       <c r="K276" s="2" t="inlineStr"/>
-      <c r="L276" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3</t>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M276" s="2" t="inlineStr">
@@ -17377,7 +17377,7 @@
           <t>monacoms.com(M8 F91~F93 2020~ 키), obdii365.com(Autel BDC3: 8시리즈 G14/G15/G16 2020-2024)</t>
         </is>
       </c>
-      <c r="N276" s="6" t="inlineStr"/>
+      <c r="N276" s="2" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -20381,7 +20381,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F325" s="6" t="inlineStr">
+      <c r="F325" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro/EWS5)</t>
         </is>
@@ -20403,9 +20403,9 @@
         </is>
       </c>
       <c r="K325" s="2" t="inlineStr"/>
-      <c r="L325" s="6" t="inlineStr">
-        <is>
-          <t>CAS4 / CAS4+</t>
+      <c r="L325" s="2" t="inlineStr">
+        <is>
+          <t>CAS4(2012 중반 이전 생산) / CAS4+(2012 중반 이후 생산, 일부 자료는 2013~)</t>
         </is>
       </c>
       <c r="M325" s="2" t="inlineStr">
@@ -20413,7 +20413,7 @@
           <t>carandtruckremotes.com(2012 X3 YGOHUF5662 CAS4, PCF7953P EWS5), automodulelab.com(CAS4+ 2012 중반~)</t>
         </is>
       </c>
-      <c r="N325" s="6" t="inlineStr">
+      <c r="N325" s="2" t="inlineStr">
         <is>
           <t>CAS4+ 도입: 2012 중반 이후 생산분(automodulelab) vs 2013~(xhorsetool) — 생산월 확인</t>
         </is>
@@ -20981,7 +20981,7 @@
       <c r="K334" s="9" t="inlineStr"/>
       <c r="L334" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M334" s="9" t="inlineStr">
@@ -21045,7 +21045,7 @@
       <c r="K335" s="9" t="inlineStr"/>
       <c r="L335" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M335" s="9" t="inlineStr">
@@ -21497,7 +21497,7 @@
       <c r="K343" s="9" t="inlineStr"/>
       <c r="L343" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M343" s="9" t="inlineStr">
@@ -21561,7 +21561,7 @@
       <c r="K344" s="9" t="inlineStr"/>
       <c r="L344" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M344" s="9" t="inlineStr">
@@ -22393,7 +22393,7 @@
       <c r="K357" s="9" t="inlineStr"/>
       <c r="L357" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M357" s="9" t="inlineStr">
@@ -22457,7 +22457,7 @@
       <c r="K358" s="9" t="inlineStr"/>
       <c r="L358" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M358" s="9" t="inlineStr">
@@ -22905,7 +22905,7 @@
       <c r="K365" s="9" t="inlineStr"/>
       <c r="L365" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M365" s="9" t="inlineStr">
@@ -22969,7 +22969,7 @@
       <c r="K366" s="9" t="inlineStr"/>
       <c r="L366" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M366" s="9" t="inlineStr">
@@ -23929,7 +23929,7 @@
       <c r="K381" s="9" t="inlineStr"/>
       <c r="L381" s="9" t="inlineStr">
         <is>
-          <t>CAS3 / CAS3+</t>
+          <t>CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)</t>
         </is>
       </c>
       <c r="M381" s="9" t="inlineStr">
@@ -24761,7 +24761,7 @@
       <c r="K394" s="9" t="inlineStr"/>
       <c r="L394" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M394" s="9" t="inlineStr">
@@ -24825,7 +24825,7 @@
       <c r="K395" s="9" t="inlineStr"/>
       <c r="L395" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M395" s="9" t="inlineStr">
@@ -25465,7 +25465,7 @@
       <c r="K405" s="9" t="inlineStr"/>
       <c r="L405" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M405" s="9" t="inlineStr">
@@ -25529,7 +25529,7 @@
       <c r="K406" s="9" t="inlineStr"/>
       <c r="L406" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M406" s="9" t="inlineStr">
@@ -25913,7 +25913,7 @@
       <c r="K412" s="9" t="inlineStr"/>
       <c r="L412" s="9" t="inlineStr">
         <is>
-          <t>CAS3 / CAS3+</t>
+          <t>CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)</t>
         </is>
       </c>
       <c r="M412" s="9" t="inlineStr">
@@ -26809,7 +26809,7 @@
       <c r="K426" s="9" t="inlineStr"/>
       <c r="L426" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M426" s="9" t="inlineStr">
@@ -26873,7 +26873,7 @@
       <c r="K427" s="9" t="inlineStr"/>
       <c r="L427" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M427" s="9" t="inlineStr">
@@ -27513,7 +27513,7 @@
       <c r="K437" s="9" t="inlineStr"/>
       <c r="L437" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M437" s="9" t="inlineStr">
@@ -27577,7 +27577,7 @@
       <c r="K438" s="9" t="inlineStr"/>
       <c r="L438" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M438" s="9" t="inlineStr">
@@ -28025,7 +28025,7 @@
       <c r="K445" s="9" t="inlineStr"/>
       <c r="L445" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M445" s="9" t="inlineStr">
@@ -28089,7 +28089,7 @@
       <c r="K446" s="9" t="inlineStr"/>
       <c r="L446" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M446" s="9" t="inlineStr">
@@ -29801,7 +29801,7 @@
       <c r="K474" s="9" t="inlineStr"/>
       <c r="L474" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M474" s="9" t="inlineStr">
@@ -29865,7 +29865,7 @@
       <c r="K475" s="9" t="inlineStr"/>
       <c r="L475" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M475" s="9" t="inlineStr">
@@ -31889,7 +31889,7 @@
       <c r="K507" s="9" t="inlineStr"/>
       <c r="L507" s="9" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3</t>
+          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M507" s="9" t="inlineStr">
@@ -32279,7 +32279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -32371,64 +32371,71 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>- 주황색: 생산월 기준 전환기(CAS3→CAS3+, CAS4→CAS4+, FEM→BDC, BDC2→BDC3)이거나 출처가 서로 상충하는 경우 — 작업 전 VIN/실물 모듈로 재확인.</t>
+          <t>- 주황색: 출처가 서로 상충하거나 원문으로 직접 확인되지 않은 경우 — 작업 전 VIN/실물 모듈로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>- 하늘색: 연식별 개별 검색을 끝내지 못한 행(웹 검색 한도 200회 도달). 앞서 받은 세대 단위 검색결과로 임시 기입했으며, 다음 작업에서 연식별로 재검색해야 합니다.</t>
+          <t>- 전환기(CAS3→CAS3+, CAS4→CAS4+, FEM→BDC, BDC2→BDC3)는 색 표시 없이 이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
+          <t>- 하늘색: 연식별 개별 검색을 끝내지 못한 행(웹 검색 한도 200회 도달). 앞서 받은 세대 단위 검색결과로 임시 기입했으며, 다음 작업에서 연식별로 재검색해야 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">   대상: X3(F25 2013~, G01, G45), X3 M, X4 전 세대, X4 M, X5 전 세대, X5 M, X6 전 세대, X6 M, X7, XM, Z4 전 세대, i3, i8, i4, iX, iX3, 1M 쿠페</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>※ 조사하며 확인된 주요 사항</t>
-        </is>
-      </c>
+      <c r="A18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>- CAS4/CAS4+ 키의 칩은 PCF7953(Hitag Pro, ID49, EWS5)입니다(이전 초안의 'Hitag2' 표기는 오류였음).</t>
+          <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>- CAS4+ 도입 시점은 자료마다 다릅니다(2012 중반 이후 생산분 vs 2013년 F10부터) — 2012년식은 주황색.</t>
+          <t>- CAS4/CAS4+ 키의 칩은 PCF7953(Hitag Pro, ID49, EWS5)입니다(이전 초안의 'Hitag2' 표기는 오류였음).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>- BDC3는 G30/G31 기준 2020.7 이후 생산분부터(Autel 자료). BDC2 키: N5F-ID21A(9367401-01), 2022년 이후 순정 키: IYZBK1.</t>
+          <t>- CAS4+ 도입 시점은 자료마다 다릅니다(2012 중반 이후 생산분 vs 2013년 F10부터) — 2012년식은 주황색.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>- U섀시(U06/U10/U11)는 BCP 이모빌라이저 + UWB 키(NCF2951/Hitag Pro/ID49, FCC IYZBK1).</t>
+          <t>- BDC3는 G30/G31 기준 2020.7 이후 생산분부터(Autel 자료). BDC2 키: N5F-ID21A(9367401-01), 2022년 이후 순정 키: IYZBK1.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>- U섀시(U06/U10/U11)는 BCP 이모빌라이저 + UWB 키(NCF2951/Hitag Pro/ID49, FCC IYZBK1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>- F40·F44는 G시리즈 전장이라 BDC2/BDC3 표기가 자료마다 다릅니다(주황색).</t>
         </is>

--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -58,12 +58,12 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF9C0006"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -143,13 +143,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -902,7 +902,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>abkeys.com, keyshop-online.com(F20/F21 2011-2017 PCF7953P 적용)</t>
+          <t>abkeys.com, keyshop-online.com(F20/F21 2011-2017 PCF7953P 적용), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>keystation.co.uk, yourcarkeyguys.com(HU100R 비상키), key4.com</t>
+          <t>keystation.co.uk, yourcarkeyguys.com(HU100R 비상키), key4.com, 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>abrites.com(BN016), obdii365.com(F20/F21 2011-2017 FEM)</t>
+          <t>abrites.com(BN016), obdii365.com(F20/F21 2011-2017 FEM), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1077,19 +1077,15 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>FEM(LCI 이전 생산) / BDC(LCI 이후 생산)</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>mk3.com, amazon(YGOHUF5662 F20/F21 2011-2017), transpondery.com(전환기 생산일자 확인 권고)</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2015 LCI 전후 FEM → BDC 전환기 — 생산월·실물 모듈로 구분 필요</t>
-        </is>
-      </c>
+          <t>mk3.com, amazon(YGOHUF5662 F20/F21 2011-2017), transpondery.com(전환기 생산일자 확인 권고), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1137,12 +1133,12 @@
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>keyshop-online.com(2008-2020 HUF5767 OEM), ebay(9367401-01 N5F-ID21A 참고)</t>
+          <t>keyshop-online.com(2008-2020 HUF5767 OEM), ebay(9367401-01 N5F-ID21A 참고), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
@@ -1193,12 +1189,12 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>vvdishop.com(BDC 올키분실), ebay(F20/F21/F40 키등록)</t>
+          <t>vvdishop.com(BDC 올키분실), ebay(F20/F21/F40 키등록), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr"/>
@@ -1249,12 +1245,12 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>ebay.co.uk(F20 F22 F30 433MHz ID49 BDC), amazon(NBGIDGNG1-01)</t>
+          <t>ebay.co.uk(F20 F22 F30 433MHz ID49 BDC), amazon(NBGIDGNG1-01), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
@@ -1305,12 +1301,12 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>keyecu.com, tlkeys.com(PCF7953V), habicare.nz</t>
+          <t>keyecu.com, tlkeys.com(PCF7953V), habicare.nz, 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr"/>
@@ -1341,7 +1337,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -1359,21 +1355,17 @@
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>BDC</t>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>keyshop-online.com(2009-2020 HUF7953), regallocksmiths.co.uk(F20/21 2010-2019)</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>F20 글로벌 생산은 2019년 종료 — 2020년식은 국내 재고분 판매</t>
-        </is>
-      </c>
+          <t>keyshop-online.com(2009-2020 HUF7953), regallocksmiths.co.uk(F20/21 2010-2019), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1401,7 +1393,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro, NCF2951 계열)</t>
         </is>
@@ -1419,21 +1411,17 @@
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (출처 상충)</t>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>keyshop-online.com(G섀시 BDC2 9877472-01), key4.com(N5F-ID21A)</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>F40은 이름만 F, 실제 G시리즈 전장(UKL2/FAAR)</t>
-        </is>
-      </c>
+          <t>keyshop-online.com(G섀시 BDC2 9877472-01), key4.com(N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1461,7 +1449,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro, NCF2951 계열)</t>
         </is>
@@ -1479,17 +1467,17 @@
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (출처 상충)</t>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>maplekeysupply.ca(G시리즈 BDC2 N5F-ID21A), go-parts.com</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr"/>
+          <t>maplekeysupply.ca(G시리즈 BDC2 N5F-ID21A), go-parts.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1517,7 +1505,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro, NCF2951 계열)</t>
         </is>
@@ -1535,21 +1523,17 @@
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (출처 상충)</t>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>mhhauto.com(F40 올키분실: "F40은 BDC-3"), obdii365.com(BDC2 올키분실 2026.5 지원)</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>mhhauto: F40은 BDC-3 → 키 추가 어려움 / 다른 자료는 BDC2 — 출처 상충</t>
-        </is>
-      </c>
+          <t>mhhauto.com(F40 올키분실: "F40은 BDC-3"), obdii365.com(BDC2 올키분실 2026.5 지원), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1577,7 +1561,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro, NCF2951 계열)</t>
         </is>
@@ -1599,17 +1583,17 @@
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (출처 상충)</t>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>auto-keys.eu(G시리즈 OEM 스마트키 N5F-ID2A), abkeys.com(ABK-2338 블레이드)</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr"/>
+          <t>auto-keys.eu(G시리즈 OEM 스마트키 N5F-ID2A), abkeys.com(ABK-2338 블레이드), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1637,7 +1621,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro, NCF2951 계열)</t>
         </is>
@@ -1655,21 +1639,17 @@
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (출처 상충)</t>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>go-parts.com(G시리즈 2016-2025 키), wikipedia(F40 2019-2024 생산)</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>F40 생산 2024.6 종료, 2024.7부터 F70</t>
-        </is>
-      </c>
+          <t>go-parts.com(G시리즈 2016-2025 키), wikipedia(F40 2019-2024 생산), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1697,7 +1677,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro, NCF2951 계열)</t>
         </is>
@@ -1715,21 +1695,17 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (출처 상충)</t>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(F70 2024.7 생산 시작), go-parts.com</t>
-        </is>
-      </c>
-      <c r="N20" s="6" t="inlineStr">
-        <is>
-          <t>국내 2025년식은 재고분 — F70과 연식 겹침</t>
-        </is>
-      </c>
+          <t>wikipedia(F70 2024.7 생산 시작), go-parts.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1742,10 +1718,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="7" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>확인 불가(F70 전용 자료 없음)</t>
         </is>
@@ -1759,7 +1735,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="8" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>BDC3 추정 — 확인 불가</t>
         </is>
@@ -1769,7 +1745,7 @@
           <t>go-parts.com(G시리즈 2016-2025 BDC 키), rallyebmw.com(디지털키 NFC/UWB)</t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr">
+      <c r="N21" s="7" t="inlineStr">
         <is>
           <t>F70(2024.7~) 전용 키/이모빌라이저 자료 검색 안 됨. 디지털키 플러스(UWB) 지원 세대</t>
         </is>
@@ -1786,10 +1762,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr"/>
-      <c r="D22" s="7" t="inlineStr"/>
-      <c r="E22" s="7" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>확인 불가(F70 전용 자료 없음)</t>
         </is>
@@ -1803,7 +1779,7 @@
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>BDC3 추정 — 확인 불가</t>
         </is>
@@ -1813,7 +1789,7 @@
           <t>autelkeytools.com(BDC02/BDC03 키 등록 업데이트), go-parts.com</t>
         </is>
       </c>
-      <c r="N22" s="8" t="inlineStr">
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>F70(2024.7~) 전용 키/이모빌라이저 자료 검색 안 됨. 디지털키 플러스(UWB) 지원 세대</t>
         </is>
@@ -1870,7 +1846,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>amazon(YGOHUF5662 2014-2017 F22/F23), abkeys.com(F시리즈 CAS4/FEM/BDC)</t>
+          <t>amazon(YGOHUF5662 2014-2017 F22/F23), abkeys.com(F시리즈 CAS4/FEM/BDC), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -1925,19 +1901,15 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>FEM(LCI 이전 생산) / BDC(LCI 이후 생산)</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2015 228i F22 Key Fob 부품목록), ebay(FEM/BDC F22 키등록)</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>FEM → BDC 전환기</t>
-        </is>
-      </c>
+          <t>bmwpartsdeal.com(2015 228i F22 Key Fob 부품목록), ebay(FEM/BDC F22 키등록), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1985,12 +1957,12 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>abrites.com(BN016 F시리즈 FEM/BDC/CAS4), wikipedia(F22)</t>
+          <t>abrites.com(BN016 F시리즈 FEM/BDC/CAS4), wikipedia(F22), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr"/>
@@ -2041,12 +2013,12 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>autoecupart.net(F20~F83 ID49 9312538 HUF5767), bmwpartsdeal.com(2017 230i F22 키 부품목록)</t>
+          <t>autoecupart.net(F20~F83 ID49 9312538 HUF5767), bmwpartsdeal.com(2017 230i F22 키 부품목록), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
@@ -2097,19 +2069,15 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>ebay(YGOHUF5662 F22/F25/F32), carkeyhelper.com(F22/F23 2017-2018 BDC1 스마트키)</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>carkeyhelper: 2017-2018 F22/F23용 BDC1·FEM 스마트키 모두 존재</t>
-        </is>
-      </c>
+          <t>ebay(YGOHUF5662 F22/F25/F32), carkeyhelper.com(F22/F23 2017-2018 BDC1 스마트키), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2157,12 +2125,12 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>amazon(NBGIDGNG1-09), ebay(B46 F22/F23 DME·BDC 키세트)</t>
+          <t>amazon(NBGIDGNG1-09), ebay(B46 F22/F23 DME·BDC 키세트), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
@@ -2213,12 +2181,12 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>ebay(66128723575 FEM BDC), monacoms.com(F87/F22/F23 2014-2021 키)</t>
+          <t>ebay(66128723575 FEM BDC), monacoms.com(F87/F22/F23 2014-2021 키), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
@@ -2269,19 +2237,15 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(F22 2013-2021), go-parts.com(2009-2021 CAS/FEM/BDC)</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>F22 마지막 연식, G42로 교체</t>
-        </is>
-      </c>
+          <t>wikipedia(F22 2013-2021), go-parts.com(2009-2021 CAS/FEM/BDC), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2325,19 +2289,15 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>BDC2 (VIN 확인 필요)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(G42 2021.9 생산), keyshop-online.com(G섀시 BDC2)</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>국내 출시 2021년 말</t>
-        </is>
-      </c>
+          <t>wikipedia(G42 2021.9 생산), keyshop-online.com(G섀시 BDC2), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2385,19 +2345,15 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>BDC2 (VIN 확인 필요)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>servicereset.net(G42 2021~ 컴포트액세스 키, CR2032), keyshop-online.com</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>G섀시 BDC2 FCC ID는 연식별로 달라 VIN 확인 권장</t>
-        </is>
-      </c>
+          <t>servicereset.net(G42 2021~ 컴포트액세스 키, CR2032), keyshop-online.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2425,7 +2381,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -2439,21 +2395,17 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (VIN 확인 필요)</t>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>bmwpartsnow.com, instacarkey.com(FEM/BDC), rallyebmw.com</t>
-        </is>
-      </c>
-      <c r="N33" s="6" t="inlineStr">
-        <is>
-          <t>2023년부터 BMW 신품 키는 딜러에서 VIN 맞춤 주문(사전 프로그래밍) 방식</t>
-        </is>
-      </c>
+          <t>bmwpartsnow.com, instacarkey.com(FEM/BDC), rallyebmw.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2481,7 +2433,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -2499,17 +2451,17 @@
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (VIN 확인 필요)</t>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>go-parts.com(2022-2025 2시리즈 키), ebay(F46/G42 순정 8708351)</t>
-        </is>
-      </c>
-      <c r="N34" s="6" t="inlineStr"/>
+          <t>go-parts.com(2022-2025 2시리즈 키), ebay(F46/G42 순정 8708351), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2537,7 +2489,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -2555,21 +2507,17 @@
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="6" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>BDC3</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>obdii365.com(G시리즈 BDC3 KEYDIY KD-X4 키 추가), g87.bimmerpost.com(MY25 LCI 디지털키 플러스), transpondery.com(BDC3/BDC4 = ID49 Hitag Pro 변형)</t>
-        </is>
-      </c>
-      <c r="N35" s="6" t="inlineStr">
-        <is>
-          <t>MY25 LCI 디지털키 플러스(UWB) 적용</t>
-        </is>
-      </c>
+          <t>obdii365.com(G시리즈 BDC3 KEYDIY KD-X4 키 추가), g87.bimmerpost.com(MY25 LCI 디지털키 플러스), transpondery.com(BDC3/BDC4 = ID49 Hitag Pro 변형), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2597,7 +2545,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -2615,17 +2563,17 @@
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="6" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>BDC3</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>uobdii.com(KD-X4 BDC2/BDC3 지원목록), obdii365.com(CGDI K2 BDC2/BDC3 키 복사 2026.9), transpondery.com(BDC3/BDC4 = ID49 Hitag Pro 변형)</t>
-        </is>
-      </c>
-      <c r="N36" s="6" t="inlineStr"/>
+          <t>uobdii.com(KD-X4 BDC2/BDC3 지원목록), obdii365.com(CGDI K2 BDC2/BDC3 키 복사 2026.9), transpondery.com(BDC3/BDC4 = ID49 Hitag Pro 변형), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2653,7 +2601,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -2671,21 +2619,17 @@
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (확인 필요)</t>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>keyecu.com(M2 F87 2015-2017 PCF7953), abrites.com(BN016 FEM/BDC)</t>
-        </is>
-      </c>
-      <c r="N37" s="6" t="inlineStr">
-        <is>
-          <t>F87 초기 생산분 FEM/BDC 여부 원문 미확인</t>
-        </is>
-      </c>
+          <t>keyecu.com(M2 F87 2015-2017 PCF7953), abrites.com(BN016 FEM/BDC), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2733,12 +2677,12 @@
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>ebay(9337244, NBGIDGNG1 2014-2018), ecstuning.com(F87 M2 키)</t>
+          <t>ebay(9337244, NBGIDGNG1 2014-2018), ecstuning.com(F87 M2 키), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
@@ -2769,7 +2713,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -2787,21 +2731,17 @@
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>abrites.com(BN016), automodulelab.com(FEM/BDC 벤치작업: FEM ISN↔DME), mperformance.parts(F87 M2C S55 FEM 61359438730)</t>
-        </is>
-      </c>
-      <c r="N39" s="6" t="inlineStr">
-        <is>
-          <t>M2 컴페티션(S55) 출시 / mperformance.parts: F80·F82·F87 M2C(S55)용 FEM 61359438730 + 키 66129312537 세트 판매 — M2C도 FEM일 가능성</t>
-        </is>
-      </c>
+          <t>abrites.com(BN016), automodulelab.com(FEM/BDC 벤치작업: FEM ISN↔DME), mperformance.parts(F87 M2C S55 FEM 61359438730), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2829,7 +2769,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -2847,21 +2787,17 @@
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2019 M2 Competition 키 부품목록), ebay(HUF5767 8723602), mperformance.parts(F87 M2C S55 FEM 61359438730)</t>
-        </is>
-      </c>
-      <c r="N40" s="6" t="inlineStr">
-        <is>
-          <t>mperformance.parts: F80·F82·F87 M2C(S55)용 FEM 61359438730 + 키 66129312537 세트 판매 — M2C도 FEM일 가능성</t>
-        </is>
-      </c>
+          <t>bmwpartsdeal.com(2019 M2 Competition 키 부품목록), ebay(HUF5767 8723602), mperformance.parts(F87 M2C S55 FEM 61359438730), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2889,7 +2825,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -2907,21 +2843,17 @@
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>amazon(YGOHUF5767 M2 F87), f87.bimmerpost.com, mperformance.parts(F87 M2C S55 FEM 61359438730)</t>
-        </is>
-      </c>
-      <c r="N41" s="6" t="inlineStr">
-        <is>
-          <t>mperformance.parts: F80·F82·F87 M2C(S55)용 FEM 61359438730 + 키 66129312537 세트 판매 — M2C도 FEM일 가능성</t>
-        </is>
-      </c>
+          <t>amazon(YGOHUF5767 M2 F87), f87.bimmerpost.com, mperformance.parts(F87 M2C S55 FEM 61359438730), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2949,7 +2881,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -2967,21 +2899,17 @@
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>pelicanparts.com(F22/F23/F87 2014-2021 키), wikipedia(M2 CS 2020.3 생산), mperformance.parts(F87 M2C S55 FEM 61359438730)</t>
-        </is>
-      </c>
-      <c r="N42" s="6" t="inlineStr">
-        <is>
-          <t>M2 CS 포함 / mperformance.parts: F80·F82·F87 M2C(S55)용 FEM 61359438730 + 키 66129312537 세트 판매 — M2C도 FEM일 가능성</t>
-        </is>
-      </c>
+          <t>pelicanparts.com(F22/F23/F87 2014-2021 키), wikipedia(M2 CS 2020.3 생산), mperformance.parts(F87 M2C S55 FEM 61359438730), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3009,7 +2937,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -3027,21 +2955,17 @@
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>BDC3</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>obdii365.com(Autel IM508/IM608 BDC3 키추가: 2시리즈 G87 2020-2024 포함), transpondery.com(BDC3/BDC4 = ID49 Hitag Pro 변형)</t>
-        </is>
-      </c>
-      <c r="N43" s="6" t="inlineStr">
-        <is>
-          <t>BDC3는 모듈이 아닌 원키에서 이모빌라이저 데이터 획득</t>
-        </is>
-      </c>
+          <t>obdii365.com(Autel IM508/IM608 BDC3 키추가: 2시리즈 G87 2020-2024 포함), transpondery.com(BDC3/BDC4 = ID49 Hitag Pro 변형), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3069,7 +2993,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -3091,17 +3015,17 @@
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="6" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>BDC3</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>abkeys.com(ABK-4629), auto-keys.eu(G시리즈 OEM N5F-ID2A), g87.bimmerpost.com</t>
-        </is>
-      </c>
-      <c r="N44" s="6" t="inlineStr"/>
+          <t>abkeys.com(ABK-4629), auto-keys.eu(G시리즈 OEM N5F-ID2A), g87.bimmerpost.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3129,7 +3053,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -3147,21 +3071,17 @@
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="6" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>BDC3</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>g87.bimmerpost.com(MY25 LCI 디지털키 플러스), amazon(Autel IKEYBW004AL)</t>
-        </is>
-      </c>
-      <c r="N45" s="6" t="inlineStr">
-        <is>
-          <t>MY25 LCI 디지털키 플러스</t>
-        </is>
-      </c>
+          <t>g87.bimmerpost.com(MY25 LCI 디지털키 플러스), amazon(Autel IKEYBW004AL), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3189,7 +3109,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -3207,17 +3127,17 @@
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="6" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>BDC3</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>amazon(Autel IKEYBW004AL 2026), obdii365.com(BDC3 키추가)</t>
-        </is>
-      </c>
-      <c r="N46" s="6" t="inlineStr"/>
+          <t>amazon(Autel IKEYBW004AL 2026), obdii365.com(BDC3 키추가), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3270,7 +3190,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>motospecperformance.com(F45 2014-2017 ID49-PRO BDC), keyshop-online.com</t>
+          <t>motospecperformance.com(F45 2014-2017 ID49-PRO BDC), keyshop-online.com, 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3330,7 +3250,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>ebay.co.uk(F45 2016 3버튼 스마트키), hubauer-shop.de(218d F45 키 부품카탈로그)</t>
+          <t>ebay.co.uk(F45 2016 3버튼 스마트키), hubauer-shop.de(218d F45 키 부품카탈로그), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr"/>
@@ -3382,7 +3302,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>thegarageegy.com(F45 BDC 리모컨 등록 11/2013~04/2018), abrites.com(BN016)</t>
+          <t>thegarageegy.com(F45 BDC 리모컨 등록 11/2013~04/2018), abrites.com(BN016), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr"/>
@@ -3438,7 +3358,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>ebay(IDGNG1 FEM BDC 9337240), autoevolution.com(F45 LCI 2018)</t>
+          <t>ebay(IDGNG1 FEM BDC 9337240), autoevolution.com(F45 LCI 2018), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -3494,7 +3414,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>keyshop-online.com(2009-2019 FEM/BDC ID49), abrites.com(BN016 F45 지원)</t>
+          <t>keyshop-online.com(2009-2019 FEM/BDC ID49), abrites.com(BN016 F45 지원), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr"/>
@@ -3546,7 +3466,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>autodoc.co.uk(F45 220i 2014-2021), keyshop-online.com</t>
+          <t>autodoc.co.uk(F45 220i 2014-2021), keyshop-online.com, 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr"/>
@@ -3602,7 +3522,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>autokeys247.com(F45 2014-2021 3버튼 키)</t>
+          <t>autokeys247.com(F45 2014-2021 3버튼 키), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr"/>
@@ -3633,7 +3553,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -3647,21 +3567,17 @@
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="6" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>BDC</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(F45 → U06 교체), go-parts.com(2014-2024 BDC)</t>
-        </is>
-      </c>
-      <c r="N54" s="6" t="inlineStr">
-        <is>
-          <t>2022년식 F45 자료 별도 확인 안 됨 — 재고분</t>
-        </is>
-      </c>
+          <t>wikipedia(F45 → U06 교체), go-parts.com(2014-2024 BDC), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3861,7 +3777,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>ID49(NCF2951, Hitag Pro)</t>
         </is>
@@ -3879,7 +3795,7 @@
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="6" t="inlineStr">
+      <c r="L58" s="8" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -3889,7 +3805,7 @@
           <t>obdii365.com(Autel IMMO BDC02/BDC03/BCP 키추가), automobile-catalog.com(2025 U06)</t>
         </is>
       </c>
-      <c r="N58" s="6" t="inlineStr">
+      <c r="N58" s="8" t="inlineStr">
         <is>
           <t>2025년식 BCP 적용 원문 직접 확인은 안 됨(2021-2024 목록 기준 연장)</t>
         </is>
@@ -3921,7 +3837,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>ID49(NCF2951, Hitag Pro)</t>
         </is>
@@ -3939,7 +3855,7 @@
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="6" t="inlineStr">
+      <c r="L59" s="8" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -3949,7 +3865,7 @@
           <t>obdii365.com(KEYDIY KD-X4 U섀시 BCP UWB 키 복사)</t>
         </is>
       </c>
-      <c r="N59" s="6" t="inlineStr">
+      <c r="N59" s="8" t="inlineStr">
         <is>
           <t>2026년식 원문 미확인 — 2021-2024 목록 기준</t>
         </is>
@@ -3981,7 +3897,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -3995,21 +3911,17 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (VIN 확인 필요)</t>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2020 228i F44 Key Fob 부품목록), f44.bimmerpost.com(애플 카키)</t>
-        </is>
-      </c>
-      <c r="N60" s="6" t="inlineStr">
-        <is>
-          <t>F44는 F40과 같은 FAAR(G시리즈 전장) — F40처럼 BDC3 적용설 있음</t>
-        </is>
-      </c>
+          <t>bmwpartsdeal.com(2020 228i F44 Key Fob 부품목록), f44.bimmerpost.com(애플 카키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4037,7 +3949,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -4051,17 +3963,17 @@
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (VIN 확인 필요)</t>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>abrites.com(BN020 G/F시리즈 BDC2), uobdii.com(KD-X4 BDC2/BDC3 지원목록)</t>
-        </is>
-      </c>
-      <c r="N61" s="6" t="inlineStr"/>
+          <t>abrites.com(BN020 G/F시리즈 BDC2), uobdii.com(KD-X4 BDC2/BDC3 지원목록), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4089,7 +4001,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -4103,17 +4015,17 @@
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (VIN 확인 필요)</t>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>servicerususa.com(BDC2/BDC3), remkeys.com(BN020)</t>
-        </is>
-      </c>
-      <c r="N62" s="6" t="inlineStr"/>
+          <t>servicerususa.com(BDC2/BDC3), remkeys.com(BN020), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4141,7 +4053,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -4159,17 +4071,17 @@
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (출처 상충)</t>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 530i/740i/M2~M4), bmwpartsdeal.com(F44 키케이스 82292355519)</t>
-        </is>
-      </c>
-      <c r="N63" s="6" t="inlineStr"/>
+          <t>ebay(IYZBK1 2022-2025 530i/740i/M2~M4), bmwpartsdeal.com(F44 키케이스 82292355519), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4197,7 +4109,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -4211,17 +4123,17 @@
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (출처 상충)</t>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>fcpeuro.com, bmwpartsnow.com</t>
-        </is>
-      </c>
-      <c r="N64" s="6" t="inlineStr"/>
+          <t>fcpeuro.com, bmwpartsnow.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4249,7 +4161,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -4267,21 +4179,17 @@
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (출처 상충)</t>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>go-parts.com(228i F44: BDC2 기재), ebay.de(F44 2020-2025 순정 리모컨)</t>
-        </is>
-      </c>
-      <c r="N65" s="6" t="inlineStr">
-        <is>
-          <t>go-parts는 BDC2, mhhauto(F40 동일 전장)는 BDC-3 — 상충</t>
-        </is>
-      </c>
+          <t>go-parts.com(228i F44: BDC2 기재), ebay.de(F44 2020-2025 순정 리모컨), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4294,10 +4202,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr"/>
-      <c r="D66" s="7" t="inlineStr"/>
-      <c r="E66" s="7" t="inlineStr"/>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr"/>
+      <c r="D66" s="6" t="inlineStr"/>
+      <c r="E66" s="6" t="inlineStr"/>
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>확인 불가(F74 전용 자료 없음)</t>
         </is>
@@ -4311,7 +4219,7 @@
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="8" t="inlineStr">
+      <c r="L66" s="7" t="inlineStr">
         <is>
           <t>확인 불가(BCP 추정)</t>
         </is>
@@ -4321,7 +4229,7 @@
           <t>press.bmwgroup.com(2025 2시리즈 그란쿠페: 디지털키 플러스 UWB), wikipedia(F74 2024.11 생산)</t>
         </is>
       </c>
-      <c r="N66" s="8" t="inlineStr">
+      <c r="N66" s="7" t="inlineStr">
         <is>
           <t>F70과 플랫폼 공유(UKL2). 키/이모빌라이저 원문 없음</t>
         </is>
@@ -4338,10 +4246,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr"/>
-      <c r="D67" s="7" t="inlineStr"/>
-      <c r="E67" s="7" t="inlineStr"/>
-      <c r="F67" s="8" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr"/>
+      <c r="D67" s="6" t="inlineStr"/>
+      <c r="E67" s="6" t="inlineStr"/>
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>확인 불가(F74 전용 자료 없음)</t>
         </is>
@@ -4355,7 +4263,7 @@
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="8" t="inlineStr">
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>확인 불가(BCP 추정)</t>
         </is>
@@ -4365,7 +4273,7 @@
           <t>faq.bmwusa.com(2시리즈 GC MY25 디지털키 요건), 딜러 일반 키등록 안내</t>
         </is>
       </c>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4890,7 +4798,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>mk3.com(9312525-04, 9312531-02), remkeys.com(F30 FEM/CAS4+ PCF7953P), digital-kaos.co.uk(2012 F30 FEM)</t>
+          <t>mk3.com(9312525-04, 9312531-02), remkeys.com(F30 FEM/CAS4+ PCF7953P), digital-kaos.co.uk(2012 F30 FEM), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -4950,7 +4858,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>locksmithkeyless.com(2013-2018 FEM YGOHUF5767), autoecupart.net(9312538)</t>
+          <t>locksmithkeyless.com(2013-2018 FEM YGOHUF5767), autoecupart.net(9312538), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr"/>
@@ -5006,7 +4914,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2014 320i F30 키 부품목록), birminghamdiagnostics.co.uk(F20/F30/F32 ID49 PRO 434MHz)</t>
+          <t>bmwpartsdeal.com(2014 320i F30 키 부품목록), birminghamdiagnostics.co.uk(F20/F30/F32 ID49 PRO 434MHz), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr"/>
@@ -5057,19 +4965,15 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>FEM(LCI 이전 생산) / BDC(LCI 이후 생산)</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>press.bmwgroup.com(F30 LCI 07/2015), transpondery.com(전환기 생산일자·모듈로 확인)</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>F30 LCI 2015.7 — FEM → BDC 전환기</t>
-        </is>
-      </c>
+          <t>press.bmwgroup.com(F30 LCI 07/2015), transpondery.com(전환기 생산일자·모듈로 확인), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5117,12 +5021,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>ebay(2016-2018 330i F30 B48 ECU·BCM·키세트 9868383/8692971), locksmithkeyless.com</t>
+          <t>ebay(2016-2018 330i F30 B48 ECU·BCM·키세트 9868383/8692971), locksmithkeyless.com, 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr"/>
@@ -5173,12 +5077,12 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>vvdishop.com(2017 F30 320d FEM/BDC 키추가), abkeys.com(9317128, KEYDIY FGB23)</t>
+          <t>vvdishop.com(2017 F30 320d FEM/BDC 키추가), abkeys.com(9317128, KEYDIY FGB23), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr"/>
@@ -5229,12 +5133,12 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>monacoms.com(F30 2012-2018 키), locksmithkeyless.com(LCD 스마트키 FEM/BDC)</t>
+          <t>monacoms.com(F30 2012-2018 키), locksmithkeyless.com(LCD 스마트키 FEM/BDC), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr"/>
@@ -5285,19 +5189,15 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(F30 2011.10-2019), keyshop-online.com(2009-2019 FEM/BDC)</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>G20과 연식 겹침</t>
-        </is>
-      </c>
+          <t>wikipedia(F30 2011.10-2019), keyshop-online.com(2009-2019 FEM/BDC), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5345,19 +5245,15 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>BDC2</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>walmart/linkobd.com(N5F-ID21A 2019 G20/G30/G32/G11/G15/G29), yourcarkeyguys.com(BDC2 N5F-ID21A)</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>G20 생산 2018.10~</t>
-        </is>
-      </c>
+          <t>walmart/linkobd.com(N5F-ID21A 2019 G20/G30/G32/G11/G15/G29), yourcarkeyguys.com(BDC2 N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5385,7 +5281,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -5403,21 +5299,17 @@
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (출처 상충)</t>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>abrites.com(BN020: BDC2는 대략 2021년까지 G시리즈), obdii365.com(Autel BDC3 목록: G20 2020-2024)</t>
-        </is>
-      </c>
-      <c r="N85" s="6" t="inlineStr">
-        <is>
-          <t>Abrites 기준 BDC2, Autel BDC3 차종목록엔 2020부터 포함 — VIN/모듈 확인</t>
-        </is>
-      </c>
+          <t>abrites.com(BN020: BDC2는 대략 2021년까지 G시리즈), obdii365.com(Autel BDC3 목록: G20 2020-2024), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5445,7 +5337,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -5463,17 +5355,17 @@
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
-      <c r="L86" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (출처 상충)</t>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>recambiosyaccesoriosbmw.com(디스플레이키 66125A66288 G20), keyaccessni.com(G20 2020-2024 스마트키)</t>
-        </is>
-      </c>
-      <c r="N86" s="6" t="inlineStr"/>
+          <t>recambiosyaccesoriosbmw.com(디스플레이키 66125A66288 G20), keyaccessni.com(G20 2020-2024 스마트키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5526,7 +5418,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>go-parts.com(2022-2025 IYZBK1, OEM 5A06C06·5A55D03-04), ebay(IYZBK1 2022-2026)</t>
+          <t>go-parts.com(2022-2025 IYZBK1, OEM 5A06C06·5A55D03-04), ebay(IYZBK1 2022-2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -5586,7 +5478,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>g20.bimmerpost.com(2023+ 키 변경·경량화), turnermotorsport.com(G20 키)</t>
+          <t>g20.bimmerpost.com(2023+ 키 변경·경량화), turnermotorsport.com(G20 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr"/>
@@ -5642,7 +5534,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>obdii365.com(Autel BDC3: G20/G21/G28/G80/G81 2020-2024, Hungary 표기 키 성공률↑)</t>
+          <t>obdii365.com(Autel BDC3: G20/G21/G28/G80/G81 2020-2024, Hungary 표기 키 성공률↑), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr"/>
@@ -5698,7 +5590,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>autel.us(2024/2025 IMMO 키등록 추가), auteltools.eu(BDC02/BDC3 구독)</t>
+          <t>autel.us(2024/2025 IMMO 키등록 추가), auteltools.eu(BDC02/BDC3 구독), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr"/>
@@ -5754,7 +5646,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2026 순정), carsine.com(F/G시리즈 키 2012-2026), wikipedia(G20 2026년식까지)</t>
+          <t>ebay(IYZBK1 2022-2026 순정), carsine.com(F/G시리즈 키 2012-2026), wikipedia(G20 2026년식까지), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr"/>
@@ -5810,7 +5702,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>ecstuning.com(F80 M3 키), mperformance.parts(F80 M3/F82 M4/F87 M2C S55 FEM 61359438730 + 키 66129312537)</t>
+          <t>ecstuning.com(F80 M3 키), mperformance.parts(F80 M3/F82 M4/F87 M2C S55 FEM 61359438730 + 키 66129312537), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -5845,7 +5737,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -5863,21 +5755,17 @@
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
-      <c r="L93" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>go-parts.com(M3 2016~: FEM 또는 BDC), mperformance.parts(F80 M3/F82 M4/F87 M2C S55 FEM 61359438730 + 키 66129312537)</t>
-        </is>
-      </c>
-      <c r="N93" s="6" t="inlineStr">
-        <is>
-          <t>S55 M카는 LCI 후에도 FEM 세트 판매 사례 — 모듈 확인</t>
-        </is>
-      </c>
+          <t>go-parts.com(M3 2016~: FEM 또는 BDC), mperformance.parts(F80 M3/F82 M4/F87 M2C S55 FEM 61359438730 + 키 66129312537), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5905,7 +5793,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -5923,17 +5811,17 @@
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>f80.bimmerpost.com(M3/M4 키), locksmithkeyless.com(FEM 2013-2018)</t>
-        </is>
-      </c>
-      <c r="N94" s="6" t="inlineStr"/>
+          <t>f80.bimmerpost.com(M3/M4 키), locksmithkeyless.com(FEM 2013-2018), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5961,7 +5849,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -5979,17 +5867,17 @@
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>ebay(YGOHUF5767 2015-2018 M3/M4, 8723610-02·8723598·8723602)</t>
-        </is>
-      </c>
-      <c r="N95" s="6" t="inlineStr"/>
+          <t>ebay(YGOHUF5767 2015-2018 M3/M4, 8723610-02·8723598·8723602), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6017,7 +5905,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -6035,17 +5923,17 @@
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>monacoms.com(F80/F82/F83 2014-2020 키), transpondery.com(FEM PCF7953P OEM키 목록)</t>
-        </is>
-      </c>
-      <c r="N96" s="6" t="inlineStr"/>
+          <t>monacoms.com(F80/F82/F83 2014-2020 키), transpondery.com(FEM PCF7953P OEM키 목록), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6073,7 +5961,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -6091,17 +5979,17 @@
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
-      <c r="L97" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>monacoms.com(2014-2020), f80.bimmerpost.com(F시리즈 키 교체)</t>
-        </is>
-      </c>
-      <c r="N97" s="6" t="inlineStr"/>
+          <t>monacoms.com(2014-2020), f80.bimmerpost.com(F시리즈 키 교체), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6129,7 +6017,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -6147,21 +6035,17 @@
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>americankeysupply.com, wikipedia(F80 생산 2014-2018, 국내 판매 2021까지)</t>
-        </is>
-      </c>
-      <c r="N98" s="6" t="inlineStr">
-        <is>
-          <t>글로벌 생산 2018 종료(M3 CS 포함) — 국내 2019~2021년식은 재고/연식 표기분</t>
-        </is>
-      </c>
+          <t>americankeysupply.com, wikipedia(F80 생산 2014-2018, 국내 판매 2021까지), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6189,7 +6073,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -6207,21 +6091,17 @@
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
-      <c r="L99" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (VIN 확인 필요)</t>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>monacoms.com(G80/G82/G83 2021~ 키), g80.bimmerpost.com, transpondery.com(BDC3/BDC4 = ID49)</t>
-        </is>
-      </c>
-      <c r="N99" s="6" t="inlineStr">
-        <is>
-          <t>G80 생산 2021~</t>
-        </is>
-      </c>
+          <t>monacoms.com(G80/G82/G83 2021~ 키), g80.bimmerpost.com, transpondery.com(BDC3/BDC4 = ID49), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6274,7 +6154,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 M2/M3/M4 순정), obdii365.com(Autel BDC3: G80 2020-2024)</t>
+          <t>ebay(IYZBK1 2022-2025 M2/M3/M4 순정), obdii365.com(Autel BDC3: G80 2020-2024), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr"/>
@@ -6330,7 +6210,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>g80.bimmerpost.com(2023 M3 키 코딩), ecstuning.com(G80 키)</t>
+          <t>g80.bimmerpost.com(2023 M3 키 코딩), ecstuning.com(G80 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr"/>
@@ -6386,7 +6266,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>g80.bimmerpost.com(2024 M3 Comp 키), obdii365.com(KEYDIY KD-X4 BDC3 키추가)</t>
+          <t>g80.bimmerpost.com(2024 M3 Comp 키), obdii365.com(KEYDIY KD-X4 BDC3 키추가), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr"/>
@@ -6442,7 +6322,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>ebay(BMW M3 Key G80 2025), go-parts.com(2016-2025 M3 키)</t>
+          <t>ebay(BMW M3 Key G80 2025), go-parts.com(2016-2025 M3 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -6502,7 +6382,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>ebay(2026 M3 G80 OEM 5버튼 스마트키), carkeysexpress.com(2026 M3 키 페어링)</t>
+          <t>ebay(2026 M3 G80 OEM 5버튼 스마트키), carkeysexpress.com(2026 M3 키 페어링), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr"/>
@@ -6558,7 +6438,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>mobilekeysolutions.uk(F32 2012-2019 ID49 433MHz HU100R), locksmithkeyless.com(YGOHUF5662 2009-2018)</t>
+          <t>mobilekeysolutions.uk(F32 2012-2019 ID49 433MHz HU100R), locksmithkeyless.com(YGOHUF5662 2009-2018), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -6618,7 +6498,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>ebay(2014 428i 순정 스마트키), amazon(YGOHUF5662 F32/F36 2014-2017)</t>
+          <t>ebay(2014 428i 순정 스마트키), amazon(YGOHUF5662 F32/F36 2014-2017), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr"/>
@@ -6649,7 +6529,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F107" s="6" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -6667,21 +6547,17 @@
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr"/>
-      <c r="L107" s="6" t="inlineStr">
-        <is>
-          <t>FEM(LCI 이전 생산) / BDC(LCI 이후 생산)</t>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>abrites.com(BN016 F32/F33/F36), rpmmotorsport.net(F32 11/2012-02/2017, LCI 05/2016~)</t>
-        </is>
-      </c>
-      <c r="N107" s="6" t="inlineStr">
-        <is>
-          <t>FEM → BDC 전환 시점(2015 중반 vs 2016 LCI) 자료 상충</t>
-        </is>
-      </c>
+          <t>abrites.com(BN016 F32/F33/F36), rpmmotorsport.net(F32 11/2012-02/2017, LCI 05/2016~), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6729,19 +6605,15 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>FEM(LCI 이전 생산) / BDC(LCI 이후 생산)</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>rpmmotorsport.net(F32 LCI 05/2016~, F36 LCI 05/2016~), thegarageegy.com</t>
-        </is>
-      </c>
-      <c r="N108" s="2" t="inlineStr">
-        <is>
-          <t>2016.5 LCI 전후</t>
-        </is>
-      </c>
+          <t>rpmmotorsport.net(F32 LCI 05/2016~, F36 LCI 05/2016~), thegarageegy.com, 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6789,12 +6661,12 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2018 430i F32·F36 키 부품목록), transpondery.com 검색결과(9317167-02, 69337244)</t>
+          <t>bmwpartsdeal.com(2018 430i F32·F36 키 부품목록), transpondery.com 검색결과(9317167-02, 69337244), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr"/>
@@ -6845,12 +6717,12 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>bmwoforlandpark.com(430i 82292219911), bmwpartsdeal.com(2018 430i F32)</t>
+          <t>bmwoforlandpark.com(430i 82292219911), bmwpartsdeal.com(2018 430i F32), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr"/>
@@ -6901,12 +6773,12 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>ebay(4시리즈 2013-2020 FEM/BDC 키등록), autokeys247.com(F36 2014-2019 3버튼키)</t>
+          <t>ebay(4시리즈 2013-2020 FEM/BDC 키등록), autokeys247.com(F36 2014-2019 3버튼키), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr"/>
@@ -6957,12 +6829,12 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>monacoms.com(F32/F33/F36 2014-2020 키), wikipedia(4시리즈 1세대 2020 종료)</t>
+          <t>monacoms.com(F32/F33/F36 2014-2020 키), wikipedia(4시리즈 1세대 2020 종료), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr"/>
@@ -6993,7 +6865,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F113" s="6" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -7007,17 +6879,17 @@
       <c r="I113" s="2" t="inlineStr"/>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
-      <c r="L113" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (VIN 확인 필요)</t>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(G22 2020.6 출시), go-parts.com(G시리즈 BDC2), ebay(BDC2/BDC3 G시리즈 키복사 서비스)</t>
-        </is>
-      </c>
-      <c r="N113" s="6" t="inlineStr"/>
+          <t>wikipedia(G22 2020.6 출시), go-parts.com(G시리즈 BDC2), ebay(BDC2/BDC3 G시리즈 키복사 서비스), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7074,7 +6946,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 순정 인서트키 포함), pelicanparts.com(G26 430i GC 2022-2023)</t>
+          <t>ebay(IYZBK1 2022-2025 순정 인서트키 포함), pelicanparts.com(G26 430i GC 2022-2023), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr"/>
@@ -7130,7 +7002,7 @@
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>go-parts.com(G22 4버튼 스마트키), obdii365.com(KEYDIY KD-X4 BDC3)</t>
+          <t>go-parts.com(G22 4버튼 스마트키), obdii365.com(KEYDIY KD-X4 BDC3), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr"/>
@@ -7186,7 +7058,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>obdii365.com(Autel BDC3: 4시리즈 G22/G23/G26/G82/G83 2020-2024), amazon(BDC3 2020-2024 키데이터 리더)</t>
+          <t>obdii365.com(Autel BDC3: 4시리즈 G22/G23/G26/G82/G83 2020-2024), amazon(BDC3 2020-2024 키데이터 리더), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -7246,7 +7118,7 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 430 4시리즈 포함)</t>
+          <t>ebay(IYZBK1 2022-2025 430 4시리즈 포함), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr"/>
@@ -7302,7 +7174,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2026), carkeysexpress.com(2026 i4/G26 키 페어링)</t>
+          <t>ebay(IYZBK1 2022-2026), carkeysexpress.com(2026 i4/G26 키 페어링), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr"/>
@@ -7358,7 +7230,7 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>locksmithkeyless.com(FEM 2013-2018 YGOHUF5767), mperformance.parts(F82 M4 S55 FEM 61359438730 + 키 66129312537)</t>
+          <t>locksmithkeyless.com(FEM 2013-2018 YGOHUF5767), mperformance.parts(F82 M4 S55 FEM 61359438730 + 키 66129312537), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr"/>
@@ -7389,7 +7261,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F120" s="6" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -7407,21 +7279,17 @@
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2016 M4 GTS F82 키 부품목록), ebay(2016 M4 F82 4버튼 칩키), mperformance.parts(F82 M4 S55 FEM 61359438730 + 키 66129312537)</t>
-        </is>
-      </c>
-      <c r="N120" s="6" t="inlineStr">
-        <is>
-          <t>S55 M카 FEM 세트 판매 사례 — 모듈 확인</t>
-        </is>
-      </c>
+          <t>bmwpartsdeal.com(2016 M4 GTS F82 키 부품목록), ebay(2016 M4 F82 4버튼 칩키), mperformance.parts(F82 M4 S55 FEM 61359438730 + 키 66129312537), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7449,7 +7317,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F121" s="6" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -7467,17 +7335,17 @@
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr"/>
-      <c r="L121" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>keyecu.com(F80/F82/F83 2013-2017 PCF7953), ebay(2017-2019 F섀시 434MHz)</t>
-        </is>
-      </c>
-      <c r="N121" s="6" t="inlineStr"/>
+          <t>keyecu.com(F80/F82/F83 2013-2017 PCF7953), ebay(2017-2019 F섀시 434MHz), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7505,7 +7373,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F122" s="6" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -7523,17 +7391,17 @@
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr"/>
-      <c r="L122" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2018 M4 F82 키 부품목록), mperformance.parts(F82 M4 S55 FEM 61359438730 + 키 66129312537)</t>
-        </is>
-      </c>
-      <c r="N122" s="6" t="inlineStr"/>
+          <t>bmwpartsdeal.com(2018 M4 F82 키 부품목록), mperformance.parts(F82 M4 S55 FEM 61359438730 + 키 66129312537), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7561,7 +7429,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -7579,17 +7447,17 @@
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr"/>
-      <c r="L123" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>pelicanparts.com(F82/F83 2015-2020 키), ebay(F섀시 2010-2019 FEM/BDC)</t>
-        </is>
-      </c>
-      <c r="N123" s="6" t="inlineStr"/>
+          <t>pelicanparts.com(F82/F83 2015-2020 키), ebay(F섀시 2010-2019 FEM/BDC), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7617,7 +7485,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F124" s="6" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -7635,21 +7503,17 @@
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>realoem.com(F82N M4 CS 키 82795A08684), bmwpartsdeal.com(2019 M4 CS 키)</t>
-        </is>
-      </c>
-      <c r="N124" s="6" t="inlineStr">
-        <is>
-          <t>F82 마지막 생산 2020</t>
-        </is>
-      </c>
+          <t>realoem.com(F82N M4 CS 키 82795A08684), bmwpartsdeal.com(2019 M4 CS 키), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7677,7 +7541,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F125" s="6" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>ID49(PCF7953P, Hitag Pro)</t>
         </is>
@@ -7695,21 +7559,17 @@
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr"/>
-      <c r="L125" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (출처 상충)</t>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>FEM</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>ebay(2015-2020 F80/F82/F83 순정 키), pelicanparts.com(F82/F83 2015-2020)</t>
-        </is>
-      </c>
-      <c r="N125" s="6" t="inlineStr">
-        <is>
-          <t>글로벌 생산 2020 종료 — 국내 2021년식은 재고/연식 표기분</t>
-        </is>
-      </c>
+          <t>ebay(2015-2020 F80/F82/F83 순정 키), pelicanparts.com(F82/F83 2015-2020), 이모빌라이저 검증: 딜러 부품 FEM 61355A7FB57(F22/F23/F30~F36/F80/F82/F83), F30 LCI FEM 매물, M2C FEM 61359438730(2016/09~2019/12)</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7737,7 +7597,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F126" s="6" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -7755,17 +7615,17 @@
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (VIN 확인 필요)</t>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>mpartsworldwide.com(G20·G80·G82·G83 순정 키 2019-2022), locksmithsanantonio.org(G82 2021-2025 BDC)</t>
-        </is>
-      </c>
-      <c r="N126" s="6" t="inlineStr"/>
+          <t>mpartsworldwide.com(G20·G80·G82·G83 순정 키 2019-2022), locksmithsanantonio.org(G82 2021-2025 BDC), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7818,7 +7678,7 @@
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>ebay(2022 M4 G82 S58 ECU·BCM·키 세트), obdii365.com(Autel BDC3: G82 2020-2024)</t>
+          <t>ebay(2022 M4 G82 S58 ECU·BCM·키 세트), obdii365.com(Autel BDC3: G82 2020-2024), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr"/>
@@ -7874,7 +7734,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2026), citymotorsparts.com(2021-2025 M4 G82 순정 스마트키)</t>
+          <t>ebay(IYZBK1 2022-2026), citymotorsparts.com(2021-2025 M4 G82 순정 스마트키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -7934,7 +7794,7 @@
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>ecstuning.com(G82 M4 Comp 키), obdii365.com(Autel BDC3 2020-2024)</t>
+          <t>ecstuning.com(G82 M4 Comp 키), obdii365.com(Autel BDC3 2020-2024), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr"/>
@@ -7990,7 +7850,7 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>citymotorsparts.com(2021-2025 G82 키), amazon(Autel IKEYBW004AL)</t>
+          <t>citymotorsparts.com(2021-2025 G82 키), amazon(Autel IKEYBW004AL), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr"/>
@@ -8046,7 +7906,7 @@
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>amazon(Autel IKEYBW004AL 2026), realoem.com(G82 LCI)</t>
+          <t>amazon(Autel IKEYBW004AL 2026), realoem.com(G82 LCI), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr"/>
@@ -8077,7 +7937,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F132" s="6" t="inlineStr">
+      <c r="F132" s="8" t="inlineStr">
         <is>
           <t>ID44(PCF7935)</t>
         </is>
@@ -8099,7 +7959,7 @@
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="6" t="inlineStr">
+      <c r="L132" s="8" t="inlineStr">
         <is>
           <t>EWS3</t>
         </is>
@@ -8109,7 +7969,7 @@
           <t>uhs-hardware.com(2000-2009 HU92 PCF7935 EWS), autokeys.us(HU92 PCF7935 ID44 3/5/7시리즈)</t>
         </is>
       </c>
-      <c r="N132" s="6" t="inlineStr">
+      <c r="N132" s="8" t="inlineStr">
         <is>
           <t>PCF7935(ID44) = EWS3.x/EWS4.x 공용</t>
         </is>
@@ -8141,7 +8001,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr">
+      <c r="F133" s="8" t="inlineStr">
         <is>
           <t>ID44(PCF7935)</t>
         </is>
@@ -8163,7 +8023,7 @@
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr"/>
-      <c r="L133" s="6" t="inlineStr">
+      <c r="L133" s="8" t="inlineStr">
         <is>
           <t>EWS3</t>
         </is>
@@ -8173,7 +8033,7 @@
           <t>yourcarkeyguys.com(2000-2009 HU92 PCF7935 ID44), diamondkeysupply.com(EWS 리모컨키)</t>
         </is>
       </c>
-      <c r="N133" s="6" t="inlineStr">
+      <c r="N133" s="8" t="inlineStr">
         <is>
           <t>1997-2004 E39는 HU58 4트랙 키도 사용 — 실물 키 확인</t>
         </is>
@@ -8205,7 +8065,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr">
+      <c r="F134" s="8" t="inlineStr">
         <is>
           <t>ID44(PCF7935)</t>
         </is>
@@ -8227,7 +8087,7 @@
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="6" t="inlineStr">
+      <c r="L134" s="8" t="inlineStr">
         <is>
           <t>EWS3 (EWS3D/EWS4.3 병존)</t>
         </is>
@@ -8237,7 +8097,7 @@
           <t>amazon(2002 530i E39 EWS3 ID44 HU58), precisionecu.com(1997-2003 E39 EWS3/EWS3D/EWS4.3)</t>
         </is>
       </c>
-      <c r="N134" s="6" t="inlineStr"/>
+      <c r="N134" s="8" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8517,17 +8377,17 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>CAS2(이전) / CAS3(이후)</t>
+          <t>CAS2</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>amazon(CAS2 E60 2004-2006), scribd(E60 CAS2 ~2006)</t>
+          <t>amazon(CAS2 E60 2004-2006), scribd(E60 CAS2 ~2006), 이모빌라이저 검증: MHH Auto CAS 적용표·bimmerfest(E60 CAS2 2003~2007, LCI CAS3)</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>CAS2 → CAS3 전환 시점(2006~2007) 원문 미확인</t>
+          <t>일부 판매처는 2006~ CAS3 표기 — 국내 2006년식은 LCI(2007.3) 이전 생산분</t>
         </is>
       </c>
     </row>
@@ -8577,17 +8437,17 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>CAS3</t>
+          <t>CAS2(2007.3 LCI 이전 생산) / CAS3(2007.3 LCI 이후 생산)</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>amazon(FLYPIG 525i/528i/530i 2007-2011 KR55WK49123/49127), amazon(TG Auto CAS3 PCF7945 E60)</t>
+          <t>amazon(FLYPIG 525i/528i/530i 2007-2011 KR55WK49123/49127), amazon(TG Auto CAS3 PCF7945 E60), 이모빌라이저 검증: MHH Auto CAS 적용표·bimmerfest(E60 CAS2 2003~2007, LCI CAS3)</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>2007 LCI — CAS3</t>
+          <t>2007.3 LCI 전후 CAS 모듈 상이</t>
         </is>
       </c>
     </row>
@@ -9913,12 +9773,12 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC2(2020.6 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>autelscanner.org(BDC03 = G30/G31/G60 2020.7 이후 생산), abrites.com(BN020 BDC2)</t>
+          <t>autelscanner.org(BDC03 = G30/G31/G60 2020.7 이후 생산), abrites.com(BN020 BDC2), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G30/G31/G32/F90 BDC2 ~2020/06, BDC3 2020/07~)</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -9969,7 +9829,7 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
@@ -10121,7 +9981,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F167" s="6" t="inlineStr">
+      <c r="F167" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -10139,7 +9999,7 @@
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr"/>
-      <c r="L167" s="6" t="inlineStr">
+      <c r="L167" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (출처 상충)</t>
         </is>
@@ -10149,7 +10009,7 @@
           <t>mykeysupply.com(2023-2026 5/7시리즈 스마트키 IYZBK1), wikipedia(G60 2023.7~)</t>
         </is>
       </c>
-      <c r="N167" s="6" t="inlineStr">
+      <c r="N167" s="8" t="inlineStr">
         <is>
           <t>autelscanner는 G60을 BDC03 절차에 포함, 신세대 U/G70 계열은 BCP — 확인 필요</t>
         </is>
@@ -10181,7 +10041,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F168" s="6" t="inlineStr">
+      <c r="F168" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -10199,7 +10059,7 @@
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr"/>
-      <c r="L168" s="6" t="inlineStr">
+      <c r="L168" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (출처 상충)</t>
         </is>
@@ -10209,7 +10069,7 @@
           <t>go-parts.com(2023-2025 5/7시리즈 BDC), bmwnorthwest.com(66125B3E8B9)</t>
         </is>
       </c>
-      <c r="N168" s="6" t="inlineStr"/>
+      <c r="N168" s="8" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -10237,7 +10097,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F169" s="6" t="inlineStr">
+      <c r="F169" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -10255,7 +10115,7 @@
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr"/>
-      <c r="L169" s="6" t="inlineStr">
+      <c r="L169" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (출처 상충)</t>
         </is>
@@ -10265,7 +10125,7 @@
           <t>xhorsetool.com(G/U시리즈 BDC3/BCP 키복사), obdii365.com(KEYDIY BDC3 키복사)</t>
         </is>
       </c>
-      <c r="N169" s="6" t="inlineStr"/>
+      <c r="N169" s="8" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -10293,7 +10153,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F170" s="6" t="inlineStr">
+      <c r="F170" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -10311,7 +10171,7 @@
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="6" t="inlineStr">
+      <c r="L170" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (출처 상충)</t>
         </is>
@@ -10321,7 +10181,7 @@
           <t>g05.bimmerpost.com(2026년식 기본 키 1개 + 디지털키), amazon(Autel IKEYBW004AL)</t>
         </is>
       </c>
-      <c r="N170" s="6" t="inlineStr">
+      <c r="N170" s="8" t="inlineStr">
         <is>
           <t>2026년식은 순정 키 1개 + 디지털키 플러스(UWB) 제공 사례</t>
         </is>
@@ -10353,7 +10213,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F171" s="6" t="inlineStr">
+      <c r="F171" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -10371,7 +10231,7 @@
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr"/>
-      <c r="L171" s="6" t="inlineStr">
+      <c r="L171" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (출처 상충)</t>
         </is>
@@ -10381,7 +10241,7 @@
           <t>mykeysupply.com(2023-2026 5/7시리즈 IYZBK1), wikipedia(G60 2023.7~)</t>
         </is>
       </c>
-      <c r="N171" s="6" t="inlineStr">
+      <c r="N171" s="8" t="inlineStr">
         <is>
           <t>i5 국내 출시 2023.10</t>
         </is>
@@ -10413,7 +10273,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F172" s="6" t="inlineStr">
+      <c r="F172" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -10431,7 +10291,7 @@
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="6" t="inlineStr">
+      <c r="L172" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (출처 상충)</t>
         </is>
@@ -10441,7 +10301,7 @@
           <t>ebay(2024 i5 G60 OEM 5A89449), bmwnorthwest.com(2024 i5 66125B3E8B9)</t>
         </is>
       </c>
-      <c r="N172" s="6" t="inlineStr"/>
+      <c r="N172" s="8" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -10469,7 +10329,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F173" s="6" t="inlineStr">
+      <c r="F173" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -10487,7 +10347,7 @@
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
-      <c r="L173" s="6" t="inlineStr">
+      <c r="L173" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (출처 상충)</t>
         </is>
@@ -10497,7 +10357,7 @@
           <t>go-parts.com(2018-2025 BMW 키), autel.us(2024/2025 IMMO 키등록)</t>
         </is>
       </c>
-      <c r="N173" s="6" t="inlineStr"/>
+      <c r="N173" s="8" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -10525,7 +10385,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F174" s="6" t="inlineStr">
+      <c r="F174" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -10543,7 +10403,7 @@
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="6" t="inlineStr">
+      <c r="L174" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (출처 상충)</t>
         </is>
@@ -10553,7 +10413,7 @@
           <t>g60.bimmerpost.com(신형 i5 키 1개만 제공 사례, 2025.7 생산분은 2개), fieldsbmworlando.com(디지털키 플러스 2026.9)</t>
         </is>
       </c>
-      <c r="N174" s="6" t="inlineStr">
+      <c r="N174" s="8" t="inlineStr">
         <is>
           <t>2026년식 키 1개 + 디지털키 플러스(UWB)/키카드</t>
         </is>
@@ -10909,17 +10769,17 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>CAS2(이전) / CAS3(이후)</t>
+          <t>CAS2</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>keyecu.com(CAS2 E60/E63 2004-2006 HU92 KR55WK47)</t>
+          <t>keyecu.com(CAS2 E60/E63 2004-2006 HU92 KR55WK47), 이모빌라이저 검증: MHH Auto CAS 적용표·bimmerfest(E60 CAS2 2003~2007, LCI CAS3)</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr">
         <is>
-          <t>CAS2 → CAS3 전환 시점 원문 미확인</t>
+          <t>일부 판매처는 2006~ CAS3 표기 — 국내 2006년식은 LCI(2007.3) 이전 생산분</t>
         </is>
       </c>
     </row>
@@ -10969,15 +10829,19 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>CAS3</t>
+          <t>CAS2(2007.3 LCI 이전 생산) / CAS3(2007.3 LCI 이후 생산)</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>locksmithkeyless.com(2006-2010 CAS3+ 컴포트액세스 KR55WK49147), m5board.com(E60 컴포트액세스)</t>
-        </is>
-      </c>
-      <c r="N181" s="2" t="inlineStr"/>
+          <t>locksmithkeyless.com(2006-2010 CAS3+ 컴포트액세스 KR55WK49147), m5board.com(E60 컴포트액세스), 이모빌라이저 검증: MHH Auto CAS 적용표·bimmerfest(E60 CAS2 2003~2007, LCI CAS3)</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>2007.3 LCI 전후 CAS 모듈 상이</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -11713,12 +11577,12 @@
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC2(2020.6 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2020 M5 F90 키), autelscanner.org(G30계열 2020.7~ BDC03)</t>
+          <t>bmwpartsdeal.com(2020 M5 F90 키), autelscanner.org(G30계열 2020.7~ BDC03), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G30/G31/G32/F90 BDC2 ~2020/06, BDC3 2020/07~)</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr">
@@ -11981,7 +11845,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F199" s="6" t="inlineStr">
+      <c r="F199" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -11999,7 +11863,7 @@
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
-      <c r="L199" s="6" t="inlineStr">
+      <c r="L199" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (확인 필요)</t>
         </is>
@@ -12009,7 +11873,7 @@
           <t>g90.bimmerpost.com(G90 M5와 키 공유 차종 문의), go-parts.com(2023-2025 5/7시리즈 BDC)</t>
         </is>
       </c>
-      <c r="N199" s="6" t="inlineStr">
+      <c r="N199" s="8" t="inlineStr">
         <is>
           <t>G90 = G60 기반 PHEV</t>
         </is>
@@ -12041,7 +11905,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F200" s="6" t="inlineStr">
+      <c r="F200" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -12059,7 +11923,7 @@
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
-      <c r="L200" s="6" t="inlineStr">
+      <c r="L200" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (확인 필요)</t>
         </is>
@@ -12069,7 +11933,7 @@
           <t>obdii365.com(Autel BDC2/BDC3/BCP 키복사 2026.1), getbmwparts.com(G90/G99 M5 2025+)</t>
         </is>
       </c>
-      <c r="N200" s="6" t="inlineStr"/>
+      <c r="N200" s="8" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -12097,7 +11961,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F201" s="6" t="inlineStr">
+      <c r="F201" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -12115,7 +11979,7 @@
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
-      <c r="L201" s="6" t="inlineStr">
+      <c r="L201" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (확인 필요)</t>
         </is>
@@ -12125,7 +11989,7 @@
           <t>g90.bimmerpost.com(2026 M5: 키 1개·디지털키 카드·서비스 카드 제공)</t>
         </is>
       </c>
-      <c r="N201" s="6" t="inlineStr">
+      <c r="N201" s="8" t="inlineStr">
         <is>
           <t>2026년식 순정 키 1개 제공 사례</t>
         </is>
@@ -12349,17 +12213,17 @@
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>CAS2(이전) / CAS3(이후)</t>
+          <t>CAS2</t>
         </is>
       </c>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>keyecu.com(CAS2 E63 2004-2006 HU92)</t>
+          <t>keyecu.com(CAS2 E63 2004-2006 HU92), 이모빌라이저 검증: MHH Auto CAS 적용표·bimmerfest(E60 CAS2 2003~2007, LCI CAS3)</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>CAS2 → CAS3 전환기(2006~2007)</t>
+          <t>일부 판매처는 2006~ CAS3 표기 — 국내 2006년식은 LCI(2007.3) 이전 생산분</t>
         </is>
       </c>
     </row>
@@ -12409,17 +12273,17 @@
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>CAS3</t>
+          <t>CAS2(2007.3 LCI 이전 생산) / CAS3(2007.3 LCI 이후 생산)</t>
         </is>
       </c>
       <c r="M206" s="2" t="inlineStr">
         <is>
-          <t>bimmerfest.com(6시리즈 컴포트액세스 2007~), locksmithkeyless.com(2006-2010 CAS3+ 컴포트액세스)</t>
+          <t>bimmerfest.com(6시리즈 컴포트액세스 2007~), locksmithkeyless.com(2006-2010 CAS3+ 컴포트액세스), 이모빌라이저 검증: MHH Auto CAS 적용표·bimmerfest(E60 CAS2 2003~2007, LCI CAS3)</t>
         </is>
       </c>
       <c r="N206" s="2" t="inlineStr">
         <is>
-          <t>2007 LCI</t>
+          <t>2007.3 LCI 전후 CAS 모듈 상이</t>
         </is>
       </c>
     </row>
@@ -13265,12 +13129,12 @@
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC2(2020.6 이전 생산) / BDC3(2020.7 이후 생산)</t>
         </is>
       </c>
       <c r="M221" s="2" t="inlineStr">
         <is>
-          <t>autoevolution.com(G32 LCI 2020), autelscanner.org(G30계열 2020.7~ BDC03)</t>
+          <t>autoevolution.com(G32 LCI 2020), autelscanner.org(G30계열 2020.7~ BDC03), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G30/G31/G32/F90 BDC2 ~2020/06, BDC3 2020/07~)</t>
         </is>
       </c>
       <c r="N221" s="2" t="inlineStr">
@@ -13305,7 +13169,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F222" s="6" t="inlineStr">
+      <c r="F222" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -13319,9 +13183,9 @@
       <c r="I222" s="2" t="inlineStr"/>
       <c r="J222" s="2" t="inlineStr"/>
       <c r="K222" s="2" t="inlineStr"/>
-      <c r="L222" s="6" t="inlineStr">
-        <is>
-          <t>BDC3 (추정)</t>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M222" s="2" t="inlineStr">
@@ -13329,11 +13193,7 @@
           <t>ultimatespecs.com(G32 LCI 2021 48V 마일드하이브리드), autelscanner.org</t>
         </is>
       </c>
-      <c r="N222" s="6" t="inlineStr">
-        <is>
-          <t>G32 전용 BDC3 원문은 없음 — G30 기준 추정</t>
-        </is>
-      </c>
+      <c r="N222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -13361,7 +13221,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F223" s="6" t="inlineStr">
+      <c r="F223" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -13379,9 +13239,9 @@
         </is>
       </c>
       <c r="K223" s="2" t="inlineStr"/>
-      <c r="L223" s="6" t="inlineStr">
-        <is>
-          <t>BDC3 (추정)</t>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M223" s="2" t="inlineStr">
@@ -13389,7 +13249,7 @@
           <t>ebay(IYZBK1 2022-2026), wikipedia(G32 2017-2023)</t>
         </is>
       </c>
-      <c r="N223" s="6" t="inlineStr"/>
+      <c r="N223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -13417,7 +13277,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F224" s="6" t="inlineStr">
+      <c r="F224" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -13435,9 +13295,9 @@
         </is>
       </c>
       <c r="K224" s="2" t="inlineStr"/>
-      <c r="L224" s="6" t="inlineStr">
-        <is>
-          <t>BDC3 (추정)</t>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M224" s="2" t="inlineStr">
@@ -13445,7 +13305,7 @@
           <t>ebay(IYZBK1 2022-2025), wikipedia(G32 2023 종료)</t>
         </is>
       </c>
-      <c r="N224" s="6" t="inlineStr"/>
+      <c r="N224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -13933,7 +13793,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F233" s="6" t="inlineStr">
+      <c r="F233" s="8" t="inlineStr">
         <is>
           <t>ID44(PCF7935)</t>
         </is>
@@ -13951,7 +13811,7 @@
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr"/>
-      <c r="L233" s="6" t="inlineStr">
+      <c r="L233" s="8" t="inlineStr">
         <is>
           <t>EWS3</t>
         </is>
@@ -13961,7 +13821,7 @@
           <t>precisionecu.com(1997-2001 E38 EWS3/EWS3D/EWS4.3), ebay(E38/E39/E46 HU92 EWS ID44)</t>
         </is>
       </c>
-      <c r="N233" s="6" t="inlineStr"/>
+      <c r="N233" s="8" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -13989,7 +13849,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F234" s="6" t="inlineStr">
+      <c r="F234" s="8" t="inlineStr">
         <is>
           <t>ID44(PCF7935)</t>
         </is>
@@ -14007,7 +13867,7 @@
         </is>
       </c>
       <c r="K234" s="2" t="inlineStr"/>
-      <c r="L234" s="6" t="inlineStr">
+      <c r="L234" s="8" t="inlineStr">
         <is>
           <t>EWS3</t>
         </is>
@@ -14017,7 +13877,7 @@
           <t>maxcoolautoparts.com.au(E46/E39/E38 315MHz ID44 HU92), autokeycenter.com(IR EWS HU92)</t>
         </is>
       </c>
-      <c r="N234" s="6" t="inlineStr">
+      <c r="N234" s="8" t="inlineStr">
         <is>
           <t>HU58 블레이드 키도 존재 — 실물 확인</t>
         </is>
@@ -14074,7 +13934,7 @@
       </c>
       <c r="M235" s="2" t="inlineStr">
         <is>
-          <t>royalkeysupply.com(2002-2008 7시리즈 CAS1 LX8766S PN 6959044), abkeys.com(CAS1 2002+ PCF7942)</t>
+          <t>royalkeysupply.com(2002-2008 7시리즈 CAS1 LX8766S PN 6959044), abkeys.com(CAS1 2002+ PCF7942), 이모빌라이저 검증: MHH Auto CAS 적용표(E65 CAS1 ~2005 LCI, 이후 CAS2)</t>
         </is>
       </c>
       <c r="N235" s="2" t="inlineStr">
@@ -14134,7 +13994,7 @@
       </c>
       <c r="M236" s="2" t="inlineStr">
         <is>
-          <t>amazon(2002-2008 745i/750i/760i LX8766S CAS1), transpondery.com(7er E65 CAS1 키 설명)</t>
+          <t>amazon(2002-2008 745i/750i/760i LX8766S CAS1), transpondery.com(7er E65 CAS1 키 설명), 이모빌라이저 검증: MHH Auto CAS 적용표(E65 CAS1 ~2005 LCI, 이후 CAS2)</t>
         </is>
       </c>
       <c r="N236" s="2" t="inlineStr"/>
@@ -14190,7 +14050,7 @@
       </c>
       <c r="M237" s="2" t="inlineStr">
         <is>
-          <t>justanswer.com(2004 745i 스마트키), abkeys.com(CAS1 315/868MHz)</t>
+          <t>justanswer.com(2004 745i 스마트키), abkeys.com(CAS1 315/868MHz), 이모빌라이저 검증: MHH Auto CAS 적용표(E65 CAS1 ~2005 LCI, 이후 CAS2)</t>
         </is>
       </c>
       <c r="N237" s="2" t="inlineStr"/>
@@ -14221,7 +14081,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F238" s="6" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>ID46(PCF7942)</t>
         </is>
@@ -14239,19 +14099,19 @@
         </is>
       </c>
       <c r="K238" s="2" t="inlineStr"/>
-      <c r="L238" s="6" t="inlineStr">
-        <is>
-          <t>CAS1 / CAS2 (출처 상충)</t>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>CAS1(2005 LCI 이전 생산) / CAS2(2005 LCI 이후 생산)</t>
         </is>
       </c>
       <c r="M238" s="2" t="inlineStr">
         <is>
-          <t>key-programmer.com 검색결과(7시리즈 CAS1 2002-2004, CAS2 2005-2008), abkeys.com(CAS1 2002+)</t>
-        </is>
-      </c>
-      <c r="N238" s="6" t="inlineStr">
-        <is>
-          <t>7시리즈 2005 LCI 이후 CAS2라는 자료 vs 전 기간 CAS1 자료 상충</t>
+          <t>key-programmer.com 검색결과(7시리즈 CAS1 2002-2004, CAS2 2005-2008), abkeys.com(CAS1 2002+), 이모빌라이저 검증: MHH Auto CAS 적용표(E65 CAS1 ~2005 LCI, 이후 CAS2)</t>
+        </is>
+      </c>
+      <c r="N238" s="2" t="inlineStr">
+        <is>
+          <t>2005 LCI 전후 CAS 모듈 상이</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14141,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F239" s="6" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>ID46(PCF7942)</t>
         </is>
@@ -14299,17 +14159,17 @@
         </is>
       </c>
       <c r="K239" s="2" t="inlineStr"/>
-      <c r="L239" s="6" t="inlineStr">
-        <is>
-          <t>CAS1 / CAS2 (출처 상충)</t>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>CAS2</t>
         </is>
       </c>
       <c r="M239" s="2" t="inlineStr">
         <is>
-          <t>keyecu.com(CAS1 E65/E66/E67 2006-2011 LX8766S), autoecupart.net(CAS1 2002-2008 ID7942/7944)</t>
-        </is>
-      </c>
-      <c r="N239" s="6" t="inlineStr"/>
+          <t>keyecu.com(CAS1 E65/E66/E67 2006-2011 LX8766S), autoecupart.net(CAS1 2002-2008 ID7942/7944), 이모빌라이저 검증: MHH Auto CAS 적용표(E65 CAS1 ~2005 LCI, 이후 CAS2)</t>
+        </is>
+      </c>
+      <c r="N239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -14337,7 +14197,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F240" s="6" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>ID46(PCF7942)</t>
         </is>
@@ -14355,17 +14215,17 @@
         </is>
       </c>
       <c r="K240" s="2" t="inlineStr"/>
-      <c r="L240" s="6" t="inlineStr">
-        <is>
-          <t>CAS1 / CAS2 (출처 상충)</t>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>CAS2</t>
         </is>
       </c>
       <c r="M240" s="2" t="inlineStr">
         <is>
-          <t>fasterautokeys.com(CAS 7시리즈 2001-2008), precisionecu.com(2002-2008 E65/E66/E67)</t>
-        </is>
-      </c>
-      <c r="N240" s="6" t="inlineStr"/>
+          <t>fasterautokeys.com(CAS 7시리즈 2001-2008), precisionecu.com(2002-2008 E65/E66/E67), 이모빌라이저 검증: MHH Auto CAS 적용표(E65 CAS1 ~2005 LCI, 이후 CAS2)</t>
+        </is>
+      </c>
+      <c r="N240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -14393,7 +14253,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F241" s="6" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>ID46(PCF7942)</t>
         </is>
@@ -14411,17 +14271,17 @@
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr"/>
-      <c r="L241" s="6" t="inlineStr">
-        <is>
-          <t>CAS1 / CAS2 (출처 상충)</t>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>CAS2</t>
         </is>
       </c>
       <c r="M241" s="2" t="inlineStr">
         <is>
-          <t>ebay(2002-2008 E65/E66/E67 리모컨키), autokeystore.com(E65 CAS1 868MHz)</t>
-        </is>
-      </c>
-      <c r="N241" s="6" t="inlineStr"/>
+          <t>ebay(2002-2008 E65/E66/E67 리모컨키), autokeystore.com(E65 CAS1 868MHz), 이모빌라이저 검증: MHH Auto CAS 적용표(E65 CAS1 ~2005 LCI, 이후 CAS2)</t>
+        </is>
+      </c>
+      <c r="N241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -15105,17 +14965,17 @@
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>BDC2</t>
+          <t>BDC2(2019.2 이전 생산) / BDC3(2019.3 이후 생산)</t>
         </is>
       </c>
       <c r="M253" s="2" t="inlineStr">
         <is>
-          <t>keyecu.com(BDM G11 2015-2019), turnermotorsport.com</t>
+          <t>keyecu.com(BDM G11 2015-2019), turnermotorsport.com, 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G11/G12 BDC2 ~2019/02, BDC3 2019/03~)</t>
         </is>
       </c>
       <c r="N253" s="2" t="inlineStr">
         <is>
-          <t>2019 LCI</t>
+          <t>2019 LCI 시점 BDC3 전환</t>
         </is>
       </c>
     </row>
@@ -15165,19 +15025,15 @@
       <c r="K254" s="2" t="inlineStr"/>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M254" s="2" t="inlineStr">
         <is>
-          <t>abrites.com(BDC2 대략 2021까지), autelscanner.org(BDC03 G시리즈 2020~)</t>
-        </is>
-      </c>
-      <c r="N254" s="2" t="inlineStr">
-        <is>
-          <t>G11 전용 BDC3 전환 원문 없음</t>
-        </is>
-      </c>
+          <t>abrites.com(BDC2 대략 2021까지), autelscanner.org(BDC03 G시리즈 2020~), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G11/G12 BDC3 2019/03~)</t>
+        </is>
+      </c>
+      <c r="N254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -15225,19 +15081,15 @@
       <c r="K255" s="2" t="inlineStr"/>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M255" s="2" t="inlineStr">
         <is>
-          <t>tlkeys.com(순정 N5F-ID21A 434MHz), remotefobcentre.com(G11/G12 2015-2022 키)</t>
-        </is>
-      </c>
-      <c r="N255" s="2" t="inlineStr">
-        <is>
-          <t>G11 전용 BDC3 전환 원문 없음</t>
-        </is>
-      </c>
+          <t>tlkeys.com(순정 N5F-ID21A 434MHz), remotefobcentre.com(G11/G12 2015-2022 키), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G11/G12 BDC3 2019/03~)</t>
+        </is>
+      </c>
+      <c r="N255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -15285,19 +15137,15 @@
       <c r="K256" s="2" t="inlineStr"/>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M256" s="2" t="inlineStr">
         <is>
-          <t>ebay(740i 순정 디스플레이키), wikipedia(G11 2015-2022)</t>
-        </is>
-      </c>
-      <c r="N256" s="2" t="inlineStr">
-        <is>
-          <t>G70과 연식 겹침</t>
-        </is>
-      </c>
+          <t>ebay(740i 순정 디스플레이키), wikipedia(G11 2015-2022), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G11/G12 BDC3 2019/03~)</t>
+        </is>
+      </c>
+      <c r="N256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -15325,7 +15173,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F257" s="6" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -15343,21 +15191,17 @@
         </is>
       </c>
       <c r="K257" s="2" t="inlineStr"/>
-      <c r="L257" s="6" t="inlineStr">
-        <is>
-          <t>BCP (추정)</t>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="M257" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 740i/760i), wikipedia(G70 2022.7 생산)</t>
-        </is>
-      </c>
-      <c r="N257" s="6" t="inlineStr">
-        <is>
-          <t>g07.bimmerpost: i7 등 i모델 컴포트액세스는 BCP 모듈 제어</t>
-        </is>
-      </c>
+          <t>ebay(IYZBK1 2022-2025 740i/760i), wikipedia(G70 2022.7 생산), 이모빌라이저 검증: 딜러 부품 카탈로그 i7 "Control u.basic computing platform (BCP)" 61355A9A210</t>
+        </is>
+      </c>
+      <c r="N257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -15385,7 +15229,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F258" s="6" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -15403,21 +15247,17 @@
         </is>
       </c>
       <c r="K258" s="2" t="inlineStr"/>
-      <c r="L258" s="6" t="inlineStr">
-        <is>
-          <t>BCP (추정)</t>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="M258" s="2" t="inlineStr">
         <is>
-          <t>mykeysupply.com(2023-2026 5/7시리즈 OEM IYZBK1), carandtruckremotes.com(2023 7시리즈 키등록)</t>
-        </is>
-      </c>
-      <c r="N258" s="6" t="inlineStr">
-        <is>
-          <t>2023~ 신품 키는 딜러 VIN 주문</t>
-        </is>
-      </c>
+          <t>mykeysupply.com(2023-2026 5/7시리즈 OEM IYZBK1), carandtruckremotes.com(2023 7시리즈 키등록), 이모빌라이저 검증: 딜러 부품 카탈로그 i7 "Control u.basic computing platform (BCP)" 61355A9A210</t>
+        </is>
+      </c>
+      <c r="N258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -15445,7 +15285,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F259" s="6" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -15463,17 +15303,17 @@
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr"/>
-      <c r="L259" s="6" t="inlineStr">
-        <is>
-          <t>BCP (추정)</t>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="M259" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 740i), fcpeuro.com(740i 키)</t>
-        </is>
-      </c>
-      <c r="N259" s="6" t="inlineStr"/>
+          <t>ebay(IYZBK1 2022-2025 740i), fcpeuro.com(740i 키), 이모빌라이저 검증: 딜러 부품 카탈로그 i7 "Control u.basic computing platform (BCP)" 61355A9A210</t>
+        </is>
+      </c>
+      <c r="N259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -15501,7 +15341,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F260" s="6" t="inlineStr">
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -15519,17 +15359,17 @@
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr"/>
-      <c r="L260" s="6" t="inlineStr">
-        <is>
-          <t>BCP (추정)</t>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="M260" s="2" t="inlineStr">
         <is>
-          <t>mykeysupply.com(2023-2026 5/7시리즈), go-parts.com(2016-2025 G시리즈)</t>
-        </is>
-      </c>
-      <c r="N260" s="6" t="inlineStr"/>
+          <t>mykeysupply.com(2023-2026 5/7시리즈), go-parts.com(2016-2025 G시리즈), 이모빌라이저 검증: 딜러 부품 카탈로그 i7 "Control u.basic computing platform (BCP)" 61355A9A210</t>
+        </is>
+      </c>
+      <c r="N260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -15557,7 +15397,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F261" s="6" t="inlineStr">
+      <c r="F261" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -15575,17 +15415,17 @@
         </is>
       </c>
       <c r="K261" s="2" t="inlineStr"/>
-      <c r="L261" s="6" t="inlineStr">
-        <is>
-          <t>BCP (추정)</t>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="M261" s="2" t="inlineStr">
         <is>
-          <t>mykeysupply.com(2023-2026 IYZBK1), faq.bmwusa.com(디지털키 요건)</t>
-        </is>
-      </c>
-      <c r="N261" s="6" t="inlineStr"/>
+          <t>mykeysupply.com(2023-2026 IYZBK1), faq.bmwusa.com(디지털키 요건), 이모빌라이저 검증: 딜러 부품 카탈로그 i7 "Control u.basic computing platform (BCP)" 61355A9A210</t>
+        </is>
+      </c>
+      <c r="N261" s="2" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -15613,7 +15453,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F262" s="6" t="inlineStr">
+      <c r="F262" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -15631,21 +15471,17 @@
         </is>
       </c>
       <c r="K262" s="2" t="inlineStr"/>
-      <c r="L262" s="6" t="inlineStr">
-        <is>
-          <t>BCP (추정)</t>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="M262" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 740i/760i), wikipedia(G70 2022.7 생산)</t>
-        </is>
-      </c>
-      <c r="N262" s="6" t="inlineStr">
-        <is>
-          <t>g07.bimmerpost: i7 등 i모델 컴포트액세스는 BCP 모듈 제어</t>
-        </is>
-      </c>
+          <t>ebay(IYZBK1 2022-2025 740i/760i), wikipedia(G70 2022.7 생산), 이모빌라이저 검증: 딜러 부품 카탈로그 i7 "Control u.basic computing platform (BCP)" 61355A9A210</t>
+        </is>
+      </c>
+      <c r="N262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -15673,7 +15509,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F263" s="6" t="inlineStr">
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -15691,21 +15527,17 @@
         </is>
       </c>
       <c r="K263" s="2" t="inlineStr"/>
-      <c r="L263" s="6" t="inlineStr">
-        <is>
-          <t>BCP (추정)</t>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="M263" s="2" t="inlineStr">
         <is>
-          <t>mykeysupply.com(2023-2026 5/7시리즈 OEM IYZBK1), carandtruckremotes.com(2023 7시리즈 키등록)</t>
-        </is>
-      </c>
-      <c r="N263" s="6" t="inlineStr">
-        <is>
-          <t>2023~ 신품 키는 딜러 VIN 주문</t>
-        </is>
-      </c>
+          <t>mykeysupply.com(2023-2026 5/7시리즈 OEM IYZBK1), carandtruckremotes.com(2023 7시리즈 키등록), 이모빌라이저 검증: 딜러 부품 카탈로그 i7 "Control u.basic computing platform (BCP)" 61355A9A210</t>
+        </is>
+      </c>
+      <c r="N263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -15733,7 +15565,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F264" s="6" t="inlineStr">
+      <c r="F264" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -15751,17 +15583,17 @@
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr"/>
-      <c r="L264" s="6" t="inlineStr">
-        <is>
-          <t>BCP (추정)</t>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="M264" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 740i), fcpeuro.com(740i 키)</t>
-        </is>
-      </c>
-      <c r="N264" s="6" t="inlineStr"/>
+          <t>ebay(IYZBK1 2022-2025 740i), fcpeuro.com(740i 키), 이모빌라이저 검증: 딜러 부품 카탈로그 i7 "Control u.basic computing platform (BCP)" 61355A9A210</t>
+        </is>
+      </c>
+      <c r="N264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -15789,7 +15621,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F265" s="6" t="inlineStr">
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -15807,17 +15639,17 @@
         </is>
       </c>
       <c r="K265" s="2" t="inlineStr"/>
-      <c r="L265" s="6" t="inlineStr">
-        <is>
-          <t>BCP (추정)</t>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="M265" s="2" t="inlineStr">
         <is>
-          <t>mykeysupply.com(2023-2026 5/7시리즈), go-parts.com(2016-2025 G시리즈)</t>
-        </is>
-      </c>
-      <c r="N265" s="6" t="inlineStr"/>
+          <t>mykeysupply.com(2023-2026 5/7시리즈), go-parts.com(2016-2025 G시리즈), 이모빌라이저 검증: 딜러 부품 카탈로그 i7 "Control u.basic computing platform (BCP)" 61355A9A210</t>
+        </is>
+      </c>
+      <c r="N265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -15845,7 +15677,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F266" s="6" t="inlineStr">
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -15863,17 +15695,17 @@
         </is>
       </c>
       <c r="K266" s="2" t="inlineStr"/>
-      <c r="L266" s="6" t="inlineStr">
-        <is>
-          <t>BCP (추정)</t>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="M266" s="2" t="inlineStr">
         <is>
-          <t>mykeysupply.com(2023-2026 IYZBK1), faq.bmwusa.com(디지털키 요건)</t>
-        </is>
-      </c>
-      <c r="N266" s="6" t="inlineStr"/>
+          <t>mykeysupply.com(2023-2026 IYZBK1), faq.bmwusa.com(디지털키 요건), 이모빌라이저 검증: 딜러 부품 카탈로그 i7 "Control u.basic computing platform (BCP)" 61355A9A210</t>
+        </is>
+      </c>
+      <c r="N266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -15921,19 +15753,15 @@
       <c r="K267" s="2" t="inlineStr"/>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t>BDC2</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M267" s="2" t="inlineStr">
         <is>
-          <t>walmart(N5F-ID21A 2019 BDM G15 포함), locksmithkeyless.com(2014-2023 N5F-ID21A 9367401-01)</t>
-        </is>
-      </c>
-      <c r="N267" s="2" t="inlineStr">
-        <is>
-          <t>G15 2018~ 생산</t>
-        </is>
-      </c>
+          <t>walmart(N5F-ID21A 2019 BDM G15 포함), locksmithkeyless.com(2014-2023 N5F-ID21A 9367401-01), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -15981,12 +15809,12 @@
       <c r="K268" s="2" t="inlineStr"/>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M268" s="2" t="inlineStr">
         <is>
-          <t>ebay(2020 BMW N5F-ID21A 키), autelscanner.org(G시리즈 2020~ BDC03)</t>
+          <t>ebay(2020 BMW N5F-ID21A 키), autelscanner.org(G시리즈 2020~ BDC03), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N268" s="2" t="inlineStr"/>
@@ -16042,7 +15870,7 @@
       </c>
       <c r="M269" s="2" t="inlineStr">
         <is>
-          <t>obdii365.com(Autel BDC3 8시리즈 G14/G15/G16 2020-2024), go-parts.com(8시리즈 디스플레이키)</t>
+          <t>obdii365.com(Autel BDC3 8시리즈 G14/G15/G16 2020-2024), go-parts.com(8시리즈 디스플레이키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N269" s="2" t="inlineStr"/>
@@ -16098,7 +15926,7 @@
       </c>
       <c r="M270" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 840i·M5·M8), f92.bimmerpost.com(22년식 840i 추가 키)</t>
+          <t>ebay(IYZBK1 2022-2025 840i·M5·M8), f92.bimmerpost.com(22년식 840i 추가 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N270" s="2" t="inlineStr"/>
@@ -16154,7 +15982,7 @@
       </c>
       <c r="M271" s="2" t="inlineStr">
         <is>
-          <t>f92.bimmerpost.com(2023 키), obdii365.com(Autel BDC3 2020-2024)</t>
+          <t>f92.bimmerpost.com(2023 키), obdii365.com(Autel BDC3 2020-2024), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N271" s="2" t="inlineStr"/>
@@ -16210,7 +16038,7 @@
       </c>
       <c r="M272" s="2" t="inlineStr">
         <is>
-          <t>classic.com(2024 840i G15), bmwofbloomfield.com(2024 M8 GC 키리스 부품)</t>
+          <t>classic.com(2024 840i G15), bmwofbloomfield.com(2024 M8 GC 키리스 부품), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N272" s="2" t="inlineStr"/>
@@ -16266,7 +16094,7 @@
       </c>
       <c r="M273" s="2" t="inlineStr">
         <is>
-          <t>go-parts.com(2016-2025 G시리즈 키), amazon(Autel IKEYBW004AL)</t>
+          <t>go-parts.com(2016-2025 G시리즈 키), amazon(Autel IKEYBW004AL), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N273" s="2" t="inlineStr"/>
@@ -16322,7 +16150,7 @@
       </c>
       <c r="M274" s="2" t="inlineStr">
         <is>
-          <t>graysonbmw.com(2026 8시리즈 FAQ: 2026 파이널 에디션), ebay(IYZBK1 2022-2026)</t>
+          <t>graysonbmw.com(2026 8시리즈 FAQ: 2026 파이널 에디션), ebay(IYZBK1 2022-2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N274" s="2" t="inlineStr">
@@ -16377,19 +16205,15 @@
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>BDC2</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M275" s="2" t="inlineStr">
         <is>
-          <t>wikipedia(M8 F91/F92 2019.6, F93 2019.10), bmwpartsdeal.com(2020 M8 F92/F91 키 부품목록)</t>
-        </is>
-      </c>
-      <c r="N275" s="2" t="inlineStr">
-        <is>
-          <t>M8 섀시코드 F91/F92/F93</t>
-        </is>
-      </c>
+          <t>wikipedia(M8 F91/F92 2019.6, F93 2019.10), bmwpartsdeal.com(2020 M8 F92/F91 키 부품목록), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N275" s="2" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -16437,12 +16261,12 @@
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M276" s="2" t="inlineStr">
         <is>
-          <t>monacoms.com(M8 F91~F93 2020~ 키), obdii365.com(Autel BDC3: 8시리즈 G14/G15/G16 2020-2024)</t>
+          <t>monacoms.com(M8 F91~F93 2020~ 키), obdii365.com(Autel BDC3: 8시리즈 G14/G15/G16 2020-2024), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N276" s="2" t="inlineStr"/>
@@ -16498,7 +16322,7 @@
       </c>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t>obdii365.com(Autel BDC3 8시리즈 2020-2024), f92.bimmerpost.com(M8 키 교체 옵션)</t>
+          <t>obdii365.com(Autel BDC3 8시리즈 2020-2024), f92.bimmerpost.com(M8 키 교체 옵션), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N277" s="2" t="inlineStr"/>
@@ -16554,7 +16378,7 @@
       </c>
       <c r="M278" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 840i·M5·M8), f92.bimmerpost.com(22년식 840i 추가 키)</t>
+          <t>ebay(IYZBK1 2022-2025 840i·M5·M8), f92.bimmerpost.com(22년식 840i 추가 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N278" s="2" t="inlineStr"/>
@@ -16610,7 +16434,7 @@
       </c>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t>f92.bimmerpost.com(2023 키), obdii365.com(Autel BDC3 2020-2024)</t>
+          <t>f92.bimmerpost.com(2023 키), obdii365.com(Autel BDC3 2020-2024), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N279" s="2" t="inlineStr"/>
@@ -16666,7 +16490,7 @@
       </c>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t>classic.com(2024 840i G15), bmwofbloomfield.com(2024 M8 GC 키리스 부품)</t>
+          <t>classic.com(2024 840i G15), bmwofbloomfield.com(2024 M8 GC 키리스 부품), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N280" s="2" t="inlineStr"/>
@@ -16722,7 +16546,7 @@
       </c>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>go-parts.com(2016-2025 G시리즈 키), amazon(Autel IKEYBW004AL)</t>
+          <t>go-parts.com(2016-2025 G시리즈 키), amazon(Autel IKEYBW004AL), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N281" s="2" t="inlineStr"/>
@@ -16778,7 +16602,7 @@
       </c>
       <c r="M282" s="2" t="inlineStr">
         <is>
-          <t>graysonbmw.com(2026 8시리즈 FAQ: 2026 파이널 에디션), ebay(IYZBK1 2022-2026)</t>
+          <t>graysonbmw.com(2026 8시리즈 FAQ: 2026 파이널 에디션), ebay(IYZBK1 2022-2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N282" s="2" t="inlineStr">
@@ -17677,7 +17501,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F298" s="6" t="inlineStr">
+      <c r="F298" s="8" t="inlineStr">
         <is>
           <t>ID49(NCF2951, Hitag Pro)</t>
         </is>
@@ -17695,7 +17519,7 @@
         </is>
       </c>
       <c r="K298" s="2" t="inlineStr"/>
-      <c r="L298" s="6" t="inlineStr">
+      <c r="L298" s="8" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -17705,7 +17529,7 @@
           <t>go-parts.com(2022-2025 X1/iX 5버튼 스마트키, 딜러/전문 로크스미스 등록 필수), keyless2go.com(2024 X1 키등록)</t>
         </is>
       </c>
-      <c r="N298" s="6" t="inlineStr">
+      <c r="N298" s="8" t="inlineStr">
         <is>
           <t>2025년식 BCP 원문 직접 확인 없음(목록 2022-2024 연장)</t>
         </is>
@@ -17737,7 +17561,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F299" s="6" t="inlineStr">
+      <c r="F299" s="8" t="inlineStr">
         <is>
           <t>ID49(NCF2951, Hitag Pro)</t>
         </is>
@@ -17755,7 +17579,7 @@
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr"/>
-      <c r="L299" s="6" t="inlineStr">
+      <c r="L299" s="8" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -17765,7 +17589,7 @@
           <t>u11.bimmerpost.com(2026 X1: 키 1개·디지털키 카드·서비스 카드, 2025는 키 2개)</t>
         </is>
       </c>
-      <c r="N299" s="6" t="inlineStr">
+      <c r="N299" s="8" t="inlineStr">
         <is>
           <t>2026년식 순정 키 1개 제공</t>
         </is>
@@ -17913,7 +17737,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F302" s="6" t="inlineStr">
+      <c r="F302" s="8" t="inlineStr">
         <is>
           <t>ID49(NCF2951, Hitag Pro)</t>
         </is>
@@ -17931,7 +17755,7 @@
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
-      <c r="L302" s="6" t="inlineStr">
+      <c r="L302" s="8" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -17941,7 +17765,7 @@
           <t>go-parts.com(2022-2025 X1/iX 5버튼 스마트키, 딜러/전문 로크스미스 등록 필수), keyless2go.com(2024 X1 키등록)</t>
         </is>
       </c>
-      <c r="N302" s="6" t="inlineStr">
+      <c r="N302" s="8" t="inlineStr">
         <is>
           <t>2025년식 BCP 원문 직접 확인 없음(목록 2022-2024 연장)</t>
         </is>
@@ -17973,7 +17797,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F303" s="6" t="inlineStr">
+      <c r="F303" s="8" t="inlineStr">
         <is>
           <t>ID49(NCF2951, Hitag Pro)</t>
         </is>
@@ -17991,7 +17815,7 @@
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
-      <c r="L303" s="6" t="inlineStr">
+      <c r="L303" s="8" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -18001,7 +17825,7 @@
           <t>u11.bimmerpost.com(2026 X1: 키 1개·디지털키 카드·서비스 카드, 2025는 키 2개)</t>
         </is>
       </c>
-      <c r="N303" s="6" t="inlineStr">
+      <c r="N303" s="8" t="inlineStr">
         <is>
           <t>2026년식 순정 키 1개 제공</t>
         </is>
@@ -18493,7 +18317,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F312" s="6" t="inlineStr">
+      <c r="F312" s="8" t="inlineStr">
         <is>
           <t>ID49(NCF2951, Hitag Pro)</t>
         </is>
@@ -18511,7 +18335,7 @@
         </is>
       </c>
       <c r="K312" s="2" t="inlineStr"/>
-      <c r="L312" s="6" t="inlineStr">
+      <c r="L312" s="8" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -18521,7 +18345,7 @@
           <t>carkeyhelper.com(X2 2024-2026 스마트키), u11.bimmerpost.com(U11/U10 SP21 전장 UWB)</t>
         </is>
       </c>
-      <c r="N312" s="6" t="inlineStr">
+      <c r="N312" s="8" t="inlineStr">
         <is>
           <t>2025년식 BCP 원문 직접 확인은 없음</t>
         </is>
@@ -18553,7 +18377,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F313" s="6" t="inlineStr">
+      <c r="F313" s="8" t="inlineStr">
         <is>
           <t>ID49(NCF2951, Hitag Pro)</t>
         </is>
@@ -18571,7 +18395,7 @@
         </is>
       </c>
       <c r="K313" s="2" t="inlineStr"/>
-      <c r="L313" s="6" t="inlineStr">
+      <c r="L313" s="8" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -18581,7 +18405,7 @@
           <t>u11.bimmerpost.com(2026 X1/X2 키 1개·디지털키 카드), carkeyhelper.com</t>
         </is>
       </c>
-      <c r="N313" s="6" t="inlineStr">
+      <c r="N313" s="8" t="inlineStr">
         <is>
           <t>MY26 디지털키 플러스 기본</t>
         </is>
@@ -18729,7 +18553,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F316" s="6" t="inlineStr">
+      <c r="F316" s="8" t="inlineStr">
         <is>
           <t>ID49(NCF2951, Hitag Pro)</t>
         </is>
@@ -18747,7 +18571,7 @@
         </is>
       </c>
       <c r="K316" s="2" t="inlineStr"/>
-      <c r="L316" s="6" t="inlineStr">
+      <c r="L316" s="8" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -18757,7 +18581,7 @@
           <t>carkeyhelper.com(X2 2024-2026 스마트키), u11.bimmerpost.com(U11/U10 SP21 전장 UWB)</t>
         </is>
       </c>
-      <c r="N316" s="6" t="inlineStr">
+      <c r="N316" s="8" t="inlineStr">
         <is>
           <t>2025년식 BCP 원문 직접 확인은 없음</t>
         </is>
@@ -18789,7 +18613,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F317" s="6" t="inlineStr">
+      <c r="F317" s="8" t="inlineStr">
         <is>
           <t>ID49(NCF2951, Hitag Pro)</t>
         </is>
@@ -18807,7 +18631,7 @@
         </is>
       </c>
       <c r="K317" s="2" t="inlineStr"/>
-      <c r="L317" s="6" t="inlineStr">
+      <c r="L317" s="8" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -18817,7 +18641,7 @@
           <t>u11.bimmerpost.com(2026 X1/X2 키 1개·디지털키 카드), carkeyhelper.com</t>
         </is>
       </c>
-      <c r="N317" s="6" t="inlineStr">
+      <c r="N317" s="8" t="inlineStr">
         <is>
           <t>MY26 디지털키 플러스 기본</t>
         </is>
@@ -18873,12 +18697,12 @@
       <c r="K318" s="2" t="inlineStr"/>
       <c r="L318" s="2" t="inlineStr">
         <is>
-          <t>EWS3 (EWS3D/EWS4.3)</t>
+          <t>EWS3</t>
         </is>
       </c>
       <c r="M318" s="2" t="inlineStr">
         <is>
-          <t>royalkeysupply.com(2000-2009 X3/X5/Z8 EWS HU92), abkeys.com(EWS3 LX8FZV HU92)</t>
+          <t>royalkeysupply.com(2000-2009 X3/X5/Z8 EWS HU92), abkeys.com(EWS3 LX8FZV HU92), 이모빌라이저 검증: bimmerfest(E83 2004-2006 EWS3, 2006 중 EWS4 전환, 2007 LCI EWS4 — AK90 EWS4 어댑터 필요)</t>
         </is>
       </c>
       <c r="N318" s="2" t="inlineStr">
@@ -18913,7 +18737,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F319" s="6" t="inlineStr">
+      <c r="F319" s="2" t="inlineStr">
         <is>
           <t>ID44(PCF7935)</t>
         </is>
@@ -18935,21 +18759,17 @@
         </is>
       </c>
       <c r="K319" s="2" t="inlineStr"/>
-      <c r="L319" s="6" t="inlineStr">
-        <is>
-          <t>EWS3 (EWS3D/EWS4.3)</t>
+      <c r="L319" s="2" t="inlineStr">
+        <is>
+          <t>EWS3(2006 중반 이전 생산) / EWS4(2006 중반 이후 생산)</t>
         </is>
       </c>
       <c r="M319" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(2003-2009 X3 HU92 PCF7935), bestkeysupply.com(2000-2009 HU92)</t>
-        </is>
-      </c>
-      <c r="N319" s="6" t="inlineStr">
-        <is>
-          <t>일부 자료는 2005~ CAS(ID46) 병기 — E83은 EWS 계열</t>
-        </is>
-      </c>
+          <t>uhs-hardware.com(2003-2009 X3 HU92 PCF7935), bestkeysupply.com(2000-2009 HU92), 이모빌라이저 검증: bimmerfest(E83 2004-2006 EWS3, 2006 중 EWS4 전환, 2007 LCI EWS4 — AK90 EWS4 어댑터 필요)</t>
+        </is>
+      </c>
+      <c r="N319" s="2" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -18997,12 +18817,12 @@
       <c r="K320" s="2" t="inlineStr"/>
       <c r="L320" s="2" t="inlineStr">
         <is>
-          <t>EWS3 (EWS3D/EWS4.3)</t>
+          <t>EWS4</t>
         </is>
       </c>
       <c r="M320" s="2" t="inlineStr">
         <is>
-          <t>bimmerfest.com(2007 E83 LCI 키 재등록: EWS), lost-car-keys-replacement.com(X3 2004-2010 EWS PCF7935)</t>
+          <t>bimmerfest.com(2007 E83 LCI 키 재등록: EWS), lost-car-keys-replacement.com(X3 2004-2010 EWS PCF7935), 이모빌라이저 검증: bimmerfest(E83 2004-2006 EWS3, 2006 중 EWS4 전환, 2007 LCI EWS4 — AK90 EWS4 어댑터 필요)</t>
         </is>
       </c>
       <c r="N320" s="2" t="inlineStr">
@@ -19057,15 +18877,19 @@
       <c r="K321" s="2" t="inlineStr"/>
       <c r="L321" s="2" t="inlineStr">
         <is>
-          <t>EWS3 (EWS3D/EWS4.3)</t>
+          <t>EWS4</t>
         </is>
       </c>
       <c r="M321" s="2" t="inlineStr">
         <is>
-          <t>transpondery.com 검색결과(PCF7935 EWS3.x/EWS4.x), rpmmotorsport.net(E83 2003-2010 키세트)</t>
-        </is>
-      </c>
-      <c r="N321" s="2" t="inlineStr"/>
+          <t>transpondery.com 검색결과(PCF7935 EWS3.x/EWS4.x), rpmmotorsport.net(E83 2003-2010 키세트), 이모빌라이저 검증: bimmerfest(E83 2004-2006 EWS3, 2006 중 EWS4 전환, 2007 LCI EWS4 — AK90 EWS4 어댑터 필요)</t>
+        </is>
+      </c>
+      <c r="N321" s="2" t="inlineStr">
+        <is>
+          <t>2007 LCI</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -19113,15 +18937,19 @@
       <c r="K322" s="2" t="inlineStr"/>
       <c r="L322" s="2" t="inlineStr">
         <is>
-          <t>EWS3 (EWS3D/EWS4.3)</t>
+          <t>EWS4</t>
         </is>
       </c>
       <c r="M322" s="2" t="inlineStr">
         <is>
-          <t>ebay(X3 E83/X5 E53 2003-2010 EWS 플립키), accessfobs.co.uk(EWS 3버튼)</t>
-        </is>
-      </c>
-      <c r="N322" s="2" t="inlineStr"/>
+          <t>ebay(X3 E83/X5 E53 2003-2010 EWS 플립키), accessfobs.co.uk(EWS 3버튼), 이모빌라이저 검증: bimmerfest(E83 2004-2006 EWS3, 2006 중 EWS4 전환, 2007 LCI EWS4 — AK90 EWS4 어댑터 필요)</t>
+        </is>
+      </c>
+      <c r="N322" s="2" t="inlineStr">
+        <is>
+          <t>2007 LCI</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -19169,15 +18997,19 @@
       <c r="K323" s="2" t="inlineStr"/>
       <c r="L323" s="2" t="inlineStr">
         <is>
-          <t>EWS3 (EWS3D/EWS4.3)</t>
+          <t>EWS4</t>
         </is>
       </c>
       <c r="M323" s="2" t="inlineStr">
         <is>
-          <t>precisionecu.com(2003-2011 E83 EWS3/EWS3D/EWS4.3), bmw-key-replacement.com(EWS PCF7935 HU92)</t>
-        </is>
-      </c>
-      <c r="N323" s="2" t="inlineStr"/>
+          <t>precisionecu.com(2003-2011 E83 EWS3/EWS3D/EWS4.3), bmw-key-replacement.com(EWS PCF7935 HU92), 이모빌라이저 검증: bimmerfest(E83 2004-2006 EWS3, 2006 중 EWS4 전환, 2007 LCI EWS4 — AK90 EWS4 어댑터 필요)</t>
+        </is>
+      </c>
+      <c r="N323" s="2" t="inlineStr">
+        <is>
+          <t>2007 LCI</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -19325,7 +19157,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F326" s="6" t="inlineStr">
+      <c r="F326" s="8" t="inlineStr">
         <is>
           <t>ID49(PCF7945P/PCF7953, Hitag Pro)</t>
         </is>
@@ -19343,7 +19175,7 @@
         </is>
       </c>
       <c r="K326" s="2" t="inlineStr"/>
-      <c r="L326" s="6" t="inlineStr">
+      <c r="L326" s="8" t="inlineStr">
         <is>
           <t>CAS4+</t>
         </is>
@@ -19353,7 +19185,7 @@
           <t>mr-key.com(3/5/6/X3/X5/X6 FEM/CAS4+ 434MHz, 블레이드 HU127 표기), carandtruckremotes.com(2013 X3 YGOHUF5662 CAS4)</t>
         </is>
       </c>
-      <c r="N326" s="6" t="inlineStr">
+      <c r="N326" s="8" t="inlineStr">
         <is>
           <t>블레이드 표기 HU127(mr-key) vs HU100R(타 자료) 상충</t>
         </is>
@@ -19642,14 +19474,10 @@
       </c>
       <c r="M331" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A 2017-2021 X3 G01, 키웨이 HU100R), servicereset.net(X3 G01 2017~ 비상 블레이드)</t>
-        </is>
-      </c>
-      <c r="N331" s="2" t="inlineStr">
-        <is>
-          <t>G01 2017.8 생산</t>
-        </is>
-      </c>
+          <t>uhs-hardware.com(N5F-ID21A 2017-2021 X3 G01, 키웨이 HU100R), servicereset.net(X3 G01 2017~ 비상 블레이드), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
+        </is>
+      </c>
+      <c r="N331" s="2" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -19702,7 +19530,7 @@
       </c>
       <c r="M332" s="2" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2018 X3 M40i G01 키 부품목록), tlkeys.com(순정 N5F-ID21A X3/X1)</t>
+          <t>bmwpartsdeal.com(2018 X3 M40i G01 키 부품목록), tlkeys.com(순정 N5F-ID21A X3/X1), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="N332" s="2" t="inlineStr"/>
@@ -19758,7 +19586,7 @@
       </c>
       <c r="M333" s="2" t="inlineStr">
         <is>
-          <t>ebay(N5F-ID21A BDM X3/X4 G시리즈 2015-2019), bmwpartsdeal.com(2019 X3 sDrive30i G01 키 부품목록), getbmwparts.com(2019 X3 키리스 부품)</t>
+          <t>ebay(N5F-ID21A BDM X3/X4 G시리즈 2015-2019), bmwpartsdeal.com(2019 X3 sDrive30i G01 키 부품목록), getbmwparts.com(2019 X3 키리스 부품), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="N333" s="2" t="inlineStr"/>
@@ -19809,12 +19637,12 @@
       <c r="K334" s="2" t="inlineStr"/>
       <c r="L334" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC2</t>
         </is>
       </c>
       <c r="M334" s="2" t="inlineStr">
         <is>
-          <t>abrites.com(BN020: X3/X4/iX3 F97/F98/G01/G02/G08 BDC2, 대략 2021까지), autel(BDC3 X3 G01/G08/G45 2020-2024)</t>
+          <t>abrites.com(BN020: X3/X4/iX3 F97/F98/G01/G02/G08 BDC2, 대략 2021까지), autel(BDC3 X3 G01/G08/G45 2020-2024), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="N334" s="2" t="inlineStr"/>
@@ -19865,19 +19693,15 @@
       <c r="K335" s="2" t="inlineStr"/>
       <c r="L335" s="2" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3 (VIN 확인)</t>
+          <t>BDC2(2021.7 이전 생산) / BDC3(2021.8 이후 생산)</t>
         </is>
       </c>
       <c r="M335" s="2" t="inlineStr">
         <is>
-          <t>x3.xbimmers.com(G01 분실키 교체), carandtruckremotes.com(X3 키), bmwoforlandpark.com(2021 X3 키 관련 부품 51210414778)</t>
-        </is>
-      </c>
-      <c r="N335" s="2" t="inlineStr">
-        <is>
-          <t>2021년식은 BDC2·BDC3 모두 가능(BDC2 ~2021, BDC3 2020~)</t>
-        </is>
-      </c>
+          <t>x3.xbimmers.com(G01 분실키 교체), carandtruckremotes.com(X3 키), bmwoforlandpark.com(2021 X3 키 관련 부품 51210414778), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07, BDC3 2021/08~)</t>
+        </is>
+      </c>
+      <c r="N335" s="2" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -20077,7 +19901,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F339" s="6" t="inlineStr">
+      <c r="F339" s="8" t="inlineStr">
         <is>
           <t>ID49(NCF2951, Hitag Pro) — U섀시 BCP 키 기준 추정</t>
         </is>
@@ -20095,7 +19919,7 @@
         </is>
       </c>
       <c r="K339" s="2" t="inlineStr"/>
-      <c r="L339" s="6" t="inlineStr">
+      <c r="L339" s="8" t="inlineStr">
         <is>
           <t>BCP (추정)</t>
         </is>
@@ -20105,7 +19929,7 @@
           <t>autel(BDC3 목록에 X3 G45 2020-2024 포함 표기), obdexpress.co.uk(2025 X3 UWB는 BCP 키)</t>
         </is>
       </c>
-      <c r="N339" s="6" t="inlineStr">
+      <c r="N339" s="8" t="inlineStr">
         <is>
           <t>G45 2024.8 생산 — 2024년식은 BDC3 목록 표기와 BCP 자료가 상충</t>
         </is>
@@ -20137,7 +19961,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F340" s="6" t="inlineStr">
+      <c r="F340" s="8" t="inlineStr">
         <is>
           <t>ID49(NCF2951, Hitag Pro) — U섀시 BCP 키 기준 추정</t>
         </is>
@@ -20155,7 +19979,7 @@
         </is>
       </c>
       <c r="K340" s="2" t="inlineStr"/>
-      <c r="L340" s="6" t="inlineStr">
+      <c r="L340" s="8" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -20165,7 +19989,7 @@
           <t>obdexpress.co.uk(Lonsdor K518 PRO: 2025 BMW X3 UWB에 BCP 키 추가, ADP40 어댑터), go-parts.com(2018-2025 X3 433MHz CR2032)</t>
         </is>
       </c>
-      <c r="N340" s="6" t="inlineStr">
+      <c r="N340" s="8" t="inlineStr">
         <is>
           <t>칩 세부형식은 이 연식 검색에서 직접 확인 안 됨</t>
         </is>
@@ -20182,10 +20006,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C341" s="7" t="inlineStr"/>
-      <c r="D341" s="7" t="inlineStr"/>
-      <c r="E341" s="7" t="inlineStr"/>
-      <c r="F341" s="8" t="inlineStr">
+      <c r="C341" s="6" t="inlineStr"/>
+      <c r="D341" s="6" t="inlineStr"/>
+      <c r="E341" s="6" t="inlineStr"/>
+      <c r="F341" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -20199,7 +20023,7 @@
       <c r="I341" s="2" t="inlineStr"/>
       <c r="J341" s="2" t="inlineStr"/>
       <c r="K341" s="2" t="inlineStr"/>
-      <c r="L341" s="8" t="inlineStr">
+      <c r="L341" s="7" t="inlineStr">
         <is>
           <t>BCP (2025년식 기준 추정)</t>
         </is>
@@ -20209,7 +20033,7 @@
           <t>mechanicwiki.com(X3 키 등록 일반), justanswer.com(X3 중고키 등록) — 2026 G45 전용 자료 없음</t>
         </is>
       </c>
-      <c r="N341" s="8" t="inlineStr"/>
+      <c r="N341" s="7" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -20262,14 +20086,10 @@
       </c>
       <c r="M342" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A BDC2: 2019-2021 X3 F97), yourcarkeyguys.com(BDC2 N5F-ID21A)</t>
-        </is>
-      </c>
-      <c r="N342" s="2" t="inlineStr">
-        <is>
-          <t>BDC2 키 등록은 BDC2 탈거 벤치작업(ACDP/VVDI/CGDI)</t>
-        </is>
-      </c>
+          <t>uhs-hardware.com(N5F-ID21A BDC2: 2019-2021 X3 F97), yourcarkeyguys.com(BDC2 N5F-ID21A), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
+        </is>
+      </c>
+      <c r="N342" s="2" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -20317,12 +20137,12 @@
       <c r="K343" s="2" t="inlineStr"/>
       <c r="L343" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC2</t>
         </is>
       </c>
       <c r="M343" s="2" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2020 X3 M F97 키 부품목록), uhs-hardware.com(F97 2019-2021 N5F-ID21A)</t>
+          <t>bmwpartsdeal.com(2020 X3 M F97 키 부품목록), uhs-hardware.com(F97 2019-2021 N5F-ID21A), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="N343" s="2" t="inlineStr"/>
@@ -20373,19 +20193,15 @@
       <c r="K344" s="2" t="inlineStr"/>
       <c r="L344" s="2" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3 (VIN 확인)</t>
+          <t>BDC2(2021.7 이전 생산) / BDC3(2021.8 이후 생산)</t>
         </is>
       </c>
       <c r="M344" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A: X3 F97 04/2019-07/2021, 비상 블레이드 미포함), ebay(M 순정 8717525-01 N5F-ID21A)</t>
-        </is>
-      </c>
-      <c r="N344" s="2" t="inlineStr">
-        <is>
-          <t>F97 전기형 2021.7까지 — 이후 LCI</t>
-        </is>
-      </c>
+          <t>uhs-hardware.com(N5F-ID21A: X3 F97 04/2019-07/2021, 비상 블레이드 미포함), ebay(M 순정 8717525-01 N5F-ID21A), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07, BDC3 2021/08~)</t>
+        </is>
+      </c>
+      <c r="N344" s="2" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -20574,10 +20390,10 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C348" s="7" t="inlineStr"/>
-      <c r="D348" s="7" t="inlineStr"/>
-      <c r="E348" s="7" t="inlineStr"/>
-      <c r="F348" s="8" t="inlineStr">
+      <c r="C348" s="6" t="inlineStr"/>
+      <c r="D348" s="6" t="inlineStr"/>
+      <c r="E348" s="6" t="inlineStr"/>
+      <c r="F348" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -20587,7 +20403,7 @@
       <c r="I348" s="2" t="inlineStr"/>
       <c r="J348" s="2" t="inlineStr"/>
       <c r="K348" s="2" t="inlineStr"/>
-      <c r="L348" s="8" t="inlineStr">
+      <c r="L348" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -20597,7 +20413,7 @@
           <t>bmwblog.com(F97 2024 종료, 후속 X3 M 없음 — G45 X3 M50으로 대체)</t>
         </is>
       </c>
-      <c r="N348" s="8" t="inlineStr">
+      <c r="N348" s="7" t="inlineStr">
         <is>
           <t>F97은 2024년 생산 종료 — 국내 2025년식 여부 확인 필요</t>
         </is>
@@ -20614,10 +20430,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C349" s="7" t="inlineStr"/>
-      <c r="D349" s="7" t="inlineStr"/>
-      <c r="E349" s="7" t="inlineStr"/>
-      <c r="F349" s="8" t="inlineStr">
+      <c r="C349" s="6" t="inlineStr"/>
+      <c r="D349" s="6" t="inlineStr"/>
+      <c r="E349" s="6" t="inlineStr"/>
+      <c r="F349" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -20627,7 +20443,7 @@
       <c r="I349" s="2" t="inlineStr"/>
       <c r="J349" s="2" t="inlineStr"/>
       <c r="K349" s="2" t="inlineStr"/>
-      <c r="L349" s="8" t="inlineStr">
+      <c r="L349" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -20637,7 +20453,7 @@
           <t>bmwblog.com(F97 2024 종료), g45.bimmerpost.com(2026 X3 키)</t>
         </is>
       </c>
-      <c r="N349" s="8" t="inlineStr">
+      <c r="N349" s="7" t="inlineStr">
         <is>
           <t>F97은 2024년 생산 종료 — 원본 목록의 현재 표기 확인 필요</t>
         </is>
@@ -20982,14 +20798,10 @@
       </c>
       <c r="M355" s="2" t="inlineStr">
         <is>
-          <t>yourcarkeyguys.com(BDC2 N5F-ID21A: 2018-2021 X4 G02), uhs-hardware.com(2017-2021 X4 G02)</t>
-        </is>
-      </c>
-      <c r="N355" s="2" t="inlineStr">
-        <is>
-          <t>G02 2018.4 생산</t>
-        </is>
-      </c>
+          <t>yourcarkeyguys.com(BDC2 N5F-ID21A: 2018-2021 X4 G02), uhs-hardware.com(2017-2021 X4 G02), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
+        </is>
+      </c>
+      <c r="N355" s="2" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -21042,7 +20854,7 @@
       </c>
       <c r="M356" s="2" t="inlineStr">
         <is>
-          <t>maplekeysupply.ca(BDC2 N5F-ID21A), locksmithkeyless.com(2014-2023 N5F-ID21A 9367401-01)</t>
+          <t>maplekeysupply.ca(BDC2 N5F-ID21A), locksmithkeyless.com(2014-2023 N5F-ID21A 9367401-01), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="N356" s="2" t="inlineStr"/>
@@ -21093,12 +20905,12 @@
       <c r="K357" s="2" t="inlineStr"/>
       <c r="L357" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC2</t>
         </is>
       </c>
       <c r="M357" s="2" t="inlineStr">
         <is>
-          <t>vxdas.com(APP2 BDC02: X4 G02 2018-2021), abrites.com(BN020 BDC2 대략 2021까지)</t>
+          <t>vxdas.com(APP2 BDC02: X4 G02 2018-2021), abrites.com(BN020 BDC2 대략 2021까지), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="N357" s="2" t="inlineStr"/>
@@ -21149,12 +20961,12 @@
       <c r="K358" s="2" t="inlineStr"/>
       <c r="L358" s="2" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3 (VIN 확인)</t>
+          <t>BDC2(2021.7 이전 생산) / BDC3(2021.8 이후 생산)</t>
         </is>
       </c>
       <c r="M358" s="2" t="inlineStr">
         <is>
-          <t>americankeysupply.com(BN020 BDC2), vxdas.com(APP2: X4 G02 2018-2021 BDC02)</t>
+          <t>americankeysupply.com(BN020 BDC2), vxdas.com(APP2: X4 G02 2018-2021 BDC02), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07, BDC3 2021/08~)</t>
         </is>
       </c>
       <c r="N358" s="2" t="inlineStr"/>
@@ -21402,10 +21214,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C363" s="7" t="inlineStr"/>
-      <c r="D363" s="7" t="inlineStr"/>
-      <c r="E363" s="7" t="inlineStr"/>
-      <c r="F363" s="8" t="inlineStr">
+      <c r="C363" s="6" t="inlineStr"/>
+      <c r="D363" s="6" t="inlineStr"/>
+      <c r="E363" s="6" t="inlineStr"/>
+      <c r="F363" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -21415,7 +21227,7 @@
       <c r="I363" s="2" t="inlineStr"/>
       <c r="J363" s="2" t="inlineStr"/>
       <c r="K363" s="2" t="inlineStr"/>
-      <c r="L363" s="8" t="inlineStr">
+      <c r="L363" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -21425,7 +21237,7 @@
           <t>wikipedia(X4 G02 2025년식으로 종료)</t>
         </is>
       </c>
-      <c r="N363" s="8" t="inlineStr">
+      <c r="N363" s="7" t="inlineStr">
         <is>
           <t>G02는 2025년식까지 — 국내 2026년식 여부 확인 필요</t>
         </is>
@@ -21482,7 +21294,7 @@
       </c>
       <c r="M364" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A: X4 F98 04/2019-07/2021), ebay(2015-2020 X1/X4/X5/X6 N5F-ID21A)</t>
+          <t>uhs-hardware.com(N5F-ID21A: X4 F98 04/2019-07/2021), ebay(2015-2020 X1/X4/X5/X6 N5F-ID21A), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="N364" s="2" t="inlineStr"/>
@@ -21533,12 +21345,12 @@
       <c r="K365" s="2" t="inlineStr"/>
       <c r="L365" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC2</t>
         </is>
       </c>
       <c r="M365" s="2" t="inlineStr">
         <is>
-          <t>ebay(2020 BMW N5F-ID21A 스마트키), uhs-hardware.com(F98 2019-2021)</t>
+          <t>ebay(2020 BMW N5F-ID21A 스마트키), uhs-hardware.com(F98 2019-2021), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="N365" s="2" t="inlineStr"/>
@@ -21589,19 +21401,15 @@
       <c r="K366" s="2" t="inlineStr"/>
       <c r="L366" s="2" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3 (VIN 확인)</t>
+          <t>BDC2(2021.7 이전 생산) / BDC3(2021.8 이후 생산)</t>
         </is>
       </c>
       <c r="M366" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A: F98 04/2019-07/2021), etsy(F98 X4M LCI 키 = G18 X5·G07 X7 LCI·G70·XM·U11·iX와 같은 신형 키 케이스)</t>
-        </is>
-      </c>
-      <c r="N366" s="2" t="inlineStr">
-        <is>
-          <t>2021.8 LCI부터 신형 키</t>
-        </is>
-      </c>
+          <t>uhs-hardware.com(N5F-ID21A: F98 04/2019-07/2021), etsy(F98 X4M LCI 키 = G18 X5·G07 X7 LCI·G70·XM·U11·iX와 같은 신형 키 케이스), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07, BDC3 2021/08~)</t>
+        </is>
+      </c>
+      <c r="N366" s="2" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -21842,10 +21650,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C371" s="7" t="inlineStr"/>
-      <c r="D371" s="7" t="inlineStr"/>
-      <c r="E371" s="7" t="inlineStr"/>
-      <c r="F371" s="8" t="inlineStr">
+      <c r="C371" s="6" t="inlineStr"/>
+      <c r="D371" s="6" t="inlineStr"/>
+      <c r="E371" s="6" t="inlineStr"/>
+      <c r="F371" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -21855,7 +21663,7 @@
       <c r="I371" s="2" t="inlineStr"/>
       <c r="J371" s="2" t="inlineStr"/>
       <c r="K371" s="2" t="inlineStr"/>
-      <c r="L371" s="8" t="inlineStr">
+      <c r="L371" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -21865,7 +21673,7 @@
           <t>bmwblog.com(X4 생산 종료 2025.11, 후속 iX4 NA7 2027 예정)</t>
         </is>
       </c>
-      <c r="N371" s="8" t="inlineStr">
+      <c r="N371" s="7" t="inlineStr">
         <is>
           <t>국내 2026년식 여부 확인 필요</t>
         </is>
@@ -22761,7 +22569,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F387" s="6" t="inlineStr">
+      <c r="F387" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 128bit)</t>
         </is>
@@ -22779,21 +22587,17 @@
         </is>
       </c>
       <c r="K387" s="2" t="inlineStr"/>
-      <c r="L387" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 표기 혼재)</t>
+      <c r="L387" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M387" s="2" t="inlineStr">
         <is>
-          <t>locksmithkeyless.com(2014-2018 X5/X6 FEM/BDC NBGIDGNG1), amazon(2014-2019 X5 NBGIDGNG1 FEM/BDC) — 2013년식 전용 자료 없음</t>
-        </is>
-      </c>
-      <c r="N387" s="6" t="inlineStr">
-        <is>
-          <t>F15 2013.11 생산</t>
-        </is>
-      </c>
+          <t>locksmithkeyless.com(2014-2018 X5/X6 FEM/BDC NBGIDGNG1), amazon(2014-2019 X5 NBGIDGNG1 FEM/BDC) — 2013년식 전용 자료 없음, 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N387" s="2" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -22821,7 +22625,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F388" s="6" t="inlineStr">
+      <c r="F388" s="2" t="inlineStr">
         <is>
           <t>ID49(NXP Hitag Pro 128bit)</t>
         </is>
@@ -22839,17 +22643,17 @@
         </is>
       </c>
       <c r="K388" s="2" t="inlineStr"/>
-      <c r="L388" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 표기 혼재)</t>
+      <c r="L388" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M388" s="2" t="inlineStr">
         <is>
-          <t>amazon(2014-2019 X5 X6 NBGIDGNG1 FEM/BDC), key4.com(NBGIDGNG1 FEM/BDC 4버튼), yourcarkeyguys.com(2014-2019 NBGIDGNG1)</t>
-        </is>
-      </c>
-      <c r="N388" s="6" t="inlineStr"/>
+          <t>amazon(2014-2019 X5 X6 NBGIDGNG1 FEM/BDC), key4.com(NBGIDGNG1 FEM/BDC 4버튼), yourcarkeyguys.com(2014-2019 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N388" s="2" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -22877,7 +22681,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F389" s="6" t="inlineStr">
+      <c r="F389" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -22895,21 +22699,17 @@
         </is>
       </c>
       <c r="K389" s="2" t="inlineStr"/>
-      <c r="L389" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L389" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M389" s="2" t="inlineStr">
         <is>
-          <t>northcoastkeyless.com(2014-2016 X5 N5F-ID21A 9367401-01), ebay(2014-2016 X5/X6 순정 9367401-01), go-parts.com(F15·F85·F16·F86은 BDC 사용)</t>
-        </is>
-      </c>
-      <c r="N389" s="6" t="inlineStr">
-        <is>
-          <t>go-parts는 BDC, ebay 모듈 매물은 F15/F16 FEM 표기</t>
-        </is>
-      </c>
+          <t>northcoastkeyless.com(2014-2016 X5 N5F-ID21A 9367401-01), ebay(2014-2016 X5/X6 순정 9367401-01), go-parts.com(F15·F85·F16·F86은 BDC 사용), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N389" s="2" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -22937,7 +22737,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F390" s="6" t="inlineStr">
+      <c r="F390" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -22955,17 +22755,17 @@
         </is>
       </c>
       <c r="K390" s="2" t="inlineStr"/>
-      <c r="L390" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L390" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M390" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(2014-2018 X5/X6 9367401-01 FEM/BDC 434MHz), keyinnovations.com(N5F-ID21A 9367401-01)</t>
-        </is>
-      </c>
-      <c r="N390" s="6" t="inlineStr"/>
+          <t>uhs-hardware.com(2014-2018 X5/X6 9367401-01 FEM/BDC 434MHz), keyinnovations.com(N5F-ID21A 9367401-01), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N390" s="2" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -22993,7 +22793,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F391" s="6" t="inlineStr">
+      <c r="F391" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -23011,17 +22811,17 @@
         </is>
       </c>
       <c r="K391" s="2" t="inlineStr"/>
-      <c r="L391" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L391" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M391" s="2" t="inlineStr">
         <is>
-          <t>locksmithkeyless.com(2014-2018 X5/X6 FEM/BDC NBGIDGNG1, PN 69337244, ILCO PRX-BMW-4B3), f15.bimmerpost.com(키 등록)</t>
-        </is>
-      </c>
-      <c r="N391" s="6" t="inlineStr"/>
+          <t>locksmithkeyless.com(2014-2018 X5/X6 FEM/BDC NBGIDGNG1, PN 69337244, ILCO PRX-BMW-4B3), f15.bimmerpost.com(키 등록), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N391" s="2" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -23049,7 +22849,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F392" s="6" t="inlineStr">
+      <c r="F392" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -23067,21 +22867,17 @@
         </is>
       </c>
       <c r="K392" s="2" t="inlineStr"/>
-      <c r="L392" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L392" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M392" s="2" t="inlineStr">
         <is>
-          <t>ebay(2014-2018 F15 X5 순정 스마트키), smallwoodlock.com(ILCO 2014-2018 X5 PRX-BMW-4B1), bimmerfest.com(2018 F15 X5d 키 교체 비용)</t>
-        </is>
-      </c>
-      <c r="N392" s="6" t="inlineStr">
-        <is>
-          <t>G05와 연식 겹침</t>
-        </is>
-      </c>
+          <t>ebay(2014-2018 F15 X5 순정 스마트키), smallwoodlock.com(ILCO 2014-2018 X5 PRX-BMW-4B1), bimmerfest.com(2018 F15 X5d 키 교체 비용), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N392" s="2" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -23129,19 +22925,15 @@
       <c r="K393" s="2" t="inlineStr"/>
       <c r="L393" s="2" t="inlineStr">
         <is>
-          <t>BDC2</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M393" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A BDC2: 2019-2024 X5), adlhardware.com(2016-2024 G바디 N5F-ID21A), g05.bimmerpost.com(G05 키)</t>
-        </is>
-      </c>
-      <c r="N393" s="2" t="inlineStr">
-        <is>
-          <t>BDC2 키 등록은 BDC2 탈거 벤치작업</t>
-        </is>
-      </c>
+          <t>uhs-hardware.com(N5F-ID21A BDC2: 2019-2024 X5), adlhardware.com(2016-2024 G바디 N5F-ID21A), g05.bimmerpost.com(G05 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N393" s="2" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -23189,12 +22981,12 @@
       <c r="K394" s="2" t="inlineStr"/>
       <c r="L394" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M394" s="2" t="inlineStr">
         <is>
-          <t>autel(2020 이후 BDC03 키추가, XP400Pro), g05.bimmerpost.com(새 키 코딩)</t>
+          <t>autel(2020 이후 BDC03 키추가, XP400Pro), g05.bimmerpost.com(새 키 코딩), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N394" s="2" t="inlineStr"/>
@@ -23245,12 +23037,12 @@
       <c r="K395" s="2" t="inlineStr"/>
       <c r="L395" s="2" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3 (VIN 확인)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M395" s="2" t="inlineStr">
         <is>
-          <t>uobdii.com(KD-X4 BDC2/BDC3 지원목록), vvdishop.com(Xhorse G BDC2/BDC3 라이선스)</t>
+          <t>uobdii.com(KD-X4 BDC2/BDC3 지원목록), vvdishop.com(Xhorse G BDC2/BDC3 라이선스), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N395" s="2" t="inlineStr"/>
@@ -23306,7 +23098,7 @@
       </c>
       <c r="M396" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 X1~X7), g05.bimmerpost.com(G05 교체 키)</t>
+          <t>ebay(IYZBK1 2022-2025 X1~X7), g05.bimmerpost.com(G05 교체 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N396" s="2" t="inlineStr"/>
@@ -23362,7 +23154,7 @@
       </c>
       <c r="M397" s="2" t="inlineStr">
         <is>
-          <t>g05.bimmerpost.com(2023년식 교체 키: BMW가 블레이드 커팅·등록서류 필요, 공키는 스티어링 센서에 대어 페어링)</t>
+          <t>g05.bimmerpost.com(2023년식 교체 키: BMW가 블레이드 커팅·등록서류 필요, 공키는 스티어링 센서에 대어 페어링), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N397" s="2" t="inlineStr"/>
@@ -23418,7 +23210,7 @@
       </c>
       <c r="M398" s="2" t="inlineStr">
         <is>
-          <t>transpondery.com 검색결과(BDC3/BDC4: ID49 Hitag Pro 변형 SP21, OEM 66125A56C30·66125A56C38), carkeyhelper.com(X5 G05 LCI 2024- 스마트키), schmiedmann.com(G05 LCI 키)</t>
+          <t>transpondery.com 검색결과(BDC3/BDC4: ID49 Hitag Pro 변형 SP21, OEM 66125A56C30·66125A56C38), carkeyhelper.com(X5 G05 LCI 2024- 스마트키), schmiedmann.com(G05 LCI 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N398" s="2" t="inlineStr">
@@ -23478,7 +23270,7 @@
       </c>
       <c r="M399" s="2" t="inlineStr">
         <is>
-          <t>programyourremote.com(2025 X5: 온보드 등록 불가, 전문가 등록), go-parts.com(2018-2025 X5 키)</t>
+          <t>programyourremote.com(2025 X5: 온보드 등록 불가, 전문가 등록), go-parts.com(2018-2025 X5 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N399" s="2" t="inlineStr">
@@ -23513,7 +23305,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F400" s="6" t="inlineStr">
+      <c r="F400" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -23531,7 +23323,7 @@
         </is>
       </c>
       <c r="K400" s="2" t="inlineStr"/>
-      <c r="L400" s="6" t="inlineStr">
+      <c r="L400" s="8" t="inlineStr">
         <is>
           <t>BDC3 (추정)</t>
         </is>
@@ -23541,7 +23333,7 @@
           <t>ebay(2026 X5 순정 키), g05.bimmerpost.com(2026 X5 키 2개+NFC 카드, 디지털키는 키 2개 필요)</t>
         </is>
       </c>
-      <c r="N400" s="6" t="inlineStr">
+      <c r="N400" s="8" t="inlineStr">
         <is>
           <t>2026년식 이모빌라이저 세대 원문 미확인</t>
         </is>
@@ -23573,7 +23365,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F401" s="6" t="inlineStr">
+      <c r="F401" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -23591,17 +23383,17 @@
         </is>
       </c>
       <c r="K401" s="2" t="inlineStr"/>
-      <c r="L401" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L401" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M401" s="2" t="inlineStr">
         <is>
-          <t>ebay(2014-2016 X5/X6 순정 N5F-ID21A 9367401-01), monacoms.com(X5M F85 2015-2019 키)</t>
-        </is>
-      </c>
-      <c r="N401" s="6" t="inlineStr"/>
+          <t>ebay(2014-2016 X5/X6 순정 N5F-ID21A 9367401-01), monacoms.com(X5M F85 2015-2019 키), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N401" s="2" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -23629,7 +23421,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F402" s="6" t="inlineStr">
+      <c r="F402" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -23647,17 +23439,17 @@
         </is>
       </c>
       <c r="K402" s="2" t="inlineStr"/>
-      <c r="L402" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M402" s="2" t="inlineStr">
         <is>
-          <t>northcoastkeyless.com(2014-2016 X5 N5F-ID21A), uhs-hardware.com(2014-2018 X5/X6 FEM/BDC)</t>
-        </is>
-      </c>
-      <c r="N402" s="6" t="inlineStr"/>
+          <t>northcoastkeyless.com(2014-2016 X5 N5F-ID21A), uhs-hardware.com(2014-2018 X5/X6 FEM/BDC), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N402" s="2" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -23685,7 +23477,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F403" s="6" t="inlineStr">
+      <c r="F403" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -23703,17 +23495,17 @@
         </is>
       </c>
       <c r="K403" s="2" t="inlineStr"/>
-      <c r="L403" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L403" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M403" s="2" t="inlineStr">
         <is>
-          <t>ebay(2014-2018 X5 M·X6 OEM N5F-ID2A), locksmithkeyless.com(2014-2018 X5/X6 NBGIDGNG1)</t>
-        </is>
-      </c>
-      <c r="N403" s="6" t="inlineStr"/>
+          <t>ebay(2014-2018 X5 M·X6 OEM N5F-ID2A), locksmithkeyless.com(2014-2018 X5/X6 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N403" s="2" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -23741,7 +23533,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F404" s="6" t="inlineStr">
+      <c r="F404" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -23759,17 +23551,17 @@
         </is>
       </c>
       <c r="K404" s="2" t="inlineStr"/>
-      <c r="L404" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L404" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M404" s="2" t="inlineStr">
         <is>
-          <t>ebay(2014-2018 X5 M OEM N5F-ID2A), bmwmpower247.com(F85/F86 키)</t>
-        </is>
-      </c>
-      <c r="N404" s="6" t="inlineStr"/>
+          <t>ebay(2014-2018 X5 M OEM N5F-ID2A), bmwmpower247.com(F85/F86 키), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N404" s="2" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -23817,12 +23609,12 @@
       <c r="K405" s="2" t="inlineStr"/>
       <c r="L405" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M405" s="2" t="inlineStr">
         <is>
-          <t>locksmithsanantonio.org(X5 M Comp F95 2020-2025: BDC, 스마트키+디지털키, HITAG Pro/DST-AES), monacoms.com(X5M F95 2020~ 키)</t>
+          <t>locksmithsanantonio.org(X5 M Comp F95 2020-2025: BDC, 스마트키+디지털키, HITAG Pro/DST-AES), monacoms.com(X5M F95 2020~ 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N405" s="2" t="inlineStr"/>
@@ -23873,12 +23665,12 @@
       <c r="K406" s="2" t="inlineStr"/>
       <c r="L406" s="2" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3 (VIN 확인)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M406" s="2" t="inlineStr">
         <is>
-          <t>locksmithsanantonio.org(F95 BDC), g05.bimmerpost.com(G05 계열 키)</t>
+          <t>locksmithsanantonio.org(F95 BDC), g05.bimmerpost.com(G05 계열 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N406" s="2" t="inlineStr"/>
@@ -23934,7 +23726,7 @@
       </c>
       <c r="M407" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 X5, 순정 인서트키 포함)</t>
+          <t>ebay(IYZBK1 2022-2025 X5, 순정 인서트키 포함), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N407" s="2" t="inlineStr"/>
@@ -23990,7 +23782,7 @@
       </c>
       <c r="M408" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2026), g05.bimmerpost.com</t>
+          <t>ebay(IYZBK1 2022-2026), g05.bimmerpost.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N408" s="2" t="inlineStr"/>
@@ -24046,7 +23838,7 @@
       </c>
       <c r="M409" s="2" t="inlineStr">
         <is>
-          <t>g05.bimmerpost.com(2024 LCI 키 품질 불만: 크고 가벼움), amazon(X5 F95/G05/G18 2024-2025 키커버)</t>
+          <t>g05.bimmerpost.com(2024 LCI 키 품질 불만: 크고 가벼움), amazon(X5 F95/G05/G18 2024-2025 키커버), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N409" s="2" t="inlineStr">
@@ -24106,7 +23898,7 @@
       </c>
       <c r="M410" s="2" t="inlineStr">
         <is>
-          <t>amazon(F95 2024-2025 키커버), ebay(IYZBK1 2022-2026)</t>
+          <t>amazon(F95 2024-2025 키커버), ebay(IYZBK1 2022-2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N410" s="2" t="inlineStr"/>
@@ -24137,7 +23929,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F411" s="6" t="inlineStr">
+      <c r="F411" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -24155,7 +23947,7 @@
         </is>
       </c>
       <c r="K411" s="2" t="inlineStr"/>
-      <c r="L411" s="6" t="inlineStr">
+      <c r="L411" s="8" t="inlineStr">
         <is>
           <t>BDC3 (추정)</t>
         </is>
@@ -24165,7 +23957,7 @@
           <t>ebay(2026 X5 순정 키), g05.bimmerpost.com(2026 X5 50e 키 2개+발레카드)</t>
         </is>
       </c>
-      <c r="N411" s="6" t="inlineStr">
+      <c r="N411" s="8" t="inlineStr">
         <is>
           <t>2026년식 이모빌라이저 세대 원문 미확인</t>
         </is>
@@ -24601,7 +24393,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F419" s="6" t="inlineStr">
+      <c r="F419" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro, PCF7953V)</t>
         </is>
@@ -24619,17 +24411,17 @@
         </is>
       </c>
       <c r="K419" s="2" t="inlineStr"/>
-      <c r="L419" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L419" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M419" s="2" t="inlineStr">
         <is>
-          <t>northcoastkeyless.com(2014-2016 X6 N5F-ID21A 9367401-01)</t>
-        </is>
-      </c>
-      <c r="N419" s="6" t="inlineStr"/>
+          <t>northcoastkeyless.com(2014-2016 X6 N5F-ID21A 9367401-01), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N419" s="2" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -24657,7 +24449,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F420" s="6" t="inlineStr">
+      <c r="F420" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro, PCF7953V)</t>
         </is>
@@ -24675,17 +24467,17 @@
         </is>
       </c>
       <c r="K420" s="2" t="inlineStr"/>
-      <c r="L420" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L420" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M420" s="2" t="inlineStr">
         <is>
-          <t>ebay(2014-2016 X5/X6 순정 N5F-ID21A), uhs-hardware.com(2014-2018 X6 FEM/BDC)</t>
-        </is>
-      </c>
-      <c r="N420" s="6" t="inlineStr"/>
+          <t>ebay(2014-2016 X5/X6 순정 N5F-ID21A), uhs-hardware.com(2014-2018 X6 FEM/BDC), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N420" s="2" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -24713,7 +24505,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F421" s="6" t="inlineStr">
+      <c r="F421" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro, PCF7953V)</t>
         </is>
@@ -24731,17 +24523,17 @@
         </is>
       </c>
       <c r="K421" s="2" t="inlineStr"/>
-      <c r="L421" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L421" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M421" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A 칩 HITAG Pro ID49 PCF7953V), northcoastkeyless.com(2014-2016 X6)</t>
-        </is>
-      </c>
-      <c r="N421" s="6" t="inlineStr"/>
+          <t>uhs-hardware.com(N5F-ID21A 칩 HITAG Pro ID49 PCF7953V), northcoastkeyless.com(2014-2016 X6), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N421" s="2" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -24769,7 +24561,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F422" s="6" t="inlineStr">
+      <c r="F422" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro, PCF7953V)</t>
         </is>
@@ -24787,17 +24579,17 @@
         </is>
       </c>
       <c r="K422" s="2" t="inlineStr"/>
-      <c r="L422" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L422" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M422" s="2" t="inlineStr">
         <is>
-          <t>ebay(2014-2019 X5/X6 NBGIDGNG1), amazon(Kilessgo 2016-2019 X6 NBGIDGNG1)</t>
-        </is>
-      </c>
-      <c r="N422" s="6" t="inlineStr"/>
+          <t>ebay(2014-2019 X5/X6 NBGIDGNG1), amazon(Kilessgo 2016-2019 X6 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N422" s="2" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -24825,7 +24617,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F423" s="6" t="inlineStr">
+      <c r="F423" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro, PCF7953V)</t>
         </is>
@@ -24843,17 +24635,17 @@
         </is>
       </c>
       <c r="K423" s="2" t="inlineStr"/>
-      <c r="L423" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L423" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M423" s="2" t="inlineStr">
         <is>
-          <t>locksmithkeyless.com(2014-2018 X5/X6 FEM/BDC NBGIDGNG1), key4.com(NBGIDGNG1 X5/X6)</t>
-        </is>
-      </c>
-      <c r="N423" s="6" t="inlineStr"/>
+          <t>locksmithkeyless.com(2014-2018 X5/X6 FEM/BDC NBGIDGNG1), key4.com(NBGIDGNG1 X5/X6), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N423" s="2" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -24881,7 +24673,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F424" s="6" t="inlineStr">
+      <c r="F424" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro, PCF7953V)</t>
         </is>
@@ -24899,21 +24691,17 @@
         </is>
       </c>
       <c r="K424" s="2" t="inlineStr"/>
-      <c r="L424" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L424" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M424" s="2" t="inlineStr">
         <is>
-          <t>nectechkeysupply.com(2014-2019 X2/X5/X6 NBGIDGNG1 BDC), amazon(Keylessbest 2014-2019 X6)</t>
-        </is>
-      </c>
-      <c r="N424" s="6" t="inlineStr">
-        <is>
-          <t>G06과 연식 겹침</t>
-        </is>
-      </c>
+          <t>nectechkeysupply.com(2014-2019 X2/X5/X6 NBGIDGNG1 BDC), amazon(Keylessbest 2014-2019 X6), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N424" s="2" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -24961,12 +24749,12 @@
       <c r="K425" s="2" t="inlineStr"/>
       <c r="L425" s="2" t="inlineStr">
         <is>
-          <t>BDC2</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M425" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A BDC2 G시리즈), locksmithkeyless.com(2014-2023 N5F-ID21A)</t>
+          <t>uhs-hardware.com(N5F-ID21A BDC2 G시리즈), locksmithkeyless.com(2014-2023 N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N425" s="2" t="inlineStr"/>
@@ -25017,12 +24805,12 @@
       <c r="K426" s="2" t="inlineStr"/>
       <c r="L426" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M426" s="2" t="inlineStr">
         <is>
-          <t>ebay(2020 BMW N5F-ID21A 키), yourcarkeyguys.com(BDC2 N5F-ID21A)</t>
+          <t>ebay(2020 BMW N5F-ID21A 키), yourcarkeyguys.com(BDC2 N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N426" s="2" t="inlineStr"/>
@@ -25073,12 +24861,12 @@
       <c r="K427" s="2" t="inlineStr"/>
       <c r="L427" s="2" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3 (VIN 확인)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M427" s="2" t="inlineStr">
         <is>
-          <t>ebay(G06 2019-2025 M스포츠 키), go-parts.com(G시리즈 BDC)</t>
+          <t>ebay(G06 2019-2025 M스포츠 키), go-parts.com(G시리즈 BDC), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N427" s="2" t="inlineStr"/>
@@ -25134,7 +24922,7 @@
       </c>
       <c r="M428" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 X6), go-parts.com(2022-2025 키 딜러/전문가 등록 필수)</t>
+          <t>ebay(IYZBK1 2022-2025 X6), go-parts.com(2022-2025 키 딜러/전문가 등록 필수), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N428" s="2" t="inlineStr"/>
@@ -25190,7 +24978,7 @@
       </c>
       <c r="M429" s="2" t="inlineStr">
         <is>
-          <t>keyecu.com(2023-2024 X1/iX/XM/X5/X6/X7/i7 신형 스마트키 쉘), ebay(IYZBK1)</t>
+          <t>keyecu.com(2023-2024 X1/iX/XM/X5/X6/X7/i7 신형 스마트키 쉘), ebay(IYZBK1), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N429" s="2" t="inlineStr">
@@ -25250,7 +25038,7 @@
       </c>
       <c r="M430" s="2" t="inlineStr">
         <is>
-          <t>g05.bimmerpost.com(2024 LCI 키: 대형·경량, 디지털키 플러스), programyourremote.com(2024 X6 키등록)</t>
+          <t>g05.bimmerpost.com(2024 LCI 키: 대형·경량, 디지털키 플러스), programyourremote.com(2024 X6 키등록), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N430" s="2" t="inlineStr"/>
@@ -25306,7 +25094,7 @@
       </c>
       <c r="M431" s="2" t="inlineStr">
         <is>
-          <t>amazon(X6 F96/G06 2024-2025 키커버), ecstuning.com(G06 X6 키)</t>
+          <t>amazon(X6 F96/G06 2024-2025 키커버), ecstuning.com(G06 X6 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N431" s="2" t="inlineStr"/>
@@ -25337,7 +25125,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F432" s="6" t="inlineStr">
+      <c r="F432" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -25355,7 +25143,7 @@
         </is>
       </c>
       <c r="K432" s="2" t="inlineStr"/>
-      <c r="L432" s="6" t="inlineStr">
+      <c r="L432" s="8" t="inlineStr">
         <is>
           <t>BDC3 (추정)</t>
         </is>
@@ -25365,7 +25153,7 @@
           <t>g05.bimmerpost.com(2026 X6 M60i 키 인식 문제, 2027 X6 키 디자인 변경)</t>
         </is>
       </c>
-      <c r="N432" s="6" t="inlineStr">
+      <c r="N432" s="8" t="inlineStr">
         <is>
           <t>2026년식 이모빌라이저 세대 원문 미확인</t>
         </is>
@@ -25397,7 +25185,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F433" s="6" t="inlineStr">
+      <c r="F433" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -25415,17 +25203,17 @@
         </is>
       </c>
       <c r="K433" s="2" t="inlineStr"/>
-      <c r="L433" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L433" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M433" s="2" t="inlineStr">
         <is>
-          <t>ebay(2014-2016 X5/X6 순정 N5F-ID21A 9367401-01)</t>
-        </is>
-      </c>
-      <c r="N433" s="6" t="inlineStr"/>
+          <t>ebay(2014-2016 X5/X6 순정 N5F-ID21A 9367401-01), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N433" s="2" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -25453,7 +25241,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F434" s="6" t="inlineStr">
+      <c r="F434" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -25471,17 +25259,17 @@
         </is>
       </c>
       <c r="K434" s="2" t="inlineStr"/>
-      <c r="L434" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L434" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M434" s="2" t="inlineStr">
         <is>
-          <t>northcoastkeyless.com(2014-2016 X6 N5F-ID21A)</t>
-        </is>
-      </c>
-      <c r="N434" s="6" t="inlineStr"/>
+          <t>northcoastkeyless.com(2014-2016 X6 N5F-ID21A), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N434" s="2" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -25509,7 +25297,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F435" s="6" t="inlineStr">
+      <c r="F435" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -25527,17 +25315,17 @@
         </is>
       </c>
       <c r="K435" s="2" t="inlineStr"/>
-      <c r="L435" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L435" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M435" s="2" t="inlineStr">
         <is>
-          <t>ebay(2014-2018 5시리즈/X5/X6 순정 N5F-ID21A)</t>
-        </is>
-      </c>
-      <c r="N435" s="6" t="inlineStr"/>
+          <t>ebay(2014-2018 5시리즈/X5/X6 순정 N5F-ID21A), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N435" s="2" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -25565,7 +25353,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F436" s="6" t="inlineStr">
+      <c r="F436" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -25583,17 +25371,17 @@
         </is>
       </c>
       <c r="K436" s="2" t="inlineStr"/>
-      <c r="L436" s="6" t="inlineStr">
-        <is>
-          <t>FEM / BDC (자료마다 명칭 혼재)</t>
+      <c r="L436" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M436" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(2014-2018 X5/X6 9367401-01 FEM/BDC), locksmithkeyless.com(2014-2018 NBGIDGNG1)</t>
-        </is>
-      </c>
-      <c r="N436" s="6" t="inlineStr"/>
+          <t>uhs-hardware.com(2014-2018 X5/X6 9367401-01 FEM/BDC), locksmithkeyless.com(2014-2018 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N436" s="2" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -25641,12 +25429,12 @@
       <c r="K437" s="2" t="inlineStr"/>
       <c r="L437" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M437" s="2" t="inlineStr">
         <is>
-          <t>pelicanparts.com(F96 X6 M Comp 2020-2021 키), keyless2go.com(2020 X6 키 전문가 등록), monacoms.com(X6M F96 2020~ 키)</t>
+          <t>pelicanparts.com(F96 X6 M Comp 2020-2021 키), keyless2go.com(2020 X6 키 전문가 등록), monacoms.com(X6M F96 2020~ 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N437" s="2" t="inlineStr"/>
@@ -25697,12 +25485,12 @@
       <c r="K438" s="2" t="inlineStr"/>
       <c r="L438" s="2" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3 (VIN 확인)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M438" s="2" t="inlineStr">
         <is>
-          <t>pelicanparts.com(F96 2020-2021 키), bimmerworld.com(M 퍼포먼스 키케이스 F95/F96)</t>
+          <t>pelicanparts.com(F96 2020-2021 키), bimmerworld.com(M 퍼포먼스 키케이스 F95/F96), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N438" s="2" t="inlineStr"/>
@@ -25758,7 +25546,7 @@
       </c>
       <c r="M439" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 X6)</t>
+          <t>ebay(IYZBK1 2022-2025 X6), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N439" s="2" t="inlineStr"/>
@@ -25814,7 +25602,7 @@
       </c>
       <c r="M440" s="2" t="inlineStr">
         <is>
-          <t>amazon(SANRILY X6 F96 2023-2024 키커버), ebay(IYZBK1)</t>
+          <t>amazon(SANRILY X6 F96 2023-2024 키커버), ebay(IYZBK1), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N440" s="2" t="inlineStr"/>
@@ -25870,7 +25658,7 @@
       </c>
       <c r="M441" s="2" t="inlineStr">
         <is>
-          <t>programyourremote.com(2024 X6 키 등록), amazon(X5/X6 2024-2025 신형 키 케이스)</t>
+          <t>programyourremote.com(2024 X6 키 등록), amazon(X5/X6 2024-2025 신형 키 케이스), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N441" s="2" t="inlineStr"/>
@@ -25926,7 +25714,7 @@
       </c>
       <c r="M442" s="2" t="inlineStr">
         <is>
-          <t>amazon(Jaronx X5/X6 2025 키커버), ebay(IYZBK1 2022-2026)</t>
+          <t>amazon(Jaronx X5/X6 2025 키커버), ebay(IYZBK1 2022-2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N442" s="2" t="inlineStr"/>
@@ -25957,7 +25745,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F443" s="6" t="inlineStr">
+      <c r="F443" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -25975,7 +25763,7 @@
         </is>
       </c>
       <c r="K443" s="2" t="inlineStr"/>
-      <c r="L443" s="6" t="inlineStr">
+      <c r="L443" s="8" t="inlineStr">
         <is>
           <t>BDC3 (추정)</t>
         </is>
@@ -25985,7 +25773,7 @@
           <t>g05.bimmerpost.com(2026 X6 키), ebay(IYZBK1 2022-2026)</t>
         </is>
       </c>
-      <c r="N443" s="6" t="inlineStr">
+      <c r="N443" s="8" t="inlineStr">
         <is>
           <t>2026년식 이모빌라이저 세대 원문 미확인</t>
         </is>
@@ -26037,12 +25825,12 @@
       <c r="K444" s="2" t="inlineStr"/>
       <c r="L444" s="2" t="inlineStr">
         <is>
-          <t>BDC2</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M444" s="2" t="inlineStr">
         <is>
-          <t>go-parts.com(BDC2 OEM 66125A3D720·66125A06CA2 N5F-ID21A), g07.bimmerpost.com(2019 X7 디스플레이키)</t>
+          <t>go-parts.com(BDC2 OEM 66125A3D720·66125A06CA2 N5F-ID21A), g07.bimmerpost.com(2019 X7 디스플레이키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N444" s="2" t="inlineStr"/>
@@ -26097,12 +25885,12 @@
       <c r="K445" s="2" t="inlineStr"/>
       <c r="L445" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M445" s="2" t="inlineStr">
         <is>
-          <t>prokeyfob.com(2020 X7 인서트 키 블레이드), keyshop-online.com(BDC2 디스플레이키 2016-2021)</t>
+          <t>prokeyfob.com(2020 X7 인서트 키 블레이드), keyshop-online.com(BDC2 디스플레이키 2016-2021), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N445" s="2" t="inlineStr"/>
@@ -26133,7 +25921,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F446" s="6" t="inlineStr">
+      <c r="F446" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -26151,17 +25939,17 @@
         </is>
       </c>
       <c r="K446" s="2" t="inlineStr"/>
-      <c r="L446" s="6" t="inlineStr">
-        <is>
-          <t>BDC2 / BDC3 (VIN 확인)</t>
+      <c r="L446" s="2" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M446" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2021-2025 X7), pelicanparts.com(G07 X7 2019-2024 키)</t>
-        </is>
-      </c>
-      <c r="N446" s="6" t="inlineStr"/>
+          <t>ebay(IYZBK1 2021-2025 X7), pelicanparts.com(G07 X7 2019-2024 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N446" s="2" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -26214,7 +26002,7 @@
       </c>
       <c r="M447" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 X7)</t>
+          <t>ebay(IYZBK1 2022-2025 X7), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N447" s="2" t="inlineStr"/>
@@ -26270,7 +26058,7 @@
       </c>
       <c r="M448" s="2" t="inlineStr">
         <is>
-          <t>ebay(2023 순정 IYZBK1 2701A-BK1), g07.bimmerpost.com(X7 키 분실)</t>
+          <t>ebay(2023 순정 IYZBK1 2701A-BK1), g07.bimmerpost.com(X7 키 분실), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N448" s="2" t="inlineStr">
@@ -26305,7 +26093,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F449" s="6" t="inlineStr">
+      <c r="F449" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -26323,7 +26111,7 @@
         </is>
       </c>
       <c r="K449" s="2" t="inlineStr"/>
-      <c r="L449" s="6" t="inlineStr">
+      <c r="L449" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (확인 필요)</t>
         </is>
@@ -26333,7 +26121,7 @@
           <t>g07.bimmerpost.com(2024 신형 실물키: LCI는 새 리모컨 디자인, i모델은 다른 프로토콜)</t>
         </is>
       </c>
-      <c r="N449" s="6" t="inlineStr"/>
+      <c r="N449" s="8" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -26361,7 +26149,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F450" s="6" t="inlineStr">
+      <c r="F450" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -26379,7 +26167,7 @@
         </is>
       </c>
       <c r="K450" s="2" t="inlineStr"/>
-      <c r="L450" s="6" t="inlineStr">
+      <c r="L450" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (확인 필요)</t>
         </is>
@@ -26389,7 +26177,7 @@
           <t>keylessentryremotefob.com(2025 X7 키)</t>
         </is>
       </c>
-      <c r="N450" s="6" t="inlineStr"/>
+      <c r="N450" s="8" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -26417,7 +26205,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F451" s="6" t="inlineStr">
+      <c r="F451" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -26435,7 +26223,7 @@
         </is>
       </c>
       <c r="K451" s="2" t="inlineStr"/>
-      <c r="L451" s="6" t="inlineStr">
+      <c r="L451" s="8" t="inlineStr">
         <is>
           <t>BDC3 / BCP (확인 필요)</t>
         </is>
@@ -26445,7 +26233,7 @@
           <t>g07.bimmerpost.com(MY26 신차는 키 1개, X5·X7 제외)</t>
         </is>
       </c>
-      <c r="N451" s="6" t="inlineStr"/>
+      <c r="N451" s="8" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -26473,7 +26261,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F452" s="6" t="inlineStr">
+      <c r="F452" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -26491,7 +26279,7 @@
         </is>
       </c>
       <c r="K452" s="2" t="inlineStr"/>
-      <c r="L452" s="6" t="inlineStr">
+      <c r="L452" s="8" t="inlineStr">
         <is>
           <t>BDC3 (G섀시 분류 기준)</t>
         </is>
@@ -26501,7 +26289,7 @@
           <t>obdexpress.co.uk·obdii365.com(G섀시 BDC3/U섀시 BCP 구분, XM=G09 → BDC3), key4.com(GODIAG BDC3/BCP 어댑터)</t>
         </is>
       </c>
-      <c r="N452" s="6" t="inlineStr">
+      <c r="N452" s="8" t="inlineStr">
         <is>
           <t>XM 전용 이모빌라이저 원문은 없음 — G09 섀시 분류로 판단</t>
         </is>
@@ -26533,7 +26321,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F453" s="6" t="inlineStr">
+      <c r="F453" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -26551,7 +26339,7 @@
         </is>
       </c>
       <c r="K453" s="2" t="inlineStr"/>
-      <c r="L453" s="6" t="inlineStr">
+      <c r="L453" s="8" t="inlineStr">
         <is>
           <t>BDC3 (G섀시 분류 기준)</t>
         </is>
@@ -26561,7 +26349,7 @@
           <t>keyecu.com(2023-2024 XM 포함 신형 스마트키 쉘), go-parts.com(딜러/전문가 등록 필수)</t>
         </is>
       </c>
-      <c r="N453" s="6" t="inlineStr">
+      <c r="N453" s="8" t="inlineStr">
         <is>
           <t>XM 전용 이모빌라이저 원문은 없음 — G09 섀시 분류로 판단</t>
         </is>
@@ -26593,7 +26381,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F454" s="6" t="inlineStr">
+      <c r="F454" s="8" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro 변형, BDC3)</t>
         </is>
@@ -26611,7 +26399,7 @@
         </is>
       </c>
       <c r="K454" s="2" t="inlineStr"/>
-      <c r="L454" s="6" t="inlineStr">
+      <c r="L454" s="8" t="inlineStr">
         <is>
           <t>BDC3 (G섀시 분류 기준)</t>
         </is>
@@ -26621,7 +26409,7 @@
           <t>programyourremote.com(2025 XM 스마트키 등록 안내)</t>
         </is>
       </c>
-      <c r="N454" s="6" t="inlineStr">
+      <c r="N454" s="8" t="inlineStr">
         <is>
           <t>XM 전용 이모빌라이저 원문은 없음 — G09 섀시 분류로 판단</t>
         </is>
@@ -26638,10 +26426,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C455" s="7" t="inlineStr"/>
-      <c r="D455" s="7" t="inlineStr"/>
-      <c r="E455" s="7" t="inlineStr"/>
-      <c r="F455" s="8" t="inlineStr">
+      <c r="C455" s="6" t="inlineStr"/>
+      <c r="D455" s="6" t="inlineStr"/>
+      <c r="E455" s="6" t="inlineStr"/>
+      <c r="F455" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -26655,7 +26443,7 @@
       <c r="I455" s="2" t="inlineStr"/>
       <c r="J455" s="2" t="inlineStr"/>
       <c r="K455" s="2" t="inlineStr"/>
-      <c r="L455" s="8" t="inlineStr">
+      <c r="L455" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -26665,7 +26453,7 @@
           <t>2026 XM 전용 자료 없음</t>
         </is>
       </c>
-      <c r="N455" s="8" t="inlineStr">
+      <c r="N455" s="7" t="inlineStr">
         <is>
           <t>XM 전용 이모빌라이저 원문은 없음 — G09 섀시 분류로 판단</t>
         </is>
@@ -27550,10 +27338,10 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="C471" s="7" t="inlineStr"/>
-      <c r="D471" s="7" t="inlineStr"/>
-      <c r="E471" s="7" t="inlineStr"/>
-      <c r="F471" s="8" t="inlineStr">
+      <c r="C471" s="6" t="inlineStr"/>
+      <c r="D471" s="6" t="inlineStr"/>
+      <c r="E471" s="6" t="inlineStr"/>
+      <c r="F471" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -27563,7 +27351,7 @@
       <c r="I471" s="2" t="inlineStr"/>
       <c r="J471" s="2" t="inlineStr"/>
       <c r="K471" s="2" t="inlineStr"/>
-      <c r="L471" s="8" t="inlineStr">
+      <c r="L471" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -27573,7 +27361,7 @@
           <t>boostmonkey.com(E89 생산 01/2008-08/2016), wikipedia(G29가 2019년식부터 후속)</t>
         </is>
       </c>
-      <c r="N471" s="8" t="inlineStr">
+      <c r="N471" s="7" t="inlineStr">
         <is>
           <t>E89 생산은 2016.8 종료 — 국내 2017~2018년식은 재고분 여부 확인 필요</t>
         </is>
@@ -27590,10 +27378,10 @@
           <t>2018(단종)</t>
         </is>
       </c>
-      <c r="C472" s="7" t="inlineStr"/>
-      <c r="D472" s="7" t="inlineStr"/>
-      <c r="E472" s="7" t="inlineStr"/>
-      <c r="F472" s="8" t="inlineStr">
+      <c r="C472" s="6" t="inlineStr"/>
+      <c r="D472" s="6" t="inlineStr"/>
+      <c r="E472" s="6" t="inlineStr"/>
+      <c r="F472" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -27603,7 +27391,7 @@
       <c r="I472" s="2" t="inlineStr"/>
       <c r="J472" s="2" t="inlineStr"/>
       <c r="K472" s="2" t="inlineStr"/>
-      <c r="L472" s="8" t="inlineStr">
+      <c r="L472" s="7" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -27613,7 +27401,7 @@
           <t>boostmonkey.com(E89 생산 01/2008-08/2016), wikipedia(G29가 2019년식부터 후속)</t>
         </is>
       </c>
-      <c r="N472" s="8" t="inlineStr">
+      <c r="N472" s="7" t="inlineStr">
         <is>
           <t>E89 생산은 2016.8 종료 — 국내 2017~2018년식은 재고분 여부 확인 필요</t>
         </is>
@@ -27665,19 +27453,15 @@
       <c r="K473" s="2" t="inlineStr"/>
       <c r="L473" s="2" t="inlineStr">
         <is>
-          <t>BDC2</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M473" s="2" t="inlineStr">
         <is>
-          <t>keyecu.com(BDM G20/G30/G32/G11/G15/G29 2015-2019 N5F-ID21A/ID21B/ID21C), ecutool.com(BDM N5F-ID21A)</t>
-        </is>
-      </c>
-      <c r="N473" s="2" t="inlineStr">
-        <is>
-          <t>G29 2018 생산</t>
-        </is>
-      </c>
+          <t>keyecu.com(BDM G20/G30/G32/G11/G15/G29 2015-2019 N5F-ID21A/ID21B/ID21C), ecutool.com(BDM N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="N473" s="2" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -27725,12 +27509,12 @@
       <c r="K474" s="2" t="inlineStr"/>
       <c r="L474" s="2" t="inlineStr">
         <is>
-          <t>BDC2(2020.7 이전 생산) / BDC3(2020.7 이후 생산)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M474" s="2" t="inlineStr">
         <is>
-          <t>linkobd.com(N5F-ID21A BDM G29), uhs-hardware.com(BDC2 N5F-ID21A)</t>
+          <t>linkobd.com(N5F-ID21A BDM G29), uhs-hardware.com(BDC2 N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N474" s="2" t="inlineStr"/>
@@ -27781,12 +27565,12 @@
       <c r="K475" s="2" t="inlineStr"/>
       <c r="L475" s="2" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3 (VIN 확인)</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="M475" s="2" t="inlineStr">
         <is>
-          <t>g29.bimmerpost.com(G29 키카드·컴포트액세스), go-parts.com(G시리즈 BDC)</t>
+          <t>g29.bimmerpost.com(G29 키카드·컴포트액세스), go-parts.com(G시리즈 BDC), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N475" s="2" t="inlineStr"/>
@@ -27842,7 +27626,7 @@
       </c>
       <c r="M476" s="2" t="inlineStr">
         <is>
-          <t>go-parts.com(2022-2025 Z4 IYZBK1, OEM 5A06C06·5A55D03-04·8708351·9367401-01)</t>
+          <t>go-parts.com(2022-2025 Z4 IYZBK1, OEM 5A06C06·5A55D03-04·8708351·9367401-01), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N476" s="2" t="inlineStr"/>
@@ -27898,7 +27682,7 @@
       </c>
       <c r="M477" s="2" t="inlineStr">
         <is>
-          <t>go-parts.com(2022-2025 Z4 IYZBK1), ebay(IYZBK1 2022-2026)</t>
+          <t>go-parts.com(2022-2025 Z4 IYZBK1), ebay(IYZBK1 2022-2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N477" s="2" t="inlineStr"/>
@@ -27954,7 +27738,7 @@
       </c>
       <c r="M478" s="2" t="inlineStr">
         <is>
-          <t>obdexpress.co.uk(G섀시 BDC3 키추가: KD-X4·Autel), autotecknic.com(G29 키)</t>
+          <t>obdexpress.co.uk(G섀시 BDC3 키추가: KD-X4·Autel), autotecknic.com(G29 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N478" s="2" t="inlineStr"/>
@@ -28010,7 +27794,7 @@
       </c>
       <c r="M479" s="2" t="inlineStr">
         <is>
-          <t>go-parts.com(2016-2025 G시리즈 키), g29.bimmerpost.com(키로 컨버터블 작동)</t>
+          <t>go-parts.com(2016-2025 G시리즈 키), g29.bimmerpost.com(키로 컨버터블 작동), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N479" s="2" t="inlineStr"/>
@@ -28066,7 +27850,7 @@
       </c>
       <c r="M480" s="2" t="inlineStr">
         <is>
-          <t>aol.com(2026 Z4 파이널 에디션 — Z4 단종), ebay(IYZBK1 2022-2026), amazon(Autel IKEYBW004AL 2026)</t>
+          <t>aol.com(2026 Z4 파이널 에디션 — Z4 단종), ebay(IYZBK1 2022-2026), amazon(Autel IKEYBW004AL 2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N480" s="2" t="inlineStr">
@@ -28101,7 +27885,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F481" s="6" t="inlineStr">
+      <c r="F481" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -28119,21 +27903,17 @@
         </is>
       </c>
       <c r="K481" s="2" t="inlineStr"/>
-      <c r="L481" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L481" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M481" s="2" t="inlineStr">
         <is>
-          <t>abkeys.com(i3/i8 2015+ 9317163-02·9317161-02 FEM/BDC), amazon(i3/i8 2014-2020 NBGIDGNG1 434MHz)</t>
-        </is>
-      </c>
-      <c r="N481" s="6" t="inlineStr">
-        <is>
-          <t>i3 국내 2014~</t>
-        </is>
-      </c>
+          <t>abkeys.com(i3/i8 2015+ 9317163-02·9317161-02 FEM/BDC), amazon(i3/i8 2014-2020 NBGIDGNG1 434MHz), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N481" s="2" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -28161,7 +27941,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F482" s="6" t="inlineStr">
+      <c r="F482" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -28179,17 +27959,17 @@
         </is>
       </c>
       <c r="K482" s="2" t="inlineStr"/>
-      <c r="L482" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L482" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M482" s="2" t="inlineStr">
         <is>
-          <t>mykeysupply.com(2015-2018 i3/i8 OEM 4버튼 2013DJ5983 BMW 9362177-02, 비상 인서트키 포함), locksmithkeyless.com(2015-2017 i3/i8 NBGIDGNG1)</t>
-        </is>
-      </c>
-      <c r="N482" s="6" t="inlineStr"/>
+          <t>mykeysupply.com(2015-2018 i3/i8 OEM 4버튼 2013DJ5983 BMW 9362177-02, 비상 인서트키 포함), locksmithkeyless.com(2015-2017 i3/i8 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N482" s="2" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -28217,7 +27997,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F483" s="6" t="inlineStr">
+      <c r="F483" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -28235,17 +28015,17 @@
         </is>
       </c>
       <c r="K483" s="2" t="inlineStr"/>
-      <c r="L483" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L483" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M483" s="2" t="inlineStr">
         <is>
-          <t>keyshop-online.com(2013-2017 i3/i8 BDC 2013DJ5983 HU100R), yourcarkeyguys.com(2015-2017 i3 4버튼 NBGIDGNG1)</t>
-        </is>
-      </c>
-      <c r="N483" s="6" t="inlineStr"/>
+          <t>keyshop-online.com(2013-2017 i3/i8 BDC 2013DJ5983 HU100R), yourcarkeyguys.com(2015-2017 i3 4버튼 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N483" s="2" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -28273,7 +28053,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F484" s="6" t="inlineStr">
+      <c r="F484" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -28291,17 +28071,17 @@
         </is>
       </c>
       <c r="K484" s="2" t="inlineStr"/>
-      <c r="L484" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L484" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M484" s="2" t="inlineStr">
         <is>
-          <t>programyourremote.com(2017 i3 키등록), keyshop-online.com(2013-2017 i3 BDC)</t>
-        </is>
-      </c>
-      <c r="N484" s="6" t="inlineStr"/>
+          <t>programyourremote.com(2017 i3 키등록), keyshop-online.com(2013-2017 i3 BDC), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N484" s="2" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -28329,7 +28109,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F485" s="6" t="inlineStr">
+      <c r="F485" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -28347,17 +28127,17 @@
         </is>
       </c>
       <c r="K485" s="2" t="inlineStr"/>
-      <c r="L485" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L485" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M485" s="2" t="inlineStr">
         <is>
-          <t>mykeysupply.com(2015-2018 i3/i8 OEM), fixautosmart.com(i3 2013-2020 키 교체)</t>
-        </is>
-      </c>
-      <c r="N485" s="6" t="inlineStr"/>
+          <t>mykeysupply.com(2015-2018 i3/i8 OEM), fixautosmart.com(i3 2013-2020 키 교체), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N485" s="2" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -28385,7 +28165,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F486" s="6" t="inlineStr">
+      <c r="F486" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -28403,21 +28183,17 @@
         </is>
       </c>
       <c r="K486" s="2" t="inlineStr"/>
-      <c r="L486" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L486" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M486" s="2" t="inlineStr">
         <is>
-          <t>mybmwi3.com(i3 백업 키), amazon(i3/i8 2014-2020 NBGIDGNG1)</t>
-        </is>
-      </c>
-      <c r="N486" s="6" t="inlineStr">
-        <is>
-          <t>검색결과: 2019-2021 i3는 N5F-ID21A 아닌 NBGIDGNG1</t>
-        </is>
-      </c>
+          <t>mybmwi3.com(i3 백업 키), amazon(i3/i8 2014-2020 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N486" s="2" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -28445,7 +28221,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F487" s="6" t="inlineStr">
+      <c r="F487" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -28463,17 +28239,17 @@
         </is>
       </c>
       <c r="K487" s="2" t="inlineStr"/>
-      <c r="L487" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L487" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M487" s="2" t="inlineStr">
         <is>
-          <t>amazon(i3/i8 2014-2020 NBGIDGNG1), fixautosmart.com(i3 2013-2020)</t>
-        </is>
-      </c>
-      <c r="N487" s="6" t="inlineStr"/>
+          <t>amazon(i3/i8 2014-2020 NBGIDGNG1), fixautosmart.com(i3 2013-2020), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N487" s="2" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -28501,7 +28277,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F488" s="6" t="inlineStr">
+      <c r="F488" s="2" t="inlineStr">
         <is>
           <t>ID49(Hitag Pro)</t>
         </is>
@@ -28519,21 +28295,17 @@
         </is>
       </c>
       <c r="K488" s="2" t="inlineStr"/>
-      <c r="L488" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L488" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M488" s="2" t="inlineStr">
         <is>
-          <t>diamondkeysupply.com(i8/i3 315MHz 프록시미티), ebay(2014-2021 i3 NBGIDGNG1)</t>
-        </is>
-      </c>
-      <c r="N488" s="6" t="inlineStr">
-        <is>
-          <t>i3 생산 2022.7 종료</t>
-        </is>
-      </c>
+          <t>diamondkeysupply.com(i8/i3 315MHz 프록시미티), ebay(2014-2021 i3 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N488" s="2" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -28561,7 +28333,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F489" s="6" t="inlineStr">
+      <c r="F489" s="2" t="inlineStr">
         <is>
           <t>ID49(NXP Hitag Pro 128bit)</t>
         </is>
@@ -28579,21 +28351,17 @@
         </is>
       </c>
       <c r="K489" s="2" t="inlineStr"/>
-      <c r="L489" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L489" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M489" s="2" t="inlineStr">
         <is>
-          <t>yourcarkeyguys.com(2015-2017 i8 NBGIDGNG1), abkeys.com(i3/i8 2015+ 9317161-02)</t>
-        </is>
-      </c>
-      <c r="N489" s="6" t="inlineStr">
-        <is>
-          <t>2014년식 적용 키는 자료상 미확인</t>
-        </is>
-      </c>
+          <t>yourcarkeyguys.com(2015-2017 i8 NBGIDGNG1), abkeys.com(i3/i8 2015+ 9317161-02), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N489" s="2" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -28621,7 +28389,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F490" s="6" t="inlineStr">
+      <c r="F490" s="2" t="inlineStr">
         <is>
           <t>ID49(NXP Hitag Pro 128bit)</t>
         </is>
@@ -28639,17 +28407,17 @@
         </is>
       </c>
       <c r="K490" s="2" t="inlineStr"/>
-      <c r="L490" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L490" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M490" s="2" t="inlineStr">
         <is>
-          <t>locksmithkeyless.com(2015-2017 i3/i8 NBGIDGNG1 CAS4+/FEM), yourcarkeyguys.com(i8 I12 4버튼)</t>
-        </is>
-      </c>
-      <c r="N490" s="6" t="inlineStr"/>
+          <t>locksmithkeyless.com(2015-2017 i3/i8 NBGIDGNG1 CAS4+/FEM), yourcarkeyguys.com(i8 I12 4버튼), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N490" s="2" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -28677,7 +28445,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F491" s="6" t="inlineStr">
+      <c r="F491" s="2" t="inlineStr">
         <is>
           <t>ID49(NXP Hitag Pro 128bit)</t>
         </is>
@@ -28695,17 +28463,17 @@
         </is>
       </c>
       <c r="K491" s="2" t="inlineStr"/>
-      <c r="L491" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L491" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M491" s="2" t="inlineStr">
         <is>
-          <t>mykeysupply.com(2015-2018 i3/i8 OEM), ebay(i8 순정 NBGIDGNG1)</t>
-        </is>
-      </c>
-      <c r="N491" s="6" t="inlineStr"/>
+          <t>mykeysupply.com(2015-2018 i3/i8 OEM), ebay(i8 순정 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N491" s="2" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -28733,7 +28501,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F492" s="6" t="inlineStr">
+      <c r="F492" s="2" t="inlineStr">
         <is>
           <t>ID49(NXP Hitag Pro 128bit)</t>
         </is>
@@ -28751,17 +28519,17 @@
         </is>
       </c>
       <c r="K492" s="2" t="inlineStr"/>
-      <c r="L492" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L492" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M492" s="2" t="inlineStr">
         <is>
-          <t>diamondkeysupply.com(i8/i3 315MHz 프록시미티), locksmithkeyless.com</t>
-        </is>
-      </c>
-      <c r="N492" s="6" t="inlineStr"/>
+          <t>diamondkeysupply.com(i8/i3 315MHz 프록시미티), locksmithkeyless.com, 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N492" s="2" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -28789,7 +28557,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F493" s="6" t="inlineStr">
+      <c r="F493" s="2" t="inlineStr">
         <is>
           <t>ID49(NXP Hitag Pro 128bit)</t>
         </is>
@@ -28807,21 +28575,17 @@
         </is>
       </c>
       <c r="K493" s="2" t="inlineStr"/>
-      <c r="L493" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L493" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M493" s="2" t="inlineStr">
         <is>
-          <t>ebay(i8 순정 6805984-01), bimmerfest.com(i8 로드스터 디스플레이키), bmwpartsdeal.com(2018 i8 컨버터블 I15)</t>
-        </is>
-      </c>
-      <c r="N493" s="6" t="inlineStr">
-        <is>
-          <t>I15 로드스터 2018~</t>
-        </is>
-      </c>
+          <t>ebay(i8 순정 6805984-01), bimmerfest.com(i8 로드스터 디스플레이키), bmwpartsdeal.com(2018 i8 컨버터블 I15), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N493" s="2" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -28849,7 +28613,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F494" s="6" t="inlineStr">
+      <c r="F494" s="2" t="inlineStr">
         <is>
           <t>ID49(NXP Hitag Pro 128bit)</t>
         </is>
@@ -28867,17 +28631,17 @@
         </is>
       </c>
       <c r="K494" s="2" t="inlineStr"/>
-      <c r="L494" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L494" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M494" s="2" t="inlineStr">
         <is>
-          <t>amazon(Beefunny i3/i8 2014-2020 NBGIDGNG1 434MHz)</t>
-        </is>
-      </c>
-      <c r="N494" s="6" t="inlineStr"/>
+          <t>amazon(Beefunny i3/i8 2014-2020 NBGIDGNG1 434MHz), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N494" s="2" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -28905,7 +28669,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F495" s="6" t="inlineStr">
+      <c r="F495" s="2" t="inlineStr">
         <is>
           <t>ID49(NXP Hitag Pro 128bit)</t>
         </is>
@@ -28923,17 +28687,17 @@
         </is>
       </c>
       <c r="K495" s="2" t="inlineStr"/>
-      <c r="L495" s="6" t="inlineStr">
-        <is>
-          <t>BDC (일부 자료 CAS4+/FEM 표기)</t>
+      <c r="L495" s="2" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="M495" s="2" t="inlineStr">
         <is>
-          <t>amazon(i3/i8 2014-2020 NBGIDGNG1), wikipedia(i8 2014-2020)</t>
-        </is>
-      </c>
-      <c r="N495" s="6" t="inlineStr"/>
+          <t>amazon(i3/i8 2014-2020 NBGIDGNG1), wikipedia(i8 2014-2020), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="N495" s="2" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -28986,7 +28750,7 @@
       </c>
       <c r="M496" s="2" t="inlineStr">
         <is>
-          <t>ebay(OEM IYZBK1 2022-2026), go-parts.com(2022-2025 i4 계열 IYZBK1)</t>
+          <t>ebay(OEM IYZBK1 2022-2026), go-parts.com(2022-2025 i4 계열 IYZBK1), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N496" s="2" t="inlineStr">
@@ -29046,7 +28810,7 @@
       </c>
       <c r="M497" s="2" t="inlineStr">
         <is>
-          <t>ebay(2023 i4 OE 키 3248AID21A), bmwnorthwest.com(2023 i4 키), bmwi.bimmerpost.com(i 모델 키·디지털키)</t>
+          <t>ebay(2023 i4 OE 키 3248AID21A), bmwnorthwest.com(2023 i4 키), bmwi.bimmerpost.com(i 모델 키·디지털키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N497" s="2" t="inlineStr">
@@ -29106,7 +28870,7 @@
       </c>
       <c r="M498" s="2" t="inlineStr">
         <is>
-          <t>i4talk.com(i4는 G섀시 표준 키, 디지털키 미지원 의견), i4talk.com(키 교체)</t>
+          <t>i4talk.com(i4는 G섀시 표준 키, 디지털키 미지원 의견), i4talk.com(키 교체), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N498" s="2" t="inlineStr">
@@ -29166,7 +28930,7 @@
       </c>
       <c r="M499" s="2" t="inlineStr">
         <is>
-          <t>amazon(i4 2025 키커버), i4talk.com</t>
+          <t>amazon(i4 2025 키커버), i4talk.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N499" s="2" t="inlineStr"/>
@@ -29222,7 +28986,7 @@
       </c>
       <c r="M500" s="2" t="inlineStr">
         <is>
-          <t>carkeysexpress.com(2026 i4 키 페어링)</t>
+          <t>carkeysexpress.com(2026 i4 키 페어링), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="N500" s="2" t="inlineStr"/>
@@ -29278,7 +29042,7 @@
       </c>
       <c r="M501" s="2" t="inlineStr">
         <is>
-          <t>press.bmwgroup.com·bmwblog.com(iX가 디지털키 플러스 UWB 최초 적용), wikipedia(iX 2021.7 생산)</t>
+          <t>press.bmwgroup.com·bmwblog.com(iX가 디지털키 플러스 UWB 최초 적용), wikipedia(iX 2021.7 생산), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
         </is>
       </c>
       <c r="N501" s="2" t="inlineStr"/>
@@ -29334,7 +29098,7 @@
       </c>
       <c r="M502" s="2" t="inlineStr">
         <is>
-          <t>static.nhtsa.gov(TSB MC-10227565: iX 디지털키 플러스 증상 — BCP 교환 후), ixforums.com(iX 키)</t>
+          <t>static.nhtsa.gov(TSB MC-10227565: iX 디지털키 플러스 증상 — BCP 교환 후), ixforums.com(iX 키), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
         </is>
       </c>
       <c r="N502" s="2" t="inlineStr">
@@ -29398,7 +29162,7 @@
       </c>
       <c r="M503" s="2" t="inlineStr">
         <is>
-          <t>tlkeys.com/ebay(IYZBK1 ID49 NCF795xV, IN-151), battery.guru(2023-2024 iX 키 CR2032), static.nhtsa.gov(iX BCP)</t>
+          <t>tlkeys.com/ebay(IYZBK1 ID49 NCF795xV, IN-151), battery.guru(2023-2024 iX 키 CR2032), static.nhtsa.gov(iX BCP), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
         </is>
       </c>
       <c r="N503" s="2" t="inlineStr"/>
@@ -29454,7 +29218,7 @@
       </c>
       <c r="M504" s="2" t="inlineStr">
         <is>
-          <t>ebay(2023-2024 X1/iX/XM/X5/X6/X7 키), yourcarkeyguys.com(2023-2025 IYZBK1), static.nhtsa.gov(iX BCP)</t>
+          <t>ebay(2023-2024 X1/iX/XM/X5/X6/X7 키), yourcarkeyguys.com(2023-2025 IYZBK1), static.nhtsa.gov(iX BCP), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
         </is>
       </c>
       <c r="N504" s="2" t="inlineStr"/>
@@ -29510,7 +29274,7 @@
       </c>
       <c r="M505" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1: 2025-2026 iX), amazon(iX 2023-2025 키커버), static.nhtsa.gov(iX BCP)</t>
+          <t>ebay(IYZBK1: 2025-2026 iX), amazon(iX 2023-2025 키커버), static.nhtsa.gov(iX BCP), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
         </is>
       </c>
       <c r="N505" s="2" t="inlineStr">
@@ -29570,7 +29334,7 @@
       </c>
       <c r="M506" s="2" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2025-2026 iX), amazon(Autel 2026 BMW 공키), static.nhtsa.gov(iX BCP)</t>
+          <t>ebay(IYZBK1 2025-2026 iX), amazon(Autel 2026 BMW 공키), static.nhtsa.gov(iX BCP), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
         </is>
       </c>
       <c r="N506" s="2" t="inlineStr"/>
@@ -29621,12 +29385,12 @@
       <c r="K507" s="2" t="inlineStr"/>
       <c r="L507" s="2" t="inlineStr">
         <is>
-          <t>BDC2 / BDC3 (VIN 확인)</t>
+          <t>BDC2(2021.8 이전 생산) / BDC3(2021.9 이후 생산)</t>
         </is>
       </c>
       <c r="M507" s="2" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A: 2018-2021 X3/iX3 G08, BDC2), maplekeysupply.ca(BDC2)</t>
+          <t>uhs-hardware.com(N5F-ID21A: 2018-2021 X3/iX3 G08, BDC2), maplekeysupply.ca(BDC2), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G08 BDC2 ~2021/08)</t>
         </is>
       </c>
       <c r="N507" s="2" t="inlineStr"/>
@@ -29866,10 +29630,10 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="C512" s="7" t="inlineStr"/>
-      <c r="D512" s="7" t="inlineStr"/>
-      <c r="E512" s="7" t="inlineStr"/>
-      <c r="F512" s="6" t="inlineStr">
+      <c r="C512" s="6" t="inlineStr"/>
+      <c r="D512" s="6" t="inlineStr"/>
+      <c r="E512" s="6" t="inlineStr"/>
+      <c r="F512" s="8" t="inlineStr">
         <is>
           <t>확인 불가</t>
         </is>
@@ -29883,7 +29647,7 @@
         </is>
       </c>
       <c r="K512" s="2" t="inlineStr"/>
-      <c r="L512" s="6" t="inlineStr">
+      <c r="L512" s="8" t="inlineStr">
         <is>
           <t>ZSM(노이어 클라쎄 존 컨트롤러) — 듀얼 EME ISN</t>
         </is>
@@ -29893,7 +29657,7 @@
           <t>coreautologic.com(iX3 NA5 2026: ZSM 교체 시 두 EME와 ISN 동기화·키 재적응·디지털키 플러스 재등록), bmw.ca(iX3 NA5 디지털키 플러스/실물키)</t>
         </is>
       </c>
-      <c r="N512" s="6" t="inlineStr">
+      <c r="N512" s="8" t="inlineStr">
         <is>
           <t>기존 CAS/FEM/BDC/BCP와 다른 신규 구조 — 칩 형식 원문 없음</t>
         </is>
@@ -29971,7 +29735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -30077,7 +29841,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>- 전환기(CAS3→CAS3+, CAS4→CAS4+, FEM→BDC, BDC2→BDC3)는 색 표시 없이 이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)).</t>
+          <t>- 전환기(EWS3→EWS4, CAS1→CAS2, CAS2→CAS3, CAS3→CAS3+, CAS4→CAS4+, BDC2→BDC3)는 색 표시 없이 이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)).</t>
         </is>
       </c>
     </row>
@@ -30108,21 +29872,49 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>- BDC3는 G30/G31 기준 2020.7 이후 생산분부터(Autel 자료). BDC2 키: N5F-ID21A(9367401-01), 2022년 이후 순정 키: IYZBK1.</t>
+          <t>- [이모빌라이저 재검증] F20/F22/F30/F32/F80/F82/F87은 LCI 이후에도 FEM(딜러 부품 FEM 61355A7FB57 등) — BDC가 아닙니다. F15/F16/F85/F86/F45/F48/F39/i3/i8은 BDC.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>- U섀시(U06/U10/U11)는 BCP 이모빌라이저 + UWB 키(NCF2951/Hitag Pro/ID49, FCC IYZBK1).</t>
+          <t>- BDC2(BDC_G11): G11/G12(~2019.2), G30/G31/G32/F90(~2020.6), G01/G02/F97/F98(~2021.7), G08(~2021.8). 이후 생산분은 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>- F40·F44는 G시리즈 전장이라 BDC2/BDC3 표기가 자료마다 다릅니다(주황색).</t>
+          <t>- BDC3(BDC_G05): G05/G06/G07/G20/G15/G29/F40/F44/G42/G22/G80/G82/G87/F95/F96은 출시부터 BDC3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>- BCP: i7/7시리즈 G70·iX(딜러 부품 'Control u.basic computing platform (BCP)' 61355A9A210), U06/U10/U11, G45. G60/i5/G90은 BDC3·BCP 자료 상충(주황색).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>- BDC2 키: N5F-ID21A(9367401-01), 2022년 이후 순정 키: IYZBK1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>- U섀시(U06/U10/U11)는 BCP 이모빌라이저 + UWB 키(NCF2951/Hitag Pro/ID49, FCC IYZBK1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>- E65는 2005 LCI 전 CAS1, 이후 CAS2. E60/E61/E63은 2007.3 LCI 전 CAS2, 이후 CAS3. E83은 2006 중 EWS3→EWS4.</t>
         </is>
       </c>
     </row>

--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -129,10 +129,10 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -147,13 +147,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,7 +540,7 @@
     <col width="48" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>모델명</t>

--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -11,7 +11,7 @@
     <sheet name="안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BMW 트랜스폰더 DB'!$A$1:$P$513</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BMW 트랜스폰더 DB'!$A$1:$P$508</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,16 @@
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF9C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF006100"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -126,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -166,6 +176,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P513"/>
+  <dimension ref="A1:P508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1913,12 +1935,24 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>ID49[추정]</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -1926,18 +1960,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr"/>
       <c r="L21" s="11" t="inlineStr"/>
       <c r="M21" s="11" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>BDC3[추정]</t>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t>BCP[추정]</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
@@ -1945,9 +1983,9 @@
           <t>go-parts.com(G시리즈 2016-2025 BDC 키), rallyebmw.com(디지털키 NFC/UWB)</t>
         </is>
       </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>신형 섀시(F70/F74) 전용 칩·이모빌라이저 자료 없음</t>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>F70 전용 칩 자료 없음 — 같은 비상키(51215A65D30)를 쓰는 U11·G60 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -1967,12 +2005,24 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>ID49[추정]</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
@@ -1980,18 +2030,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr"/>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr"/>
       <c r="L22" s="11" t="inlineStr"/>
       <c r="M22" s="11" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>BDC3[추정]</t>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t>BCP[추정]</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
@@ -1999,9 +2053,9 @@
           <t>autelkeytools.com(BDC02/BDC03 키 등록 업데이트), go-parts.com</t>
         </is>
       </c>
-      <c r="P22" s="7" t="inlineStr">
-        <is>
-          <t>신형 섀시(F70/F74) 전용 칩·이모빌라이저 자료 없음</t>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>F70 전용 칩 자료 없음 — 같은 비상키(51215A65D30)를 쓰는 U11·G60 키 기준 추정</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4368,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G58" s="8" t="inlineStr">
+      <c r="G58" s="17" t="inlineStr">
         <is>
           <t>ID49(NCF2951)</t>
         </is>
@@ -4324,7 +4378,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I58" s="11" t="inlineStr"/>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J58" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -4337,7 +4395,7 @@
         </is>
       </c>
       <c r="M58" s="11" t="inlineStr"/>
-      <c r="N58" s="8" t="inlineStr">
+      <c r="N58" s="17" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -4347,11 +4405,7 @@
           <t>obdii365.com(Autel IMMO BDC02/BDC03/BCP 키추가), automobile-catalog.com(2025 U06)</t>
         </is>
       </c>
-      <c r="P58" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P58" s="17" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -4384,7 +4438,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G59" s="8" t="inlineStr">
+      <c r="G59" s="17" t="inlineStr">
         <is>
           <t>ID49(NCF2951)</t>
         </is>
@@ -4394,7 +4448,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I59" s="11" t="inlineStr"/>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J59" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -4407,7 +4465,7 @@
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr"/>
-      <c r="N59" s="8" t="inlineStr">
+      <c r="N59" s="17" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -4417,11 +4475,7 @@
           <t>obdii365.com(KEYDIY KD-X4 U섀시 BCP UWB 키 복사)</t>
         </is>
       </c>
-      <c r="P59" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P59" s="17" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
@@ -4815,12 +4869,24 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr"/>
-      <c r="E66" s="6" t="inlineStr"/>
-      <c r="F66" s="6" t="inlineStr"/>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>ID49[추정]</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
@@ -4837,9 +4903,9 @@
       <c r="K66" s="11" t="inlineStr"/>
       <c r="L66" s="11" t="inlineStr"/>
       <c r="M66" s="11" t="inlineStr"/>
-      <c r="N66" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="N66" s="8" t="inlineStr">
+        <is>
+          <t>BCP[추정]</t>
         </is>
       </c>
       <c r="O66" s="11" t="inlineStr">
@@ -4847,9 +4913,9 @@
           <t>press.bmwgroup.com(2025 2시리즈 그란쿠페: 디지털키 플러스 UWB), wikipedia(F74 2024.11 생산)</t>
         </is>
       </c>
-      <c r="P66" s="7" t="inlineStr">
-        <is>
-          <t>신형 섀시(F70/F74) 전용 칩·이모빌라이저 자료 없음</t>
+      <c r="P66" s="8" t="inlineStr">
+        <is>
+          <t>F74 전용 자료 없음 — 같은 플랫폼 F70 기준 추정</t>
         </is>
       </c>
     </row>
@@ -4869,12 +4935,24 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr"/>
-      <c r="E67" s="6" t="inlineStr"/>
-      <c r="F67" s="6" t="inlineStr"/>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>ID49[추정]</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
@@ -4891,9 +4969,9 @@
       <c r="K67" s="11" t="inlineStr"/>
       <c r="L67" s="11" t="inlineStr"/>
       <c r="M67" s="11" t="inlineStr"/>
-      <c r="N67" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="N67" s="8" t="inlineStr">
+        <is>
+          <t>BCP[추정]</t>
         </is>
       </c>
       <c r="O67" s="11" t="inlineStr">
@@ -4901,9 +4979,9 @@
           <t>faq.bmwusa.com(2시리즈 GC MY25 디지털키 요건), 딜러 일반 키등록 안내</t>
         </is>
       </c>
-      <c r="P67" s="7" t="inlineStr">
-        <is>
-          <t>신형 섀시(F70/F74) 전용 칩·이모빌라이저 자료 없음</t>
+      <c r="P67" s="8" t="inlineStr">
+        <is>
+          <t>F74 전용 자료 없음 — 같은 플랫폼 F70 기준 추정</t>
         </is>
       </c>
     </row>
@@ -11462,7 +11540,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I167" s="11" t="inlineStr"/>
+      <c r="I167" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J167" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -11487,7 +11569,7 @@
       </c>
       <c r="P167" s="8" t="inlineStr">
         <is>
-          <t>이모빌라이저 BDC3·BCP 출처 상충</t>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
         </is>
       </c>
     </row>
@@ -11532,7 +11614,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I168" s="11" t="inlineStr"/>
+      <c r="I168" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J168" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -11557,7 +11643,7 @@
       </c>
       <c r="P168" s="8" t="inlineStr">
         <is>
-          <t>이모빌라이저 BDC3·BCP 출처 상충</t>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
         </is>
       </c>
     </row>
@@ -11602,7 +11688,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I169" s="11" t="inlineStr"/>
+      <c r="I169" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J169" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -11627,7 +11717,7 @@
       </c>
       <c r="P169" s="8" t="inlineStr">
         <is>
-          <t>이모빌라이저 BDC3·BCP 출처 상충</t>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11762,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I170" s="11" t="inlineStr"/>
+      <c r="I170" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J170" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -11697,7 +11791,7 @@
       </c>
       <c r="P170" s="8" t="inlineStr">
         <is>
-          <t>이모빌라이저 BDC3·BCP 출처 상충</t>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
         </is>
       </c>
     </row>
@@ -11742,7 +11836,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I171" s="11" t="inlineStr"/>
+      <c r="I171" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J171" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -11767,7 +11865,7 @@
       </c>
       <c r="P171" s="8" t="inlineStr">
         <is>
-          <t>이모빌라이저 BDC3·BCP 출처 상충</t>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11910,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I172" s="11" t="inlineStr"/>
+      <c r="I172" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J172" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -11837,7 +11939,7 @@
       </c>
       <c r="P172" s="8" t="inlineStr">
         <is>
-          <t>이모빌라이저 BDC3·BCP 출처 상충</t>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11984,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I173" s="11" t="inlineStr"/>
+      <c r="I173" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J173" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -11907,7 +12013,7 @@
       </c>
       <c r="P173" s="8" t="inlineStr">
         <is>
-          <t>이모빌라이저 BDC3·BCP 출처 상충</t>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
         </is>
       </c>
     </row>
@@ -11952,7 +12058,11 @@
           <t>스마트키,카드키</t>
         </is>
       </c>
-      <c r="I174" s="11" t="inlineStr"/>
+      <c r="I174" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J174" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -11977,7 +12087,7 @@
       </c>
       <c r="P174" s="8" t="inlineStr">
         <is>
-          <t>이모빌라이저 BDC3·BCP 출처 상충</t>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13724,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I199" s="11" t="inlineStr"/>
+      <c r="I199" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J199" s="11" t="inlineStr">
         <is>
           <t>HU100R[추정]</t>
@@ -13639,7 +13753,7 @@
       </c>
       <c r="P199" s="8" t="inlineStr">
         <is>
-          <t>이 연식 이모빌라이저 BDC3·BCP 자료 상충(확인 필요)</t>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13798,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I200" s="11" t="inlineStr"/>
+      <c r="I200" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J200" s="11" t="inlineStr">
         <is>
           <t>HU100R[추정]</t>
@@ -13709,7 +13827,7 @@
       </c>
       <c r="P200" s="8" t="inlineStr">
         <is>
-          <t>이 연식 이모빌라이저 BDC3·BCP 자료 상충(확인 필요)</t>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13872,11 @@
           <t>스마트키,카드키</t>
         </is>
       </c>
-      <c r="I201" s="11" t="inlineStr"/>
+      <c r="I201" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J201" s="11" t="inlineStr">
         <is>
           <t>HU100R[추정]</t>
@@ -13775,7 +13897,7 @@
       </c>
       <c r="P201" s="8" t="inlineStr">
         <is>
-          <t>이 연식 이모빌라이저 BDC3·BCP 자료 상충(확인 필요)</t>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
         </is>
       </c>
     </row>
@@ -20130,7 +20252,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G298" s="8" t="inlineStr">
+      <c r="G298" s="17" t="inlineStr">
         <is>
           <t>ID49(NCF2951)</t>
         </is>
@@ -20140,7 +20262,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I298" s="11" t="inlineStr"/>
+      <c r="I298" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J298" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -20149,11 +20275,11 @@
       <c r="K298" s="11" t="inlineStr"/>
       <c r="L298" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC IYZBK1[UWB]</t>
         </is>
       </c>
       <c r="M298" s="11" t="inlineStr"/>
-      <c r="N298" s="8" t="inlineStr">
+      <c r="N298" s="17" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -20163,11 +20289,7 @@
           <t>go-parts.com(2022-2025 X1/iX 5버튼 스마트키, 딜러/전문 로크스미스 등록 필수), keyless2go.com(2024 X1 키등록)</t>
         </is>
       </c>
-      <c r="P298" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P298" s="17" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
@@ -20200,7 +20322,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G299" s="8" t="inlineStr">
+      <c r="G299" s="17" t="inlineStr">
         <is>
           <t>ID49(NCF2951)</t>
         </is>
@@ -20210,16 +20332,24 @@
           <t>스마트키,카드키</t>
         </is>
       </c>
-      <c r="I299" s="11" t="inlineStr"/>
+      <c r="I299" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J299" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K299" s="11" t="inlineStr"/>
-      <c r="L299" s="11" t="n"/>
+      <c r="L299" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1[UWB]</t>
+        </is>
+      </c>
       <c r="M299" s="11" t="inlineStr"/>
-      <c r="N299" s="8" t="inlineStr">
+      <c r="N299" s="17" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -20229,11 +20359,7 @@
           <t>u11.bimmerpost.com(2026 X1: 키 1개·디지털키 카드·서비스 카드, 2025는 키 2개)</t>
         </is>
       </c>
-      <c r="P299" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P299" s="17" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
@@ -20398,7 +20524,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G302" s="8" t="inlineStr">
+      <c r="G302" s="17" t="inlineStr">
         <is>
           <t>ID49(NCF2951)</t>
         </is>
@@ -20408,7 +20534,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I302" s="11" t="inlineStr"/>
+      <c r="I302" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J302" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -20417,11 +20547,11 @@
       <c r="K302" s="11" t="inlineStr"/>
       <c r="L302" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC IYZBK1[UWB]</t>
         </is>
       </c>
       <c r="M302" s="11" t="inlineStr"/>
-      <c r="N302" s="8" t="inlineStr">
+      <c r="N302" s="17" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -20431,11 +20561,7 @@
           <t>go-parts.com(2022-2025 X1/iX 5버튼 스마트키, 딜러/전문 로크스미스 등록 필수), keyless2go.com(2024 X1 키등록)</t>
         </is>
       </c>
-      <c r="P302" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P302" s="17" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
@@ -20468,7 +20594,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G303" s="8" t="inlineStr">
+      <c r="G303" s="17" t="inlineStr">
         <is>
           <t>ID49(NCF2951)</t>
         </is>
@@ -20478,16 +20604,24 @@
           <t>스마트키,카드키</t>
         </is>
       </c>
-      <c r="I303" s="11" t="inlineStr"/>
+      <c r="I303" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J303" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K303" s="11" t="inlineStr"/>
-      <c r="L303" s="11" t="n"/>
+      <c r="L303" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1[UWB]</t>
+        </is>
+      </c>
       <c r="M303" s="11" t="inlineStr"/>
-      <c r="N303" s="8" t="inlineStr">
+      <c r="N303" s="17" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -20497,11 +20631,7 @@
           <t>u11.bimmerpost.com(2026 X1: 키 1개·디지털키 카드·서비스 카드, 2025는 키 2개)</t>
         </is>
       </c>
-      <c r="P303" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P303" s="17" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="11" t="inlineStr">
@@ -21050,7 +21180,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G312" s="8" t="inlineStr">
+      <c r="G312" s="17" t="inlineStr">
         <is>
           <t>ID49(NCF2951)</t>
         </is>
@@ -21060,7 +21190,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I312" s="11" t="inlineStr"/>
+      <c r="I312" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J312" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -21073,7 +21207,7 @@
         </is>
       </c>
       <c r="M312" s="11" t="inlineStr"/>
-      <c r="N312" s="8" t="inlineStr">
+      <c r="N312" s="17" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -21083,11 +21217,7 @@
           <t>carkeyhelper.com(X2 2024-2026 스마트키), u11.bimmerpost.com(U11/U10 SP21 전장 UWB)</t>
         </is>
       </c>
-      <c r="P312" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P312" s="17" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="11" t="inlineStr">
@@ -21120,7 +21250,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G313" s="8" t="inlineStr">
+      <c r="G313" s="17" t="inlineStr">
         <is>
           <t>ID49(NCF2951)</t>
         </is>
@@ -21130,16 +21260,24 @@
           <t>스마트키,카드키</t>
         </is>
       </c>
-      <c r="I313" s="11" t="inlineStr"/>
+      <c r="I313" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J313" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K313" s="11" t="inlineStr"/>
-      <c r="L313" s="11" t="n"/>
+      <c r="L313" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1[UWB]</t>
+        </is>
+      </c>
       <c r="M313" s="11" t="inlineStr"/>
-      <c r="N313" s="8" t="inlineStr">
+      <c r="N313" s="17" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -21149,11 +21287,7 @@
           <t>u11.bimmerpost.com(2026 X1/X2 키 1개·디지털키 카드), carkeyhelper.com</t>
         </is>
       </c>
-      <c r="P313" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P313" s="17" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="11" t="inlineStr">
@@ -21318,7 +21452,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G316" s="8" t="inlineStr">
+      <c r="G316" s="17" t="inlineStr">
         <is>
           <t>ID49(NCF2951)</t>
         </is>
@@ -21328,7 +21462,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I316" s="11" t="inlineStr"/>
+      <c r="I316" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J316" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -21341,7 +21479,7 @@
         </is>
       </c>
       <c r="M316" s="11" t="inlineStr"/>
-      <c r="N316" s="8" t="inlineStr">
+      <c r="N316" s="17" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -21351,11 +21489,7 @@
           <t>carkeyhelper.com(X2 2024-2026 스마트키), u11.bimmerpost.com(U11/U10 SP21 전장 UWB)</t>
         </is>
       </c>
-      <c r="P316" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P316" s="17" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
@@ -21388,7 +21522,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G317" s="8" t="inlineStr">
+      <c r="G317" s="17" t="inlineStr">
         <is>
           <t>ID49(NCF2951)</t>
         </is>
@@ -21398,16 +21532,24 @@
           <t>스마트키,카드키</t>
         </is>
       </c>
-      <c r="I317" s="11" t="inlineStr"/>
+      <c r="I317" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J317" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K317" s="11" t="inlineStr"/>
-      <c r="L317" s="11" t="n"/>
+      <c r="L317" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1[UWB]</t>
+        </is>
+      </c>
       <c r="M317" s="11" t="inlineStr"/>
-      <c r="N317" s="8" t="inlineStr">
+      <c r="N317" s="17" t="inlineStr">
         <is>
           <t>BCP</t>
         </is>
@@ -21417,11 +21559,7 @@
           <t>u11.bimmerpost.com(2026 X1/X2 키 1개·디지털키 카드), carkeyhelper.com</t>
         </is>
       </c>
-      <c r="P317" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+      <c r="P317" s="17" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
@@ -21982,7 +22120,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G326" s="8" t="inlineStr">
+      <c r="G326" s="17" t="inlineStr">
         <is>
           <t>ID49(PCF7945P), ID49(PCF7953)</t>
         </is>
@@ -21995,7 +22133,7 @@
       <c r="I326" s="11" t="inlineStr"/>
       <c r="J326" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준], HU127[일부 자료]</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K326" s="11" t="inlineStr"/>
@@ -22005,7 +22143,7 @@
         </is>
       </c>
       <c r="M326" s="11" t="inlineStr"/>
-      <c r="N326" s="8" t="inlineStr">
+      <c r="N326" s="17" t="inlineStr">
         <is>
           <t>CAS4+</t>
         </is>
@@ -22015,11 +22153,7 @@
           <t>mr-key.com(3/5/6/X3/X5/X6 FEM/CAS4+ 434MHz, 블레이드 HU127 표기), carandtruckremotes.com(2013 X3 YGOHUF5662 CAS4)</t>
         </is>
       </c>
-      <c r="P326" s="8" t="inlineStr">
-        <is>
-          <t>블레이드 표기 HU127 vs HU100R 상충</t>
-        </is>
-      </c>
+      <c r="P326" s="17" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="11" t="inlineStr">
@@ -22838,7 +22972,7 @@
       </c>
       <c r="G339" s="8" t="inlineStr">
         <is>
-          <t>ID49(NCF2951)[추정]</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H339" s="11" t="inlineStr">
@@ -22846,14 +22980,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I339" s="11" t="inlineStr"/>
+      <c r="I339" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J339" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K339" s="11" t="inlineStr"/>
-      <c r="L339" s="11" t="n"/>
+      <c r="L339" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M339" s="11" t="inlineStr"/>
       <c r="N339" s="8" t="inlineStr">
         <is>
@@ -22867,7 +23009,7 @@
       </c>
       <c r="P339" s="8" t="inlineStr">
         <is>
-          <t>2024년식 BDC3 vs BCP 자료 상충, 칩은 U섀시 기준 추정</t>
+          <t>키(IYZBK1, ID49) 확인 — 이모빌라이저 BCP·BDC3 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22904,7 +23046,7 @@
       </c>
       <c r="G340" s="8" t="inlineStr">
         <is>
-          <t>ID49(NCF2951)[추정]</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H340" s="11" t="inlineStr">
@@ -22912,18 +23054,26 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I340" s="11" t="inlineStr"/>
+      <c r="I340" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J340" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K340" s="11" t="inlineStr"/>
-      <c r="L340" s="11" t="n"/>
+      <c r="L340" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M340" s="11" t="inlineStr"/>
       <c r="N340" s="8" t="inlineStr">
         <is>
-          <t>BCP</t>
+          <t>BCP[추정]</t>
         </is>
       </c>
       <c r="O340" s="11" t="inlineStr">
@@ -22933,7 +23083,7 @@
       </c>
       <c r="P340" s="8" t="inlineStr">
         <is>
-          <t>칩 세부형식 직접 확인 안 됨(U섀시 기준 추정)</t>
+          <t>키(IYZBK1, ID49) 확인 — 이모빌라이저 BCP·BDC3 원문 없음</t>
         </is>
       </c>
     </row>
@@ -22953,12 +23103,24 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D341" s="6" t="inlineStr"/>
-      <c r="E341" s="6" t="inlineStr"/>
-      <c r="F341" s="6" t="inlineStr"/>
-      <c r="G341" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="D341" s="14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E341" s="15" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F341" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G341" s="8" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H341" s="11" t="inlineStr">
@@ -22966,16 +23128,24 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I341" s="11" t="inlineStr"/>
+      <c r="I341" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J341" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K341" s="11" t="inlineStr"/>
-      <c r="L341" s="11" t="inlineStr"/>
+      <c r="L341" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M341" s="11" t="inlineStr"/>
-      <c r="N341" s="7" t="inlineStr">
+      <c r="N341" s="8" t="inlineStr">
         <is>
           <t>BCP[추정]</t>
         </is>
@@ -22985,9 +23155,9 @@
           <t>mechanicwiki.com(X3 키 등록 일반), justanswer.com(X3 중고키 등록) — 2026 G45 전용 자료 없음</t>
         </is>
       </c>
-      <c r="P341" s="7" t="inlineStr">
-        <is>
-          <t>2026년식 칩 자료 없음</t>
+      <c r="P341" s="8" t="inlineStr">
+        <is>
+          <t>키(IYZBK1, ID49) 확인 — 이모빌라이저 BCP·BDC3 원문 없음</t>
         </is>
       </c>
     </row>
@@ -23334,7 +23504,7 @@
       </c>
       <c r="C347" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024(단종)</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -23395,20 +23565,32 @@
       </c>
       <c r="B348" s="11" t="inlineStr">
         <is>
-          <t>X3 M (F97)</t>
+          <t>X4 (F26, 1세대)</t>
         </is>
       </c>
       <c r="C348" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D348" s="6" t="inlineStr"/>
-      <c r="E348" s="6" t="inlineStr"/>
-      <c r="F348" s="6" t="inlineStr"/>
-      <c r="G348" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="D348" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F348" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G348" s="11" t="inlineStr">
+        <is>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H348" s="11" t="inlineStr">
@@ -23417,25 +23599,29 @@
         </is>
       </c>
       <c r="I348" s="11" t="inlineStr"/>
-      <c r="J348" s="11" t="inlineStr"/>
+      <c r="J348" s="11" t="inlineStr">
+        <is>
+          <t>HU100R[세대 기준]</t>
+        </is>
+      </c>
       <c r="K348" s="11" t="inlineStr"/>
-      <c r="L348" s="11" t="inlineStr"/>
+      <c r="L348" s="11" t="inlineStr">
+        <is>
+          <t>ILCO AX00014800[애프터마켓]</t>
+        </is>
+      </c>
       <c r="M348" s="11" t="inlineStr"/>
-      <c r="N348" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="N348" s="11" t="inlineStr">
+        <is>
+          <t>CAS4+</t>
         </is>
       </c>
       <c r="O348" s="11" t="inlineStr">
         <is>
-          <t>bmwblog.com(F97 2024 종료, 후속 X3 M 없음 — G45 X3 M50으로 대체)</t>
-        </is>
-      </c>
-      <c r="P348" s="7" t="inlineStr">
-        <is>
-          <t>해당 섀시 생산 종료 후 연식 — 국내 해당 연식 존재 여부 확인 불가</t>
-        </is>
-      </c>
+          <t>carandtruckremotes.com(2014 X4 YGOHUF5662 CAS4/CAS4+ EWS5, BMW PN 9 259 718-01, ILCO AX00014800)</t>
+        </is>
+      </c>
+      <c r="P348" s="11" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="11" t="inlineStr">
@@ -23445,20 +23631,32 @@
       </c>
       <c r="B349" s="11" t="inlineStr">
         <is>
-          <t>X3 M (F97)</t>
+          <t>X4 (F26, 1세대)</t>
         </is>
       </c>
       <c r="C349" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D349" s="6" t="inlineStr"/>
-      <c r="E349" s="6" t="inlineStr"/>
-      <c r="F349" s="6" t="inlineStr"/>
-      <c r="G349" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D349" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F349" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G349" s="11" t="inlineStr">
+        <is>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H349" s="11" t="inlineStr">
@@ -23467,25 +23665,29 @@
         </is>
       </c>
       <c r="I349" s="11" t="inlineStr"/>
-      <c r="J349" s="11" t="inlineStr"/>
+      <c r="J349" s="11" t="inlineStr">
+        <is>
+          <t>HU100R[세대 기준]</t>
+        </is>
+      </c>
       <c r="K349" s="11" t="inlineStr"/>
-      <c r="L349" s="11" t="inlineStr"/>
+      <c r="L349" s="11" t="inlineStr">
+        <is>
+          <t>9259718-01, FCC YGOHUF5662</t>
+        </is>
+      </c>
       <c r="M349" s="11" t="inlineStr"/>
-      <c r="N349" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="N349" s="11" t="inlineStr">
+        <is>
+          <t>CAS4+</t>
         </is>
       </c>
       <c r="O349" s="11" t="inlineStr">
         <is>
-          <t>bmwblog.com(F97 2024 종료), g45.bimmerpost.com(2026 X3 키)</t>
-        </is>
-      </c>
-      <c r="P349" s="7" t="inlineStr">
-        <is>
-          <t>해당 섀시 생산 종료 후 연식 — 국내 해당 연식 존재 여부 확인 불가</t>
-        </is>
-      </c>
+          <t>carandtruckremotes.com(YGOHUF5662 X4 2014-2018), locksmithkeyless.com(2009-2018 YGOHUF5662)</t>
+        </is>
+      </c>
+      <c r="P349" s="11" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="11" t="inlineStr">
@@ -23500,7 +23702,7 @@
       </c>
       <c r="C350" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D350" s="4" t="inlineStr">
@@ -23520,7 +23722,7 @@
       </c>
       <c r="G350" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953P)</t>
+          <t>ID49(PCF7953), ID49(PCF7945P)[일부 자료]</t>
         </is>
       </c>
       <c r="H350" s="11" t="inlineStr">
@@ -23535,11 +23737,7 @@
         </is>
       </c>
       <c r="K350" s="11" t="inlineStr"/>
-      <c r="L350" s="11" t="inlineStr">
-        <is>
-          <t>ILCO AX00014800[애프터마켓]</t>
-        </is>
-      </c>
+      <c r="L350" s="11" t="inlineStr"/>
       <c r="M350" s="11" t="inlineStr"/>
       <c r="N350" s="11" t="inlineStr">
         <is>
@@ -23548,7 +23746,7 @@
       </c>
       <c r="O350" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes.com(2014 X4 YGOHUF5662 CAS4/CAS4+ EWS5, BMW PN 9 259 718-01, ILCO AX00014800)</t>
+          <t>bmwpartsdeal.com(2016 X4 xDrive28i·35i F26 키 부품목록), carandtruckremotes.com(2016 X4 YGOHUF5662), accessfobs.co.uk(X4 F26 2014-2018 CAS4 868MHz)</t>
         </is>
       </c>
       <c r="P350" s="11" t="inlineStr"/>
@@ -23566,7 +23764,7 @@
       </c>
       <c r="C351" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -23586,7 +23784,7 @@
       </c>
       <c r="G351" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953P)</t>
+          <t>ID49(PCF7953)</t>
         </is>
       </c>
       <c r="H351" s="11" t="inlineStr">
@@ -23603,7 +23801,7 @@
       <c r="K351" s="11" t="inlineStr"/>
       <c r="L351" s="11" t="inlineStr">
         <is>
-          <t>9259718-01, FCC YGOHUF5662</t>
+          <t>FCC YGOHUF5662</t>
         </is>
       </c>
       <c r="M351" s="11" t="inlineStr"/>
@@ -23614,7 +23812,7 @@
       </c>
       <c r="O351" s="11" t="inlineStr">
         <is>
-          <t>carandtruckremotes.com(YGOHUF5662 X4 2014-2018), locksmithkeyless.com(2009-2018 YGOHUF5662)</t>
+          <t>bmwpartsdeal.com(2017 X4 M40i F26 키 부품목록), carandtruckremotes.com(2017 X4)</t>
         </is>
       </c>
       <c r="P351" s="11" t="inlineStr"/>
@@ -23632,7 +23830,7 @@
       </c>
       <c r="C352" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2018(단종)</t>
         </is>
       </c>
       <c r="D352" s="4" t="inlineStr">
@@ -23652,7 +23850,7 @@
       </c>
       <c r="G352" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953), ID49(PCF7945P)[일부 자료]</t>
+          <t>ID49(PCF7953)</t>
         </is>
       </c>
       <c r="H352" s="11" t="inlineStr">
@@ -23667,7 +23865,11 @@
         </is>
       </c>
       <c r="K352" s="11" t="inlineStr"/>
-      <c r="L352" s="11" t="inlineStr"/>
+      <c r="L352" s="11" t="inlineStr">
+        <is>
+          <t>FCC YGOHUF5662</t>
+        </is>
+      </c>
       <c r="M352" s="11" t="inlineStr"/>
       <c r="N352" s="11" t="inlineStr">
         <is>
@@ -23676,7 +23878,7 @@
       </c>
       <c r="O352" s="11" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2016 X4 xDrive28i·35i F26 키 부품목록), carandtruckremotes.com(2016 X4 YGOHUF5662), accessfobs.co.uk(X4 F26 2014-2018 CAS4 868MHz)</t>
+          <t>bmwpartsdeal.com(2018 X4 M40i F26 키 부품목록), carandtruckremotes.com(2018 X4)</t>
         </is>
       </c>
       <c r="P352" s="11" t="inlineStr"/>
@@ -23689,12 +23891,12 @@
       </c>
       <c r="B353" s="11" t="inlineStr">
         <is>
-          <t>X4 (F26, 1세대)</t>
+          <t>X4 (G02, 2세대)</t>
         </is>
       </c>
       <c r="C353" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -23714,7 +23916,7 @@
       </c>
       <c r="G353" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953)</t>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H353" s="11" t="inlineStr">
@@ -23731,18 +23933,18 @@
       <c r="K353" s="11" t="inlineStr"/>
       <c r="L353" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662</t>
+          <t>9367401-01, FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M353" s="11" t="inlineStr"/>
       <c r="N353" s="11" t="inlineStr">
         <is>
-          <t>CAS4+</t>
+          <t>BDC2</t>
         </is>
       </c>
       <c r="O353" s="11" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2017 X4 M40i F26 키 부품목록), carandtruckremotes.com(2017 X4)</t>
+          <t>yourcarkeyguys.com(BDC2 N5F-ID21A: 2018-2021 X4 G02), uhs-hardware.com(2017-2021 X4 G02), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="P353" s="11" t="inlineStr"/>
@@ -23755,12 +23957,12 @@
       </c>
       <c r="B354" s="11" t="inlineStr">
         <is>
-          <t>X4 (F26, 1세대)</t>
+          <t>X4 (G02, 2세대)</t>
         </is>
       </c>
       <c r="C354" s="11" t="inlineStr">
         <is>
-          <t>2018(단종)</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D354" s="4" t="inlineStr">
@@ -23780,7 +23982,7 @@
       </c>
       <c r="G354" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953)</t>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H354" s="11" t="inlineStr">
@@ -23797,18 +23999,18 @@
       <c r="K354" s="11" t="inlineStr"/>
       <c r="L354" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662</t>
+          <t>9367401-01, FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M354" s="11" t="inlineStr"/>
       <c r="N354" s="11" t="inlineStr">
         <is>
-          <t>CAS4+</t>
+          <t>BDC2</t>
         </is>
       </c>
       <c r="O354" s="11" t="inlineStr">
         <is>
-          <t>bmwpartsdeal.com(2018 X4 M40i F26 키 부품목록), carandtruckremotes.com(2018 X4)</t>
+          <t>maplekeysupply.ca(BDC2 N5F-ID21A), locksmithkeyless.com(2014-2023 N5F-ID21A 9367401-01), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="P354" s="11" t="inlineStr"/>
@@ -23826,7 +24028,7 @@
       </c>
       <c r="C355" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -23863,7 +24065,7 @@
       <c r="K355" s="11" t="inlineStr"/>
       <c r="L355" s="11" t="inlineStr">
         <is>
-          <t>9367401-01, FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M355" s="11" t="inlineStr"/>
@@ -23874,7 +24076,7 @@
       </c>
       <c r="O355" s="11" t="inlineStr">
         <is>
-          <t>yourcarkeyguys.com(BDC2 N5F-ID21A: 2018-2021 X4 G02), uhs-hardware.com(2017-2021 X4 G02), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
+          <t>vxdas.com(APP2 BDC02: X4 G02 2018-2021), abrites.com(BN020 BDC2 대략 2021까지), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="P355" s="11" t="inlineStr"/>
@@ -23892,7 +24094,7 @@
       </c>
       <c r="C356" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D356" s="4" t="inlineStr">
@@ -23929,18 +24131,18 @@
       <c r="K356" s="11" t="inlineStr"/>
       <c r="L356" s="11" t="inlineStr">
         <is>
-          <t>9367401-01, FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M356" s="11" t="inlineStr"/>
       <c r="N356" s="11" t="inlineStr">
         <is>
-          <t>BDC2</t>
+          <t>BDC2[2021.7 이전 생산], BDC3[2021.8 이후 생산]</t>
         </is>
       </c>
       <c r="O356" s="11" t="inlineStr">
         <is>
-          <t>maplekeysupply.ca(BDC2 N5F-ID21A), locksmithkeyless.com(2014-2023 N5F-ID21A 9367401-01), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
+          <t>americankeysupply.com(BN020 BDC2), vxdas.com(APP2: X4 G02 2018-2021 BDC02), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07, BDC3 2021/08~)</t>
         </is>
       </c>
       <c r="P356" s="11" t="inlineStr"/>
@@ -23958,7 +24160,7 @@
       </c>
       <c r="C357" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
@@ -23978,7 +24180,7 @@
       </c>
       <c r="G357" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953P)</t>
+          <t>ID49(PCF7953V)</t>
         </is>
       </c>
       <c r="H357" s="11" t="inlineStr">
@@ -23995,18 +24197,18 @@
       <c r="K357" s="11" t="inlineStr"/>
       <c r="L357" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC IYZBK1[4버튼]</t>
         </is>
       </c>
       <c r="M357" s="11" t="inlineStr"/>
       <c r="N357" s="11" t="inlineStr">
         <is>
-          <t>BDC2</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O357" s="11" t="inlineStr">
         <is>
-          <t>vxdas.com(APP2 BDC02: X4 G02 2018-2021), abrites.com(BN020 BDC2 대략 2021까지), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
+          <t>tlkeys.com(순정 2022~ IYZBK1 433MHz, ID49 HITAG PRO PCF7953V), xhorse-tool.com(CN006121 IYZBK1 2022-2024 ID49), getbmwparts.com(G02 LCI 2022+)</t>
         </is>
       </c>
       <c r="P357" s="11" t="inlineStr"/>
@@ -24024,7 +24226,7 @@
       </c>
       <c r="C358" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D358" s="4" t="inlineStr">
@@ -24044,7 +24246,7 @@
       </c>
       <c r="G358" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953P)</t>
+          <t>ID49(NCF29Ax)</t>
         </is>
       </c>
       <c r="H358" s="11" t="inlineStr">
@@ -24061,18 +24263,18 @@
       <c r="K358" s="11" t="inlineStr"/>
       <c r="L358" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC IYZBK1, KD FGB23[애프터마켓]</t>
         </is>
       </c>
       <c r="M358" s="11" t="inlineStr"/>
       <c r="N358" s="11" t="inlineStr">
         <is>
-          <t>BDC2[2021.7 이전 생산], BDC3[2021.8 이후 생산]</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O358" s="11" t="inlineStr">
         <is>
-          <t>americankeysupply.com(BN020 BDC2), vxdas.com(APP2: X4 G02 2018-2021 BDC02), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07, BDC3 2021/08~)</t>
+          <t>obdii365.com(KEYDIY KD-X4 BDC3 키추가: 원키에서 NCF29Ax 칩 데이터 읽기, Hungary 표기 2020-2024 키 지원·암호화 키 미지원)</t>
         </is>
       </c>
       <c r="P358" s="11" t="inlineStr"/>
@@ -24090,7 +24292,7 @@
       </c>
       <c r="C359" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -24110,7 +24312,7 @@
       </c>
       <c r="G359" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953V)</t>
+          <t>ID49(NCF29Ax)</t>
         </is>
       </c>
       <c r="H359" s="11" t="inlineStr">
@@ -24127,7 +24329,7 @@
       <c r="K359" s="11" t="inlineStr"/>
       <c r="L359" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1[4버튼]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M359" s="11" t="inlineStr"/>
@@ -24138,7 +24340,7 @@
       </c>
       <c r="O359" s="11" t="inlineStr">
         <is>
-          <t>tlkeys.com(순정 2022~ IYZBK1 433MHz, ID49 HITAG PRO PCF7953V), xhorse-tool.com(CN006121 IYZBK1 2022-2024 ID49), getbmwparts.com(G02 LCI 2022+)</t>
+          <t>obdii365.com(KD-X4 BDC3 2020-2024 G시리즈), autelkeytools.com(BDC02/BDC03 키등록)</t>
         </is>
       </c>
       <c r="P359" s="11" t="inlineStr"/>
@@ -24156,7 +24358,7 @@
       </c>
       <c r="C360" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025(단종)</t>
         </is>
       </c>
       <c r="D360" s="4" t="inlineStr">
@@ -24176,7 +24378,7 @@
       </c>
       <c r="G360" s="11" t="inlineStr">
         <is>
-          <t>ID49(NCF29Ax)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H360" s="11" t="inlineStr">
@@ -24193,7 +24395,7 @@
       <c r="K360" s="11" t="inlineStr"/>
       <c r="L360" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1, KD FGB23[애프터마켓]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M360" s="11" t="inlineStr"/>
@@ -24204,7 +24406,7 @@
       </c>
       <c r="O360" s="11" t="inlineStr">
         <is>
-          <t>obdii365.com(KEYDIY KD-X4 BDC3 키추가: 원키에서 NCF29Ax 칩 데이터 읽기, Hungary 표기 2020-2024 키 지원·암호화 키 미지원)</t>
+          <t>go-parts.com(2022-2025 X4 IYZBK1, 딜러/전문 로크스미스 등록 필수), wikipedia(X4 G02 2025년식까지)</t>
         </is>
       </c>
       <c r="P360" s="11" t="inlineStr"/>
@@ -24217,12 +24419,12 @@
       </c>
       <c r="B361" s="11" t="inlineStr">
         <is>
-          <t>X4 (G02, 2세대)</t>
+          <t>X4 M (F98)</t>
         </is>
       </c>
       <c r="C361" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
@@ -24242,7 +24444,7 @@
       </c>
       <c r="G361" s="11" t="inlineStr">
         <is>
-          <t>ID49(NCF29Ax)</t>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H361" s="11" t="inlineStr">
@@ -24259,18 +24461,18 @@
       <c r="K361" s="11" t="inlineStr"/>
       <c r="L361" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>9367401-01, FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M361" s="11" t="inlineStr"/>
       <c r="N361" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC2</t>
         </is>
       </c>
       <c r="O361" s="11" t="inlineStr">
         <is>
-          <t>obdii365.com(KD-X4 BDC3 2020-2024 G시리즈), autelkeytools.com(BDC02/BDC03 키등록)</t>
+          <t>uhs-hardware.com(N5F-ID21A: X4 F98 04/2019-07/2021), ebay(2015-2020 X1/X4/X5/X6 N5F-ID21A), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="P361" s="11" t="inlineStr"/>
@@ -24283,12 +24485,12 @@
       </c>
       <c r="B362" s="11" t="inlineStr">
         <is>
-          <t>X4 (G02, 2세대)</t>
+          <t>X4 M (F98)</t>
         </is>
       </c>
       <c r="C362" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D362" s="4" t="inlineStr">
@@ -24308,7 +24510,7 @@
       </c>
       <c r="G362" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H362" s="11" t="inlineStr">
@@ -24325,18 +24527,18 @@
       <c r="K362" s="11" t="inlineStr"/>
       <c r="L362" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M362" s="11" t="inlineStr"/>
       <c r="N362" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC2</t>
         </is>
       </c>
       <c r="O362" s="11" t="inlineStr">
         <is>
-          <t>go-parts.com(2022-2025 X4 IYZBK1, 딜러/전문 로크스미스 등록 필수), wikipedia(X4 G02 2025년식까지)</t>
+          <t>ebay(2020 BMW N5F-ID21A 스마트키), uhs-hardware.com(F98 2019-2021), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
         </is>
       </c>
       <c r="P362" s="11" t="inlineStr"/>
@@ -24349,20 +24551,32 @@
       </c>
       <c r="B363" s="11" t="inlineStr">
         <is>
-          <t>X4 (G02, 2세대)</t>
+          <t>X4 M (F98)</t>
         </is>
       </c>
       <c r="C363" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D363" s="6" t="inlineStr"/>
-      <c r="E363" s="6" t="inlineStr"/>
-      <c r="F363" s="6" t="inlineStr"/>
-      <c r="G363" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D363" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E363" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F363" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G363" s="11" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H363" s="11" t="inlineStr">
@@ -24371,25 +24585,29 @@
         </is>
       </c>
       <c r="I363" s="11" t="inlineStr"/>
-      <c r="J363" s="11" t="inlineStr"/>
+      <c r="J363" s="11" t="inlineStr">
+        <is>
+          <t>HU100R[세대 기준]</t>
+        </is>
+      </c>
       <c r="K363" s="11" t="inlineStr"/>
-      <c r="L363" s="11" t="inlineStr"/>
+      <c r="L363" s="11" t="inlineStr">
+        <is>
+          <t>FCC N5F-ID21A[~2021.07]</t>
+        </is>
+      </c>
       <c r="M363" s="11" t="inlineStr"/>
-      <c r="N363" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="N363" s="11" t="inlineStr">
+        <is>
+          <t>BDC2[2021.7 이전 생산], BDC3[2021.8 이후 생산]</t>
         </is>
       </c>
       <c r="O363" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(X4 G02 2025년식으로 종료)</t>
-        </is>
-      </c>
-      <c r="P363" s="7" t="inlineStr">
-        <is>
-          <t>해당 섀시 생산 종료 후 연식 — 국내 해당 연식 존재 여부 확인 불가</t>
-        </is>
-      </c>
+          <t>uhs-hardware.com(N5F-ID21A: F98 04/2019-07/2021), etsy(F98 X4M LCI 키 = G18 X5·G07 X7 LCI·G70·XM·U11·iX와 같은 신형 키 케이스), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07, BDC3 2021/08~)</t>
+        </is>
+      </c>
+      <c r="P363" s="11" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="11" t="inlineStr">
@@ -24404,7 +24622,7 @@
       </c>
       <c r="C364" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
@@ -24424,7 +24642,7 @@
       </c>
       <c r="G364" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953P)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H364" s="11" t="inlineStr">
@@ -24441,18 +24659,18 @@
       <c r="K364" s="11" t="inlineStr"/>
       <c r="L364" s="11" t="inlineStr">
         <is>
-          <t>9367401-01, FCC N5F-ID21A</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M364" s="11" t="inlineStr"/>
       <c r="N364" s="11" t="inlineStr">
         <is>
-          <t>BDC2</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O364" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A: X4 F98 04/2019-07/2021), ebay(2015-2020 X1/X4/X5/X6 N5F-ID21A), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
+          <t>ebay(IYZBK1 2022-2025 X1~X7), etsy(F98 X4M LCI 키 케이스), bimmerworld.com(M 퍼포먼스 키케이스 82292355519)</t>
         </is>
       </c>
       <c r="P364" s="11" t="inlineStr"/>
@@ -24470,7 +24688,7 @@
       </c>
       <c r="C365" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
@@ -24490,7 +24708,7 @@
       </c>
       <c r="G365" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953P)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H365" s="11" t="inlineStr">
@@ -24507,18 +24725,18 @@
       <c r="K365" s="11" t="inlineStr"/>
       <c r="L365" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M365" s="11" t="inlineStr"/>
       <c r="N365" s="11" t="inlineStr">
         <is>
-          <t>BDC2</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O365" s="11" t="inlineStr">
         <is>
-          <t>ebay(2020 BMW N5F-ID21A 스마트키), uhs-hardware.com(F98 2019-2021), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07)</t>
+          <t>ebay(IYZBK1 2022-2025), leatherbrut.com(F98 X4M LCI 키)</t>
         </is>
       </c>
       <c r="P365" s="11" t="inlineStr"/>
@@ -24536,7 +24754,7 @@
       </c>
       <c r="C366" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
@@ -24573,18 +24791,18 @@
       <c r="K366" s="11" t="inlineStr"/>
       <c r="L366" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A[~2021.07]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M366" s="11" t="inlineStr"/>
       <c r="N366" s="11" t="inlineStr">
         <is>
-          <t>BDC2[2021.7 이전 생산], BDC3[2021.8 이후 생산]</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O366" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A: F98 04/2019-07/2021), etsy(F98 X4M LCI 키 = G18 X5·G07 X7 LCI·G70·XM·U11·iX와 같은 신형 키 케이스), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G01/G02/F97/F98 BDC2 ~2021/07, BDC3 2021/08~)</t>
+          <t>bmwblog.com(X4 생산 2025 중반 종료 발표), ebay(IYZBK1 2022-2025)</t>
         </is>
       </c>
       <c r="P366" s="11" t="inlineStr"/>
@@ -24602,7 +24820,7 @@
       </c>
       <c r="C367" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025(단종)</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -24650,7 +24868,7 @@
       </c>
       <c r="O367" s="11" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 X1~X7), etsy(F98 X4M LCI 키 케이스), bimmerworld.com(M 퍼포먼스 키케이스 82292355519)</t>
+          <t>bmwblog.com(X4 마지막 생산 2025.11), go-parts.com(2022-2025 X4 IYZBK1)</t>
         </is>
       </c>
       <c r="P367" s="11" t="inlineStr"/>
@@ -24663,22 +24881,22 @@
       </c>
       <c r="B368" s="11" t="inlineStr">
         <is>
-          <t>X4 M (F98)</t>
+          <t>X5 (E53, 1세대)</t>
         </is>
       </c>
       <c r="C368" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D368" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E368" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D368" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E368" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr">
@@ -24688,35 +24906,35 @@
       </c>
       <c r="G368" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID44(PCF7935)</t>
         </is>
       </c>
       <c r="H368" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I368" s="11" t="inlineStr"/>
       <c r="J368" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K368" s="11" t="inlineStr"/>
       <c r="L368" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC LX8FZV[3버튼]</t>
         </is>
       </c>
       <c r="M368" s="11" t="inlineStr"/>
       <c r="N368" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>EWS3, EWS3D, EWS4.3</t>
         </is>
       </c>
       <c r="O368" s="11" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025), leatherbrut.com(F98 X4M LCI 키)</t>
+          <t>amazon.co.uk(EWS E53 ID44 PCF7935 HU92 433MHz), precisionecu.com(1999-2006 E53 EWS3/EWS3D/EWS4.3), locksmithkeyless.com(EWS 1998~ 315MHz 2트랙)</t>
         </is>
       </c>
       <c r="P368" s="11" t="inlineStr"/>
@@ -24729,22 +24947,22 @@
       </c>
       <c r="B369" s="11" t="inlineStr">
         <is>
-          <t>X4 M (F98)</t>
+          <t>X5 (E53, 1세대)</t>
         </is>
       </c>
       <c r="C369" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D369" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E369" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="D369" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E369" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F369" s="3" t="inlineStr">
@@ -24754,35 +24972,35 @@
       </c>
       <c r="G369" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID44(PCF7935)</t>
         </is>
       </c>
       <c r="H369" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I369" s="11" t="inlineStr"/>
       <c r="J369" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K369" s="11" t="inlineStr"/>
       <c r="L369" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC LX8FZV</t>
         </is>
       </c>
       <c r="M369" s="11" t="inlineStr"/>
       <c r="N369" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>EWS3</t>
         </is>
       </c>
       <c r="O369" s="11" t="inlineStr">
         <is>
-          <t>bmwblog.com(X4 생산 2025 중반 종료 발표), ebay(IYZBK1 2022-2025)</t>
+          <t>amazon(Keymall EWS ID44 HU92 X3/X5), accessfobs.co.uk(EWS 3버튼 X5)</t>
         </is>
       </c>
       <c r="P369" s="11" t="inlineStr"/>
@@ -24795,22 +25013,22 @@
       </c>
       <c r="B370" s="11" t="inlineStr">
         <is>
-          <t>X4 M (F98)</t>
+          <t>X5 (E53, 1세대)</t>
         </is>
       </c>
       <c r="C370" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D370" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E370" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="D370" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E370" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr">
@@ -24820,35 +25038,35 @@
       </c>
       <c r="G370" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID44(PCF7935)</t>
         </is>
       </c>
       <c r="H370" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I370" s="11" t="inlineStr"/>
       <c r="J370" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K370" s="11" t="inlineStr"/>
       <c r="L370" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC LX8FZV, 6955750</t>
         </is>
       </c>
       <c r="M370" s="11" t="inlineStr"/>
       <c r="N370" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>EWS3</t>
         </is>
       </c>
       <c r="O370" s="11" t="inlineStr">
         <is>
-          <t>bmwblog.com(X4 마지막 생산 2025.11), go-parts.com(2022-2025 X4 IYZBK1)</t>
+          <t>abkeys.com(순정 X5 1998+ LX8FZV HU92 315MHz), amazon(MechanMagic LX8FZV PN 6955750 E53 2000-2006)</t>
         </is>
       </c>
       <c r="P370" s="11" t="inlineStr"/>
@@ -24861,47 +25079,63 @@
       </c>
       <c r="B371" s="11" t="inlineStr">
         <is>
-          <t>X4 M (F98)</t>
+          <t>X5 (E53, 1세대)</t>
         </is>
       </c>
       <c r="C371" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D371" s="6" t="inlineStr"/>
-      <c r="E371" s="6" t="inlineStr"/>
-      <c r="F371" s="6" t="inlineStr"/>
-      <c r="G371" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="D371" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E371" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F371" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G371" s="11" t="inlineStr">
+        <is>
+          <t>ID44(PCF7935)</t>
         </is>
       </c>
       <c r="H371" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I371" s="11" t="inlineStr"/>
-      <c r="J371" s="11" t="inlineStr"/>
+      <c r="J371" s="11" t="inlineStr">
+        <is>
+          <t>HU92</t>
+        </is>
+      </c>
       <c r="K371" s="11" t="inlineStr"/>
-      <c r="L371" s="11" t="inlineStr"/>
+      <c r="L371" s="11" t="inlineStr">
+        <is>
+          <t>FCC LX8FZV</t>
+        </is>
+      </c>
       <c r="M371" s="11" t="inlineStr"/>
-      <c r="N371" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="N371" s="11" t="inlineStr">
+        <is>
+          <t>EWS3</t>
         </is>
       </c>
       <c r="O371" s="11" t="inlineStr">
         <is>
-          <t>bmwblog.com(X4 생산 종료 2025.11, 후속 iX4 NA7 2027 예정)</t>
-        </is>
-      </c>
-      <c r="P371" s="7" t="inlineStr">
-        <is>
-          <t>해당 섀시 생산 종료 후 연식 — 국내 해당 연식 존재 여부 확인 불가</t>
-        </is>
-      </c>
+          <t>ebay(X5 E53 2000-2008 리모컨키), walmart(HQRP E53 2000-2009 송신기)</t>
+        </is>
+      </c>
+      <c r="P371" s="11" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="11" t="inlineStr">
@@ -24916,7 +25150,7 @@
       </c>
       <c r="C372" s="11" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
@@ -24953,18 +25187,18 @@
       <c r="K372" s="11" t="inlineStr"/>
       <c r="L372" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV[3버튼]</t>
+          <t>FCC LX8FZV</t>
         </is>
       </c>
       <c r="M372" s="11" t="inlineStr"/>
       <c r="N372" s="11" t="inlineStr">
         <is>
-          <t>EWS3, EWS3D, EWS4.3</t>
+          <t>EWS4</t>
         </is>
       </c>
       <c r="O372" s="11" t="inlineStr">
         <is>
-          <t>amazon.co.uk(EWS E53 ID44 PCF7935 HU92 433MHz), precisionecu.com(1999-2006 E53 EWS3/EWS3D/EWS4.3), locksmithkeyless.com(EWS 1998~ 315MHz 2트랙)</t>
+          <t>ebay(2004-2005 E53 4.4 N62 DME·EWS 키세트 7542340: EWS4 표기), wikipedia(E53 2004 LCI)</t>
         </is>
       </c>
       <c r="P372" s="11" t="inlineStr"/>
@@ -24982,7 +25216,7 @@
       </c>
       <c r="C373" s="11" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
@@ -25025,12 +25259,12 @@
       <c r="M373" s="11" t="inlineStr"/>
       <c r="N373" s="11" t="inlineStr">
         <is>
-          <t>EWS3</t>
+          <t>EWS4</t>
         </is>
       </c>
       <c r="O373" s="11" t="inlineStr">
         <is>
-          <t>amazon(Keymall EWS ID44 HU92 X3/X5), accessfobs.co.uk(EWS 3버튼 X5)</t>
+          <t>ebay(2004-2005 E53 N62 EWS 키세트), rpmmotorsport.net(E53 1999-2006 키세트)</t>
         </is>
       </c>
       <c r="P373" s="11" t="inlineStr"/>
@@ -25048,7 +25282,7 @@
       </c>
       <c r="C374" s="11" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2006(단종)</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
@@ -25085,18 +25319,18 @@
       <c r="K374" s="11" t="inlineStr"/>
       <c r="L374" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV, 6955750</t>
+          <t>FCC LX8FZV</t>
         </is>
       </c>
       <c r="M374" s="11" t="inlineStr"/>
       <c r="N374" s="11" t="inlineStr">
         <is>
-          <t>EWS3</t>
+          <t>EWS4</t>
         </is>
       </c>
       <c r="O374" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(순정 X5 1998+ LX8FZV HU92 315MHz), amazon(MechanMagic LX8FZV PN 6955750 E53 2000-2006)</t>
+          <t>ebay(E53 4.4i N62 ECU·EWS 키 세트), transpondery.com 검색결과(ID44 EWS3.x/EWS4.x)</t>
         </is>
       </c>
       <c r="P374" s="11" t="inlineStr"/>
@@ -25109,12 +25343,12 @@
       </c>
       <c r="B375" s="11" t="inlineStr">
         <is>
-          <t>X5 (E53, 1세대)</t>
+          <t>X5 (E70, 2세대)</t>
         </is>
       </c>
       <c r="C375" s="11" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
@@ -25134,35 +25368,31 @@
       </c>
       <c r="G375" s="11" t="inlineStr">
         <is>
-          <t>ID44(PCF7935)</t>
+          <t>ID46(PCF7945A)</t>
         </is>
       </c>
       <c r="H375" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I375" s="11" t="inlineStr"/>
       <c r="J375" s="11" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K375" s="11" t="inlineStr"/>
-      <c r="L375" s="11" t="inlineStr">
-        <is>
-          <t>FCC LX8FZV</t>
-        </is>
-      </c>
+      <c r="L375" s="11" t="inlineStr"/>
       <c r="M375" s="11" t="inlineStr"/>
       <c r="N375" s="11" t="inlineStr">
         <is>
-          <t>EWS3</t>
+          <t>CAS3</t>
         </is>
       </c>
       <c r="O375" s="11" t="inlineStr">
         <is>
-          <t>ebay(X5 E53 2000-2008 리모컨키), walmart(HQRP E53 2000-2009 송신기)</t>
+          <t>locksmithkeyless.com(2006-2012 CAS 슬롯키 KR55WK49127 PN 6986583), wikipedia(E70 2006 생산)</t>
         </is>
       </c>
       <c r="P375" s="11" t="inlineStr"/>
@@ -25175,12 +25405,12 @@
       </c>
       <c r="B376" s="11" t="inlineStr">
         <is>
-          <t>X5 (E53, 1세대)</t>
+          <t>X5 (E70, 2세대)</t>
         </is>
       </c>
       <c r="C376" s="11" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
@@ -25200,35 +25430,35 @@
       </c>
       <c r="G376" s="11" t="inlineStr">
         <is>
-          <t>ID44(PCF7935)</t>
+          <t>ID46(PCF7945A)</t>
         </is>
       </c>
       <c r="H376" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I376" s="11" t="inlineStr"/>
       <c r="J376" s="11" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K376" s="11" t="inlineStr"/>
       <c r="L376" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>6986583, FCC KR55WK49127, 5WK49145, 5WK49146, 5WK49147</t>
         </is>
       </c>
       <c r="M376" s="11" t="inlineStr"/>
       <c r="N376" s="11" t="inlineStr">
         <is>
-          <t>EWS4</t>
+          <t>CAS3</t>
         </is>
       </c>
       <c r="O376" s="11" t="inlineStr">
         <is>
-          <t>ebay(2004-2005 E53 4.4 N62 DME·EWS 키세트 7542340: EWS4 표기), wikipedia(E53 2004 LCI)</t>
+          <t>ryan-keys.com(CAS3 X5 ID46 PCF7945 KR55WK49127), rpmmotorsport.net(E70/E71 2006-2013 키세트), bmw-key-replacement.com(X5 E70 2006-2013)</t>
         </is>
       </c>
       <c r="P376" s="11" t="inlineStr"/>
@@ -25241,12 +25471,12 @@
       </c>
       <c r="B377" s="11" t="inlineStr">
         <is>
-          <t>X5 (E53, 1세대)</t>
+          <t>X5 (E70, 2세대)</t>
         </is>
       </c>
       <c r="C377" s="11" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
@@ -25266,35 +25496,35 @@
       </c>
       <c r="G377" s="11" t="inlineStr">
         <is>
-          <t>ID44(PCF7935)</t>
+          <t>ID46(PCF7945A)</t>
         </is>
       </c>
       <c r="H377" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I377" s="11" t="inlineStr"/>
       <c r="J377" s="11" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K377" s="11" t="inlineStr"/>
       <c r="L377" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC KR55WK49147[컴포트액세스], 6986583-04[컴포트액세스], 926886-02[컴포트액세스], FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M377" s="11" t="inlineStr"/>
       <c r="N377" s="11" t="inlineStr">
         <is>
-          <t>EWS4</t>
+          <t>CAS3[2008 중반 이전 생산], CAS3+[2008 중반 이후 생산]</t>
         </is>
       </c>
       <c r="O377" s="11" t="inlineStr">
         <is>
-          <t>ebay(2004-2005 E53 N62 EWS 키세트), rpmmotorsport.net(E53 1999-2006 키세트)</t>
+          <t>keyinnovations.com·bestkeysupply.com(KR55WK49147 CAS3+ 컴포트액세스: X5 E70 2006-2013), ebay(PN 926886-02)</t>
         </is>
       </c>
       <c r="P377" s="11" t="inlineStr"/>
@@ -25307,12 +25537,12 @@
       </c>
       <c r="B378" s="11" t="inlineStr">
         <is>
-          <t>X5 (E53, 1세대)</t>
+          <t>X5 (E70, 2세대)</t>
         </is>
       </c>
       <c r="C378" s="11" t="inlineStr">
         <is>
-          <t>2006(단종)</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
@@ -25332,35 +25562,35 @@
       </c>
       <c r="G378" s="11" t="inlineStr">
         <is>
-          <t>ID44(PCF7935)</t>
+          <t>ID46(PCF7945A)</t>
         </is>
       </c>
       <c r="H378" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I378" s="11" t="inlineStr"/>
       <c r="J378" s="11" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K378" s="11" t="inlineStr"/>
       <c r="L378" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC KR55WK49147, 6986583-04, FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M378" s="11" t="inlineStr"/>
       <c r="N378" s="11" t="inlineStr">
         <is>
-          <t>EWS4</t>
+          <t>CAS3+</t>
         </is>
       </c>
       <c r="O378" s="11" t="inlineStr">
         <is>
-          <t>ebay(E53 4.4i N62 ECU·EWS 키 세트), transpondery.com 검색결과(ID44 EWS3.x/EWS4.x)</t>
+          <t>omegaautomotivetx.com(CAS3+ 컴포트액세스 2006-2010 KR55WK49147), diamondkeysupply.com(순정 리퍼 KR55WK49147)</t>
         </is>
       </c>
       <c r="P378" s="11" t="inlineStr"/>
@@ -25378,7 +25608,7 @@
       </c>
       <c r="C379" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
@@ -25409,7 +25639,7 @@
       <c r="I379" s="11" t="inlineStr"/>
       <c r="J379" s="11" t="inlineStr">
         <is>
-          <t>HU92[세대 기준]</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K379" s="11" t="inlineStr"/>
@@ -25417,12 +25647,12 @@
       <c r="M379" s="11" t="inlineStr"/>
       <c r="N379" s="11" t="inlineStr">
         <is>
-          <t>CAS3</t>
+          <t>CAS3+</t>
         </is>
       </c>
       <c r="O379" s="11" t="inlineStr">
         <is>
-          <t>locksmithkeyless.com(2006-2012 CAS 슬롯키 KR55WK49127 PN 6986583), wikipedia(E70 2006 생산)</t>
+          <t>amazon(315MHz HU92 CAS3 E70 리모컨키), obdii365.com(X5 E70 CAS3 키 CGDI 등록), key4.com(X5 HU92 3버튼 쉘)</t>
         </is>
       </c>
       <c r="P379" s="11" t="inlineStr"/>
@@ -25440,7 +25670,7 @@
       </c>
       <c r="C380" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
@@ -25471,24 +25701,24 @@
       <c r="I380" s="11" t="inlineStr"/>
       <c r="J380" s="11" t="inlineStr">
         <is>
-          <t>HU92[세대 기준]</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K380" s="11" t="inlineStr"/>
       <c r="L380" s="11" t="inlineStr">
         <is>
-          <t>6986583, FCC KR55WK49127, 5WK49145, 5WK49146, 5WK49147</t>
+          <t>FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M380" s="11" t="inlineStr"/>
       <c r="N380" s="11" t="inlineStr">
         <is>
-          <t>CAS3</t>
+          <t>CAS3+</t>
         </is>
       </c>
       <c r="O380" s="11" t="inlineStr">
         <is>
-          <t>ryan-keys.com(CAS3 X5 ID46 PCF7945 KR55WK49127), rpmmotorsport.net(E70/E71 2006-2013 키세트), bmw-key-replacement.com(X5 E70 2006-2013)</t>
+          <t>precisionecu.com(2007-2013 E70 리모컨키 CAS3), ecumedics.com(CAS3 키 등록)</t>
         </is>
       </c>
       <c r="P380" s="11" t="inlineStr"/>
@@ -25506,7 +25736,7 @@
       </c>
       <c r="C381" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
@@ -25526,7 +25756,7 @@
       </c>
       <c r="G381" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945A)</t>
+          <t>ID46(PCF7945)</t>
         </is>
       </c>
       <c r="H381" s="11" t="inlineStr">
@@ -25543,18 +25773,18 @@
       <c r="K381" s="11" t="inlineStr"/>
       <c r="L381" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147[컴포트액세스], 6986583-04[컴포트액세스], 926886-02[컴포트액세스], FCC KR55WK49127</t>
+          <t>FCC KR55WK49123</t>
         </is>
       </c>
       <c r="M381" s="11" t="inlineStr"/>
       <c r="N381" s="11" t="inlineStr">
         <is>
-          <t>CAS3[2008 중반 이전 생산], CAS3+[2008 중반 이후 생산]</t>
+          <t>CAS3+</t>
         </is>
       </c>
       <c r="O381" s="11" t="inlineStr">
         <is>
-          <t>keyinnovations.com·bestkeysupply.com(KR55WK49147 CAS3+ 컴포트액세스: X5 E70 2006-2013), ebay(PN 926886-02)</t>
+          <t>ebay(2007-2013 X5 KR55WK49123), ebay(315LP CAS3/CAS3+ E70), bimmerfest.com(E70 키 재등록)</t>
         </is>
       </c>
       <c r="P381" s="11" t="inlineStr"/>
@@ -25572,7 +25802,7 @@
       </c>
       <c r="C382" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2013(단종)</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
@@ -25592,7 +25822,7 @@
       </c>
       <c r="G382" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945A)</t>
+          <t>ID46(PCF7945)</t>
         </is>
       </c>
       <c r="H382" s="11" t="inlineStr">
@@ -25609,7 +25839,7 @@
       <c r="K382" s="11" t="inlineStr"/>
       <c r="L382" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147, 6986583-04, FCC KR55WK49127</t>
+          <t>FCC KR55WK49123, FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M382" s="11" t="inlineStr"/>
@@ -25620,7 +25850,7 @@
       </c>
       <c r="O382" s="11" t="inlineStr">
         <is>
-          <t>omegaautomotivetx.com(CAS3+ 컴포트액세스 2006-2010 KR55WK49147), diamondkeysupply.com(순정 리퍼 KR55WK49147)</t>
+          <t>obdii365.com(E70 CAS3, 6HP/8HP 변속기 ISN 인증), rpmmotorsport.net(E70/E71 2006-2013)</t>
         </is>
       </c>
       <c r="P382" s="11" t="inlineStr"/>
@@ -25633,22 +25863,22 @@
       </c>
       <c r="B383" s="11" t="inlineStr">
         <is>
-          <t>X5 (E70, 2세대)</t>
+          <t>X5 (F15, 3세대)</t>
         </is>
       </c>
       <c r="C383" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="D383" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E383" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="D383" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E383" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F383" s="3" t="inlineStr">
@@ -25658,7 +25888,7 @@
       </c>
       <c r="G383" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945A)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H383" s="11" t="inlineStr">
@@ -25669,20 +25899,24 @@
       <c r="I383" s="11" t="inlineStr"/>
       <c r="J383" s="11" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K383" s="11" t="inlineStr"/>
-      <c r="L383" s="11" t="inlineStr"/>
+      <c r="L383" s="11" t="inlineStr">
+        <is>
+          <t>FCC NBGIDGNG1[4버튼]</t>
+        </is>
+      </c>
       <c r="M383" s="11" t="inlineStr"/>
       <c r="N383" s="11" t="inlineStr">
         <is>
-          <t>CAS3+</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O383" s="11" t="inlineStr">
         <is>
-          <t>amazon(315MHz HU92 CAS3 E70 리모컨키), obdii365.com(X5 E70 CAS3 키 CGDI 등록), key4.com(X5 HU92 3버튼 쉘)</t>
+          <t>locksmithkeyless.com(2014-2018 X5/X6 FEM/BDC NBGIDGNG1), amazon(2014-2019 X5 NBGIDGNG1 FEM/BDC) — 2013년식 전용 자료 없음, 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P383" s="11" t="inlineStr"/>
@@ -25695,22 +25929,22 @@
       </c>
       <c r="B384" s="11" t="inlineStr">
         <is>
-          <t>X5 (E70, 2세대)</t>
+          <t>X5 (F15, 3세대)</t>
         </is>
       </c>
       <c r="C384" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D384" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E384" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="D384" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E384" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr">
@@ -25720,7 +25954,7 @@
       </c>
       <c r="G384" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945A)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H384" s="11" t="inlineStr">
@@ -25731,24 +25965,24 @@
       <c r="I384" s="11" t="inlineStr"/>
       <c r="J384" s="11" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K384" s="11" t="inlineStr"/>
       <c r="L384" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M384" s="11" t="inlineStr"/>
       <c r="N384" s="11" t="inlineStr">
         <is>
-          <t>CAS3+</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O384" s="11" t="inlineStr">
         <is>
-          <t>precisionecu.com(2007-2013 E70 리모컨키 CAS3), ecumedics.com(CAS3 키 등록)</t>
+          <t>amazon(2014-2019 X5 X6 NBGIDGNG1 FEM/BDC), key4.com(NBGIDGNG1 FEM/BDC 4버튼), yourcarkeyguys.com(2014-2019 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P384" s="11" t="inlineStr"/>
@@ -25761,22 +25995,22 @@
       </c>
       <c r="B385" s="11" t="inlineStr">
         <is>
-          <t>X5 (E70, 2세대)</t>
+          <t>X5 (F15, 3세대)</t>
         </is>
       </c>
       <c r="C385" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D385" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E385" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D385" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E385" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F385" s="3" t="inlineStr">
@@ -25786,7 +26020,7 @@
       </c>
       <c r="G385" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H385" s="11" t="inlineStr">
@@ -25797,24 +26031,24 @@
       <c r="I385" s="11" t="inlineStr"/>
       <c r="J385" s="11" t="inlineStr">
         <is>
-          <t>HU92[세대 기준]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K385" s="11" t="inlineStr"/>
       <c r="L385" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49123</t>
+          <t>9367401-01, FCC N5F-ID21A, FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M385" s="11" t="inlineStr"/>
       <c r="N385" s="11" t="inlineStr">
         <is>
-          <t>CAS3+</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O385" s="11" t="inlineStr">
         <is>
-          <t>ebay(2007-2013 X5 KR55WK49123), ebay(315LP CAS3/CAS3+ E70), bimmerfest.com(E70 키 재등록)</t>
+          <t>northcoastkeyless.com(2014-2016 X5 N5F-ID21A 9367401-01), ebay(2014-2016 X5/X6 순정 9367401-01), go-parts.com(F15·F85·F16·F86은 BDC 사용), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P385" s="11" t="inlineStr"/>
@@ -25827,22 +26061,22 @@
       </c>
       <c r="B386" s="11" t="inlineStr">
         <is>
-          <t>X5 (E70, 2세대)</t>
+          <t>X5 (F15, 3세대)</t>
         </is>
       </c>
       <c r="C386" s="11" t="inlineStr">
         <is>
-          <t>2013(단종)</t>
-        </is>
-      </c>
-      <c r="D386" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E386" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D386" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E386" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr">
@@ -25852,7 +26086,7 @@
       </c>
       <c r="G386" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H386" s="11" t="inlineStr">
@@ -25863,24 +26097,24 @@
       <c r="I386" s="11" t="inlineStr"/>
       <c r="J386" s="11" t="inlineStr">
         <is>
-          <t>HU92[세대 기준]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K386" s="11" t="inlineStr"/>
       <c r="L386" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49123, FCC KR55WK49127</t>
+          <t>9367401-01, FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M386" s="11" t="inlineStr"/>
       <c r="N386" s="11" t="inlineStr">
         <is>
-          <t>CAS3+</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O386" s="11" t="inlineStr">
         <is>
-          <t>obdii365.com(E70 CAS3, 6HP/8HP 변속기 ISN 인증), rpmmotorsport.net(E70/E71 2006-2013)</t>
+          <t>uhs-hardware.com(2014-2018 X5/X6 9367401-01 FEM/BDC 434MHz), keyinnovations.com(N5F-ID21A 9367401-01), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P386" s="11" t="inlineStr"/>
@@ -25898,7 +26132,7 @@
       </c>
       <c r="C387" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -25935,7 +26169,7 @@
       <c r="K387" s="11" t="inlineStr"/>
       <c r="L387" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1[4버튼]</t>
+          <t>69337244[애프터마켓], FCC NBGIDGNG1, ILCO AX00015030[애프터마켓]</t>
         </is>
       </c>
       <c r="M387" s="11" t="inlineStr"/>
@@ -25946,7 +26180,7 @@
       </c>
       <c r="O387" s="11" t="inlineStr">
         <is>
-          <t>locksmithkeyless.com(2014-2018 X5/X6 FEM/BDC NBGIDGNG1), amazon(2014-2019 X5 NBGIDGNG1 FEM/BDC) — 2013년식 전용 자료 없음, 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>locksmithkeyless.com(2014-2018 X5/X6 FEM/BDC NBGIDGNG1, PN 69337244, ILCO PRX-BMW-4B3), f15.bimmerpost.com(키 등록), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P387" s="11" t="inlineStr"/>
@@ -25964,7 +26198,7 @@
       </c>
       <c r="C388" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2018(단종)</t>
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr">
@@ -26001,7 +26235,7 @@
       <c r="K388" s="11" t="inlineStr"/>
       <c r="L388" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, ILCO PRX-BMW-4B1[애프터마켓]</t>
         </is>
       </c>
       <c r="M388" s="11" t="inlineStr"/>
@@ -26012,7 +26246,7 @@
       </c>
       <c r="O388" s="11" t="inlineStr">
         <is>
-          <t>amazon(2014-2019 X5 X6 NBGIDGNG1 FEM/BDC), key4.com(NBGIDGNG1 FEM/BDC 4버튼), yourcarkeyguys.com(2014-2019 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>ebay(2014-2018 F15 X5 순정 스마트키), smallwoodlock.com(ILCO 2014-2018 X5 PRX-BMW-4B1), bimmerfest.com(2018 F15 X5d 키 교체 비용), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P388" s="11" t="inlineStr"/>
@@ -26025,12 +26259,12 @@
       </c>
       <c r="B389" s="11" t="inlineStr">
         <is>
-          <t>X5 (F15, 3세대)</t>
+          <t>X5 (G05, 4세대)</t>
         </is>
       </c>
       <c r="C389" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -26067,18 +26301,18 @@
       <c r="K389" s="11" t="inlineStr"/>
       <c r="L389" s="11" t="inlineStr">
         <is>
-          <t>9367401-01, FCC N5F-ID21A, FCC NBGIDGNG1</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M389" s="11" t="inlineStr"/>
       <c r="N389" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O389" s="11" t="inlineStr">
         <is>
-          <t>northcoastkeyless.com(2014-2016 X5 N5F-ID21A 9367401-01), ebay(2014-2016 X5/X6 순정 9367401-01), go-parts.com(F15·F85·F16·F86은 BDC 사용), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>uhs-hardware.com(N5F-ID21A BDC2: 2019-2024 X5), adlhardware.com(2016-2024 G바디 N5F-ID21A), g05.bimmerpost.com(G05 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P389" s="11" t="inlineStr"/>
@@ -26091,12 +26325,12 @@
       </c>
       <c r="B390" s="11" t="inlineStr">
         <is>
-          <t>X5 (F15, 3세대)</t>
+          <t>X5 (G05, 4세대)</t>
         </is>
       </c>
       <c r="C390" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D390" s="4" t="inlineStr">
@@ -26133,18 +26367,18 @@
       <c r="K390" s="11" t="inlineStr"/>
       <c r="L390" s="11" t="inlineStr">
         <is>
-          <t>9367401-01, FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M390" s="11" t="inlineStr"/>
       <c r="N390" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O390" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(2014-2018 X5/X6 9367401-01 FEM/BDC 434MHz), keyinnovations.com(N5F-ID21A 9367401-01), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>autel(2020 이후 BDC03 키추가, XP400Pro), g05.bimmerpost.com(새 키 코딩), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P390" s="11" t="inlineStr"/>
@@ -26157,12 +26391,12 @@
       </c>
       <c r="B391" s="11" t="inlineStr">
         <is>
-          <t>X5 (F15, 3세대)</t>
+          <t>X5 (G05, 4세대)</t>
         </is>
       </c>
       <c r="C391" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
@@ -26199,18 +26433,18 @@
       <c r="K391" s="11" t="inlineStr"/>
       <c r="L391" s="11" t="inlineStr">
         <is>
-          <t>69337244[애프터마켓], FCC NBGIDGNG1, ILCO AX00015030[애프터마켓]</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M391" s="11" t="inlineStr"/>
       <c r="N391" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O391" s="11" t="inlineStr">
         <is>
-          <t>locksmithkeyless.com(2014-2018 X5/X6 FEM/BDC NBGIDGNG1, PN 69337244, ILCO PRX-BMW-4B3), f15.bimmerpost.com(키 등록), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>uobdii.com(KD-X4 BDC2/BDC3 지원목록), vvdishop.com(Xhorse G BDC2/BDC3 라이선스), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P391" s="11" t="inlineStr"/>
@@ -26223,12 +26457,12 @@
       </c>
       <c r="B392" s="11" t="inlineStr">
         <is>
-          <t>X5 (F15, 3세대)</t>
+          <t>X5 (G05, 4세대)</t>
         </is>
       </c>
       <c r="C392" s="11" t="inlineStr">
         <is>
-          <t>2018(단종)</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D392" s="4" t="inlineStr">
@@ -26265,18 +26499,18 @@
       <c r="K392" s="11" t="inlineStr"/>
       <c r="L392" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1, ILCO PRX-BMW-4B1[애프터마켓]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M392" s="11" t="inlineStr"/>
       <c r="N392" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O392" s="11" t="inlineStr">
         <is>
-          <t>ebay(2014-2018 F15 X5 순정 스마트키), smallwoodlock.com(ILCO 2014-2018 X5 PRX-BMW-4B1), bimmerfest.com(2018 F15 X5d 키 교체 비용), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>ebay(IYZBK1 2022-2025 X1~X7), g05.bimmerpost.com(G05 교체 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P392" s="11" t="inlineStr"/>
@@ -26294,7 +26528,7 @@
       </c>
       <c r="C393" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
@@ -26331,7 +26565,7 @@
       <c r="K393" s="11" t="inlineStr"/>
       <c r="L393" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M393" s="11" t="inlineStr"/>
@@ -26342,7 +26576,7 @@
       </c>
       <c r="O393" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A BDC2: 2019-2024 X5), adlhardware.com(2016-2024 G바디 N5F-ID21A), g05.bimmerpost.com(G05 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>g05.bimmerpost.com(2023년식 교체 키: BMW가 블레이드 커팅·등록서류 필요, 공키는 스티어링 센서에 대어 페어링), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P393" s="11" t="inlineStr"/>
@@ -26360,7 +26594,7 @@
       </c>
       <c r="C394" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D394" s="4" t="inlineStr">
@@ -26380,7 +26614,7 @@
       </c>
       <c r="G394" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49[SP21 변형]</t>
         </is>
       </c>
       <c r="H394" s="11" t="inlineStr">
@@ -26397,7 +26631,7 @@
       <c r="K394" s="11" t="inlineStr"/>
       <c r="L394" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>66125A56C30, 66125A56C38, FCC N5F-ID21A, FCC IYZBK1</t>
         </is>
       </c>
       <c r="M394" s="11" t="inlineStr"/>
@@ -26408,7 +26642,7 @@
       </c>
       <c r="O394" s="11" t="inlineStr">
         <is>
-          <t>autel(2020 이후 BDC03 키추가, XP400Pro), g05.bimmerpost.com(새 키 코딩), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>transpondery.com 검색결과(BDC3/BDC4: ID49 Hitag Pro 변형 SP21, OEM 66125A56C30·66125A56C38), carkeyhelper.com(X5 G05 LCI 2024- 스마트키), schmiedmann.com(G05 LCI 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P394" s="11" t="inlineStr"/>
@@ -26426,7 +26660,7 @@
       </c>
       <c r="C395" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
@@ -26463,7 +26697,7 @@
       <c r="K395" s="11" t="inlineStr"/>
       <c r="L395" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M395" s="11" t="inlineStr"/>
@@ -26474,7 +26708,7 @@
       </c>
       <c r="O395" s="11" t="inlineStr">
         <is>
-          <t>uobdii.com(KD-X4 BDC2/BDC3 지원목록), vvdishop.com(Xhorse G BDC2/BDC3 라이선스), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>programyourremote.com(2025 X5: 온보드 등록 불가, 전문가 등록), go-parts.com(2018-2025 X5 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P395" s="11" t="inlineStr"/>
@@ -26492,7 +26726,7 @@
       </c>
       <c r="C396" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D396" s="4" t="inlineStr">
@@ -26510,17 +26744,21 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G396" s="11" t="inlineStr">
+      <c r="G396" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
       </c>
       <c r="H396" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I396" s="11" t="inlineStr"/>
+          <t>스마트키,카드키</t>
+        </is>
+      </c>
+      <c r="I396" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J396" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -26533,17 +26771,17 @@
         </is>
       </c>
       <c r="M396" s="11" t="inlineStr"/>
-      <c r="N396" s="11" t="inlineStr">
+      <c r="N396" s="17" t="inlineStr">
         <is>
           <t>BDC3</t>
         </is>
       </c>
       <c r="O396" s="11" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 X1~X7), g05.bimmerpost.com(G05 교체 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
-        </is>
-      </c>
-      <c r="P396" s="11" t="inlineStr"/>
+          <t>ebay(2026 X5 순정 키), g05.bimmerpost.com(2026 X5 키 2개+NFC 카드, 디지털키는 키 2개 필요)</t>
+        </is>
+      </c>
+      <c r="P396" s="17" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="11" t="inlineStr">
@@ -26553,12 +26791,12 @@
       </c>
       <c r="B397" s="11" t="inlineStr">
         <is>
-          <t>X5 (G05, 4세대)</t>
+          <t>X5 M (F85)</t>
         </is>
       </c>
       <c r="C397" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -26595,18 +26833,18 @@
       <c r="K397" s="11" t="inlineStr"/>
       <c r="L397" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>9367401-01, FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M397" s="11" t="inlineStr"/>
       <c r="N397" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O397" s="11" t="inlineStr">
         <is>
-          <t>g05.bimmerpost.com(2023년식 교체 키: BMW가 블레이드 커팅·등록서류 필요, 공키는 스티어링 센서에 대어 페어링), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>ebay(2014-2016 X5/X6 순정 N5F-ID21A 9367401-01), monacoms.com(X5M F85 2015-2019 키), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P397" s="11" t="inlineStr"/>
@@ -26619,12 +26857,12 @@
       </c>
       <c r="B398" s="11" t="inlineStr">
         <is>
-          <t>X5 (G05, 4세대)</t>
+          <t>X5 M (F85)</t>
         </is>
       </c>
       <c r="C398" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D398" s="4" t="inlineStr">
@@ -26644,7 +26882,7 @@
       </c>
       <c r="G398" s="11" t="inlineStr">
         <is>
-          <t>ID49[SP21 변형]</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H398" s="11" t="inlineStr">
@@ -26661,18 +26899,18 @@
       <c r="K398" s="11" t="inlineStr"/>
       <c r="L398" s="11" t="inlineStr">
         <is>
-          <t>66125A56C30, 66125A56C38, FCC N5F-ID21A, FCC IYZBK1</t>
+          <t>9367401-01, FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M398" s="11" t="inlineStr"/>
       <c r="N398" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O398" s="11" t="inlineStr">
         <is>
-          <t>transpondery.com 검색결과(BDC3/BDC4: ID49 Hitag Pro 변형 SP21, OEM 66125A56C30·66125A56C38), carkeyhelper.com(X5 G05 LCI 2024- 스마트키), schmiedmann.com(G05 LCI 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>northcoastkeyless.com(2014-2016 X5 N5F-ID21A), uhs-hardware.com(2014-2018 X5/X6 FEM/BDC), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P398" s="11" t="inlineStr"/>
@@ -26685,12 +26923,12 @@
       </c>
       <c r="B399" s="11" t="inlineStr">
         <is>
-          <t>X5 (G05, 4세대)</t>
+          <t>X5 M (F85)</t>
         </is>
       </c>
       <c r="C399" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
@@ -26727,18 +26965,18 @@
       <c r="K399" s="11" t="inlineStr"/>
       <c r="L399" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC N5F-ID2A</t>
         </is>
       </c>
       <c r="M399" s="11" t="inlineStr"/>
       <c r="N399" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O399" s="11" t="inlineStr">
         <is>
-          <t>programyourremote.com(2025 X5: 온보드 등록 불가, 전문가 등록), go-parts.com(2018-2025 X5 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>ebay(2014-2018 X5 M·X6 OEM N5F-ID2A), locksmithkeyless.com(2014-2018 X5/X6 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P399" s="11" t="inlineStr"/>
@@ -26751,12 +26989,12 @@
       </c>
       <c r="B400" s="11" t="inlineStr">
         <is>
-          <t>X5 (G05, 4세대)</t>
+          <t>X5 M (F85)</t>
         </is>
       </c>
       <c r="C400" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2018(단종)</t>
         </is>
       </c>
       <c r="D400" s="4" t="inlineStr">
@@ -26774,14 +27012,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G400" s="8" t="inlineStr">
+      <c r="G400" s="11" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
       </c>
       <c r="H400" s="11" t="inlineStr">
         <is>
-          <t>스마트키,카드키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I400" s="11" t="inlineStr"/>
@@ -26791,23 +27029,23 @@
         </is>
       </c>
       <c r="K400" s="11" t="inlineStr"/>
-      <c r="L400" s="11" t="n"/>
+      <c r="L400" s="11" t="inlineStr">
+        <is>
+          <t>FCC N5F-ID2A, FCC NBGIDGNG1</t>
+        </is>
+      </c>
       <c r="M400" s="11" t="inlineStr"/>
-      <c r="N400" s="8" t="inlineStr">
-        <is>
-          <t>BDC3[추정]</t>
+      <c r="N400" s="11" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O400" s="11" t="inlineStr">
         <is>
-          <t>ebay(2026 X5 순정 키), g05.bimmerpost.com(2026 X5 키 2개+NFC 카드, 디지털키는 키 2개 필요)</t>
-        </is>
-      </c>
-      <c r="P400" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+          <t>ebay(2014-2018 X5 M OEM N5F-ID2A), bmwmpower247.com(F85/F86 키), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="P400" s="11" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="11" t="inlineStr">
@@ -26817,12 +27055,12 @@
       </c>
       <c r="B401" s="11" t="inlineStr">
         <is>
-          <t>X5 M (F85)</t>
+          <t>X5 M (F95)</t>
         </is>
       </c>
       <c r="C401" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
@@ -26857,20 +27095,16 @@
         </is>
       </c>
       <c r="K401" s="11" t="inlineStr"/>
-      <c r="L401" s="11" t="inlineStr">
-        <is>
-          <t>9367401-01, FCC N5F-ID21A</t>
-        </is>
-      </c>
+      <c r="L401" s="11" t="n"/>
       <c r="M401" s="11" t="inlineStr"/>
       <c r="N401" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O401" s="11" t="inlineStr">
         <is>
-          <t>ebay(2014-2016 X5/X6 순정 N5F-ID21A 9367401-01), monacoms.com(X5M F85 2015-2019 키), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>locksmithsanantonio.org(X5 M Comp F95 2020-2025: BDC, 스마트키+디지털키, HITAG Pro/DST-AES), monacoms.com(X5M F95 2020~ 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P401" s="11" t="inlineStr"/>
@@ -26883,12 +27117,12 @@
       </c>
       <c r="B402" s="11" t="inlineStr">
         <is>
-          <t>X5 M (F85)</t>
+          <t>X5 M (F95)</t>
         </is>
       </c>
       <c r="C402" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D402" s="4" t="inlineStr">
@@ -26923,20 +27157,16 @@
         </is>
       </c>
       <c r="K402" s="11" t="inlineStr"/>
-      <c r="L402" s="11" t="inlineStr">
-        <is>
-          <t>9367401-01, FCC N5F-ID21A</t>
-        </is>
-      </c>
+      <c r="L402" s="11" t="n"/>
       <c r="M402" s="11" t="inlineStr"/>
       <c r="N402" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O402" s="11" t="inlineStr">
         <is>
-          <t>northcoastkeyless.com(2014-2016 X5 N5F-ID21A), uhs-hardware.com(2014-2018 X5/X6 FEM/BDC), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>locksmithsanantonio.org(F95 BDC), g05.bimmerpost.com(G05 계열 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P402" s="11" t="inlineStr"/>
@@ -26949,12 +27179,12 @@
       </c>
       <c r="B403" s="11" t="inlineStr">
         <is>
-          <t>X5 M (F85)</t>
+          <t>X5 M (F95)</t>
         </is>
       </c>
       <c r="C403" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
@@ -26991,18 +27221,18 @@
       <c r="K403" s="11" t="inlineStr"/>
       <c r="L403" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID2A</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M403" s="11" t="inlineStr"/>
       <c r="N403" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O403" s="11" t="inlineStr">
         <is>
-          <t>ebay(2014-2018 X5 M·X6 OEM N5F-ID2A), locksmithkeyless.com(2014-2018 X5/X6 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>ebay(IYZBK1 2022-2025 X5, 순정 인서트키 포함), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P403" s="11" t="inlineStr"/>
@@ -27015,12 +27245,12 @@
       </c>
       <c r="B404" s="11" t="inlineStr">
         <is>
-          <t>X5 M (F85)</t>
+          <t>X5 M (F95)</t>
         </is>
       </c>
       <c r="C404" s="11" t="inlineStr">
         <is>
-          <t>2018(단종)</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D404" s="4" t="inlineStr">
@@ -27057,18 +27287,18 @@
       <c r="K404" s="11" t="inlineStr"/>
       <c r="L404" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID2A, FCC NBGIDGNG1</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M404" s="11" t="inlineStr"/>
       <c r="N404" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O404" s="11" t="inlineStr">
         <is>
-          <t>ebay(2014-2018 X5 M OEM N5F-ID2A), bmwmpower247.com(F85/F86 키), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>ebay(IYZBK1 2022-2026), g05.bimmerpost.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P404" s="11" t="inlineStr"/>
@@ -27086,7 +27316,7 @@
       </c>
       <c r="C405" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
@@ -27121,7 +27351,11 @@
         </is>
       </c>
       <c r="K405" s="11" t="inlineStr"/>
-      <c r="L405" s="11" t="n"/>
+      <c r="L405" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M405" s="11" t="inlineStr"/>
       <c r="N405" s="11" t="inlineStr">
         <is>
@@ -27130,7 +27364,7 @@
       </c>
       <c r="O405" s="11" t="inlineStr">
         <is>
-          <t>locksmithsanantonio.org(X5 M Comp F95 2020-2025: BDC, 스마트키+디지털키, HITAG Pro/DST-AES), monacoms.com(X5M F95 2020~ 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>g05.bimmerpost.com(2024 LCI 키 품질 불만: 크고 가벼움), amazon(X5 F95/G05/G18 2024-2025 키커버), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P405" s="11" t="inlineStr"/>
@@ -27148,7 +27382,7 @@
       </c>
       <c r="C406" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D406" s="4" t="inlineStr">
@@ -27183,7 +27417,11 @@
         </is>
       </c>
       <c r="K406" s="11" t="inlineStr"/>
-      <c r="L406" s="11" t="n"/>
+      <c r="L406" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M406" s="11" t="inlineStr"/>
       <c r="N406" s="11" t="inlineStr">
         <is>
@@ -27192,7 +27430,7 @@
       </c>
       <c r="O406" s="11" t="inlineStr">
         <is>
-          <t>locksmithsanantonio.org(F95 BDC), g05.bimmerpost.com(G05 계열 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>amazon(F95 2024-2025 키커버), ebay(IYZBK1 2022-2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P406" s="11" t="inlineStr"/>
@@ -27210,7 +27448,7 @@
       </c>
       <c r="C407" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D407" s="4" t="inlineStr">
@@ -27228,17 +27466,21 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G407" s="11" t="inlineStr">
+      <c r="G407" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
       </c>
       <c r="H407" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I407" s="11" t="inlineStr"/>
+          <t>스마트키,카드키</t>
+        </is>
+      </c>
+      <c r="I407" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J407" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -27251,17 +27493,17 @@
         </is>
       </c>
       <c r="M407" s="11" t="inlineStr"/>
-      <c r="N407" s="11" t="inlineStr">
+      <c r="N407" s="17" t="inlineStr">
         <is>
           <t>BDC3</t>
         </is>
       </c>
       <c r="O407" s="11" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 X5, 순정 인서트키 포함), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
-        </is>
-      </c>
-      <c r="P407" s="11" t="inlineStr"/>
+          <t>ebay(2026 X5 순정 키), g05.bimmerpost.com(2026 X5 50e 키 2개+발레카드)</t>
+        </is>
+      </c>
+      <c r="P407" s="17" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="11" t="inlineStr">
@@ -27271,22 +27513,22 @@
       </c>
       <c r="B408" s="11" t="inlineStr">
         <is>
-          <t>X5 M (F95)</t>
+          <t>X6 (E71, 1세대)</t>
         </is>
       </c>
       <c r="C408" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D408" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E408" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="D408" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E408" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr">
@@ -27296,7 +27538,7 @@
       </c>
       <c r="G408" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46(PCF7945A)</t>
         </is>
       </c>
       <c r="H408" s="11" t="inlineStr">
@@ -27307,24 +27549,24 @@
       <c r="I408" s="11" t="inlineStr"/>
       <c r="J408" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K408" s="11" t="inlineStr"/>
       <c r="L408" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC KR55WK49127[3버튼]</t>
         </is>
       </c>
       <c r="M408" s="11" t="inlineStr"/>
       <c r="N408" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>CAS3[2008 중반 이전 생산], CAS3+[2008 중반 이후 생산]</t>
         </is>
       </c>
       <c r="O408" s="11" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2026), g05.bimmerpost.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>ebay(2008-2014 E71 리모컨키), ryan-keys.com(CAS3 X6 ID46 PCF7945), clechrono.com(E70/E71 ID7945 공키)</t>
         </is>
       </c>
       <c r="P408" s="11" t="inlineStr"/>
@@ -27337,22 +27579,22 @@
       </c>
       <c r="B409" s="11" t="inlineStr">
         <is>
-          <t>X5 M (F95)</t>
+          <t>X6 (E71, 1세대)</t>
         </is>
       </c>
       <c r="C409" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D409" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E409" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="D409" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E409" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F409" s="3" t="inlineStr">
@@ -27362,7 +27604,7 @@
       </c>
       <c r="G409" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46(PCF7945A)</t>
         </is>
       </c>
       <c r="H409" s="11" t="inlineStr">
@@ -27373,24 +27615,24 @@
       <c r="I409" s="11" t="inlineStr"/>
       <c r="J409" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K409" s="11" t="inlineStr"/>
       <c r="L409" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M409" s="11" t="inlineStr"/>
       <c r="N409" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>CAS3+</t>
         </is>
       </c>
       <c r="O409" s="11" t="inlineStr">
         <is>
-          <t>g05.bimmerpost.com(2024 LCI 키 품질 불만: 크고 가벼움), amazon(X5 F95/G05/G18 2024-2025 키커버), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>keyecu.com(키리스고 PCF7945 X5/X6 2006-2011 5WK49145), motospecperformance.com(CAS3 868MHz X6)</t>
         </is>
       </c>
       <c r="P409" s="11" t="inlineStr"/>
@@ -27403,22 +27645,22 @@
       </c>
       <c r="B410" s="11" t="inlineStr">
         <is>
-          <t>X5 M (F95)</t>
+          <t>X6 (E71, 1세대)</t>
         </is>
       </c>
       <c r="C410" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D410" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E410" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="D410" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E410" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr">
@@ -27428,7 +27670,7 @@
       </c>
       <c r="G410" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46(PCF7945A)</t>
         </is>
       </c>
       <c r="H410" s="11" t="inlineStr">
@@ -27439,24 +27681,24 @@
       <c r="I410" s="11" t="inlineStr"/>
       <c r="J410" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K410" s="11" t="inlineStr"/>
       <c r="L410" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC KR55WK49147[컴포트액세스], 926886-02[컴포트액세스]</t>
         </is>
       </c>
       <c r="M410" s="11" t="inlineStr"/>
       <c r="N410" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>CAS3+</t>
         </is>
       </c>
       <c r="O410" s="11" t="inlineStr">
         <is>
-          <t>amazon(F95 2024-2025 키커버), ebay(IYZBK1 2022-2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>ebay(KR55WK49147 컴포트액세스: 2008-2014 X6 E71), omegaautomotivetx.com(CAS3+ 컴포트액세스)</t>
         </is>
       </c>
       <c r="P410" s="11" t="inlineStr"/>
@@ -27469,22 +27711,22 @@
       </c>
       <c r="B411" s="11" t="inlineStr">
         <is>
-          <t>X5 M (F95)</t>
+          <t>X6 (E71, 1세대)</t>
         </is>
       </c>
       <c r="C411" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D411" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E411" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="D411" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E411" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F411" s="3" t="inlineStr">
@@ -27492,40 +27734,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G411" s="8" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G411" s="11" t="inlineStr">
+        <is>
+          <t>ID46(PCF7945A)</t>
         </is>
       </c>
       <c r="H411" s="11" t="inlineStr">
         <is>
-          <t>스마트키,카드키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I411" s="11" t="inlineStr"/>
       <c r="J411" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K411" s="11" t="inlineStr"/>
-      <c r="L411" s="11" t="n"/>
+      <c r="L411" s="11" t="inlineStr">
+        <is>
+          <t>FCC KR55WK49147, FCC KR55WK49127</t>
+        </is>
+      </c>
       <c r="M411" s="11" t="inlineStr"/>
-      <c r="N411" s="8" t="inlineStr">
-        <is>
-          <t>BDC3[추정]</t>
+      <c r="N411" s="11" t="inlineStr">
+        <is>
+          <t>CAS3+</t>
         </is>
       </c>
       <c r="O411" s="11" t="inlineStr">
         <is>
-          <t>ebay(2026 X5 순정 키), g05.bimmerpost.com(2026 X5 50e 키 2개+발레카드)</t>
-        </is>
-      </c>
-      <c r="P411" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+          <t>diamondkeysupply.com(순정 리퍼 KR55WK49147), prokeybox.com(KR55WK49147 OBD 등록)</t>
+        </is>
+      </c>
+      <c r="P411" s="11" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="11" t="inlineStr">
@@ -27540,7 +27782,7 @@
       </c>
       <c r="C412" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
@@ -27575,20 +27817,16 @@
         </is>
       </c>
       <c r="K412" s="11" t="inlineStr"/>
-      <c r="L412" s="11" t="inlineStr">
-        <is>
-          <t>FCC KR55WK49127[3버튼]</t>
-        </is>
-      </c>
+      <c r="L412" s="11" t="inlineStr"/>
       <c r="M412" s="11" t="inlineStr"/>
       <c r="N412" s="11" t="inlineStr">
         <is>
-          <t>CAS3[2008 중반 이전 생산], CAS3+[2008 중반 이후 생산]</t>
+          <t>CAS3+</t>
         </is>
       </c>
       <c r="O412" s="11" t="inlineStr">
         <is>
-          <t>ebay(2008-2014 E71 리모컨키), ryan-keys.com(CAS3 X6 ID46 PCF7945), clechrono.com(E70/E71 ID7945 공키)</t>
+          <t>amazon(Boxonly 2006-2014 X6 KR55WK49127 46칩), ebay(2008-2014 E71 키)</t>
         </is>
       </c>
       <c r="P412" s="11" t="inlineStr"/>
@@ -27606,7 +27844,7 @@
       </c>
       <c r="C413" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
@@ -27643,7 +27881,7 @@
       <c r="K413" s="11" t="inlineStr"/>
       <c r="L413" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127</t>
+          <t>FCC KR55WK49127, FCC KR55WK49123</t>
         </is>
       </c>
       <c r="M413" s="11" t="inlineStr"/>
@@ -27654,7 +27892,7 @@
       </c>
       <c r="O413" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(키리스고 PCF7945 X5/X6 2006-2011 5WK49145), motospecperformance.com(CAS3 868MHz X6)</t>
+          <t>amazon(MechanMagic CAS3 X6 2005-2013 KR55WK49127·KR55WK49123), ecumedics.com(CAS3 키 등록)</t>
         </is>
       </c>
       <c r="P413" s="11" t="inlineStr"/>
@@ -27672,7 +27910,7 @@
       </c>
       <c r="C414" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2014(단종)</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
@@ -27709,7 +27947,7 @@
       <c r="K414" s="11" t="inlineStr"/>
       <c r="L414" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147[컴포트액세스], 926886-02[컴포트액세스]</t>
+          <t>FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M414" s="11" t="inlineStr"/>
@@ -27720,7 +27958,7 @@
       </c>
       <c r="O414" s="11" t="inlineStr">
         <is>
-          <t>ebay(KR55WK49147 컴포트액세스: 2008-2014 X6 E71), omegaautomotivetx.com(CAS3+ 컴포트액세스)</t>
+          <t>ebay(X6 E71 2008-2014 키), boostmonkey.com(E시리즈 키 등록)</t>
         </is>
       </c>
       <c r="P414" s="11" t="inlineStr"/>
@@ -27733,22 +27971,22 @@
       </c>
       <c r="B415" s="11" t="inlineStr">
         <is>
-          <t>X6 (E71, 1세대)</t>
+          <t>X6 (F16, 2세대)</t>
         </is>
       </c>
       <c r="C415" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D415" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E415" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="D415" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E415" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F415" s="3" t="inlineStr">
@@ -27758,7 +27996,7 @@
       </c>
       <c r="G415" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945A)</t>
+          <t>ID49(PCF7953V)</t>
         </is>
       </c>
       <c r="H415" s="11" t="inlineStr">
@@ -27769,24 +28007,24 @@
       <c r="I415" s="11" t="inlineStr"/>
       <c r="J415" s="11" t="inlineStr">
         <is>
-          <t>HU92[세대 기준]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K415" s="11" t="inlineStr"/>
       <c r="L415" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147, FCC KR55WK49127</t>
+          <t>9367401-01, FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M415" s="11" t="inlineStr"/>
       <c r="N415" s="11" t="inlineStr">
         <is>
-          <t>CAS3+</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O415" s="11" t="inlineStr">
         <is>
-          <t>diamondkeysupply.com(순정 리퍼 KR55WK49147), prokeybox.com(KR55WK49147 OBD 등록)</t>
+          <t>northcoastkeyless.com(2014-2016 X6 N5F-ID21A 9367401-01), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P415" s="11" t="inlineStr"/>
@@ -27799,22 +28037,22 @@
       </c>
       <c r="B416" s="11" t="inlineStr">
         <is>
-          <t>X6 (E71, 1세대)</t>
+          <t>X6 (F16, 2세대)</t>
         </is>
       </c>
       <c r="C416" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D416" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E416" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D416" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E416" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F416" s="3" t="inlineStr">
@@ -27824,7 +28062,7 @@
       </c>
       <c r="G416" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945A)</t>
+          <t>ID49(PCF7953V)</t>
         </is>
       </c>
       <c r="H416" s="11" t="inlineStr">
@@ -27835,20 +28073,24 @@
       <c r="I416" s="11" t="inlineStr"/>
       <c r="J416" s="11" t="inlineStr">
         <is>
-          <t>HU92[세대 기준]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K416" s="11" t="inlineStr"/>
-      <c r="L416" s="11" t="inlineStr"/>
+      <c r="L416" s="11" t="inlineStr">
+        <is>
+          <t>9367401-01, FCC N5F-ID21A</t>
+        </is>
+      </c>
       <c r="M416" s="11" t="inlineStr"/>
       <c r="N416" s="11" t="inlineStr">
         <is>
-          <t>CAS3+</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O416" s="11" t="inlineStr">
         <is>
-          <t>amazon(Boxonly 2006-2014 X6 KR55WK49127 46칩), ebay(2008-2014 E71 키)</t>
+          <t>ebay(2014-2016 X5/X6 순정 N5F-ID21A), uhs-hardware.com(2014-2018 X6 FEM/BDC), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P416" s="11" t="inlineStr"/>
@@ -27861,22 +28103,22 @@
       </c>
       <c r="B417" s="11" t="inlineStr">
         <is>
-          <t>X6 (E71, 1세대)</t>
+          <t>X6 (F16, 2세대)</t>
         </is>
       </c>
       <c r="C417" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D417" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E417" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D417" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E417" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F417" s="3" t="inlineStr">
@@ -27886,7 +28128,7 @@
       </c>
       <c r="G417" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945A)</t>
+          <t>ID49(PCF7953V)</t>
         </is>
       </c>
       <c r="H417" s="11" t="inlineStr">
@@ -27897,24 +28139,24 @@
       <c r="I417" s="11" t="inlineStr"/>
       <c r="J417" s="11" t="inlineStr">
         <is>
-          <t>HU92[세대 기준]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K417" s="11" t="inlineStr"/>
       <c r="L417" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127, FCC KR55WK49123</t>
+          <t>9367401-01, FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M417" s="11" t="inlineStr"/>
       <c r="N417" s="11" t="inlineStr">
         <is>
-          <t>CAS3+</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O417" s="11" t="inlineStr">
         <is>
-          <t>amazon(MechanMagic CAS3 X6 2005-2013 KR55WK49127·KR55WK49123), ecumedics.com(CAS3 키 등록)</t>
+          <t>uhs-hardware.com(N5F-ID21A 칩 HITAG Pro ID49 PCF7953V), northcoastkeyless.com(2014-2016 X6), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P417" s="11" t="inlineStr"/>
@@ -27927,22 +28169,22 @@
       </c>
       <c r="B418" s="11" t="inlineStr">
         <is>
-          <t>X6 (E71, 1세대)</t>
+          <t>X6 (F16, 2세대)</t>
         </is>
       </c>
       <c r="C418" s="11" t="inlineStr">
         <is>
-          <t>2014(단종)</t>
-        </is>
-      </c>
-      <c r="D418" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E418" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D418" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E418" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F418" s="3" t="inlineStr">
@@ -27952,7 +28194,7 @@
       </c>
       <c r="G418" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945A)</t>
+          <t>ID49(PCF7953V)</t>
         </is>
       </c>
       <c r="H418" s="11" t="inlineStr">
@@ -27963,24 +28205,24 @@
       <c r="I418" s="11" t="inlineStr"/>
       <c r="J418" s="11" t="inlineStr">
         <is>
-          <t>HU92[세대 기준]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K418" s="11" t="inlineStr"/>
       <c r="L418" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M418" s="11" t="inlineStr"/>
       <c r="N418" s="11" t="inlineStr">
         <is>
-          <t>CAS3+</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O418" s="11" t="inlineStr">
         <is>
-          <t>ebay(X6 E71 2008-2014 키), boostmonkey.com(E시리즈 키 등록)</t>
+          <t>ebay(2014-2019 X5/X6 NBGIDGNG1), amazon(Kilessgo 2016-2019 X6 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P418" s="11" t="inlineStr"/>
@@ -27998,7 +28240,7 @@
       </c>
       <c r="C419" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
@@ -28035,7 +28277,7 @@
       <c r="K419" s="11" t="inlineStr"/>
       <c r="L419" s="11" t="inlineStr">
         <is>
-          <t>9367401-01, FCC N5F-ID21A</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M419" s="11" t="inlineStr"/>
@@ -28046,7 +28288,7 @@
       </c>
       <c r="O419" s="11" t="inlineStr">
         <is>
-          <t>northcoastkeyless.com(2014-2016 X6 N5F-ID21A 9367401-01), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>locksmithkeyless.com(2014-2018 X5/X6 FEM/BDC NBGIDGNG1), key4.com(NBGIDGNG1 X5/X6), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P419" s="11" t="inlineStr"/>
@@ -28064,7 +28306,7 @@
       </c>
       <c r="C420" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2019(단종)</t>
         </is>
       </c>
       <c r="D420" s="4" t="inlineStr">
@@ -28101,7 +28343,7 @@
       <c r="K420" s="11" t="inlineStr"/>
       <c r="L420" s="11" t="inlineStr">
         <is>
-          <t>9367401-01, FCC N5F-ID21A</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M420" s="11" t="inlineStr"/>
@@ -28112,7 +28354,7 @@
       </c>
       <c r="O420" s="11" t="inlineStr">
         <is>
-          <t>ebay(2014-2016 X5/X6 순정 N5F-ID21A), uhs-hardware.com(2014-2018 X6 FEM/BDC), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>nectechkeysupply.com(2014-2019 X2/X5/X6 NBGIDGNG1 BDC), amazon(Keylessbest 2014-2019 X6), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P420" s="11" t="inlineStr"/>
@@ -28125,12 +28367,12 @@
       </c>
       <c r="B421" s="11" t="inlineStr">
         <is>
-          <t>X6 (F16, 2세대)</t>
+          <t>X6 (G06, 3세대)</t>
         </is>
       </c>
       <c r="C421" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
@@ -28150,7 +28392,7 @@
       </c>
       <c r="G421" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953V)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H421" s="11" t="inlineStr">
@@ -28167,18 +28409,18 @@
       <c r="K421" s="11" t="inlineStr"/>
       <c r="L421" s="11" t="inlineStr">
         <is>
-          <t>9367401-01, FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M421" s="11" t="inlineStr"/>
       <c r="N421" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O421" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A 칩 HITAG Pro ID49 PCF7953V), northcoastkeyless.com(2014-2016 X6), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>uhs-hardware.com(N5F-ID21A BDC2 G시리즈), locksmithkeyless.com(2014-2023 N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P421" s="11" t="inlineStr"/>
@@ -28191,12 +28433,12 @@
       </c>
       <c r="B422" s="11" t="inlineStr">
         <is>
-          <t>X6 (F16, 2세대)</t>
+          <t>X6 (G06, 3세대)</t>
         </is>
       </c>
       <c r="C422" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D422" s="4" t="inlineStr">
@@ -28216,7 +28458,7 @@
       </c>
       <c r="G422" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953V)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H422" s="11" t="inlineStr">
@@ -28233,18 +28475,18 @@
       <c r="K422" s="11" t="inlineStr"/>
       <c r="L422" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M422" s="11" t="inlineStr"/>
       <c r="N422" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O422" s="11" t="inlineStr">
         <is>
-          <t>ebay(2014-2019 X5/X6 NBGIDGNG1), amazon(Kilessgo 2016-2019 X6 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>ebay(2020 BMW N5F-ID21A 키), yourcarkeyguys.com(BDC2 N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P422" s="11" t="inlineStr"/>
@@ -28257,12 +28499,12 @@
       </c>
       <c r="B423" s="11" t="inlineStr">
         <is>
-          <t>X6 (F16, 2세대)</t>
+          <t>X6 (G06, 3세대)</t>
         </is>
       </c>
       <c r="C423" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
@@ -28282,7 +28524,7 @@
       </c>
       <c r="G423" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953V)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H423" s="11" t="inlineStr">
@@ -28299,18 +28541,18 @@
       <c r="K423" s="11" t="inlineStr"/>
       <c r="L423" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M423" s="11" t="inlineStr"/>
       <c r="N423" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O423" s="11" t="inlineStr">
         <is>
-          <t>locksmithkeyless.com(2014-2018 X5/X6 FEM/BDC NBGIDGNG1), key4.com(NBGIDGNG1 X5/X6), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>ebay(G06 2019-2025 M스포츠 키), go-parts.com(G시리즈 BDC), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P423" s="11" t="inlineStr"/>
@@ -28323,12 +28565,12 @@
       </c>
       <c r="B424" s="11" t="inlineStr">
         <is>
-          <t>X6 (F16, 2세대)</t>
+          <t>X6 (G06, 3세대)</t>
         </is>
       </c>
       <c r="C424" s="11" t="inlineStr">
         <is>
-          <t>2019(단종)</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D424" s="4" t="inlineStr">
@@ -28348,7 +28590,7 @@
       </c>
       <c r="G424" s="11" t="inlineStr">
         <is>
-          <t>ID49(PCF7953V)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H424" s="11" t="inlineStr">
@@ -28365,18 +28607,18 @@
       <c r="K424" s="11" t="inlineStr"/>
       <c r="L424" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M424" s="11" t="inlineStr"/>
       <c r="N424" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O424" s="11" t="inlineStr">
         <is>
-          <t>nectechkeysupply.com(2014-2019 X2/X5/X6 NBGIDGNG1 BDC), amazon(Keylessbest 2014-2019 X6), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>ebay(IYZBK1 2022-2025 X6), go-parts.com(2022-2025 키 딜러/전문가 등록 필수), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P424" s="11" t="inlineStr"/>
@@ -28394,7 +28636,7 @@
       </c>
       <c r="C425" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
@@ -28431,7 +28673,7 @@
       <c r="K425" s="11" t="inlineStr"/>
       <c r="L425" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M425" s="11" t="inlineStr"/>
@@ -28442,7 +28684,7 @@
       </c>
       <c r="O425" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A BDC2 G시리즈), locksmithkeyless.com(2014-2023 N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>keyecu.com(2023-2024 X1/iX/XM/X5/X6/X7/i7 신형 스마트키 쉘), ebay(IYZBK1), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P425" s="11" t="inlineStr"/>
@@ -28460,7 +28702,7 @@
       </c>
       <c r="C426" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D426" s="4" t="inlineStr">
@@ -28497,7 +28739,7 @@
       <c r="K426" s="11" t="inlineStr"/>
       <c r="L426" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M426" s="11" t="inlineStr"/>
@@ -28508,7 +28750,7 @@
       </c>
       <c r="O426" s="11" t="inlineStr">
         <is>
-          <t>ebay(2020 BMW N5F-ID21A 키), yourcarkeyguys.com(BDC2 N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>g05.bimmerpost.com(2024 LCI 키: 대형·경량, 디지털키 플러스), programyourremote.com(2024 X6 키등록), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P426" s="11" t="inlineStr"/>
@@ -28526,7 +28768,7 @@
       </c>
       <c r="C427" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
@@ -28563,7 +28805,7 @@
       <c r="K427" s="11" t="inlineStr"/>
       <c r="L427" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M427" s="11" t="inlineStr"/>
@@ -28574,7 +28816,7 @@
       </c>
       <c r="O427" s="11" t="inlineStr">
         <is>
-          <t>ebay(G06 2019-2025 M스포츠 키), go-parts.com(G시리즈 BDC), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>amazon(X6 F96/G06 2024-2025 키커버), ecstuning.com(G06 X6 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P427" s="11" t="inlineStr"/>
@@ -28592,7 +28834,7 @@
       </c>
       <c r="C428" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D428" s="4" t="inlineStr">
@@ -28610,7 +28852,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G428" s="11" t="inlineStr">
+      <c r="G428" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -28620,7 +28862,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I428" s="11" t="inlineStr"/>
+      <c r="I428" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J428" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -28633,17 +28879,17 @@
         </is>
       </c>
       <c r="M428" s="11" t="inlineStr"/>
-      <c r="N428" s="11" t="inlineStr">
+      <c r="N428" s="17" t="inlineStr">
         <is>
           <t>BDC3</t>
         </is>
       </c>
       <c r="O428" s="11" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 X6), go-parts.com(2022-2025 키 딜러/전문가 등록 필수), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
-        </is>
-      </c>
-      <c r="P428" s="11" t="inlineStr"/>
+          <t>g05.bimmerpost.com(2026 X6 M60i 키 인식 문제, 2027 X6 키 디자인 변경)</t>
+        </is>
+      </c>
+      <c r="P428" s="17" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="11" t="inlineStr">
@@ -28653,12 +28899,12 @@
       </c>
       <c r="B429" s="11" t="inlineStr">
         <is>
-          <t>X6 (G06, 3세대)</t>
+          <t>X6 M (F86)</t>
         </is>
       </c>
       <c r="C429" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
@@ -28695,18 +28941,18 @@
       <c r="K429" s="11" t="inlineStr"/>
       <c r="L429" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>9367401-01, FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M429" s="11" t="inlineStr"/>
       <c r="N429" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O429" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(2023-2024 X1/iX/XM/X5/X6/X7/i7 신형 스마트키 쉘), ebay(IYZBK1), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>ebay(2014-2016 X5/X6 순정 N5F-ID21A 9367401-01), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P429" s="11" t="inlineStr"/>
@@ -28719,12 +28965,12 @@
       </c>
       <c r="B430" s="11" t="inlineStr">
         <is>
-          <t>X6 (G06, 3세대)</t>
+          <t>X6 M (F86)</t>
         </is>
       </c>
       <c r="C430" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D430" s="4" t="inlineStr">
@@ -28761,18 +29007,18 @@
       <c r="K430" s="11" t="inlineStr"/>
       <c r="L430" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>9367401-01, FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M430" s="11" t="inlineStr"/>
       <c r="N430" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O430" s="11" t="inlineStr">
         <is>
-          <t>g05.bimmerpost.com(2024 LCI 키: 대형·경량, 디지털키 플러스), programyourremote.com(2024 X6 키등록), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>northcoastkeyless.com(2014-2016 X6 N5F-ID21A), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P430" s="11" t="inlineStr"/>
@@ -28785,12 +29031,12 @@
       </c>
       <c r="B431" s="11" t="inlineStr">
         <is>
-          <t>X6 (G06, 3세대)</t>
+          <t>X6 M (F86)</t>
         </is>
       </c>
       <c r="C431" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
@@ -28827,18 +29073,18 @@
       <c r="K431" s="11" t="inlineStr"/>
       <c r="L431" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M431" s="11" t="inlineStr"/>
       <c r="N431" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O431" s="11" t="inlineStr">
         <is>
-          <t>amazon(X6 F96/G06 2024-2025 키커버), ecstuning.com(G06 X6 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>ebay(2014-2018 5시리즈/X5/X6 순정 N5F-ID21A), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P431" s="11" t="inlineStr"/>
@@ -28851,12 +29097,12 @@
       </c>
       <c r="B432" s="11" t="inlineStr">
         <is>
-          <t>X6 (G06, 3세대)</t>
+          <t>X6 M (F86)</t>
         </is>
       </c>
       <c r="C432" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2018(단종)</t>
         </is>
       </c>
       <c r="D432" s="4" t="inlineStr">
@@ -28874,7 +29120,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G432" s="8" t="inlineStr">
+      <c r="G432" s="11" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -28891,23 +29137,23 @@
         </is>
       </c>
       <c r="K432" s="11" t="inlineStr"/>
-      <c r="L432" s="11" t="n"/>
+      <c r="L432" s="11" t="inlineStr">
+        <is>
+          <t>FCC N5F-ID21A, FCC NBGIDGNG1</t>
+        </is>
+      </c>
       <c r="M432" s="11" t="inlineStr"/>
-      <c r="N432" s="8" t="inlineStr">
-        <is>
-          <t>BDC3[추정]</t>
+      <c r="N432" s="11" t="inlineStr">
+        <is>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O432" s="11" t="inlineStr">
         <is>
-          <t>g05.bimmerpost.com(2026 X6 M60i 키 인식 문제, 2027 X6 키 디자인 변경)</t>
-        </is>
-      </c>
-      <c r="P432" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+          <t>uhs-hardware.com(2014-2018 X5/X6 9367401-01 FEM/BDC), locksmithkeyless.com(2014-2018 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+        </is>
+      </c>
+      <c r="P432" s="11" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="11" t="inlineStr">
@@ -28917,12 +29163,12 @@
       </c>
       <c r="B433" s="11" t="inlineStr">
         <is>
-          <t>X6 M (F86)</t>
+          <t>X6 M (F96)</t>
         </is>
       </c>
       <c r="C433" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
@@ -28957,20 +29203,16 @@
         </is>
       </c>
       <c r="K433" s="11" t="inlineStr"/>
-      <c r="L433" s="11" t="inlineStr">
-        <is>
-          <t>9367401-01, FCC N5F-ID21A</t>
-        </is>
-      </c>
+      <c r="L433" s="11" t="n"/>
       <c r="M433" s="11" t="inlineStr"/>
       <c r="N433" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O433" s="11" t="inlineStr">
         <is>
-          <t>ebay(2014-2016 X5/X6 순정 N5F-ID21A 9367401-01), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>pelicanparts.com(F96 X6 M Comp 2020-2021 키), keyless2go.com(2020 X6 키 전문가 등록), monacoms.com(X6M F96 2020~ 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P433" s="11" t="inlineStr"/>
@@ -28983,12 +29225,12 @@
       </c>
       <c r="B434" s="11" t="inlineStr">
         <is>
-          <t>X6 M (F86)</t>
+          <t>X6 M (F96)</t>
         </is>
       </c>
       <c r="C434" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D434" s="4" t="inlineStr">
@@ -29023,20 +29265,16 @@
         </is>
       </c>
       <c r="K434" s="11" t="inlineStr"/>
-      <c r="L434" s="11" t="inlineStr">
-        <is>
-          <t>9367401-01, FCC N5F-ID21A</t>
-        </is>
-      </c>
+      <c r="L434" s="11" t="n"/>
       <c r="M434" s="11" t="inlineStr"/>
       <c r="N434" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O434" s="11" t="inlineStr">
         <is>
-          <t>northcoastkeyless.com(2014-2016 X6 N5F-ID21A), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>pelicanparts.com(F96 2020-2021 키), bimmerworld.com(M 퍼포먼스 키케이스 F95/F96), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P434" s="11" t="inlineStr"/>
@@ -29049,12 +29287,12 @@
       </c>
       <c r="B435" s="11" t="inlineStr">
         <is>
-          <t>X6 M (F86)</t>
+          <t>X6 M (F96)</t>
         </is>
       </c>
       <c r="C435" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
@@ -29091,18 +29329,18 @@
       <c r="K435" s="11" t="inlineStr"/>
       <c r="L435" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M435" s="11" t="inlineStr"/>
       <c r="N435" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O435" s="11" t="inlineStr">
         <is>
-          <t>ebay(2014-2018 5시리즈/X5/X6 순정 N5F-ID21A), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>ebay(IYZBK1 2022-2025 X6), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P435" s="11" t="inlineStr"/>
@@ -29115,12 +29353,12 @@
       </c>
       <c r="B436" s="11" t="inlineStr">
         <is>
-          <t>X6 M (F86)</t>
+          <t>X6 M (F96)</t>
         </is>
       </c>
       <c r="C436" s="11" t="inlineStr">
         <is>
-          <t>2018(단종)</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D436" s="4" t="inlineStr">
@@ -29157,18 +29395,18 @@
       <c r="K436" s="11" t="inlineStr"/>
       <c r="L436" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A, FCC NBGIDGNG1</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M436" s="11" t="inlineStr"/>
       <c r="N436" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O436" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(2014-2018 X5/X6 9367401-01 FEM/BDC), locksmithkeyless.com(2014-2018 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>amazon(SANRILY X6 F96 2023-2024 키커버), ebay(IYZBK1), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P436" s="11" t="inlineStr"/>
@@ -29186,7 +29424,7 @@
       </c>
       <c r="C437" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
@@ -29221,7 +29459,11 @@
         </is>
       </c>
       <c r="K437" s="11" t="inlineStr"/>
-      <c r="L437" s="11" t="n"/>
+      <c r="L437" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M437" s="11" t="inlineStr"/>
       <c r="N437" s="11" t="inlineStr">
         <is>
@@ -29230,7 +29472,7 @@
       </c>
       <c r="O437" s="11" t="inlineStr">
         <is>
-          <t>pelicanparts.com(F96 X6 M Comp 2020-2021 키), keyless2go.com(2020 X6 키 전문가 등록), monacoms.com(X6M F96 2020~ 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>programyourremote.com(2024 X6 키 등록), amazon(X5/X6 2024-2025 신형 키 케이스), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P437" s="11" t="inlineStr"/>
@@ -29248,7 +29490,7 @@
       </c>
       <c r="C438" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D438" s="4" t="inlineStr">
@@ -29283,7 +29525,11 @@
         </is>
       </c>
       <c r="K438" s="11" t="inlineStr"/>
-      <c r="L438" s="11" t="n"/>
+      <c r="L438" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M438" s="11" t="inlineStr"/>
       <c r="N438" s="11" t="inlineStr">
         <is>
@@ -29292,7 +29538,7 @@
       </c>
       <c r="O438" s="11" t="inlineStr">
         <is>
-          <t>pelicanparts.com(F96 2020-2021 키), bimmerworld.com(M 퍼포먼스 키케이스 F95/F96), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>amazon(Jaronx X5/X6 2025 키커버), ebay(IYZBK1 2022-2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P438" s="11" t="inlineStr"/>
@@ -29310,7 +29556,7 @@
       </c>
       <c r="C439" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
@@ -29328,7 +29574,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G439" s="11" t="inlineStr">
+      <c r="G439" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -29338,7 +29584,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I439" s="11" t="inlineStr"/>
+      <c r="I439" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J439" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -29351,17 +29601,17 @@
         </is>
       </c>
       <c r="M439" s="11" t="inlineStr"/>
-      <c r="N439" s="11" t="inlineStr">
+      <c r="N439" s="17" t="inlineStr">
         <is>
           <t>BDC3</t>
         </is>
       </c>
       <c r="O439" s="11" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 X6), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
-        </is>
-      </c>
-      <c r="P439" s="11" t="inlineStr"/>
+          <t>g05.bimmerpost.com(2026 X6 키), ebay(IYZBK1 2022-2026)</t>
+        </is>
+      </c>
+      <c r="P439" s="17" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="11" t="inlineStr">
@@ -29371,12 +29621,12 @@
       </c>
       <c r="B440" s="11" t="inlineStr">
         <is>
-          <t>X6 M (F96)</t>
+          <t>X7 (G07)</t>
         </is>
       </c>
       <c r="C440" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D440" s="4" t="inlineStr">
@@ -29413,7 +29663,7 @@
       <c r="K440" s="11" t="inlineStr"/>
       <c r="L440" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>66125A3D720, 66125A06CA2, FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M440" s="11" t="inlineStr"/>
@@ -29424,7 +29674,7 @@
       </c>
       <c r="O440" s="11" t="inlineStr">
         <is>
-          <t>amazon(SANRILY X6 F96 2023-2024 키커버), ebay(IYZBK1), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>go-parts.com(BDC2 OEM 66125A3D720·66125A06CA2 N5F-ID21A), g07.bimmerpost.com(2019 X7 디스플레이키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P440" s="11" t="inlineStr"/>
@@ -29437,12 +29687,12 @@
       </c>
       <c r="B441" s="11" t="inlineStr">
         <is>
-          <t>X6 M (F96)</t>
+          <t>X7 (G07)</t>
         </is>
       </c>
       <c r="C441" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D441" s="4" t="inlineStr">
@@ -29470,7 +29720,7 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I441" s="11" t="inlineStr"/>
+      <c r="I441" s="11" t="n"/>
       <c r="J441" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -29479,7 +29729,7 @@
       <c r="K441" s="11" t="inlineStr"/>
       <c r="L441" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC N5F-ID21A, 9877472-01[디스플레이키]</t>
         </is>
       </c>
       <c r="M441" s="11" t="inlineStr"/>
@@ -29490,7 +29740,7 @@
       </c>
       <c r="O441" s="11" t="inlineStr">
         <is>
-          <t>programyourremote.com(2024 X6 키 등록), amazon(X5/X6 2024-2025 신형 키 케이스), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>prokeyfob.com(2020 X7 인서트 키 블레이드), keyshop-online.com(BDC2 디스플레이키 2016-2021), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P441" s="11" t="inlineStr"/>
@@ -29503,12 +29753,12 @@
       </c>
       <c r="B442" s="11" t="inlineStr">
         <is>
-          <t>X6 M (F96)</t>
+          <t>X7 (G07)</t>
         </is>
       </c>
       <c r="C442" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D442" s="4" t="inlineStr">
@@ -29556,7 +29806,7 @@
       </c>
       <c r="O442" s="11" t="inlineStr">
         <is>
-          <t>amazon(Jaronx X5/X6 2025 키커버), ebay(IYZBK1 2022-2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>ebay(IYZBK1 2021-2025 X7), pelicanparts.com(G07 X7 2019-2024 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P442" s="11" t="inlineStr"/>
@@ -29569,12 +29819,12 @@
       </c>
       <c r="B443" s="11" t="inlineStr">
         <is>
-          <t>X6 M (F96)</t>
+          <t>X7 (G07)</t>
         </is>
       </c>
       <c r="C443" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D443" s="4" t="inlineStr">
@@ -29592,7 +29842,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G443" s="8" t="inlineStr">
+      <c r="G443" s="11" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -29609,23 +29859,23 @@
         </is>
       </c>
       <c r="K443" s="11" t="inlineStr"/>
-      <c r="L443" s="11" t="n"/>
+      <c r="L443" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M443" s="11" t="inlineStr"/>
-      <c r="N443" s="8" t="inlineStr">
-        <is>
-          <t>BDC3[추정]</t>
+      <c r="N443" s="11" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O443" s="11" t="inlineStr">
         <is>
-          <t>g05.bimmerpost.com(2026 X6 키), ebay(IYZBK1 2022-2026)</t>
-        </is>
-      </c>
-      <c r="P443" s="8" t="inlineStr">
-        <is>
-          <t>이 연식 이모빌라이저 원문 없음 — 이전 연식 기준 추정</t>
-        </is>
-      </c>
+          <t>ebay(IYZBK1 2022-2025 X7), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="P443" s="11" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="11" t="inlineStr">
@@ -29640,7 +29890,7 @@
       </c>
       <c r="C444" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D444" s="4" t="inlineStr">
@@ -29677,7 +29927,7 @@
       <c r="K444" s="11" t="inlineStr"/>
       <c r="L444" s="11" t="inlineStr">
         <is>
-          <t>66125A3D720, 66125A06CA2, FCC N5F-ID21A</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M444" s="11" t="inlineStr"/>
@@ -29688,7 +29938,7 @@
       </c>
       <c r="O444" s="11" t="inlineStr">
         <is>
-          <t>go-parts.com(BDC2 OEM 66125A3D720·66125A06CA2 N5F-ID21A), g07.bimmerpost.com(2019 X7 디스플레이키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>ebay(2023 순정 IYZBK1 2701A-BK1), g07.bimmerpost.com(X7 키 분실), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P444" s="11" t="inlineStr"/>
@@ -29706,7 +29956,7 @@
       </c>
       <c r="C445" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D445" s="4" t="inlineStr">
@@ -29724,7 +29974,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G445" s="11" t="inlineStr">
+      <c r="G445" s="8" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -29734,7 +29984,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I445" s="11" t="n"/>
+      <c r="I445" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J445" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -29743,21 +29997,25 @@
       <c r="K445" s="11" t="inlineStr"/>
       <c r="L445" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A, 9877472-01[디스플레이키]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M445" s="11" t="inlineStr"/>
-      <c r="N445" s="11" t="inlineStr">
-        <is>
-          <t>BDC3</t>
+      <c r="N445" s="8" t="inlineStr">
+        <is>
+          <t>BDC3, BCP</t>
         </is>
       </c>
       <c r="O445" s="11" t="inlineStr">
         <is>
-          <t>prokeyfob.com(2020 X7 인서트 키 블레이드), keyshop-online.com(BDC2 디스플레이키 2016-2021), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
-        </is>
-      </c>
-      <c r="P445" s="11" t="inlineStr"/>
+          <t>g07.bimmerpost.com(2024 신형 실물키: LCI는 새 리모컨 디자인, i모델은 다른 프로토콜)</t>
+        </is>
+      </c>
+      <c r="P445" s="8" t="inlineStr">
+        <is>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="11" t="inlineStr">
@@ -29772,7 +30030,7 @@
       </c>
       <c r="C446" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D446" s="4" t="inlineStr">
@@ -29790,7 +30048,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G446" s="11" t="inlineStr">
+      <c r="G446" s="8" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -29800,7 +30058,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I446" s="11" t="inlineStr"/>
+      <c r="I446" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J446" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -29813,17 +30075,21 @@
         </is>
       </c>
       <c r="M446" s="11" t="inlineStr"/>
-      <c r="N446" s="11" t="inlineStr">
-        <is>
-          <t>BDC3</t>
+      <c r="N446" s="8" t="inlineStr">
+        <is>
+          <t>BDC3, BCP</t>
         </is>
       </c>
       <c r="O446" s="11" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2021-2025 X7), pelicanparts.com(G07 X7 2019-2024 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
-        </is>
-      </c>
-      <c r="P446" s="11" t="inlineStr"/>
+          <t>keylessentryremotefob.com(2025 X7 키)</t>
+        </is>
+      </c>
+      <c r="P446" s="8" t="inlineStr">
+        <is>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="11" t="inlineStr">
@@ -29838,7 +30104,7 @@
       </c>
       <c r="C447" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D447" s="4" t="inlineStr">
@@ -29856,7 +30122,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G447" s="11" t="inlineStr">
+      <c r="G447" s="8" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -29866,7 +30132,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I447" s="11" t="inlineStr"/>
+      <c r="I447" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J447" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -29879,17 +30149,21 @@
         </is>
       </c>
       <c r="M447" s="11" t="inlineStr"/>
-      <c r="N447" s="11" t="inlineStr">
-        <is>
-          <t>BDC3</t>
+      <c r="N447" s="8" t="inlineStr">
+        <is>
+          <t>BDC3, BCP</t>
         </is>
       </c>
       <c r="O447" s="11" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2022-2025 X7), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
-        </is>
-      </c>
-      <c r="P447" s="11" t="inlineStr"/>
+          <t>g07.bimmerpost.com(MY26 신차는 키 1개, X5·X7 제외)</t>
+        </is>
+      </c>
+      <c r="P447" s="8" t="inlineStr">
+        <is>
+          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="11" t="inlineStr">
@@ -29899,7 +30173,7 @@
       </c>
       <c r="B448" s="11" t="inlineStr">
         <is>
-          <t>X7 (G07)</t>
+          <t>XM (G09)</t>
         </is>
       </c>
       <c r="C448" s="11" t="inlineStr">
@@ -29922,7 +30196,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G448" s="11" t="inlineStr">
+      <c r="G448" s="8" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -29932,10 +30206,14 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I448" s="11" t="inlineStr"/>
+      <c r="I448" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J448" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU100R[추정]</t>
         </is>
       </c>
       <c r="K448" s="11" t="inlineStr"/>
@@ -29945,17 +30223,21 @@
         </is>
       </c>
       <c r="M448" s="11" t="inlineStr"/>
-      <c r="N448" s="11" t="inlineStr">
-        <is>
-          <t>BDC3</t>
+      <c r="N448" s="8" t="inlineStr">
+        <is>
+          <t>BDC3[추정]</t>
         </is>
       </c>
       <c r="O448" s="11" t="inlineStr">
         <is>
-          <t>ebay(2023 순정 IYZBK1 2701A-BK1), g07.bimmerpost.com(X7 키 분실), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
-        </is>
-      </c>
-      <c r="P448" s="11" t="inlineStr"/>
+          <t>obdexpress.co.uk·obdii365.com(G섀시 BDC3/U섀시 BCP 구분, XM=G09 → BDC3), key4.com(GODIAG BDC3/BCP 어댑터)</t>
+        </is>
+      </c>
+      <c r="P448" s="8" t="inlineStr">
+        <is>
+          <t>키(IYZBK1) 확인 — XM 전용 이모빌라이저 자료 없음(G섀시 BDC3 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="11" t="inlineStr">
@@ -29965,7 +30247,7 @@
       </c>
       <c r="B449" s="11" t="inlineStr">
         <is>
-          <t>X7 (G07)</t>
+          <t>XM (G09)</t>
         </is>
       </c>
       <c r="C449" s="11" t="inlineStr">
@@ -29998,28 +30280,36 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I449" s="11" t="inlineStr"/>
+      <c r="I449" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J449" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU100R[추정]</t>
         </is>
       </c>
       <c r="K449" s="11" t="inlineStr"/>
-      <c r="L449" s="11" t="n"/>
+      <c r="L449" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M449" s="11" t="inlineStr"/>
       <c r="N449" s="8" t="inlineStr">
         <is>
-          <t>BDC3, BCP</t>
+          <t>BDC3[추정]</t>
         </is>
       </c>
       <c r="O449" s="11" t="inlineStr">
         <is>
-          <t>g07.bimmerpost.com(2024 신형 실물키: LCI는 새 리모컨 디자인, i모델은 다른 프로토콜)</t>
+          <t>keyecu.com(2023-2024 XM 포함 신형 스마트키 쉘), go-parts.com(딜러/전문가 등록 필수)</t>
         </is>
       </c>
       <c r="P449" s="8" t="inlineStr">
         <is>
-          <t>이 연식 이모빌라이저 BDC3·BCP 자료 상충(확인 필요)</t>
+          <t>키(IYZBK1) 확인 — XM 전용 이모빌라이저 자료 없음(G섀시 BDC3 추정)</t>
         </is>
       </c>
     </row>
@@ -30031,7 +30321,7 @@
       </c>
       <c r="B450" s="11" t="inlineStr">
         <is>
-          <t>X7 (G07)</t>
+          <t>XM (G09)</t>
         </is>
       </c>
       <c r="C450" s="11" t="inlineStr">
@@ -30064,28 +30354,36 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I450" s="11" t="inlineStr"/>
+      <c r="I450" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J450" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU100R[추정]</t>
         </is>
       </c>
       <c r="K450" s="11" t="inlineStr"/>
-      <c r="L450" s="11" t="n"/>
+      <c r="L450" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M450" s="11" t="inlineStr"/>
       <c r="N450" s="8" t="inlineStr">
         <is>
-          <t>BDC3, BCP</t>
+          <t>BDC3[추정]</t>
         </is>
       </c>
       <c r="O450" s="11" t="inlineStr">
         <is>
-          <t>keylessentryremotefob.com(2025 X7 키)</t>
+          <t>programyourremote.com(2025 XM 스마트키 등록 안내)</t>
         </is>
       </c>
       <c r="P450" s="8" t="inlineStr">
         <is>
-          <t>이 연식 이모빌라이저 BDC3·BCP 자료 상충(확인 필요)</t>
+          <t>키(IYZBK1) 확인 — XM 전용 이모빌라이저 자료 없음(G섀시 BDC3 추정)</t>
         </is>
       </c>
     </row>
@@ -30097,7 +30395,7 @@
       </c>
       <c r="B451" s="11" t="inlineStr">
         <is>
-          <t>X7 (G07)</t>
+          <t>XM (G09)</t>
         </is>
       </c>
       <c r="C451" s="11" t="inlineStr">
@@ -30105,17 +30403,17 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="D451" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E451" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F451" s="3" t="inlineStr">
+      <c r="D451" s="14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E451" s="15" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F451" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -30130,28 +30428,36 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I451" s="11" t="inlineStr"/>
+      <c r="I451" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30</t>
+        </is>
+      </c>
       <c r="J451" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU100R[추정]</t>
         </is>
       </c>
       <c r="K451" s="11" t="inlineStr"/>
-      <c r="L451" s="11" t="n"/>
+      <c r="L451" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M451" s="11" t="inlineStr"/>
       <c r="N451" s="8" t="inlineStr">
         <is>
-          <t>BDC3, BCP</t>
+          <t>BDC3[추정]</t>
         </is>
       </c>
       <c r="O451" s="11" t="inlineStr">
         <is>
-          <t>g07.bimmerpost.com(MY26 신차는 키 1개, X5·X7 제외)</t>
+          <t>2026 XM 전용 자료 없음</t>
         </is>
       </c>
       <c r="P451" s="8" t="inlineStr">
         <is>
-          <t>이 연식 이모빌라이저 BDC3·BCP 자료 상충(확인 필요)</t>
+          <t>키(IYZBK1) 확인 — XM 전용 이모빌라이저 자료 없음(G섀시 BDC3 추정)</t>
         </is>
       </c>
     </row>
@@ -30163,22 +30469,22 @@
       </c>
       <c r="B452" s="11" t="inlineStr">
         <is>
-          <t>XM (G09)</t>
+          <t>Z4 (E85, 1세대)</t>
         </is>
       </c>
       <c r="C452" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D452" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E452" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="D452" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E452" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr">
@@ -30186,40 +30492,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G452" s="8" t="inlineStr">
-        <is>
-          <t>ID49[BDC3 변형]</t>
+      <c r="G452" s="11" t="inlineStr">
+        <is>
+          <t>ID44(PCF7935)</t>
         </is>
       </c>
       <c r="H452" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I452" s="11" t="inlineStr"/>
       <c r="J452" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K452" s="11" t="inlineStr"/>
-      <c r="L452" s="11" t="n"/>
+      <c r="L452" s="11" t="inlineStr"/>
       <c r="M452" s="11" t="inlineStr"/>
-      <c r="N452" s="8" t="inlineStr">
-        <is>
-          <t>BDC3[G섀시 기준]</t>
+      <c r="N452" s="11" t="inlineStr">
+        <is>
+          <t>EWS3</t>
         </is>
       </c>
       <c r="O452" s="11" t="inlineStr">
         <is>
-          <t>obdexpress.co.uk·obdii365.com(G섀시 BDC3/U섀시 BCP 구분, XM=G09 → BDC3), key4.com(GODIAG BDC3/BCP 어댑터)</t>
-        </is>
-      </c>
-      <c r="P452" s="8" t="inlineStr">
-        <is>
-          <t>XM 전용 이모빌라이저 자료 없음 — G09 섀시 분류로 추정</t>
-        </is>
-      </c>
+          <t>keyecu.com(LX8FZV EWS ID44 HU92), locksmithkeyless.com(EWS 1998~ 2트랙)</t>
+        </is>
+      </c>
+      <c r="P452" s="11" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="11" t="inlineStr">
@@ -30229,22 +30531,22 @@
       </c>
       <c r="B453" s="11" t="inlineStr">
         <is>
-          <t>XM (G09)</t>
+          <t>Z4 (E85, 1세대)</t>
         </is>
       </c>
       <c r="C453" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D453" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E453" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="D453" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E453" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F453" s="3" t="inlineStr">
@@ -30252,40 +30554,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G453" s="8" t="inlineStr">
-        <is>
-          <t>ID49[BDC3 변형]</t>
+      <c r="G453" s="11" t="inlineStr">
+        <is>
+          <t>ID44(PCF7935)</t>
         </is>
       </c>
       <c r="H453" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I453" s="11" t="inlineStr"/>
       <c r="J453" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K453" s="11" t="inlineStr"/>
-      <c r="L453" s="11" t="n"/>
+      <c r="L453" s="11" t="inlineStr">
+        <is>
+          <t>FCC LX8FZV</t>
+        </is>
+      </c>
       <c r="M453" s="11" t="inlineStr"/>
-      <c r="N453" s="8" t="inlineStr">
-        <is>
-          <t>BDC3[G섀시 기준]</t>
+      <c r="N453" s="11" t="inlineStr">
+        <is>
+          <t>EWS3</t>
         </is>
       </c>
       <c r="O453" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(2023-2024 XM 포함 신형 스마트키 쉘), go-parts.com(딜러/전문가 등록 필수)</t>
-        </is>
-      </c>
-      <c r="P453" s="8" t="inlineStr">
-        <is>
-          <t>XM 전용 이모빌라이저 자료 없음 — G09 섀시 분류로 추정</t>
-        </is>
-      </c>
+          <t>amazon(Keyecu EWS 플립키 X5/Z3/Z4 2001-2005 HU92), amazon(Keymall EWS ID44 HU92 Z4)</t>
+        </is>
+      </c>
+      <c r="P453" s="11" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="11" t="inlineStr">
@@ -30295,22 +30597,22 @@
       </c>
       <c r="B454" s="11" t="inlineStr">
         <is>
-          <t>XM (G09)</t>
+          <t>Z4 (E85, 1세대)</t>
         </is>
       </c>
       <c r="C454" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D454" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E454" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="D454" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E454" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F454" s="3" t="inlineStr">
@@ -30318,40 +30620,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G454" s="8" t="inlineStr">
-        <is>
-          <t>ID49[BDC3 변형]</t>
+      <c r="G454" s="11" t="inlineStr">
+        <is>
+          <t>ID44(PCF7935)</t>
         </is>
       </c>
       <c r="H454" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I454" s="11" t="inlineStr"/>
       <c r="J454" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K454" s="11" t="inlineStr"/>
-      <c r="L454" s="11" t="n"/>
+      <c r="L454" s="11" t="inlineStr">
+        <is>
+          <t>FCC LX8FZV</t>
+        </is>
+      </c>
       <c r="M454" s="11" t="inlineStr"/>
-      <c r="N454" s="8" t="inlineStr">
-        <is>
-          <t>BDC3[G섀시 기준]</t>
+      <c r="N454" s="11" t="inlineStr">
+        <is>
+          <t>EWS3</t>
         </is>
       </c>
       <c r="O454" s="11" t="inlineStr">
         <is>
-          <t>programyourremote.com(2025 XM 스마트키 등록 안내)</t>
-        </is>
-      </c>
-      <c r="P454" s="8" t="inlineStr">
-        <is>
-          <t>XM 전용 이모빌라이저 자료 없음 — G09 섀시 분류로 추정</t>
-        </is>
-      </c>
+          <t>accessfobs.co.uk(EWS 3버튼 Z4), yourcarkeyguys.com(2000-2009 HU92 PCF7935 ID44)</t>
+        </is>
+      </c>
+      <c r="P454" s="11" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="11" t="inlineStr">
@@ -30361,51 +30663,63 @@
       </c>
       <c r="B455" s="11" t="inlineStr">
         <is>
-          <t>XM (G09)</t>
+          <t>Z4 (E85, 1세대)</t>
         </is>
       </c>
       <c r="C455" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D455" s="6" t="inlineStr"/>
-      <c r="E455" s="6" t="inlineStr"/>
-      <c r="F455" s="6" t="inlineStr"/>
-      <c r="G455" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D455" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E455" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F455" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G455" s="11" t="inlineStr">
+        <is>
+          <t>ID44(PCF7935)</t>
         </is>
       </c>
       <c r="H455" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I455" s="11" t="inlineStr"/>
       <c r="J455" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K455" s="11" t="inlineStr"/>
-      <c r="L455" s="11" t="inlineStr"/>
+      <c r="L455" s="11" t="inlineStr">
+        <is>
+          <t>FCC LX8FZV</t>
+        </is>
+      </c>
       <c r="M455" s="11" t="inlineStr"/>
-      <c r="N455" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="N455" s="11" t="inlineStr">
+        <is>
+          <t>EWS3D[엔진별], EWS4.3[엔진별]</t>
         </is>
       </c>
       <c r="O455" s="11" t="inlineStr">
         <is>
-          <t>2026 XM 전용 자료 없음</t>
-        </is>
-      </c>
-      <c r="P455" s="7" t="inlineStr">
-        <is>
-          <t>XM 전용 이모빌라이저 자료 없음 — G09 섀시 분류로 추정 / 2026년식 자료 없음</t>
-        </is>
-      </c>
+          <t>precisionecu.com(2002-2008 E85/E86 EWS3/EWS3D/EWS4.3), bimmerfest.com(EWS 4.3 AK90 키 등록)</t>
+        </is>
+      </c>
+      <c r="P455" s="11" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="11" t="inlineStr">
@@ -30420,7 +30734,7 @@
       </c>
       <c r="C456" s="11" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
@@ -30455,16 +30769,20 @@
         </is>
       </c>
       <c r="K456" s="11" t="inlineStr"/>
-      <c r="L456" s="11" t="inlineStr"/>
+      <c r="L456" s="11" t="inlineStr">
+        <is>
+          <t>FCC LX8FZV</t>
+        </is>
+      </c>
       <c r="M456" s="11" t="inlineStr"/>
       <c r="N456" s="11" t="inlineStr">
         <is>
-          <t>EWS3</t>
+          <t>EWS3D[엔진별], EWS4.3[엔진별]</t>
         </is>
       </c>
       <c r="O456" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(LX8FZV EWS ID44 HU92), locksmithkeyless.com(EWS 1998~ 2트랙)</t>
+          <t>dudmd.com(Z4 E85/E86 3.0i N52 MSV70 EWS), rpmmotorsport.net(E85/E86 키세트)</t>
         </is>
       </c>
       <c r="P456" s="11" t="inlineStr"/>
@@ -30482,7 +30800,7 @@
       </c>
       <c r="C457" s="11" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D457" s="3" t="inlineStr">
@@ -30525,12 +30843,12 @@
       <c r="M457" s="11" t="inlineStr"/>
       <c r="N457" s="11" t="inlineStr">
         <is>
-          <t>EWS3</t>
+          <t>EWS3D[엔진별], EWS4.3[엔진별]</t>
         </is>
       </c>
       <c r="O457" s="11" t="inlineStr">
         <is>
-          <t>amazon(Keyecu EWS 플립키 X5/Z3/Z4 2001-2005 HU92), amazon(Keymall EWS ID44 HU92 Z4)</t>
+          <t>precisionecu.com(2002-2008 E85/E86 EWS3/EWS3D/EWS4.3), walmart(HQRP E85/E86 2003-2009 송신기)</t>
         </is>
       </c>
       <c r="P457" s="11" t="inlineStr"/>
@@ -30548,7 +30866,7 @@
       </c>
       <c r="C458" s="11" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2009(단종)</t>
         </is>
       </c>
       <c r="D458" s="3" t="inlineStr">
@@ -30591,12 +30909,12 @@
       <c r="M458" s="11" t="inlineStr"/>
       <c r="N458" s="11" t="inlineStr">
         <is>
-          <t>EWS3</t>
+          <t>EWS4.3</t>
         </is>
       </c>
       <c r="O458" s="11" t="inlineStr">
         <is>
-          <t>accessfobs.co.uk(EWS 3버튼 Z4), yourcarkeyguys.com(2000-2009 HU92 PCF7935 ID44)</t>
+          <t>hqrp.com(E85/E86 2003-2009 송신기), z4-forum.com(교체 키)</t>
         </is>
       </c>
       <c r="P458" s="11" t="inlineStr"/>
@@ -30609,12 +30927,12 @@
       </c>
       <c r="B459" s="11" t="inlineStr">
         <is>
-          <t>Z4 (E85, 1세대)</t>
+          <t>Z4 (E89, 2세대)</t>
         </is>
       </c>
       <c r="C459" s="11" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D459" s="3" t="inlineStr">
@@ -30634,35 +30952,31 @@
       </c>
       <c r="G459" s="11" t="inlineStr">
         <is>
-          <t>ID44(PCF7935)</t>
+          <t>ID46(PCF7945)</t>
         </is>
       </c>
       <c r="H459" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I459" s="11" t="inlineStr"/>
       <c r="J459" s="11" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K459" s="11" t="inlineStr"/>
-      <c r="L459" s="11" t="inlineStr">
-        <is>
-          <t>FCC LX8FZV</t>
-        </is>
-      </c>
+      <c r="L459" s="11" t="inlineStr"/>
       <c r="M459" s="11" t="inlineStr"/>
       <c r="N459" s="11" t="inlineStr">
         <is>
-          <t>EWS3D[엔진별], EWS4.3[엔진별]</t>
+          <t>CAS3+</t>
         </is>
       </c>
       <c r="O459" s="11" t="inlineStr">
         <is>
-          <t>precisionecu.com(2002-2008 E85/E86 EWS3/EWS3D/EWS4.3), bimmerfest.com(EWS 4.3 AK90 키 등록)</t>
+          <t>ebay(PCF7945 CAS3 키: 2009-2013 Z4 E89), rpmmotorsport.net(E89 2009-2016 키세트)</t>
         </is>
       </c>
       <c r="P459" s="11" t="inlineStr"/>
@@ -30675,12 +30989,12 @@
       </c>
       <c r="B460" s="11" t="inlineStr">
         <is>
-          <t>Z4 (E85, 1세대)</t>
+          <t>Z4 (E89, 2세대)</t>
         </is>
       </c>
       <c r="C460" s="11" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
@@ -30700,35 +31014,35 @@
       </c>
       <c r="G460" s="11" t="inlineStr">
         <is>
-          <t>ID44(PCF7935)</t>
+          <t>ID46(PCF7945)</t>
         </is>
       </c>
       <c r="H460" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I460" s="11" t="inlineStr"/>
       <c r="J460" s="11" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K460" s="11" t="inlineStr"/>
       <c r="L460" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M460" s="11" t="inlineStr"/>
       <c r="N460" s="11" t="inlineStr">
         <is>
-          <t>EWS3D[엔진별], EWS4.3[엔진별]</t>
+          <t>CAS3+</t>
         </is>
       </c>
       <c r="O460" s="11" t="inlineStr">
         <is>
-          <t>dudmd.com(Z4 E85/E86 3.0i N52 MSV70 EWS), rpmmotorsport.net(E85/E86 키세트)</t>
+          <t>precisionecu.com(2009-2016 E89 리모컨키), keyecu.com(CAS3 Z4 ID46 PCF7945)</t>
         </is>
       </c>
       <c r="P460" s="11" t="inlineStr"/>
@@ -30741,12 +31055,12 @@
       </c>
       <c r="B461" s="11" t="inlineStr">
         <is>
-          <t>Z4 (E85, 1세대)</t>
+          <t>Z4 (E89, 2세대)</t>
         </is>
       </c>
       <c r="C461" s="11" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D461" s="3" t="inlineStr">
@@ -30766,35 +31080,35 @@
       </c>
       <c r="G461" s="11" t="inlineStr">
         <is>
-          <t>ID44(PCF7935)</t>
+          <t>ID46(PCF7945)</t>
         </is>
       </c>
       <c r="H461" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I461" s="11" t="inlineStr"/>
       <c r="J461" s="11" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K461" s="11" t="inlineStr"/>
       <c r="L461" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M461" s="11" t="inlineStr"/>
       <c r="N461" s="11" t="inlineStr">
         <is>
-          <t>EWS3D[엔진별], EWS4.3[엔진별]</t>
+          <t>CAS3+</t>
         </is>
       </c>
       <c r="O461" s="11" t="inlineStr">
         <is>
-          <t>precisionecu.com(2002-2008 E85/E86 EWS3/EWS3D/EWS4.3), walmart(HQRP E85/E86 2003-2009 송신기)</t>
+          <t>hivekeys.com(CAS3 PCF7945A/7953A), clechrono.com(ID7945 공키 Z4)</t>
         </is>
       </c>
       <c r="P461" s="11" t="inlineStr"/>
@@ -30807,12 +31121,12 @@
       </c>
       <c r="B462" s="11" t="inlineStr">
         <is>
-          <t>Z4 (E85, 1세대)</t>
+          <t>Z4 (E89, 2세대)</t>
         </is>
       </c>
       <c r="C462" s="11" t="inlineStr">
         <is>
-          <t>2009(단종)</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
@@ -30832,35 +31146,35 @@
       </c>
       <c r="G462" s="11" t="inlineStr">
         <is>
-          <t>ID44(PCF7935)</t>
+          <t>ID46(PCF7945)</t>
         </is>
       </c>
       <c r="H462" s="11" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I462" s="11" t="inlineStr"/>
       <c r="J462" s="11" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K462" s="11" t="inlineStr"/>
       <c r="L462" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC KR55WK49147[컴포트액세스], FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M462" s="11" t="inlineStr"/>
       <c r="N462" s="11" t="inlineStr">
         <is>
-          <t>EWS4.3</t>
+          <t>CAS3+</t>
         </is>
       </c>
       <c r="O462" s="11" t="inlineStr">
         <is>
-          <t>hqrp.com(E85/E86 2003-2009 송신기), z4-forum.com(교체 키)</t>
+          <t>reidsremotes.com.au(X1 E84·Z4 E89 컴포트액세스 CAS3), go-parts.com(2009-2016 Z4 E89 CAS3+)</t>
         </is>
       </c>
       <c r="P462" s="11" t="inlineStr"/>
@@ -30878,7 +31192,7 @@
       </c>
       <c r="C463" s="11" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D463" s="3" t="inlineStr">
@@ -30913,7 +31227,11 @@
         </is>
       </c>
       <c r="K463" s="11" t="inlineStr"/>
-      <c r="L463" s="11" t="inlineStr"/>
+      <c r="L463" s="11" t="inlineStr">
+        <is>
+          <t>FCC KR55WK49147, FCC KR55WK49127</t>
+        </is>
+      </c>
       <c r="M463" s="11" t="inlineStr"/>
       <c r="N463" s="11" t="inlineStr">
         <is>
@@ -30922,7 +31240,7 @@
       </c>
       <c r="O463" s="11" t="inlineStr">
         <is>
-          <t>ebay(PCF7945 CAS3 키: 2009-2013 Z4 E89), rpmmotorsport.net(E89 2009-2016 키세트)</t>
+          <t>z4-forum.com(E89 컴포트액세스), keylibrary.co.uk(CAS3 컴포트액세스 3버튼)</t>
         </is>
       </c>
       <c r="P463" s="11" t="inlineStr"/>
@@ -30940,7 +31258,7 @@
       </c>
       <c r="C464" s="11" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D464" s="3" t="inlineStr">
@@ -30977,7 +31295,7 @@
       <c r="K464" s="11" t="inlineStr"/>
       <c r="L464" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127</t>
+          <t>FCC KR55WK49147, FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M464" s="11" t="inlineStr"/>
@@ -30988,7 +31306,7 @@
       </c>
       <c r="O464" s="11" t="inlineStr">
         <is>
-          <t>precisionecu.com(2009-2016 E89 리모컨키), keyecu.com(CAS3 Z4 ID46 PCF7945)</t>
+          <t>justanswer.com(2014 Z4 E89 컴포트액세스 키 교체), codemyeuro.com(CAS2/3 컴포트 스페어키)</t>
         </is>
       </c>
       <c r="P464" s="11" t="inlineStr"/>
@@ -31006,7 +31324,7 @@
       </c>
       <c r="C465" s="11" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D465" s="3" t="inlineStr">
@@ -31043,7 +31361,7 @@
       <c r="K465" s="11" t="inlineStr"/>
       <c r="L465" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127</t>
+          <t>5WK49145, 5WK49146, 5WK49147, FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M465" s="11" t="inlineStr"/>
@@ -31054,7 +31372,7 @@
       </c>
       <c r="O465" s="11" t="inlineStr">
         <is>
-          <t>hivekeys.com(CAS3 PCF7945A/7953A), clechrono.com(ID7945 공키 Z4)</t>
+          <t>precisionecu.com(2009-2016 E89 CAS3), rpmmotorsport.net(E89 28i~35is 2009-2016 키세트)</t>
         </is>
       </c>
       <c r="P465" s="11" t="inlineStr"/>
@@ -31072,7 +31390,7 @@
       </c>
       <c r="C466" s="11" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
@@ -31109,7 +31427,7 @@
       <c r="K466" s="11" t="inlineStr"/>
       <c r="L466" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147[컴포트액세스], FCC KR55WK49127</t>
+          <t>5WK49145, 5WK49146, 5WK49147, FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M466" s="11" t="inlineStr"/>
@@ -31120,7 +31438,7 @@
       </c>
       <c r="O466" s="11" t="inlineStr">
         <is>
-          <t>reidsremotes.com.au(X1 E84·Z4 E89 컴포트액세스 CAS3), go-parts.com(2009-2016 Z4 E89 CAS3+)</t>
+          <t>boostmonkey.com(E섀시 CAS3 키 등록: Z4 E89 01/2008-08/2016)</t>
         </is>
       </c>
       <c r="P466" s="11" t="inlineStr"/>
@@ -31138,25 +31456,25 @@
       </c>
       <c r="C467" s="11" t="inlineStr">
         <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D467" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E467" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F467" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G467" s="11" t="inlineStr">
+          <t>2017(단종)</t>
+        </is>
+      </c>
+      <c r="D467" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E467" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F467" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G467" s="17" t="inlineStr">
         <is>
           <t>ID46(PCF7945)</t>
         </is>
@@ -31175,21 +31493,21 @@
       <c r="K467" s="11" t="inlineStr"/>
       <c r="L467" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147, FCC KR55WK49127</t>
+          <t>5WK49145, 5WK49146, 5WK49147, FCC KR55WK49127</t>
         </is>
       </c>
       <c r="M467" s="11" t="inlineStr"/>
-      <c r="N467" s="11" t="inlineStr">
+      <c r="N467" s="17" t="inlineStr">
         <is>
           <t>CAS3+</t>
         </is>
       </c>
       <c r="O467" s="11" t="inlineStr">
         <is>
-          <t>z4-forum.com(E89 컴포트액세스), keylibrary.co.uk(CAS3 컴포트액세스 3버튼)</t>
-        </is>
-      </c>
-      <c r="P467" s="11" t="inlineStr"/>
+          <t>boostmonkey.com(E89 생산 01/2008-08/2016), wikipedia(G29가 2019년식부터 후속)</t>
+        </is>
+      </c>
+      <c r="P467" s="17" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="11" t="inlineStr">
@@ -31199,22 +31517,22 @@
       </c>
       <c r="B468" s="11" t="inlineStr">
         <is>
-          <t>Z4 (E89, 2세대)</t>
+          <t>Z4 (G29, 3세대)</t>
         </is>
       </c>
       <c r="C468" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D468" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E468" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D468" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E468" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F468" s="3" t="inlineStr">
@@ -31224,7 +31542,7 @@
       </c>
       <c r="G468" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H468" s="11" t="inlineStr">
@@ -31235,24 +31553,24 @@
       <c r="I468" s="11" t="inlineStr"/>
       <c r="J468" s="11" t="inlineStr">
         <is>
-          <t>HU92[세대 기준]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K468" s="11" t="inlineStr"/>
       <c r="L468" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147, FCC KR55WK49127</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M468" s="11" t="inlineStr"/>
       <c r="N468" s="11" t="inlineStr">
         <is>
-          <t>CAS3+</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O468" s="11" t="inlineStr">
         <is>
-          <t>justanswer.com(2014 Z4 E89 컴포트액세스 키 교체), codemyeuro.com(CAS2/3 컴포트 스페어키)</t>
+          <t>keyecu.com(BDM G20/G30/G32/G11/G15/G29 2015-2019 N5F-ID21A/ID21B/ID21C), ecutool.com(BDM N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P468" s="11" t="inlineStr"/>
@@ -31265,22 +31583,22 @@
       </c>
       <c r="B469" s="11" t="inlineStr">
         <is>
-          <t>Z4 (E89, 2세대)</t>
+          <t>Z4 (G29, 3세대)</t>
         </is>
       </c>
       <c r="C469" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="D469" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E469" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D469" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E469" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F469" s="3" t="inlineStr">
@@ -31290,7 +31608,7 @@
       </c>
       <c r="G469" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H469" s="11" t="inlineStr">
@@ -31301,24 +31619,24 @@
       <c r="I469" s="11" t="inlineStr"/>
       <c r="J469" s="11" t="inlineStr">
         <is>
-          <t>HU92[세대 기준]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K469" s="11" t="inlineStr"/>
       <c r="L469" s="11" t="inlineStr">
         <is>
-          <t>5WK49145, 5WK49146, 5WK49147, FCC KR55WK49127</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M469" s="11" t="inlineStr"/>
       <c r="N469" s="11" t="inlineStr">
         <is>
-          <t>CAS3+</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O469" s="11" t="inlineStr">
         <is>
-          <t>precisionecu.com(2009-2016 E89 CAS3), rpmmotorsport.net(E89 28i~35is 2009-2016 키세트)</t>
+          <t>linkobd.com(N5F-ID21A BDM G29), uhs-hardware.com(BDC2 N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P469" s="11" t="inlineStr"/>
@@ -31331,22 +31649,22 @@
       </c>
       <c r="B470" s="11" t="inlineStr">
         <is>
-          <t>Z4 (E89, 2세대)</t>
+          <t>Z4 (G29, 3세대)</t>
         </is>
       </c>
       <c r="C470" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="D470" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E470" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D470" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E470" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F470" s="3" t="inlineStr">
@@ -31356,35 +31674,35 @@
       </c>
       <c r="G470" s="11" t="inlineStr">
         <is>
-          <t>ID46(PCF7945)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H470" s="11" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>스마트키,카드키</t>
         </is>
       </c>
       <c r="I470" s="11" t="inlineStr"/>
       <c r="J470" s="11" t="inlineStr">
         <is>
-          <t>HU92[세대 기준]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K470" s="11" t="inlineStr"/>
       <c r="L470" s="11" t="inlineStr">
         <is>
-          <t>5WK49145, 5WK49146, 5WK49147, FCC KR55WK49127</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M470" s="11" t="inlineStr"/>
       <c r="N470" s="11" t="inlineStr">
         <is>
-          <t>CAS3+</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O470" s="11" t="inlineStr">
         <is>
-          <t>boostmonkey.com(E섀시 CAS3 키 등록: Z4 E89 01/2008-08/2016)</t>
+          <t>g29.bimmerpost.com(G29 키카드·컴포트액세스), go-parts.com(G시리즈 BDC), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P470" s="11" t="inlineStr"/>
@@ -31397,20 +31715,32 @@
       </c>
       <c r="B471" s="11" t="inlineStr">
         <is>
-          <t>Z4 (E89, 2세대)</t>
+          <t>Z4 (G29, 3세대)</t>
         </is>
       </c>
       <c r="C471" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D471" s="6" t="inlineStr"/>
-      <c r="E471" s="6" t="inlineStr"/>
-      <c r="F471" s="6" t="inlineStr"/>
-      <c r="G471" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D471" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E471" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F471" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G471" s="11" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H471" s="11" t="inlineStr">
@@ -31419,25 +31749,29 @@
         </is>
       </c>
       <c r="I471" s="11" t="inlineStr"/>
-      <c r="J471" s="11" t="inlineStr"/>
+      <c r="J471" s="11" t="inlineStr">
+        <is>
+          <t>HU100R[세대 기준]</t>
+        </is>
+      </c>
       <c r="K471" s="11" t="inlineStr"/>
-      <c r="L471" s="11" t="inlineStr"/>
+      <c r="L471" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1, 5A06C06, 5A55D03-04</t>
+        </is>
+      </c>
       <c r="M471" s="11" t="inlineStr"/>
-      <c r="N471" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="N471" s="11" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O471" s="11" t="inlineStr">
         <is>
-          <t>boostmonkey.com(E89 생산 01/2008-08/2016), wikipedia(G29가 2019년식부터 후속)</t>
-        </is>
-      </c>
-      <c r="P471" s="7" t="inlineStr">
-        <is>
-          <t>E89 생산 2016.8 종료 — 국내 해당 연식 존재 여부 확인 불가</t>
-        </is>
-      </c>
+          <t>go-parts.com(2022-2025 Z4 IYZBK1, OEM 5A06C06·5A55D03-04·8708351·9367401-01), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="P471" s="11" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="11" t="inlineStr">
@@ -31447,20 +31781,32 @@
       </c>
       <c r="B472" s="11" t="inlineStr">
         <is>
-          <t>Z4 (E89, 2세대)</t>
+          <t>Z4 (G29, 3세대)</t>
         </is>
       </c>
       <c r="C472" s="11" t="inlineStr">
         <is>
-          <t>2018(단종)</t>
-        </is>
-      </c>
-      <c r="D472" s="6" t="inlineStr"/>
-      <c r="E472" s="6" t="inlineStr"/>
-      <c r="F472" s="6" t="inlineStr"/>
-      <c r="G472" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D472" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E472" s="5" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F472" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G472" s="11" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H472" s="11" t="inlineStr">
@@ -31469,25 +31815,29 @@
         </is>
       </c>
       <c r="I472" s="11" t="inlineStr"/>
-      <c r="J472" s="11" t="inlineStr"/>
+      <c r="J472" s="11" t="inlineStr">
+        <is>
+          <t>HU100R[세대 기준]</t>
+        </is>
+      </c>
       <c r="K472" s="11" t="inlineStr"/>
-      <c r="L472" s="11" t="inlineStr"/>
+      <c r="L472" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M472" s="11" t="inlineStr"/>
-      <c r="N472" s="7" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
+      <c r="N472" s="11" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O472" s="11" t="inlineStr">
         <is>
-          <t>boostmonkey.com(E89 생산 01/2008-08/2016), wikipedia(G29가 2019년식부터 후속)</t>
-        </is>
-      </c>
-      <c r="P472" s="7" t="inlineStr">
-        <is>
-          <t>E89 생산 2016.8 종료 — 국내 해당 연식 존재 여부 확인 불가</t>
-        </is>
-      </c>
+          <t>go-parts.com(2022-2025 Z4 IYZBK1), ebay(IYZBK1 2022-2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+        </is>
+      </c>
+      <c r="P472" s="11" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="11" t="inlineStr">
@@ -31502,7 +31852,7 @@
       </c>
       <c r="C473" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D473" s="4" t="inlineStr">
@@ -31539,7 +31889,7 @@
       <c r="K473" s="11" t="inlineStr"/>
       <c r="L473" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M473" s="11" t="inlineStr"/>
@@ -31550,7 +31900,7 @@
       </c>
       <c r="O473" s="11" t="inlineStr">
         <is>
-          <t>keyecu.com(BDM G20/G30/G32/G11/G15/G29 2015-2019 N5F-ID21A/ID21B/ID21C), ecutool.com(BDM N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>obdexpress.co.uk(G섀시 BDC3 키추가: KD-X4·Autel), autotecknic.com(G29 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P473" s="11" t="inlineStr"/>
@@ -31568,7 +31918,7 @@
       </c>
       <c r="C474" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D474" s="4" t="inlineStr">
@@ -31605,7 +31955,7 @@
       <c r="K474" s="11" t="inlineStr"/>
       <c r="L474" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M474" s="11" t="inlineStr"/>
@@ -31616,7 +31966,7 @@
       </c>
       <c r="O474" s="11" t="inlineStr">
         <is>
-          <t>linkobd.com(N5F-ID21A BDM G29), uhs-hardware.com(BDC2 N5F-ID21A), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>go-parts.com(2016-2025 G시리즈 키), g29.bimmerpost.com(키로 컨버터블 작동), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P474" s="11" t="inlineStr"/>
@@ -31634,7 +31984,7 @@
       </c>
       <c r="C475" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D475" s="4" t="inlineStr">
@@ -31659,7 +32009,7 @@
       </c>
       <c r="H475" s="11" t="inlineStr">
         <is>
-          <t>스마트키,카드키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I475" s="11" t="inlineStr"/>
@@ -31671,7 +32021,7 @@
       <c r="K475" s="11" t="inlineStr"/>
       <c r="L475" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC IYZBK1, IKEYBW004AL[애프터마켓]</t>
         </is>
       </c>
       <c r="M475" s="11" t="inlineStr"/>
@@ -31682,7 +32032,7 @@
       </c>
       <c r="O475" s="11" t="inlineStr">
         <is>
-          <t>g29.bimmerpost.com(G29 키카드·컴포트액세스), go-parts.com(G시리즈 BDC), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>aol.com(2026 Z4 파이널 에디션 — Z4 단종), ebay(IYZBK1 2022-2026), amazon(Autel IKEYBW004AL 2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P475" s="11" t="inlineStr"/>
@@ -31695,12 +32045,12 @@
       </c>
       <c r="B476" s="11" t="inlineStr">
         <is>
-          <t>Z4 (G29, 3세대)</t>
+          <t>i3 (I01)</t>
         </is>
       </c>
       <c r="C476" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D476" s="4" t="inlineStr">
@@ -31737,18 +32087,18 @@
       <c r="K476" s="11" t="inlineStr"/>
       <c r="L476" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1, 5A06C06, 5A55D03-04</t>
+          <t>FCC NBGIDGNG1, 9317163-02, 9317161-02</t>
         </is>
       </c>
       <c r="M476" s="11" t="inlineStr"/>
       <c r="N476" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O476" s="11" t="inlineStr">
         <is>
-          <t>go-parts.com(2022-2025 Z4 IYZBK1, OEM 5A06C06·5A55D03-04·8708351·9367401-01), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>abkeys.com(i3/i8 2015+ 9317163-02·9317161-02 FEM/BDC), amazon(i3/i8 2014-2020 NBGIDGNG1 434MHz), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P476" s="11" t="inlineStr"/>
@@ -31761,12 +32111,12 @@
       </c>
       <c r="B477" s="11" t="inlineStr">
         <is>
-          <t>Z4 (G29, 3세대)</t>
+          <t>i3 (I01)</t>
         </is>
       </c>
       <c r="C477" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D477" s="4" t="inlineStr">
@@ -31803,18 +32153,18 @@
       <c r="K477" s="11" t="inlineStr"/>
       <c r="L477" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>9362177-02, 2013DJ5983, 9317163-02, FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M477" s="11" t="inlineStr"/>
       <c r="N477" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O477" s="11" t="inlineStr">
         <is>
-          <t>go-parts.com(2022-2025 Z4 IYZBK1), ebay(IYZBK1 2022-2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>mykeysupply.com(2015-2018 i3/i8 OEM 4버튼 2013DJ5983 BMW 9362177-02, 비상 인서트키 포함), locksmithkeyless.com(2015-2017 i3/i8 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P477" s="11" t="inlineStr"/>
@@ -31827,12 +32177,12 @@
       </c>
       <c r="B478" s="11" t="inlineStr">
         <is>
-          <t>Z4 (G29, 3세대)</t>
+          <t>i3 (I01)</t>
         </is>
       </c>
       <c r="C478" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D478" s="4" t="inlineStr">
@@ -31863,24 +32213,24 @@
       <c r="I478" s="11" t="inlineStr"/>
       <c r="J478" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K478" s="11" t="inlineStr"/>
       <c r="L478" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>2013DJ5983, FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M478" s="11" t="inlineStr"/>
       <c r="N478" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O478" s="11" t="inlineStr">
         <is>
-          <t>obdexpress.co.uk(G섀시 BDC3 키추가: KD-X4·Autel), autotecknic.com(G29 키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>keyshop-online.com(2013-2017 i3/i8 BDC 2013DJ5983 HU100R), yourcarkeyguys.com(2015-2017 i3 4버튼 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P478" s="11" t="inlineStr"/>
@@ -31893,12 +32243,12 @@
       </c>
       <c r="B479" s="11" t="inlineStr">
         <is>
-          <t>Z4 (G29, 3세대)</t>
+          <t>i3 (I01)</t>
         </is>
       </c>
       <c r="C479" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D479" s="4" t="inlineStr">
@@ -31929,24 +32279,24 @@
       <c r="I479" s="11" t="inlineStr"/>
       <c r="J479" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU100R</t>
         </is>
       </c>
       <c r="K479" s="11" t="inlineStr"/>
       <c r="L479" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>2013DJ5983, FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M479" s="11" t="inlineStr"/>
       <c r="N479" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O479" s="11" t="inlineStr">
         <is>
-          <t>go-parts.com(2016-2025 G시리즈 키), g29.bimmerpost.com(키로 컨버터블 작동), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>programyourremote.com(2017 i3 키등록), keyshop-online.com(2013-2017 i3 BDC), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P479" s="11" t="inlineStr"/>
@@ -31959,12 +32309,12 @@
       </c>
       <c r="B480" s="11" t="inlineStr">
         <is>
-          <t>Z4 (G29, 3세대)</t>
+          <t>i3 (I01)</t>
         </is>
       </c>
       <c r="C480" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D480" s="4" t="inlineStr">
@@ -32001,18 +32351,18 @@
       <c r="K480" s="11" t="inlineStr"/>
       <c r="L480" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1, IKEYBW004AL[애프터마켓]</t>
+          <t>9362177-02, 2013DJ5983</t>
         </is>
       </c>
       <c r="M480" s="11" t="inlineStr"/>
       <c r="N480" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BDC</t>
         </is>
       </c>
       <c r="O480" s="11" t="inlineStr">
         <is>
-          <t>aol.com(2026 Z4 파이널 에디션 — Z4 단종), ebay(IYZBK1 2022-2026), amazon(Autel IKEYBW004AL 2026), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>mykeysupply.com(2015-2018 i3/i8 OEM), fixautosmart.com(i3 2013-2020 키 교체), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P480" s="11" t="inlineStr"/>
@@ -32030,7 +32380,7 @@
       </c>
       <c r="C481" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D481" s="4" t="inlineStr">
@@ -32067,7 +32417,7 @@
       <c r="K481" s="11" t="inlineStr"/>
       <c r="L481" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1, 9317163-02, 9317161-02</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M481" s="11" t="inlineStr"/>
@@ -32078,7 +32428,7 @@
       </c>
       <c r="O481" s="11" t="inlineStr">
         <is>
-          <t>abkeys.com(i3/i8 2015+ 9317163-02·9317161-02 FEM/BDC), amazon(i3/i8 2014-2020 NBGIDGNG1 434MHz), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>mybmwi3.com(i3 백업 키), amazon(i3/i8 2014-2020 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P481" s="11" t="inlineStr"/>
@@ -32096,7 +32446,7 @@
       </c>
       <c r="C482" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D482" s="4" t="inlineStr">
@@ -32133,7 +32483,7 @@
       <c r="K482" s="11" t="inlineStr"/>
       <c r="L482" s="11" t="inlineStr">
         <is>
-          <t>9362177-02, 2013DJ5983, 9317163-02, FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M482" s="11" t="inlineStr"/>
@@ -32144,7 +32494,7 @@
       </c>
       <c r="O482" s="11" t="inlineStr">
         <is>
-          <t>mykeysupply.com(2015-2018 i3/i8 OEM 4버튼 2013DJ5983 BMW 9362177-02, 비상 인서트키 포함), locksmithkeyless.com(2015-2017 i3/i8 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>amazon(i3/i8 2014-2020 NBGIDGNG1), fixautosmart.com(i3 2013-2020), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P482" s="11" t="inlineStr"/>
@@ -32162,7 +32512,7 @@
       </c>
       <c r="C483" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2021(단종)</t>
         </is>
       </c>
       <c r="D483" s="4" t="inlineStr">
@@ -32193,13 +32543,13 @@
       <c r="I483" s="11" t="inlineStr"/>
       <c r="J483" s="11" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K483" s="11" t="inlineStr"/>
       <c r="L483" s="11" t="inlineStr">
         <is>
-          <t>2013DJ5983, FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M483" s="11" t="inlineStr"/>
@@ -32210,7 +32560,7 @@
       </c>
       <c r="O483" s="11" t="inlineStr">
         <is>
-          <t>keyshop-online.com(2013-2017 i3/i8 BDC 2013DJ5983 HU100R), yourcarkeyguys.com(2015-2017 i3 4버튼 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>diamondkeysupply.com(i8/i3 315MHz 프록시미티), ebay(2014-2021 i3 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P483" s="11" t="inlineStr"/>
@@ -32223,12 +32573,12 @@
       </c>
       <c r="B484" s="11" t="inlineStr">
         <is>
-          <t>i3 (I01)</t>
+          <t>i8 (I12/I15)</t>
         </is>
       </c>
       <c r="C484" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D484" s="4" t="inlineStr">
@@ -32259,13 +32609,13 @@
       <c r="I484" s="11" t="inlineStr"/>
       <c r="J484" s="11" t="inlineStr">
         <is>
-          <t>HU100R</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K484" s="11" t="inlineStr"/>
       <c r="L484" s="11" t="inlineStr">
         <is>
-          <t>2013DJ5983, FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1[추정]</t>
         </is>
       </c>
       <c r="M484" s="11" t="inlineStr"/>
@@ -32276,7 +32626,7 @@
       </c>
       <c r="O484" s="11" t="inlineStr">
         <is>
-          <t>programyourremote.com(2017 i3 키등록), keyshop-online.com(2013-2017 i3 BDC), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>yourcarkeyguys.com(2015-2017 i8 NBGIDGNG1), abkeys.com(i3/i8 2015+ 9317161-02), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P484" s="11" t="inlineStr"/>
@@ -32289,12 +32639,12 @@
       </c>
       <c r="B485" s="11" t="inlineStr">
         <is>
-          <t>i3 (I01)</t>
+          <t>i8 (I12/I15)</t>
         </is>
       </c>
       <c r="C485" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D485" s="4" t="inlineStr">
@@ -32331,7 +32681,7 @@
       <c r="K485" s="11" t="inlineStr"/>
       <c r="L485" s="11" t="inlineStr">
         <is>
-          <t>9362177-02, 2013DJ5983</t>
+          <t>FCC NBGIDGNG1, 9317161-02</t>
         </is>
       </c>
       <c r="M485" s="11" t="inlineStr"/>
@@ -32342,7 +32692,7 @@
       </c>
       <c r="O485" s="11" t="inlineStr">
         <is>
-          <t>mykeysupply.com(2015-2018 i3/i8 OEM), fixautosmart.com(i3 2013-2020 키 교체), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>locksmithkeyless.com(2015-2017 i3/i8 NBGIDGNG1 CAS4+/FEM), yourcarkeyguys.com(i8 I12 4버튼), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P485" s="11" t="inlineStr"/>
@@ -32355,12 +32705,12 @@
       </c>
       <c r="B486" s="11" t="inlineStr">
         <is>
-          <t>i3 (I01)</t>
+          <t>i8 (I12/I15)</t>
         </is>
       </c>
       <c r="C486" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D486" s="4" t="inlineStr">
@@ -32397,7 +32747,7 @@
       <c r="K486" s="11" t="inlineStr"/>
       <c r="L486" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 9362177-02, 2013DJ5983</t>
         </is>
       </c>
       <c r="M486" s="11" t="inlineStr"/>
@@ -32408,7 +32758,7 @@
       </c>
       <c r="O486" s="11" t="inlineStr">
         <is>
-          <t>mybmwi3.com(i3 백업 키), amazon(i3/i8 2014-2020 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>mykeysupply.com(2015-2018 i3/i8 OEM), ebay(i8 순정 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P486" s="11" t="inlineStr"/>
@@ -32421,12 +32771,12 @@
       </c>
       <c r="B487" s="11" t="inlineStr">
         <is>
-          <t>i3 (I01)</t>
+          <t>i8 (I12/I15)</t>
         </is>
       </c>
       <c r="C487" s="11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D487" s="4" t="inlineStr">
@@ -32474,7 +32824,7 @@
       </c>
       <c r="O487" s="11" t="inlineStr">
         <is>
-          <t>amazon(i3/i8 2014-2020 NBGIDGNG1), fixautosmart.com(i3 2013-2020), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>diamondkeysupply.com(i8/i3 315MHz 프록시미티), locksmithkeyless.com, 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P487" s="11" t="inlineStr"/>
@@ -32487,12 +32837,12 @@
       </c>
       <c r="B488" s="11" t="inlineStr">
         <is>
-          <t>i3 (I01)</t>
+          <t>i8 (I12/I15)</t>
         </is>
       </c>
       <c r="C488" s="11" t="inlineStr">
         <is>
-          <t>2021(단종)</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D488" s="4" t="inlineStr">
@@ -32529,7 +32879,7 @@
       <c r="K488" s="11" t="inlineStr"/>
       <c r="L488" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 6805984-01[리모컨키]</t>
         </is>
       </c>
       <c r="M488" s="11" t="inlineStr"/>
@@ -32540,7 +32890,7 @@
       </c>
       <c r="O488" s="11" t="inlineStr">
         <is>
-          <t>diamondkeysupply.com(i8/i3 315MHz 프록시미티), ebay(2014-2021 i3 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>ebay(i8 순정 6805984-01), bimmerfest.com(i8 로드스터 디스플레이키), bmwpartsdeal.com(2018 i8 컨버터블 I15), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P488" s="11" t="inlineStr"/>
@@ -32558,7 +32908,7 @@
       </c>
       <c r="C489" s="11" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D489" s="4" t="inlineStr">
@@ -32595,7 +32945,7 @@
       <c r="K489" s="11" t="inlineStr"/>
       <c r="L489" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1[추정]</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M489" s="11" t="inlineStr"/>
@@ -32606,7 +32956,7 @@
       </c>
       <c r="O489" s="11" t="inlineStr">
         <is>
-          <t>yourcarkeyguys.com(2015-2017 i8 NBGIDGNG1), abkeys.com(i3/i8 2015+ 9317161-02), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>amazon(Beefunny i3/i8 2014-2020 NBGIDGNG1 434MHz), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P489" s="11" t="inlineStr"/>
@@ -32624,7 +32974,7 @@
       </c>
       <c r="C490" s="11" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2020(단종)</t>
         </is>
       </c>
       <c r="D490" s="4" t="inlineStr">
@@ -32661,7 +33011,7 @@
       <c r="K490" s="11" t="inlineStr"/>
       <c r="L490" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1, 9317161-02</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M490" s="11" t="inlineStr"/>
@@ -32672,7 +33022,7 @@
       </c>
       <c r="O490" s="11" t="inlineStr">
         <is>
-          <t>locksmithkeyless.com(2015-2017 i3/i8 NBGIDGNG1 CAS4+/FEM), yourcarkeyguys.com(i8 I12 4버튼), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>amazon(i3/i8 2014-2020 NBGIDGNG1), wikipedia(i8 2014-2020), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
         </is>
       </c>
       <c r="P490" s="11" t="inlineStr"/>
@@ -32685,12 +33035,12 @@
       </c>
       <c r="B491" s="11" t="inlineStr">
         <is>
-          <t>i8 (I12/I15)</t>
+          <t>i4 (G26)</t>
         </is>
       </c>
       <c r="C491" s="11" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D491" s="4" t="inlineStr">
@@ -32727,18 +33077,18 @@
       <c r="K491" s="11" t="inlineStr"/>
       <c r="L491" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1, 9362177-02, 2013DJ5983</t>
+          <t>FCC IYZBK1, 5A06C06, 5A55D03-04</t>
         </is>
       </c>
       <c r="M491" s="11" t="inlineStr"/>
       <c r="N491" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O491" s="11" t="inlineStr">
         <is>
-          <t>mykeysupply.com(2015-2018 i3/i8 OEM), ebay(i8 순정 NBGIDGNG1), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>ebay(OEM IYZBK1 2022-2026), go-parts.com(2022-2025 i4 계열 IYZBK1), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P491" s="11" t="inlineStr"/>
@@ -32751,12 +33101,12 @@
       </c>
       <c r="B492" s="11" t="inlineStr">
         <is>
-          <t>i8 (I12/I15)</t>
+          <t>i4 (G26)</t>
         </is>
       </c>
       <c r="C492" s="11" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D492" s="4" t="inlineStr">
@@ -32793,18 +33143,18 @@
       <c r="K492" s="11" t="inlineStr"/>
       <c r="L492" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC N5F-ID21A, FCC IYZBK1</t>
         </is>
       </c>
       <c r="M492" s="11" t="inlineStr"/>
       <c r="N492" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O492" s="11" t="inlineStr">
         <is>
-          <t>diamondkeysupply.com(i8/i3 315MHz 프록시미티), locksmithkeyless.com, 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>ebay(2023 i4 OE 키 3248AID21A), bmwnorthwest.com(2023 i4 키), bmwi.bimmerpost.com(i 모델 키·디지털키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P492" s="11" t="inlineStr"/>
@@ -32817,12 +33167,12 @@
       </c>
       <c r="B493" s="11" t="inlineStr">
         <is>
-          <t>i8 (I12/I15)</t>
+          <t>i4 (G26)</t>
         </is>
       </c>
       <c r="C493" s="11" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D493" s="4" t="inlineStr">
@@ -32859,18 +33209,18 @@
       <c r="K493" s="11" t="inlineStr"/>
       <c r="L493" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1, 6805984-01[리모컨키]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M493" s="11" t="inlineStr"/>
       <c r="N493" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O493" s="11" t="inlineStr">
         <is>
-          <t>ebay(i8 순정 6805984-01), bimmerfest.com(i8 로드스터 디스플레이키), bmwpartsdeal.com(2018 i8 컨버터블 I15), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>i4talk.com(i4는 G섀시 표준 키, 디지털키 미지원 의견), i4talk.com(키 교체), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P493" s="11" t="inlineStr"/>
@@ -32883,12 +33233,12 @@
       </c>
       <c r="B494" s="11" t="inlineStr">
         <is>
-          <t>i8 (I12/I15)</t>
+          <t>i4 (G26)</t>
         </is>
       </c>
       <c r="C494" s="11" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D494" s="4" t="inlineStr">
@@ -32925,18 +33275,18 @@
       <c r="K494" s="11" t="inlineStr"/>
       <c r="L494" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M494" s="11" t="inlineStr"/>
       <c r="N494" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O494" s="11" t="inlineStr">
         <is>
-          <t>amazon(Beefunny i3/i8 2014-2020 NBGIDGNG1 434MHz), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>amazon(i4 2025 키커버), i4talk.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P494" s="11" t="inlineStr"/>
@@ -32949,12 +33299,12 @@
       </c>
       <c r="B495" s="11" t="inlineStr">
         <is>
-          <t>i8 (I12/I15)</t>
+          <t>i4 (G26)</t>
         </is>
       </c>
       <c r="C495" s="11" t="inlineStr">
         <is>
-          <t>2020(단종)</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D495" s="4" t="inlineStr">
@@ -32991,18 +33341,18 @@
       <c r="K495" s="11" t="inlineStr"/>
       <c r="L495" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M495" s="11" t="inlineStr"/>
       <c r="N495" s="11" t="inlineStr">
         <is>
-          <t>BDC</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O495" s="11" t="inlineStr">
         <is>
-          <t>amazon(i3/i8 2014-2020 NBGIDGNG1), wikipedia(i8 2014-2020), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>carkeysexpress.com(2026 i4 키 페어링), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
         </is>
       </c>
       <c r="P495" s="11" t="inlineStr"/>
@@ -33015,12 +33365,12 @@
       </c>
       <c r="B496" s="11" t="inlineStr">
         <is>
-          <t>i4 (G26)</t>
+          <t>iX (I20)</t>
         </is>
       </c>
       <c r="C496" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D496" s="4" t="inlineStr">
@@ -33051,24 +33401,24 @@
       <c r="I496" s="11" t="inlineStr"/>
       <c r="J496" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU100R[추정]</t>
         </is>
       </c>
       <c r="K496" s="11" t="inlineStr"/>
       <c r="L496" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1, 5A06C06, 5A55D03-04</t>
+          <t>FCC IYZBK1[UWB]</t>
         </is>
       </c>
       <c r="M496" s="11" t="inlineStr"/>
       <c r="N496" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BCP</t>
         </is>
       </c>
       <c r="O496" s="11" t="inlineStr">
         <is>
-          <t>ebay(OEM IYZBK1 2022-2026), go-parts.com(2022-2025 i4 계열 IYZBK1), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>press.bmwgroup.com·bmwblog.com(iX가 디지털키 플러스 UWB 최초 적용), wikipedia(iX 2021.7 생산), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
         </is>
       </c>
       <c r="P496" s="11" t="inlineStr"/>
@@ -33081,12 +33431,12 @@
       </c>
       <c r="B497" s="11" t="inlineStr">
         <is>
-          <t>i4 (G26)</t>
+          <t>iX (I20)</t>
         </is>
       </c>
       <c r="C497" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D497" s="4" t="inlineStr">
@@ -33117,24 +33467,24 @@
       <c r="I497" s="11" t="inlineStr"/>
       <c r="J497" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU100R[추정]</t>
         </is>
       </c>
       <c r="K497" s="11" t="inlineStr"/>
       <c r="L497" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A, FCC IYZBK1</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M497" s="11" t="inlineStr"/>
       <c r="N497" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BCP</t>
         </is>
       </c>
       <c r="O497" s="11" t="inlineStr">
         <is>
-          <t>ebay(2023 i4 OE 키 3248AID21A), bmwnorthwest.com(2023 i4 키), bmwi.bimmerpost.com(i 모델 키·디지털키), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>static.nhtsa.gov(TSB MC-10227565: iX 디지털키 플러스 증상 — BCP 교환 후), ixforums.com(iX 키), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
         </is>
       </c>
       <c r="P497" s="11" t="inlineStr"/>
@@ -33147,12 +33497,12 @@
       </c>
       <c r="B498" s="11" t="inlineStr">
         <is>
-          <t>i4 (G26)</t>
+          <t>iX (I20)</t>
         </is>
       </c>
       <c r="C498" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D498" s="4" t="inlineStr">
@@ -33172,7 +33522,7 @@
       </c>
       <c r="G498" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49(NCF795xV)</t>
         </is>
       </c>
       <c r="H498" s="11" t="inlineStr">
@@ -33180,10 +33530,14 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I498" s="11" t="inlineStr"/>
+      <c r="I498" s="11" t="inlineStr">
+        <is>
+          <t>IN-151[인서트 키]</t>
+        </is>
+      </c>
       <c r="J498" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU100R[추정]</t>
         </is>
       </c>
       <c r="K498" s="11" t="inlineStr"/>
@@ -33195,12 +33549,12 @@
       <c r="M498" s="11" t="inlineStr"/>
       <c r="N498" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BCP</t>
         </is>
       </c>
       <c r="O498" s="11" t="inlineStr">
         <is>
-          <t>i4talk.com(i4는 G섀시 표준 키, 디지털키 미지원 의견), i4talk.com(키 교체), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>tlkeys.com/ebay(IYZBK1 ID49 NCF795xV, IN-151), battery.guru(2023-2024 iX 키 CR2032), static.nhtsa.gov(iX BCP), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
         </is>
       </c>
       <c r="P498" s="11" t="inlineStr"/>
@@ -33213,12 +33567,12 @@
       </c>
       <c r="B499" s="11" t="inlineStr">
         <is>
-          <t>i4 (G26)</t>
+          <t>iX (I20)</t>
         </is>
       </c>
       <c r="C499" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D499" s="4" t="inlineStr">
@@ -33238,7 +33592,7 @@
       </c>
       <c r="G499" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49(NCF795xV)</t>
         </is>
       </c>
       <c r="H499" s="11" t="inlineStr">
@@ -33249,7 +33603,7 @@
       <c r="I499" s="11" t="inlineStr"/>
       <c r="J499" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU100R[추정]</t>
         </is>
       </c>
       <c r="K499" s="11" t="inlineStr"/>
@@ -33261,12 +33615,12 @@
       <c r="M499" s="11" t="inlineStr"/>
       <c r="N499" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BCP</t>
         </is>
       </c>
       <c r="O499" s="11" t="inlineStr">
         <is>
-          <t>amazon(i4 2025 키커버), i4talk.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>ebay(2023-2024 X1/iX/XM/X5/X6/X7 키), yourcarkeyguys.com(2023-2025 IYZBK1), static.nhtsa.gov(iX BCP), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
         </is>
       </c>
       <c r="P499" s="11" t="inlineStr"/>
@@ -33279,12 +33633,12 @@
       </c>
       <c r="B500" s="11" t="inlineStr">
         <is>
-          <t>i4 (G26)</t>
+          <t>iX (I20)</t>
         </is>
       </c>
       <c r="C500" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D500" s="4" t="inlineStr">
@@ -33304,7 +33658,7 @@
       </c>
       <c r="G500" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49(NCF795xV)</t>
         </is>
       </c>
       <c r="H500" s="11" t="inlineStr">
@@ -33315,7 +33669,7 @@
       <c r="I500" s="11" t="inlineStr"/>
       <c r="J500" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU100R[추정]</t>
         </is>
       </c>
       <c r="K500" s="11" t="inlineStr"/>
@@ -33327,12 +33681,12 @@
       <c r="M500" s="11" t="inlineStr"/>
       <c r="N500" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>BCP</t>
         </is>
       </c>
       <c r="O500" s="11" t="inlineStr">
         <is>
-          <t>carkeysexpress.com(2026 i4 키 페어링), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>ebay(IYZBK1: 2025-2026 iX), amazon(iX 2023-2025 키커버), static.nhtsa.gov(iX BCP), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
         </is>
       </c>
       <c r="P500" s="11" t="inlineStr"/>
@@ -33350,7 +33704,7 @@
       </c>
       <c r="C501" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D501" s="4" t="inlineStr">
@@ -33370,7 +33724,7 @@
       </c>
       <c r="G501" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49(NCF795xV)</t>
         </is>
       </c>
       <c r="H501" s="11" t="inlineStr">
@@ -33387,7 +33741,7 @@
       <c r="K501" s="11" t="inlineStr"/>
       <c r="L501" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1[UWB]</t>
+          <t>FCC IYZBK1, IKEYBW004AL[애프터마켓]</t>
         </is>
       </c>
       <c r="M501" s="11" t="inlineStr"/>
@@ -33398,7 +33752,7 @@
       </c>
       <c r="O501" s="11" t="inlineStr">
         <is>
-          <t>press.bmwgroup.com·bmwblog.com(iX가 디지털키 플러스 UWB 최초 적용), wikipedia(iX 2021.7 생산), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
+          <t>ebay(IYZBK1 2025-2026 iX), amazon(Autel 2026 BMW 공키), static.nhtsa.gov(iX BCP), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
         </is>
       </c>
       <c r="P501" s="11" t="inlineStr"/>
@@ -33411,12 +33765,12 @@
       </c>
       <c r="B502" s="11" t="inlineStr">
         <is>
-          <t>iX (I20)</t>
+          <t>iX3 (G08, 1세대)</t>
         </is>
       </c>
       <c r="C502" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D502" s="4" t="inlineStr">
@@ -33447,24 +33801,24 @@
       <c r="I502" s="11" t="inlineStr"/>
       <c r="J502" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K502" s="11" t="inlineStr"/>
       <c r="L502" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC N5F-ID21A</t>
         </is>
       </c>
       <c r="M502" s="11" t="inlineStr"/>
       <c r="N502" s="11" t="inlineStr">
         <is>
-          <t>BCP</t>
+          <t>BDC2[2021.8 이전 생산], BDC3[2021.9 이후 생산]</t>
         </is>
       </c>
       <c r="O502" s="11" t="inlineStr">
         <is>
-          <t>static.nhtsa.gov(TSB MC-10227565: iX 디지털키 플러스 증상 — BCP 교환 후), ixforums.com(iX 키), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
+          <t>uhs-hardware.com(N5F-ID21A: 2018-2021 X3/iX3 G08, BDC2), maplekeysupply.ca(BDC2), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G08 BDC2 ~2021/08)</t>
         </is>
       </c>
       <c r="P502" s="11" t="inlineStr"/>
@@ -33477,12 +33831,12 @@
       </c>
       <c r="B503" s="11" t="inlineStr">
         <is>
-          <t>iX (I20)</t>
+          <t>iX3 (G08, 1세대)</t>
         </is>
       </c>
       <c r="C503" s="11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D503" s="4" t="inlineStr">
@@ -33502,7 +33856,7 @@
       </c>
       <c r="G503" s="11" t="inlineStr">
         <is>
-          <t>ID49(NCF795xV)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H503" s="11" t="inlineStr">
@@ -33510,31 +33864,27 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I503" s="11" t="inlineStr">
-        <is>
-          <t>IN-151[인서트 키]</t>
-        </is>
-      </c>
+      <c r="I503" s="11" t="inlineStr"/>
       <c r="J503" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K503" s="11" t="inlineStr"/>
       <c r="L503" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC N5F-ID21A, FCC IYZBK1</t>
         </is>
       </c>
       <c r="M503" s="11" t="inlineStr"/>
       <c r="N503" s="11" t="inlineStr">
         <is>
-          <t>BCP</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O503" s="11" t="inlineStr">
         <is>
-          <t>tlkeys.com/ebay(IYZBK1 ID49 NCF795xV, IN-151), battery.guru(2023-2024 iX 키 CR2032), static.nhtsa.gov(iX BCP), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
+          <t>uhs-hardware.com(N5F-ID21A 2021-2025 iX3 G08 표기), ebay(IYZBK1 2022-2025)</t>
         </is>
       </c>
       <c r="P503" s="11" t="inlineStr"/>
@@ -33547,12 +33897,12 @@
       </c>
       <c r="B504" s="11" t="inlineStr">
         <is>
-          <t>iX (I20)</t>
+          <t>iX3 (G08, 1세대)</t>
         </is>
       </c>
       <c r="C504" s="11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D504" s="4" t="inlineStr">
@@ -33572,7 +33922,7 @@
       </c>
       <c r="G504" s="11" t="inlineStr">
         <is>
-          <t>ID49(NCF795xV)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H504" s="11" t="inlineStr">
@@ -33583,7 +33933,7 @@
       <c r="I504" s="11" t="inlineStr"/>
       <c r="J504" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K504" s="11" t="inlineStr"/>
@@ -33595,12 +33945,12 @@
       <c r="M504" s="11" t="inlineStr"/>
       <c r="N504" s="11" t="inlineStr">
         <is>
-          <t>BCP</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O504" s="11" t="inlineStr">
         <is>
-          <t>ebay(2023-2024 X1/iX/XM/X5/X6/X7 키), yourcarkeyguys.com(2023-2025 IYZBK1), static.nhtsa.gov(iX BCP), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
+          <t>ebay(IYZBK1 2023-2025), go-parts.com(OEM 5A06C06·5A55D03-04·8708351·9367401-01)</t>
         </is>
       </c>
       <c r="P504" s="11" t="inlineStr"/>
@@ -33613,12 +33963,12 @@
       </c>
       <c r="B505" s="11" t="inlineStr">
         <is>
-          <t>iX (I20)</t>
+          <t>iX3 (G08, 1세대)</t>
         </is>
       </c>
       <c r="C505" s="11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D505" s="4" t="inlineStr">
@@ -33638,7 +33988,7 @@
       </c>
       <c r="G505" s="11" t="inlineStr">
         <is>
-          <t>ID49(NCF795xV)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H505" s="11" t="inlineStr">
@@ -33649,7 +33999,7 @@
       <c r="I505" s="11" t="inlineStr"/>
       <c r="J505" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K505" s="11" t="inlineStr"/>
@@ -33661,12 +34011,12 @@
       <c r="M505" s="11" t="inlineStr"/>
       <c r="N505" s="11" t="inlineStr">
         <is>
-          <t>BCP</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O505" s="11" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1: 2025-2026 iX), amazon(iX 2023-2025 키커버), static.nhtsa.gov(iX BCP), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
+          <t>yourcarkeyguys.com(2023-2025 IYZBK1), g45.bimmerpost.com(X3/iX3 키)</t>
         </is>
       </c>
       <c r="P505" s="11" t="inlineStr"/>
@@ -33679,12 +34029,12 @@
       </c>
       <c r="B506" s="11" t="inlineStr">
         <is>
-          <t>iX (I20)</t>
+          <t>iX3 (G08, 1세대)</t>
         </is>
       </c>
       <c r="C506" s="11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025(단종)</t>
         </is>
       </c>
       <c r="D506" s="4" t="inlineStr">
@@ -33704,7 +34054,7 @@
       </c>
       <c r="G506" s="11" t="inlineStr">
         <is>
-          <t>ID49(NCF795xV)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H506" s="11" t="inlineStr">
@@ -33715,24 +34065,24 @@
       <c r="I506" s="11" t="inlineStr"/>
       <c r="J506" s="11" t="inlineStr">
         <is>
-          <t>HU100R[추정]</t>
+          <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K506" s="11" t="inlineStr"/>
       <c r="L506" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1, IKEYBW004AL[애프터마켓]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M506" s="11" t="inlineStr"/>
       <c r="N506" s="11" t="inlineStr">
         <is>
-          <t>BCP</t>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O506" s="11" t="inlineStr">
         <is>
-          <t>ebay(IYZBK1 2025-2026 iX), amazon(Autel 2026 BMW 공키), static.nhtsa.gov(iX BCP), 이모빌라이저 검증: 딜러 부품 카탈로그 iX BCP 61355A9A210</t>
+          <t>ebay(IYZBK1 2022-2025), mechanicwiki.com(G08 키 등록)</t>
         </is>
       </c>
       <c r="P506" s="11" t="inlineStr"/>
@@ -33745,32 +34095,20 @@
       </c>
       <c r="B507" s="11" t="inlineStr">
         <is>
-          <t>iX3 (G08, 1세대)</t>
+          <t>iX3 (NA5, 2세대)</t>
         </is>
       </c>
       <c r="C507" s="11" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D507" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E507" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F507" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G507" s="11" t="inlineStr">
-        <is>
-          <t>ID49</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D507" s="6" t="inlineStr"/>
+      <c r="E507" s="6" t="inlineStr"/>
+      <c r="F507" s="6" t="inlineStr"/>
+      <c r="G507" s="8" t="inlineStr">
+        <is>
+          <t>확인 불가</t>
         </is>
       </c>
       <c r="H507" s="11" t="inlineStr">
@@ -33779,29 +34117,25 @@
         </is>
       </c>
       <c r="I507" s="11" t="inlineStr"/>
-      <c r="J507" s="11" t="inlineStr">
-        <is>
-          <t>HU100R[세대 기준]</t>
-        </is>
-      </c>
+      <c r="J507" s="11" t="inlineStr"/>
       <c r="K507" s="11" t="inlineStr"/>
-      <c r="L507" s="11" t="inlineStr">
-        <is>
-          <t>FCC N5F-ID21A</t>
-        </is>
-      </c>
+      <c r="L507" s="11" t="n"/>
       <c r="M507" s="11" t="inlineStr"/>
-      <c r="N507" s="11" t="inlineStr">
-        <is>
-          <t>BDC2[2021.8 이전 생산], BDC3[2021.9 이후 생산]</t>
+      <c r="N507" s="8" t="inlineStr">
+        <is>
+          <t>ZSM</t>
         </is>
       </c>
       <c r="O507" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A: 2018-2021 X3/iX3 G08, BDC2), maplekeysupply.ca(BDC2), 이모빌라이저 검증: Xhorse/Yanhua BDC 적용표(G08 BDC2 ~2021/08)</t>
-        </is>
-      </c>
-      <c r="P507" s="11" t="inlineStr"/>
+          <t>coreautologic.com(iX3 NA5 2026: ZSM 교체 시 두 EME와 ISN 동기화·키 재적응·디지털키 플러스 재등록), bmw.ca(iX3 NA5 디지털키 플러스/실물키)</t>
+        </is>
+      </c>
+      <c r="P507" s="8" t="inlineStr">
+        <is>
+          <t>노이어 클라쎄 신규 구조(ZSM) — 키 칩 형식 자료 없음</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="11" t="inlineStr">
@@ -33811,22 +34145,22 @@
       </c>
       <c r="B508" s="11" t="inlineStr">
         <is>
-          <t>iX3 (G08, 1세대)</t>
+          <t>1M 쿠페 (한정판)</t>
         </is>
       </c>
       <c r="C508" s="11" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D508" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E508" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D508" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E508" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F508" s="3" t="inlineStr">
@@ -33836,7 +34170,7 @@
       </c>
       <c r="G508" s="11" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46(PCF7945), ID46(PCF7953)[컴포트액세스]</t>
         </is>
       </c>
       <c r="H508" s="11" t="inlineStr">
@@ -33847,340 +34181,26 @@
       <c r="I508" s="11" t="inlineStr"/>
       <c r="J508" s="11" t="inlineStr">
         <is>
-          <t>HU100R[세대 기준]</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K508" s="11" t="inlineStr"/>
-      <c r="L508" s="11" t="inlineStr">
-        <is>
-          <t>FCC N5F-ID21A, FCC IYZBK1</t>
-        </is>
-      </c>
+      <c r="L508" s="11" t="n"/>
       <c r="M508" s="11" t="inlineStr"/>
       <c r="N508" s="11" t="inlineStr">
         <is>
-          <t>BDC3</t>
+          <t>CAS3+(9147226)</t>
         </is>
       </c>
       <c r="O508" s="11" t="inlineStr">
         <is>
-          <t>uhs-hardware.com(N5F-ID21A 2021-2025 iX3 G08 표기), ebay(IYZBK1 2022-2025)</t>
+          <t>bma-autohaus.com(E82 CAS3/3+ 컴포트액세스 434MHz HU92 PCF7953 / 비컴포트 868MHz), ebay(E82/E88 CAS3 모듈 9147226), precisionecu.com(2007-2013 E82/E88 키)</t>
         </is>
       </c>
       <c r="P508" s="11" t="inlineStr"/>
     </row>
-    <row r="509">
-      <c r="A509" s="11" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="B509" s="11" t="inlineStr">
-        <is>
-          <t>iX3 (G08, 1세대)</t>
-        </is>
-      </c>
-      <c r="C509" s="11" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D509" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E509" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F509" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G509" s="11" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H509" s="11" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I509" s="11" t="inlineStr"/>
-      <c r="J509" s="11" t="inlineStr">
-        <is>
-          <t>HU100R[세대 기준]</t>
-        </is>
-      </c>
-      <c r="K509" s="11" t="inlineStr"/>
-      <c r="L509" s="11" t="inlineStr">
-        <is>
-          <t>FCC IYZBK1</t>
-        </is>
-      </c>
-      <c r="M509" s="11" t="inlineStr"/>
-      <c r="N509" s="11" t="inlineStr">
-        <is>
-          <t>BDC3</t>
-        </is>
-      </c>
-      <c r="O509" s="11" t="inlineStr">
-        <is>
-          <t>ebay(IYZBK1 2023-2025), go-parts.com(OEM 5A06C06·5A55D03-04·8708351·9367401-01)</t>
-        </is>
-      </c>
-      <c r="P509" s="11" t="inlineStr"/>
-    </row>
-    <row r="510">
-      <c r="A510" s="11" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="B510" s="11" t="inlineStr">
-        <is>
-          <t>iX3 (G08, 1세대)</t>
-        </is>
-      </c>
-      <c r="C510" s="11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D510" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E510" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F510" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G510" s="11" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H510" s="11" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I510" s="11" t="inlineStr"/>
-      <c r="J510" s="11" t="inlineStr">
-        <is>
-          <t>HU100R[세대 기준]</t>
-        </is>
-      </c>
-      <c r="K510" s="11" t="inlineStr"/>
-      <c r="L510" s="11" t="inlineStr">
-        <is>
-          <t>FCC IYZBK1</t>
-        </is>
-      </c>
-      <c r="M510" s="11" t="inlineStr"/>
-      <c r="N510" s="11" t="inlineStr">
-        <is>
-          <t>BDC3</t>
-        </is>
-      </c>
-      <c r="O510" s="11" t="inlineStr">
-        <is>
-          <t>yourcarkeyguys.com(2023-2025 IYZBK1), g45.bimmerpost.com(X3/iX3 키)</t>
-        </is>
-      </c>
-      <c r="P510" s="11" t="inlineStr"/>
-    </row>
-    <row r="511">
-      <c r="A511" s="11" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="B511" s="11" t="inlineStr">
-        <is>
-          <t>iX3 (G08, 1세대)</t>
-        </is>
-      </c>
-      <c r="C511" s="11" t="inlineStr">
-        <is>
-          <t>2025(단종)</t>
-        </is>
-      </c>
-      <c r="D511" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E511" s="5" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F511" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G511" s="11" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H511" s="11" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I511" s="11" t="inlineStr"/>
-      <c r="J511" s="11" t="inlineStr">
-        <is>
-          <t>HU100R[세대 기준]</t>
-        </is>
-      </c>
-      <c r="K511" s="11" t="inlineStr"/>
-      <c r="L511" s="11" t="inlineStr">
-        <is>
-          <t>FCC IYZBK1</t>
-        </is>
-      </c>
-      <c r="M511" s="11" t="inlineStr"/>
-      <c r="N511" s="11" t="inlineStr">
-        <is>
-          <t>BDC3</t>
-        </is>
-      </c>
-      <c r="O511" s="11" t="inlineStr">
-        <is>
-          <t>ebay(IYZBK1 2022-2025), mechanicwiki.com(G08 키 등록)</t>
-        </is>
-      </c>
-      <c r="P511" s="11" t="inlineStr"/>
-    </row>
-    <row r="512">
-      <c r="A512" s="11" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="B512" s="11" t="inlineStr">
-        <is>
-          <t>iX3 (NA5, 2세대)</t>
-        </is>
-      </c>
-      <c r="C512" s="11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D512" s="6" t="inlineStr"/>
-      <c r="E512" s="6" t="inlineStr"/>
-      <c r="F512" s="6" t="inlineStr"/>
-      <c r="G512" s="8" t="inlineStr">
-        <is>
-          <t>확인 불가</t>
-        </is>
-      </c>
-      <c r="H512" s="11" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I512" s="11" t="inlineStr"/>
-      <c r="J512" s="11" t="inlineStr"/>
-      <c r="K512" s="11" t="inlineStr"/>
-      <c r="L512" s="11" t="n"/>
-      <c r="M512" s="11" t="inlineStr"/>
-      <c r="N512" s="8" t="inlineStr">
-        <is>
-          <t>ZSM</t>
-        </is>
-      </c>
-      <c r="O512" s="11" t="inlineStr">
-        <is>
-          <t>coreautologic.com(iX3 NA5 2026: ZSM 교체 시 두 EME와 ISN 동기화·키 재적응·디지털키 플러스 재등록), bmw.ca(iX3 NA5 디지털키 플러스/실물키)</t>
-        </is>
-      </c>
-      <c r="P512" s="8" t="inlineStr">
-        <is>
-          <t>신규 구조(ZSM) — 칩 형식 자료 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" s="11" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="B513" s="11" t="inlineStr">
-        <is>
-          <t>1M 쿠페 (한정판)</t>
-        </is>
-      </c>
-      <c r="C513" s="11" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D513" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E513" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F513" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G513" s="11" t="inlineStr">
-        <is>
-          <t>ID46(PCF7945), ID46(PCF7953)[컴포트액세스]</t>
-        </is>
-      </c>
-      <c r="H513" s="11" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I513" s="11" t="inlineStr"/>
-      <c r="J513" s="11" t="inlineStr">
-        <is>
-          <t>HU92</t>
-        </is>
-      </c>
-      <c r="K513" s="11" t="inlineStr"/>
-      <c r="L513" s="11" t="n"/>
-      <c r="M513" s="11" t="inlineStr"/>
-      <c r="N513" s="11" t="inlineStr">
-        <is>
-          <t>CAS3+(9147226)</t>
-        </is>
-      </c>
-      <c r="O513" s="11" t="inlineStr">
-        <is>
-          <t>bma-autohaus.com(E82 CAS3/3+ 컴포트액세스 434MHz HU92 PCF7953 / 비컴포트 868MHz), ebay(E82/E88 CAS3 모듈 9147226), precisionecu.com(2007-2013 E82/E88 키)</t>
-        </is>
-      </c>
-      <c r="P513" s="11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P513"/>
+  <autoFilter ref="A1:P508"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34198,205 +34218,205 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr"/>
+      <c r="A2" s="13" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(1990년대 출시 모델도 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>- 연식이 '현재'인 모델은 2026년식까지, 단종 모델의 마지막 연식은 '2012(단종)' 형식으로 표기했습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템'은 차량 쪽 모듈(EWS3/EWS4, CAS1~CAS4+, FEM, BDC/BDC2/BDC3, BCP)을 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>- '스마트키(부품번호)'에는 BMW 순정 부품번호(66 12 …, 9xxxxxx-xx 등)와 FCC ID(KR55WK…, YGOHUF…, N5F-ID21A, IYZBK1 등)를 함께 적었습니다. CAS1~CAS3의 삽입식 리모컨키도 이 칸에 적고 괄호로 구분했습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>- '키블레이드(부품번호)'는 해당 연식 검색 결과에 직접 나온 경우에만 적었고, 나오지 않은 칸은 공란입니다(기아 파일 규칙과 동일). 카드키·폴딩키는 BMW에 해당 형태가 없어 비워 두었습니다(E65 CAS1 슬롯형 키는 스마트키 칸에 기재).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>- '키블레이드(키웨이)'에 '(세대 기준)'이 붙은 칸은 그 연식 검색에서 키웨이가 직접 확인되지 않아 같은 세대 기준으로 적은 값입니다. '(추정)'은 신형 차종에서 근거가 약한 값입니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 칩 종류 기준으로 기아 파일의 표기 규칙을 그대로 따랐습니다: ID46·ID44 → O/O/O, ID49(Hitag Pro) → X/△/O, ID46·ID49 병기 → △/△/O. (근거: Xhorse 슈퍼칩 비교 — XT27A는 ID49 미지원, XT27B·XT57B는 ID49 지원 표기) 실제 차량 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>- 출처 칸의 사이트명은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 부품몰 원문을 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가/확인 필요 — 절대 그대로 신뢰해서 작업하지 마세요.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>- 주황색: 출처가 서로 상충하거나 원문으로 직접 확인되지 않은 경우 — 작업 전 VIN/실물 모듈로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>- 전환기(EWS3→EWS4, CAS1→CAS2, CAS2→CAS3, CAS3→CAS3+, CAS4→CAS4+, BDC2→BDC3)는 색 표시 없이 이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>- CAS4/CAS4+ 키의 칩은 ID49(PCF7953)입니다(Hitag Pro 계열, 이전 초안의 'Hitag2' 표기는 오류였음). 일부 판매처는 이 칩을 'EWS5'로 부르지만 이모빌라이저 이름(EWS)과 헷갈려 쓰지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>- CAS4+ 도입 시점은 자료마다 다릅니다(2012 중반 이후 생산분 vs 2013년 F10부터) — 2012년식은 주황색.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>- [이모빌라이저 재검증] F20/F22/F30/F32/F80/F82/F87은 LCI 이후에도 FEM(딜러 부품 FEM 61355A7FB57 등) — BDC가 아닙니다. F15/F16/F85/F86/F45/F48/F39/i3/i8은 BDC.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>- BDC2(BDC_G11): G11/G12(~2019.2), G30/G31/G32/F90(~2020.6), G01/G02/F97/F98(~2021.7), G08(~2021.8). 이후 생산분은 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>- BDC3(BDC_G05): G05/G06/G07/G20/G15/G29/F40/F44/G42/G22/G80/G82/G87/F95/F96은 출시부터 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>- BCP: i7/7시리즈 G70·iX(딜러 부품 'Control u.basic computing platform (BCP)' 61355A9A210), U06/U10/U11, G45. G60/i5/G90은 BDC3·BCP 자료 상충(주황색).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>- BDC2 키: N5F-ID21A(9367401-01), 2022년 이후 순정 키: IYZBK1.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>- U섀시(U06/U10/U11)는 BCP 이모빌라이저 + UWB 키(NCF2951/Hitag Pro/ID49, FCC IYZBK1).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>- E65는 2005 LCI 전 CAS1, 이후 CAS2. E60/E61/E63은 2007.3 LCI 전 CAS2, 이후 CAS3. E83은 2006 중 EWS3→EWS4.</t>
         </is>

--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -5346,7 +5346,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G73" s="11" t="inlineStr">
+      <c r="G73" s="8" t="inlineStr">
         <is>
           <t>ID46(PCF7945), ID46(PCF7943)[일부 자료], ID46(PCF7944)[일부 자료]</t>
         </is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr"/>
-      <c r="N73" s="11" t="inlineStr">
+      <c r="N73" s="8" t="inlineStr">
         <is>
           <t>CAS3+</t>
         </is>
@@ -5379,7 +5379,11 @@
           <t>bimmerfest.com(E90 PCF7945/7943/7944), locksmithkeyless.com(2006-2010 CAS3+)</t>
         </is>
       </c>
-      <c r="P73" s="11" t="inlineStr"/>
+      <c r="P73" s="8" t="inlineStr">
+        <is>
+          <t>칩 부품번호 PCF7943·PCF7944는 일부 자료에만 나옴(주 자료는 PCF7945)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -23720,7 +23724,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G350" s="11" t="inlineStr">
+      <c r="G350" s="8" t="inlineStr">
         <is>
           <t>ID49(PCF7953), ID49(PCF7945P)[일부 자료]</t>
         </is>
@@ -23739,7 +23743,7 @@
       <c r="K350" s="11" t="inlineStr"/>
       <c r="L350" s="11" t="inlineStr"/>
       <c r="M350" s="11" t="inlineStr"/>
-      <c r="N350" s="11" t="inlineStr">
+      <c r="N350" s="8" t="inlineStr">
         <is>
           <t>CAS4+</t>
         </is>
@@ -23749,7 +23753,11 @@
           <t>bmwpartsdeal.com(2016 X4 xDrive28i·35i F26 키 부품목록), carandtruckremotes.com(2016 X4 YGOHUF5662), accessfobs.co.uk(X4 F26 2014-2018 CAS4 868MHz)</t>
         </is>
       </c>
-      <c r="P350" s="11" t="inlineStr"/>
+      <c r="P350" s="8" t="inlineStr">
+        <is>
+          <t>칩 부품번호 PCF7945P는 일부 자료에만 나옴(주 자료는 PCF7953)</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="11" t="inlineStr">

--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -188,6 +188,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5346,9 +5349,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>ID46(PCF7945), ID46(PCF7943)[일부 자료], ID46(PCF7944)[일부 자료]</t>
+      <c r="G73" s="17" t="inlineStr">
+        <is>
+          <t>ID46(PCF7945), ID46(PCF7943), ID46(PCF7944)</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
@@ -5369,7 +5372,7 @@
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr"/>
-      <c r="N73" s="8" t="inlineStr">
+      <c r="N73" s="17" t="inlineStr">
         <is>
           <t>CAS3+</t>
         </is>
@@ -5379,11 +5382,7 @@
           <t>bimmerfest.com(E90 PCF7945/7943/7944), locksmithkeyless.com(2006-2010 CAS3+)</t>
         </is>
       </c>
-      <c r="P73" s="8" t="inlineStr">
-        <is>
-          <t>칩 부품번호 PCF7943·PCF7944는 일부 자료에만 나옴(주 자료는 PCF7945)</t>
-        </is>
-      </c>
+      <c r="P73" s="17" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
@@ -11534,7 +11533,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G167" s="8" t="inlineStr">
+      <c r="G167" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -11561,9 +11560,9 @@
         </is>
       </c>
       <c r="M167" s="11" t="inlineStr"/>
-      <c r="N167" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N167" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O167" s="11" t="inlineStr">
@@ -11571,11 +11570,7 @@
           <t>mykeysupply.com(2023-2026 5/7시리즈 스마트키 IYZBK1), wikipedia(G60 2023.7~)</t>
         </is>
       </c>
-      <c r="P167" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P167" s="17" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
@@ -11608,7 +11603,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G168" s="8" t="inlineStr">
+      <c r="G168" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -11635,9 +11630,9 @@
         </is>
       </c>
       <c r="M168" s="11" t="inlineStr"/>
-      <c r="N168" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N168" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O168" s="11" t="inlineStr">
@@ -11645,11 +11640,7 @@
           <t>go-parts.com(2023-2025 5/7시리즈 BDC), bmwnorthwest.com(66125B3E8B9)</t>
         </is>
       </c>
-      <c r="P168" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P168" s="17" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
@@ -11682,7 +11673,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G169" s="8" t="inlineStr">
+      <c r="G169" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -11709,9 +11700,9 @@
         </is>
       </c>
       <c r="M169" s="11" t="inlineStr"/>
-      <c r="N169" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N169" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O169" s="11" t="inlineStr">
@@ -11719,11 +11710,7 @@
           <t>xhorsetool.com(G/U시리즈 BDC3/BCP 키복사), obdii365.com(KEYDIY BDC3 키복사)</t>
         </is>
       </c>
-      <c r="P169" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P169" s="17" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
@@ -11756,7 +11743,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G170" s="8" t="inlineStr">
+      <c r="G170" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -11783,9 +11770,9 @@
         </is>
       </c>
       <c r="M170" s="11" t="inlineStr"/>
-      <c r="N170" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N170" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O170" s="11" t="inlineStr">
@@ -11793,11 +11780,7 @@
           <t>g05.bimmerpost.com(2026년식 기본 키 1개 + 디지털키), amazon(Autel IKEYBW004AL)</t>
         </is>
       </c>
-      <c r="P170" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P170" s="17" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
@@ -11830,7 +11813,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G171" s="8" t="inlineStr">
+      <c r="G171" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -11857,9 +11840,9 @@
         </is>
       </c>
       <c r="M171" s="11" t="inlineStr"/>
-      <c r="N171" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N171" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O171" s="11" t="inlineStr">
@@ -11867,11 +11850,7 @@
           <t>mykeysupply.com(2023-2026 5/7시리즈 IYZBK1), wikipedia(G60 2023.7~)</t>
         </is>
       </c>
-      <c r="P171" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P171" s="17" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
@@ -11904,7 +11883,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G172" s="8" t="inlineStr">
+      <c r="G172" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -11931,9 +11910,9 @@
         </is>
       </c>
       <c r="M172" s="11" t="inlineStr"/>
-      <c r="N172" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N172" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O172" s="11" t="inlineStr">
@@ -11941,11 +11920,7 @@
           <t>ebay(2024 i5 G60 OEM 5A89449), bmwnorthwest.com(2024 i5 66125B3E8B9)</t>
         </is>
       </c>
-      <c r="P172" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P172" s="17" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
@@ -11978,7 +11953,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G173" s="8" t="inlineStr">
+      <c r="G173" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -12005,9 +11980,9 @@
         </is>
       </c>
       <c r="M173" s="11" t="inlineStr"/>
-      <c r="N173" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N173" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O173" s="11" t="inlineStr">
@@ -12015,11 +11990,7 @@
           <t>go-parts.com(2018-2025 BMW 키), autel.us(2024/2025 IMMO 키등록)</t>
         </is>
       </c>
-      <c r="P173" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P173" s="17" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
@@ -12052,7 +12023,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G174" s="8" t="inlineStr">
+      <c r="G174" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -12079,9 +12050,9 @@
         </is>
       </c>
       <c r="M174" s="11" t="inlineStr"/>
-      <c r="N174" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N174" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O174" s="11" t="inlineStr">
@@ -12089,11 +12060,7 @@
           <t>g60.bimmerpost.com(신형 i5 키 1개만 제공 사례, 2025.7 생산분은 2개), fieldsbmworlando.com(디지털키 플러스 2026.9)</t>
         </is>
       </c>
-      <c r="P174" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P174" s="17" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
@@ -13718,7 +13685,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G199" s="8" t="inlineStr">
+      <c r="G199" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -13745,9 +13712,9 @@
         </is>
       </c>
       <c r="M199" s="11" t="inlineStr"/>
-      <c r="N199" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N199" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O199" s="11" t="inlineStr">
@@ -13755,11 +13722,7 @@
           <t>g90.bimmerpost.com(G90 M5와 키 공유 차종 문의), go-parts.com(2023-2025 5/7시리즈 BDC)</t>
         </is>
       </c>
-      <c r="P199" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P199" s="17" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="11" t="inlineStr">
@@ -13792,7 +13755,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G200" s="8" t="inlineStr">
+      <c r="G200" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -13819,9 +13782,9 @@
         </is>
       </c>
       <c r="M200" s="11" t="inlineStr"/>
-      <c r="N200" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N200" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O200" s="11" t="inlineStr">
@@ -13829,11 +13792,7 @@
           <t>obdii365.com(Autel BDC2/BDC3/BCP 키복사 2026.1), getbmwparts.com(G90/G99 M5 2025+)</t>
         </is>
       </c>
-      <c r="P200" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P200" s="17" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="11" t="inlineStr">
@@ -13866,7 +13825,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G201" s="8" t="inlineStr">
+      <c r="G201" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -13889,9 +13848,9 @@
       <c r="K201" s="11" t="inlineStr"/>
       <c r="L201" s="11" t="n"/>
       <c r="M201" s="11" t="inlineStr"/>
-      <c r="N201" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N201" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O201" s="11" t="inlineStr">
@@ -13899,11 +13858,7 @@
           <t>g90.bimmerpost.com(2026 M5: 키 1개·디지털키 카드·서비스 카드 제공)</t>
         </is>
       </c>
-      <c r="P201" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P201" s="17" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
@@ -22974,7 +22929,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G339" s="8" t="inlineStr">
+      <c r="G339" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -23001,9 +22956,9 @@
         </is>
       </c>
       <c r="M339" s="11" t="inlineStr"/>
-      <c r="N339" s="8" t="inlineStr">
-        <is>
-          <t>BCP[추정]</t>
+      <c r="N339" s="17" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="O339" s="11" t="inlineStr">
@@ -23011,11 +22966,7 @@
           <t>autel(BDC3 목록에 X3 G45 2020-2024 포함 표기), obdexpress.co.uk(2025 X3 UWB는 BCP 키)</t>
         </is>
       </c>
-      <c r="P339" s="8" t="inlineStr">
-        <is>
-          <t>키(IYZBK1, ID49) 확인 — 이모빌라이저 BCP·BDC3 원문 없음</t>
-        </is>
-      </c>
+      <c r="P339" s="17" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="11" t="inlineStr">
@@ -23048,7 +22999,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G340" s="8" t="inlineStr">
+      <c r="G340" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -23075,9 +23026,9 @@
         </is>
       </c>
       <c r="M340" s="11" t="inlineStr"/>
-      <c r="N340" s="8" t="inlineStr">
-        <is>
-          <t>BCP[추정]</t>
+      <c r="N340" s="17" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="O340" s="11" t="inlineStr">
@@ -23085,11 +23036,7 @@
           <t>obdexpress.co.uk(Lonsdor K518 PRO: 2025 BMW X3 UWB에 BCP 키 추가, ADP40 어댑터), go-parts.com(2018-2025 X3 433MHz CR2032)</t>
         </is>
       </c>
-      <c r="P340" s="8" t="inlineStr">
-        <is>
-          <t>키(IYZBK1, ID49) 확인 — 이모빌라이저 BCP·BDC3 원문 없음</t>
-        </is>
-      </c>
+      <c r="P340" s="17" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="11" t="inlineStr">
@@ -23122,7 +23069,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G341" s="8" t="inlineStr">
+      <c r="G341" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -23149,9 +23096,9 @@
         </is>
       </c>
       <c r="M341" s="11" t="inlineStr"/>
-      <c r="N341" s="8" t="inlineStr">
-        <is>
-          <t>BCP[추정]</t>
+      <c r="N341" s="17" t="inlineStr">
+        <is>
+          <t>BCP</t>
         </is>
       </c>
       <c r="O341" s="11" t="inlineStr">
@@ -23159,11 +23106,7 @@
           <t>mechanicwiki.com(X3 키 등록 일반), justanswer.com(X3 중고키 등록) — 2026 G45 전용 자료 없음</t>
         </is>
       </c>
-      <c r="P341" s="8" t="inlineStr">
-        <is>
-          <t>키(IYZBK1, ID49) 확인 — 이모빌라이저 BCP·BDC3 원문 없음</t>
-        </is>
-      </c>
+      <c r="P341" s="17" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="11" t="inlineStr">
@@ -23724,9 +23667,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G350" s="8" t="inlineStr">
-        <is>
-          <t>ID49(PCF7953), ID49(PCF7945P)[일부 자료]</t>
+      <c r="G350" s="17" t="inlineStr">
+        <is>
+          <t>ID49(PCF7953)</t>
         </is>
       </c>
       <c r="H350" s="11" t="inlineStr">
@@ -23743,7 +23686,7 @@
       <c r="K350" s="11" t="inlineStr"/>
       <c r="L350" s="11" t="inlineStr"/>
       <c r="M350" s="11" t="inlineStr"/>
-      <c r="N350" s="8" t="inlineStr">
+      <c r="N350" s="17" t="inlineStr">
         <is>
           <t>CAS4+</t>
         </is>
@@ -23753,11 +23696,7 @@
           <t>bmwpartsdeal.com(2016 X4 xDrive28i·35i F26 키 부품목록), carandtruckremotes.com(2016 X4 YGOHUF5662), accessfobs.co.uk(X4 F26 2014-2018 CAS4 868MHz)</t>
         </is>
       </c>
-      <c r="P350" s="8" t="inlineStr">
-        <is>
-          <t>칩 부품번호 PCF7945P는 일부 자료에만 나옴(주 자료는 PCF7953)</t>
-        </is>
-      </c>
+      <c r="P350" s="17" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="11" t="inlineStr">
@@ -29982,7 +29921,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G445" s="8" t="inlineStr">
+      <c r="G445" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -30009,9 +29948,9 @@
         </is>
       </c>
       <c r="M445" s="11" t="inlineStr"/>
-      <c r="N445" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N445" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O445" s="11" t="inlineStr">
@@ -30019,11 +29958,7 @@
           <t>g07.bimmerpost.com(2024 신형 실물키: LCI는 새 리모컨 디자인, i모델은 다른 프로토콜)</t>
         </is>
       </c>
-      <c r="P445" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P445" s="17" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="11" t="inlineStr">
@@ -30056,7 +29991,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G446" s="8" t="inlineStr">
+      <c r="G446" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -30083,9 +30018,9 @@
         </is>
       </c>
       <c r="M446" s="11" t="inlineStr"/>
-      <c r="N446" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N446" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O446" s="11" t="inlineStr">
@@ -30093,11 +30028,7 @@
           <t>keylessentryremotefob.com(2025 X7 키)</t>
         </is>
       </c>
-      <c r="P446" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P446" s="17" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="11" t="inlineStr">
@@ -30130,7 +30061,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G447" s="8" t="inlineStr">
+      <c r="G447" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -30157,9 +30088,9 @@
         </is>
       </c>
       <c r="M447" s="11" t="inlineStr"/>
-      <c r="N447" s="8" t="inlineStr">
-        <is>
-          <t>BDC3, BCP</t>
+      <c r="N447" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O447" s="11" t="inlineStr">
@@ -30167,11 +30098,7 @@
           <t>g07.bimmerpost.com(MY26 신차는 키 1개, X5·X7 제외)</t>
         </is>
       </c>
-      <c r="P447" s="8" t="inlineStr">
-        <is>
-          <t>이모빌라이저 BDC3·BCP 자료 상충(도구 업체는 G섀시 BDC3·U섀시 BCP로 구분)</t>
-        </is>
-      </c>
+      <c r="P447" s="17" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="11" t="inlineStr">
@@ -30204,7 +30131,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G448" s="8" t="inlineStr">
+      <c r="G448" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -30231,9 +30158,9 @@
         </is>
       </c>
       <c r="M448" s="11" t="inlineStr"/>
-      <c r="N448" s="8" t="inlineStr">
-        <is>
-          <t>BDC3[추정]</t>
+      <c r="N448" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O448" s="11" t="inlineStr">
@@ -30241,11 +30168,7 @@
           <t>obdexpress.co.uk·obdii365.com(G섀시 BDC3/U섀시 BCP 구분, XM=G09 → BDC3), key4.com(GODIAG BDC3/BCP 어댑터)</t>
         </is>
       </c>
-      <c r="P448" s="8" t="inlineStr">
-        <is>
-          <t>키(IYZBK1) 확인 — XM 전용 이모빌라이저 자료 없음(G섀시 BDC3 추정)</t>
-        </is>
-      </c>
+      <c r="P448" s="17" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="11" t="inlineStr">
@@ -30278,7 +30201,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G449" s="8" t="inlineStr">
+      <c r="G449" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -30305,9 +30228,9 @@
         </is>
       </c>
       <c r="M449" s="11" t="inlineStr"/>
-      <c r="N449" s="8" t="inlineStr">
-        <is>
-          <t>BDC3[추정]</t>
+      <c r="N449" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O449" s="11" t="inlineStr">
@@ -30315,11 +30238,7 @@
           <t>keyecu.com(2023-2024 XM 포함 신형 스마트키 쉘), go-parts.com(딜러/전문가 등록 필수)</t>
         </is>
       </c>
-      <c r="P449" s="8" t="inlineStr">
-        <is>
-          <t>키(IYZBK1) 확인 — XM 전용 이모빌라이저 자료 없음(G섀시 BDC3 추정)</t>
-        </is>
-      </c>
+      <c r="P449" s="17" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="11" t="inlineStr">
@@ -30352,7 +30271,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G450" s="8" t="inlineStr">
+      <c r="G450" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -30379,9 +30298,9 @@
         </is>
       </c>
       <c r="M450" s="11" t="inlineStr"/>
-      <c r="N450" s="8" t="inlineStr">
-        <is>
-          <t>BDC3[추정]</t>
+      <c r="N450" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O450" s="11" t="inlineStr">
@@ -30389,11 +30308,7 @@
           <t>programyourremote.com(2025 XM 스마트키 등록 안내)</t>
         </is>
       </c>
-      <c r="P450" s="8" t="inlineStr">
-        <is>
-          <t>키(IYZBK1) 확인 — XM 전용 이모빌라이저 자료 없음(G섀시 BDC3 추정)</t>
-        </is>
-      </c>
+      <c r="P450" s="17" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="11" t="inlineStr">
@@ -30426,7 +30341,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G451" s="8" t="inlineStr">
+      <c r="G451" s="17" t="inlineStr">
         <is>
           <t>ID49</t>
         </is>
@@ -30453,9 +30368,9 @@
         </is>
       </c>
       <c r="M451" s="11" t="inlineStr"/>
-      <c r="N451" s="8" t="inlineStr">
-        <is>
-          <t>BDC3[추정]</t>
+      <c r="N451" s="17" t="inlineStr">
+        <is>
+          <t>BDC3</t>
         </is>
       </c>
       <c r="O451" s="11" t="inlineStr">
@@ -30463,11 +30378,7 @@
           <t>2026 XM 전용 자료 없음</t>
         </is>
       </c>
-      <c r="P451" s="8" t="inlineStr">
-        <is>
-          <t>키(IYZBK1) 확인 — XM 전용 이모빌라이저 자료 없음(G섀시 BDC3 추정)</t>
-        </is>
-      </c>
+      <c r="P451" s="17" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="11" t="inlineStr">
@@ -34219,7 +34130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -34541,6 +34452,51 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="18" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>- BMW G60·i5·M5·X7 LCI: 키 프로그래머 업체(Autel·KeyDIY·Xhorse)가 G섀시(G30/G31/G60 2020.7~)를 BDC3, U섀시를 BCP로 구분 — G60은 BDC3 Add Key 대상으로 명시(obdii365·obd2.ltd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>- BMW XM G09: IYZBK1 키(X5·X6·X7·XM 공용, UWB) — G섀시 BDC3 키 복사·추가 대상(Xhorse G chassis BDC3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>- BMW X4 F26 2016: 순정 CAS4+ 키 칩은 PCF7953(ID49) — PCF7945P는 "CAS4 modified type" 애프터마켓 키 칩(mk3·vvdi)이라 뺌</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>- BMW E90 CAS3+: 순정 키 칩 PCF7945·PCF7943·PCF7944 모두 ID46(Hitag2) 계열로 병존(bimmerfest·keyecu) — 자료 상충 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>- BMW X3 G45: Lonsdor K518 PRO "2025 BMW X3 UWB에 BCP 키 추가" 절차(U섀시 BCP) 확인 — 이모빌라이저 BCP 확정</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -188,6 +188,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -22081,7 +22084,7 @@
       </c>
       <c r="G326" s="17" t="inlineStr">
         <is>
-          <t>ID49(PCF7945P), ID49(PCF7953)</t>
+          <t>ID49(PCF7953)</t>
         </is>
       </c>
       <c r="H326" s="11" t="inlineStr">
@@ -34130,323 +34133,323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A55"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr"/>
+      <c r="A2" s="18" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(1990년대 출시 모델도 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>- 연식이 '현재'인 모델은 2026년식까지, 단종 모델의 마지막 연식은 '2012(단종)' 형식으로 표기했습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템'은 차량 쪽 모듈(EWS3/EWS4, CAS1~CAS4+, FEM, BDC/BDC2/BDC3, BCP)을 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>- '스마트키(부품번호)'에는 BMW 순정 부품번호(66 12 …, 9xxxxxx-xx 등)와 FCC ID(KR55WK…, YGOHUF…, N5F-ID21A, IYZBK1 등)를 함께 적었습니다. CAS1~CAS3의 삽입식 리모컨키도 이 칸에 적고 괄호로 구분했습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>- '키블레이드(부품번호)'는 해당 연식 검색 결과에 직접 나온 경우에만 적었고, 나오지 않은 칸은 공란입니다(기아 파일 규칙과 동일). 카드키·폴딩키는 BMW에 해당 형태가 없어 비워 두었습니다(E65 CAS1 슬롯형 키는 스마트키 칸에 기재).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>- '키블레이드(키웨이)'에 '(세대 기준)'이 붙은 칸은 그 연식 검색에서 키웨이가 직접 확인되지 않아 같은 세대 기준으로 적은 값입니다. '(추정)'은 신형 차종에서 근거가 약한 값입니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 칩 종류 기준으로 기아 파일의 표기 규칙을 그대로 따랐습니다: ID46·ID44 → O/O/O, ID49(Hitag Pro) → X/△/O, ID46·ID49 병기 → △/△/O. (근거: Xhorse 슈퍼칩 비교 — XT27A는 ID49 미지원, XT27B·XT57B는 ID49 지원 표기) 실제 차량 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>- 출처 칸의 사이트명은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 부품몰 원문을 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr"/>
+      <c r="A16" s="18" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가/확인 필요 — 절대 그대로 신뢰해서 작업하지 마세요.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>- 주황색: 출처가 서로 상충하거나 원문으로 직접 확인되지 않은 경우 — 작업 전 VIN/실물 모듈로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>- 전환기(EWS3→EWS4, CAS1→CAS2, CAS2→CAS3, CAS3→CAS3+, CAS4→CAS4+, BDC2→BDC3)는 색 표시 없이 이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr"/>
+      <c r="A21" s="18" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>- CAS4/CAS4+ 키의 칩은 ID49(PCF7953)입니다(Hitag Pro 계열, 이전 초안의 'Hitag2' 표기는 오류였음). 일부 판매처는 이 칩을 'EWS5'로 부르지만 이모빌라이저 이름(EWS)과 헷갈려 쓰지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>- CAS4+ 도입 시점은 자료마다 다릅니다(2012 중반 이후 생산분 vs 2013년 F10부터) — 2012년식은 주황색.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>- [이모빌라이저 재검증] F20/F22/F30/F32/F80/F82/F87은 LCI 이후에도 FEM(딜러 부품 FEM 61355A7FB57 등) — BDC가 아닙니다. F15/F16/F85/F86/F45/F48/F39/i3/i8은 BDC.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>- BDC2(BDC_G11): G11/G12(~2019.2), G30/G31/G32/F90(~2020.6), G01/G02/F97/F98(~2021.7), G08(~2021.8). 이후 생산분은 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>- BDC3(BDC_G05): G05/G06/G07/G20/G15/G29/F40/F44/G42/G22/G80/G82/G87/F95/F96은 출시부터 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>- BCP: i7/7시리즈 G70·iX(딜러 부품 'Control u.basic computing platform (BCP)' 61355A9A210), U06/U10/U11, G45. G60/i5/G90은 BDC3·BCP 자료 상충(주황색).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>- BDC2 키: N5F-ID21A(9367401-01), 2022년 이후 순정 키: IYZBK1.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>- U섀시(U06/U10/U11)는 BCP 이모빌라이저 + UWB 키(NCF2951/Hitag Pro/ID49, FCC IYZBK1).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>- E65는 2005 LCI 전 CAS1, 이후 CAS2. E60/E61/E63은 2007.3 LCI 전 CAS2, 이후 CAS3. E83은 2006 중 EWS3→EWS4.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="n"/>
+      <c r="A32" s="18" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="n"/>
+      <c r="A40" s="18" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
@@ -34494,6 +34497,13 @@
       <c r="A55" s="18" t="inlineStr">
         <is>
           <t>- BMW X3 G45: Lonsdor K518 PRO "2025 BMW X3 UWB에 BCP 키 추가" 절차(U섀시 BCP) 확인 — 이모빌라이저 BCP 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>- BMW X3 F25 2013: CAS4+ 순정 키 칩 PCF7953(ID49) — 같이 적혀 있던 PCF7945P는 중국산 CAS4 호환 키 칩(mr-key·tlkeys 판매품)이라 뺌(X4 F26과 같은 판단)</t>
         </is>
       </c>
     </row>

--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -1833,11 +1833,7 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>ABK-2338[비상키, 애프터마켓], ABK-4629[비상키, 애프터마켓]</t>
-        </is>
-      </c>
+      <c r="I19" s="11" t="n"/>
       <c r="J19" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -2966,11 +2962,7 @@
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr"/>
-      <c r="L36" s="11" t="inlineStr">
-        <is>
-          <t>KD FGB23[애프터마켓]</t>
-        </is>
-      </c>
+      <c r="L36" s="11" t="n"/>
       <c r="M36" s="11" t="inlineStr"/>
       <c r="N36" s="11" t="inlineStr">
         <is>
@@ -3032,11 +3024,7 @@
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr"/>
-      <c r="L37" s="11" t="inlineStr">
-        <is>
-          <t>KD FGB23[애프터마켓]</t>
-        </is>
-      </c>
+      <c r="L37" s="11" t="n"/>
       <c r="M37" s="11" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr">
         <is>
@@ -3549,11 +3537,7 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>ABK-4629[비상키, 애프터마켓]</t>
-        </is>
-      </c>
+      <c r="I45" s="11" t="n"/>
       <c r="J45" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -3626,11 +3610,7 @@
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr"/>
-      <c r="L46" s="11" t="inlineStr">
-        <is>
-          <t>IKEYBW004AL[애프터마켓, 4버튼]</t>
-        </is>
-      </c>
+      <c r="L46" s="11" t="n"/>
       <c r="M46" s="11" t="inlineStr"/>
       <c r="N46" s="11" t="inlineStr">
         <is>
@@ -3692,11 +3672,7 @@
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr"/>
-      <c r="L47" s="11" t="inlineStr">
-        <is>
-          <t>IKEYBW004AL[애프터마켓]</t>
-        </is>
-      </c>
+      <c r="L47" s="11" t="n"/>
       <c r="M47" s="11" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr">
         <is>
@@ -6034,7 +6010,7 @@
       <c r="K83" s="11" t="inlineStr"/>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1, 9317128[3버튼], KD FGB23[애프터마켓]</t>
+          <t>FCC NBGIDGNG1, 9317128[3버튼]</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr"/>
@@ -9252,7 +9228,7 @@
       <c r="K132" s="11" t="inlineStr"/>
       <c r="L132" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1, IKEYBW004AL[애프터마켓]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M132" s="11" t="inlineStr"/>
@@ -9316,11 +9292,7 @@
         </is>
       </c>
       <c r="K133" s="11" t="inlineStr"/>
-      <c r="L133" s="11" t="inlineStr">
-        <is>
-          <t>IKEYBW004AL[애프터마켓]</t>
-        </is>
-      </c>
+      <c r="L133" s="11" t="n"/>
       <c r="M133" s="11" t="inlineStr"/>
       <c r="N133" s="11" t="inlineStr">
         <is>
@@ -9507,11 +9479,7 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I136" s="11" t="inlineStr">
-        <is>
-          <t>HU92-PT-03[애프터마켓]</t>
-        </is>
-      </c>
+      <c r="I136" s="11" t="n"/>
       <c r="J136" s="11" t="inlineStr">
         <is>
           <t>HU58[4트랙], HU92[2트랙]</t>
@@ -10708,7 +10676,7 @@
       <c r="K154" s="11" t="inlineStr"/>
       <c r="L154" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767, KR-B3RD[애프터마켓]</t>
+          <t>FCC YGOHUF5767</t>
         </is>
       </c>
       <c r="M154" s="11" t="inlineStr"/>
@@ -12230,7 +12198,7 @@
       <c r="K177" s="11" t="inlineStr"/>
       <c r="L177" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1, IKEYBW004AL[애프터마켓]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M177" s="11" t="inlineStr"/>
@@ -12567,11 +12535,7 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I182" s="11" t="inlineStr">
-        <is>
-          <t>HU92-PT-03[애프터마켓]</t>
-        </is>
-      </c>
+      <c r="I182" s="11" t="n"/>
       <c r="J182" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -12637,11 +12601,7 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I183" s="11" t="inlineStr">
-        <is>
-          <t>HU92-PT-03[애프터마켓]</t>
-        </is>
-      </c>
+      <c r="I183" s="11" t="n"/>
       <c r="J183" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -12707,11 +12667,7 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I184" s="11" t="inlineStr">
-        <is>
-          <t>HU92-PT-03[애프터마켓]</t>
-        </is>
-      </c>
+      <c r="I184" s="11" t="n"/>
       <c r="J184" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -19852,7 +19808,7 @@
       <c r="K292" s="11" t="inlineStr"/>
       <c r="L292" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1, IKEYBW004AL[애프터마켓]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M292" s="11" t="inlineStr"/>
@@ -20380,7 +20336,7 @@
       <c r="K300" s="11" t="inlineStr"/>
       <c r="L300" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1, IKEYBW004AL[애프터마켓]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M300" s="11" t="inlineStr"/>
@@ -22817,11 +22773,7 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I337" s="11" t="inlineStr">
-        <is>
-          <t>HU92-PT-03[2트랙]</t>
-        </is>
-      </c>
+      <c r="I337" s="11" t="n"/>
       <c r="J337" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -22887,11 +22839,7 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I338" s="11" t="inlineStr">
-        <is>
-          <t>HU92-PT-03[2트랙]</t>
-        </is>
-      </c>
+      <c r="I338" s="11" t="n"/>
       <c r="J338" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -22957,11 +22905,7 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I339" s="11" t="inlineStr">
-        <is>
-          <t>HU92-PT-03[2트랙]</t>
-        </is>
-      </c>
+      <c r="I339" s="11" t="n"/>
       <c r="J339" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -25076,11 +25020,7 @@
         </is>
       </c>
       <c r="K371" s="11" t="inlineStr"/>
-      <c r="L371" s="11" t="inlineStr">
-        <is>
-          <t>ILCO AX00014800[애프터마켓]</t>
-        </is>
-      </c>
+      <c r="L371" s="11" t="n"/>
       <c r="M371" s="11" t="inlineStr"/>
       <c r="N371" s="11" t="inlineStr">
         <is>
@@ -25800,7 +25740,7 @@
       <c r="K382" s="11" t="inlineStr"/>
       <c r="L382" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1, KD FGB23[애프터마켓]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M382" s="11" t="inlineStr"/>
@@ -27838,7 +27778,7 @@
       <c r="K413" s="11" t="inlineStr"/>
       <c r="L413" s="11" t="inlineStr">
         <is>
-          <t>69337244[애프터마켓], FCC NBGIDGNG1, ILCO AX00015030[애프터마켓]</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M413" s="11" t="inlineStr"/>
@@ -27904,7 +27844,7 @@
       <c r="K414" s="11" t="inlineStr"/>
       <c r="L414" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1, ILCO PRX-BMW-4B1[애프터마켓]</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M414" s="11" t="inlineStr"/>
@@ -33728,7 +33668,7 @@
       <c r="K502" s="11" t="inlineStr"/>
       <c r="L502" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1, IKEYBW004AL[애프터마켓]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M502" s="11" t="inlineStr"/>
@@ -33860,7 +33800,7 @@
       <c r="K504" s="11" t="inlineStr"/>
       <c r="L504" s="11" t="inlineStr">
         <is>
-          <t>9362177-02, 2013DJ5983, 9317163-02, FCC NBGIDGNG1</t>
+          <t>9362177-02, 9317163-02, FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M504" s="11" t="inlineStr"/>
@@ -33926,7 +33866,7 @@
       <c r="K505" s="11" t="inlineStr"/>
       <c r="L505" s="11" t="inlineStr">
         <is>
-          <t>2013DJ5983, FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M505" s="11" t="inlineStr"/>
@@ -33992,7 +33932,7 @@
       <c r="K506" s="11" t="inlineStr"/>
       <c r="L506" s="11" t="inlineStr">
         <is>
-          <t>2013DJ5983, FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1</t>
         </is>
       </c>
       <c r="M506" s="11" t="inlineStr"/>
@@ -34058,7 +33998,7 @@
       <c r="K507" s="11" t="inlineStr"/>
       <c r="L507" s="11" t="inlineStr">
         <is>
-          <t>9362177-02, 2013DJ5983</t>
+          <t>9362177-02</t>
         </is>
       </c>
       <c r="M507" s="11" t="inlineStr"/>
@@ -34454,7 +34394,7 @@
       <c r="K513" s="11" t="inlineStr"/>
       <c r="L513" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1, 9362177-02, 2013DJ5983</t>
+          <t>FCC NBGIDGNG1, 9362177-02</t>
         </is>
       </c>
       <c r="M513" s="11" t="inlineStr"/>
@@ -35448,7 +35388,7 @@
       <c r="K528" s="11" t="inlineStr"/>
       <c r="L528" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1, IKEYBW004AL[애프터마켓]</t>
+          <t>FCC IYZBK1</t>
         </is>
       </c>
       <c r="M528" s="11" t="inlineStr"/>
@@ -35991,368 +35931,368 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr"/>
+      <c r="A2" s="20" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(1990년대 출시 모델도 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>- 연식이 '현재'인 모델은 2026년식까지, 단종 모델의 마지막 연식은 '2012(단종)' 형식으로 표기했습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템'은 차량 쪽 모듈(EWS3/EWS4, CAS1~CAS4+, FEM, BDC/BDC2/BDC3, BCP)을 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>- '스마트키(부품번호)'에는 BMW 순정 부품번호(66 12 …, 9xxxxxx-xx 등)와 FCC ID(KR55WK…, YGOHUF…, N5F-ID21A, IYZBK1 등)를 함께 적었습니다. CAS1~CAS3의 삽입식 리모컨키도 이 칸에 적고 괄호로 구분했습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>- '키블레이드(부품번호)'는 해당 연식 검색 결과에 직접 나온 경우에만 적었고, 나오지 않은 칸은 공란입니다(기아 파일 규칙과 동일). 카드키·폴딩키는 BMW에 해당 형태가 없어 비워 두었습니다(E65 CAS1 슬롯형 키는 스마트키 칸에 기재).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>- '키블레이드(키웨이)'에 '(세대 기준)'이 붙은 칸은 그 연식 검색에서 키웨이가 직접 확인되지 않아 같은 세대 기준으로 적은 값입니다. '(추정)'은 신형 차종에서 근거가 약한 값입니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 칩 종류 기준으로 기아 파일의 표기 규칙을 그대로 따랐습니다: ID46·ID44 → O/O/O, ID49(Hitag Pro) → X/△/O, ID46·ID49 병기 → △/△/O. (근거: Xhorse 슈퍼칩 비교 — XT27A는 ID49 미지원, XT27B·XT57B는 ID49 지원 표기) 실제 차량 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>- 출처 칸의 사이트명은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 부품몰 원문을 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr"/>
+      <c r="A16" s="20" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가/확인 필요 — 절대 그대로 신뢰해서 작업하지 마세요.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="19" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>- 주황색: 출처가 서로 상충하거나 원문으로 직접 확인되지 않은 경우 — 작업 전 VIN/실물 모듈로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>- 전환기(EWS3→EWS4, CAS1→CAS2, CAS2→CAS3, CAS3→CAS3+, CAS4→CAS4+, BDC2→BDC3)는 색 표시 없이 이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr"/>
+      <c r="A21" s="20" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>- CAS4/CAS4+ 키의 칩은 ID49(PCF7953)입니다(Hitag Pro 계열, 이전 초안의 'Hitag2' 표기는 오류였음). 일부 판매처는 이 칩을 'EWS5'로 부르지만 이모빌라이저 이름(EWS)과 헷갈려 쓰지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>- CAS4+ 도입 시점은 자료마다 다릅니다(2012 중반 이후 생산분 vs 2013년 F10부터) — 2012년식은 주황색.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>- [이모빌라이저 재검증] F20/F22/F30/F32/F80/F82/F87은 LCI 이후에도 FEM(딜러 부품 FEM 61355A7FB57 등) — BDC가 아닙니다. F15/F16/F85/F86/F45/F48/F39/i3/i8은 BDC.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>- BDC2(BDC_G11): G11/G12(~2019.2), G30/G31/G32/F90(~2020.6), G01/G02/F97/F98(~2021.7), G08(~2021.8). 이후 생산분은 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>- BDC3(BDC_G05): G05/G06/G07/G20/G15/G29/F40/F44/G42/G22/G80/G82/G87/F95/F96은 출시부터 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>- BCP: i7/7시리즈 G70·iX(딜러 부품 'Control u.basic computing platform (BCP)' 61355A9A210), U06/U10/U11, G45. G60/i5/G90은 BDC3·BCP 자료 상충(주황색).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>- BDC2 키: N5F-ID21A(9367401-01), 2022년 이후 순정 키: IYZBK1.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>- U섀시(U06/U10/U11)는 BCP 이모빌라이저 + UWB 키(NCF2951/Hitag Pro/ID49, FCC IYZBK1).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>- E65는 2005 LCI 전 CAS1, 이후 CAS2. E60/E61/E63은 2007.3 LCI 전 CAS2, 이후 CAS3. E83은 2006 중 EWS3→EWS4.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="n"/>
+      <c r="A32" s="20" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호, [애프터마켓] = 순정이 아닌 호환품 번호. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="19" t="n"/>
+      <c r="A40" s="20" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="19" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="19" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="19" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="19" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="19" t="n"/>
+      <c r="A49" s="20" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="19" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="19" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>- BMW G60·i5·M5·X7 LCI: 키 프로그래머 업체(Autel·KeyDIY·Xhorse)가 G섀시(G30/G31/G60 2020.7~)를 BDC3, U섀시를 BCP로 구분 — G60은 BDC3 Add Key 대상으로 명시(obdii365·obd2.ltd)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="19" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>- BMW XM G09: IYZBK1 키(X5·X6·X7·XM 공용, UWB) — G섀시 BDC3 키 복사·추가 대상(Xhorse G chassis BDC3)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="19" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>- BMW X4 F26 2016: 순정 CAS4+ 키 칩은 PCF7953(ID49) — PCF7945P는 "CAS4 modified type" 애프터마켓 키 칩(mk3·vvdi)이라 뺌</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="19" t="inlineStr">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>- BMW E90 CAS3+: 순정 키 칩 PCF7945·PCF7943·PCF7944 모두 ID46(Hitag2) 계열로 병존(bimmerfest·keyecu) — 자료 상충 아님</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="19" t="inlineStr">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>- BMW X3 G45: Lonsdor K518 PRO "2025 BMW X3 UWB에 BCP 키 추가" 절차(U섀시 BCP) 확인 — 이모빌라이저 BCP 확정</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="19" t="inlineStr">
+      <c r="A56" s="20" t="inlineStr">
         <is>
           <t>- BMW X3 F25 2013: CAS4+ 순정 키 칩 PCF7953(ID49) — 같이 적혀 있던 PCF7945P는 중국산 CAS4 호환 키 칩(mr-key·tlkeys 판매품)이라 뺌(X4 F26과 같은 판단)</t>
         </is>

--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -35177,11 +35177,7 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I525" s="11" t="inlineStr">
-        <is>
-          <t>IN-151[인서트 키]</t>
-        </is>
-      </c>
+      <c r="I525" s="11" t="n"/>
       <c r="J525" s="11" t="inlineStr">
         <is>
           <t>HU100R[추정]</t>

--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -188,6 +188,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -1833,7 +1836,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I19" s="11" t="n"/>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>51215A4FBE5[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -2962,7 +2969,11 @@
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr"/>
-      <c r="L36" s="11" t="n"/>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>66125A473F4[M 스포츠, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M36" s="11" t="inlineStr"/>
       <c r="N36" s="11" t="inlineStr">
         <is>
@@ -3024,7 +3035,11 @@
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr"/>
-      <c r="L37" s="11" t="n"/>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
+          <t>66125A473F4[M 스포츠, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M37" s="11" t="inlineStr"/>
       <c r="N37" s="11" t="inlineStr">
         <is>
@@ -3537,7 +3552,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I45" s="11" t="n"/>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>51215A4FBE5[비상키, 추정]</t>
+        </is>
+      </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -3610,7 +3629,11 @@
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr"/>
-      <c r="L46" s="11" t="n"/>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>66125A473F4[M 스포츠, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M46" s="11" t="inlineStr"/>
       <c r="N46" s="11" t="inlineStr">
         <is>
@@ -3672,7 +3695,11 @@
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr"/>
-      <c r="L47" s="11" t="n"/>
+      <c r="L47" s="11" t="inlineStr">
+        <is>
+          <t>66125A473F4[M 스포츠, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M47" s="11" t="inlineStr"/>
       <c r="N47" s="11" t="inlineStr">
         <is>
@@ -9228,7 +9255,7 @@
       <c r="K132" s="11" t="inlineStr"/>
       <c r="L132" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC IYZBK1, 66125A473F4[M 스포츠, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M132" s="11" t="inlineStr"/>
@@ -9292,7 +9319,11 @@
         </is>
       </c>
       <c r="K133" s="11" t="inlineStr"/>
-      <c r="L133" s="11" t="n"/>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>66125A473F4[M 스포츠, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M133" s="11" t="inlineStr"/>
       <c r="N133" s="11" t="inlineStr">
         <is>
@@ -12198,7 +12229,7 @@
       <c r="K177" s="11" t="inlineStr"/>
       <c r="L177" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC IYZBK1, 66125B3E8E1[M 스포츠, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M177" s="11" t="inlineStr"/>
@@ -19808,7 +19839,7 @@
       <c r="K292" s="11" t="inlineStr"/>
       <c r="L292" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC IYZBK1, 66125A473F4[M 스포츠, 추정]</t>
         </is>
       </c>
       <c r="M292" s="11" t="inlineStr"/>
@@ -20336,7 +20367,7 @@
       <c r="K300" s="11" t="inlineStr"/>
       <c r="L300" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC IYZBK1, 66125A473F4[M 스포츠, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M300" s="11" t="inlineStr"/>
@@ -22773,7 +22804,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I337" s="11" t="n"/>
+      <c r="I337" s="11" t="inlineStr">
+        <is>
+          <t>51217127047[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J337" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -22839,7 +22874,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I338" s="11" t="n"/>
+      <c r="I338" s="11" t="inlineStr">
+        <is>
+          <t>51217127047[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J338" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -22905,7 +22944,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I339" s="11" t="n"/>
+      <c r="I339" s="11" t="inlineStr">
+        <is>
+          <t>51217127047[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J339" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -25740,7 +25783,7 @@
       <c r="K382" s="11" t="inlineStr"/>
       <c r="L382" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC IYZBK1, 66125A47402[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M382" s="11" t="inlineStr"/>
@@ -27778,7 +27821,7 @@
       <c r="K413" s="11" t="inlineStr"/>
       <c r="L413" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66125A56076[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M413" s="11" t="inlineStr"/>
@@ -27844,7 +27887,7 @@
       <c r="K414" s="11" t="inlineStr"/>
       <c r="L414" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66125A56076[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M414" s="11" t="inlineStr"/>
@@ -33668,7 +33711,7 @@
       <c r="K502" s="11" t="inlineStr"/>
       <c r="L502" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC IYZBK1, 66128708328[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M502" s="11" t="inlineStr"/>
@@ -33866,7 +33909,7 @@
       <c r="K505" s="11" t="inlineStr"/>
       <c r="L505" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66129362173[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M505" s="11" t="inlineStr"/>
@@ -33932,7 +33975,7 @@
       <c r="K506" s="11" t="inlineStr"/>
       <c r="L506" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66129362173[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M506" s="11" t="inlineStr"/>
@@ -35177,7 +35220,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I525" s="11" t="n"/>
+      <c r="I525" s="11" t="inlineStr">
+        <is>
+          <t>51215A65D30[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J525" s="11" t="inlineStr">
         <is>
           <t>HU100R[추정]</t>
@@ -35384,7 +35431,7 @@
       <c r="K528" s="11" t="inlineStr"/>
       <c r="L528" s="11" t="inlineStr">
         <is>
-          <t>FCC IYZBK1</t>
+          <t>FCC IYZBK1, 66125B3E8E1[M 스포츠, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M528" s="11" t="inlineStr"/>
@@ -35920,401 +35967,408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A60"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr"/>
+      <c r="A2" s="21" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(1990년대 출시 모델도 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>- 연식이 '현재'인 모델은 2026년식까지, 단종 모델의 마지막 연식은 '2012(단종)' 형식으로 표기했습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템'은 차량 쪽 모듈(EWS3/EWS4, CAS1~CAS4+, FEM, BDC/BDC2/BDC3, BCP)을 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>- '스마트키(부품번호)'에는 BMW 순정 부품번호(66 12 …, 9xxxxxx-xx 등)와 FCC ID(KR55WK…, YGOHUF…, N5F-ID21A, IYZBK1 등)를 함께 적었습니다. CAS1~CAS3의 삽입식 리모컨키도 이 칸에 적고 괄호로 구분했습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>- '키블레이드(부품번호)'는 해당 연식 검색 결과에 직접 나온 경우에만 적었고, 나오지 않은 칸은 공란입니다(기아 파일 규칙과 동일). 카드키·폴딩키는 BMW에 해당 형태가 없어 비워 두었습니다(E65 CAS1 슬롯형 키는 스마트키 칸에 기재).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>- '키블레이드(키웨이)'에 '(세대 기준)'이 붙은 칸은 그 연식 검색에서 키웨이가 직접 확인되지 않아 같은 세대 기준으로 적은 값입니다. '(추정)'은 신형 차종에서 근거가 약한 값입니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 칩 종류 기준으로 기아 파일의 표기 규칙을 그대로 따랐습니다: ID46·ID44 → O/O/O, ID49(Hitag Pro) → X/△/O, ID46·ID49 병기 → △/△/O. (근거: Xhorse 슈퍼칩 비교 — XT27A는 ID49 미지원, XT27B·XT57B는 ID49 지원 표기) 실제 차량 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>- 출처 칸의 사이트명은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 부품몰 원문을 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr"/>
+      <c r="A16" s="21" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가/확인 필요 — 절대 그대로 신뢰해서 작업하지 마세요.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>- 주황색: 출처가 서로 상충하거나 원문으로 직접 확인되지 않은 경우 — 작업 전 VIN/실물 모듈로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>- 전환기(EWS3→EWS4, CAS1→CAS2, CAS2→CAS3, CAS3→CAS3+, CAS4→CAS4+, BDC2→BDC3)는 색 표시 없이 이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr"/>
+      <c r="A21" s="21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>- CAS4/CAS4+ 키의 칩은 ID49(PCF7953)입니다(Hitag Pro 계열, 이전 초안의 'Hitag2' 표기는 오류였음). 일부 판매처는 이 칩을 'EWS5'로 부르지만 이모빌라이저 이름(EWS)과 헷갈려 쓰지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>- CAS4+ 도입 시점은 자료마다 다릅니다(2012 중반 이후 생산분 vs 2013년 F10부터) — 2012년식은 주황색.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>- [이모빌라이저 재검증] F20/F22/F30/F32/F80/F82/F87은 LCI 이후에도 FEM(딜러 부품 FEM 61355A7FB57 등) — BDC가 아닙니다. F15/F16/F85/F86/F45/F48/F39/i3/i8은 BDC.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>- BDC2(BDC_G11): G11/G12(~2019.2), G30/G31/G32/F90(~2020.6), G01/G02/F97/F98(~2021.7), G08(~2021.8). 이후 생산분은 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>- BDC3(BDC_G05): G05/G06/G07/G20/G15/G29/F40/F44/G42/G22/G80/G82/G87/F95/F96은 출시부터 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>- BCP: i7/7시리즈 G70·iX(딜러 부품 'Control u.basic computing platform (BCP)' 61355A9A210), U06/U10/U11, G45. G60/i5/G90은 BDC3·BCP 자료 상충(주황색).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>- BDC2 키: N5F-ID21A(9367401-01), 2022년 이후 순정 키: IYZBK1.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>- U섀시(U06/U10/U11)는 BCP 이모빌라이저 + UWB 키(NCF2951/Hitag Pro/ID49, FCC IYZBK1).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>- E65는 2005 LCI 전 CAS1, 이후 CAS2. E60/E61/E63은 2007.3 LCI 전 CAS2, 이후 CAS3. E83은 2006 중 EWS3→EWS4.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="n"/>
+      <c r="A32" s="21" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="n"/>
+      <c r="A40" s="21" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="n"/>
+      <c r="A49" s="21" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="inlineStr">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="20" t="inlineStr">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>- BMW G60·i5·M5·X7 LCI: 키 프로그래머 업체(Autel·KeyDIY·Xhorse)가 G섀시(G30/G31/G60 2020.7~)를 BDC3, U섀시를 BCP로 구분 — G60은 BDC3 Add Key 대상으로 명시(obdii365·obd2.ltd)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="20" t="inlineStr">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>- BMW XM G09: IYZBK1 키(X5·X6·X7·XM 공용, UWB) — G섀시 BDC3 키 복사·추가 대상(Xhorse G chassis BDC3)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="20" t="inlineStr">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>- BMW X4 F26 2016: 순정 CAS4+ 키 칩은 PCF7953(ID49) — PCF7945P는 "CAS4 modified type" 애프터마켓 키 칩(mk3·vvdi)이라 뺌</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>- BMW E90 CAS3+: 순정 키 칩 PCF7945·PCF7943·PCF7944 모두 ID46(Hitag2) 계열로 병존(bimmerfest·keyecu) — 자료 상충 아님</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>- BMW X3 G45: Lonsdor K518 PRO "2025 BMW X3 UWB에 BCP 키 추가" 절차(U섀시 BCP) 확인 — 이모빌라이저 BCP 확정</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>- BMW X3 F25 2013: CAS4+ 순정 키 칩 PCF7953(ID49) — 같이 적혀 있던 PCF7945P는 중국산 CAS4 호환 키 칩(mr-key·tlkeys 판매품)이라 뺌(X4 F26과 같은 판단)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="20" t="n"/>
+      <c r="A57" s="21" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+      <c r="A58" s="21" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="20" t="inlineStr">
+      <c r="A59" s="21" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="20" t="inlineStr">
+      <c r="A60" s="21" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="21" t="inlineStr">
+        <is>
+          <t>- BMW 순정 부품번호(애프터마켓 대체): 비상키 51215A4FBE5 = F40·F44·G20·G22·G26·G42·G80·G82 등 인서트 키(recambiosyaccesoriosbmw), 51215A65D30 = U06·U10·U11·G60·G70·I20 등 인서트 키, 리모컨 66125A473F4(M 스포츠, ECE+RoW+US) = F40·F44·F9x·G01·G42·G87·G80·G82(hubauer·딜러몰), 66125A47402(기본, ECE+RoW) = G01·G02·G08·G11·G12·G30(schmiedmann), 66125A56076(기본, ECE+RoW) = F15·F16·F39·F45·F46·F48(hubauer), 66128708328(기본, ECE+RoW+US) = F40·G29(hubauer), 66125B3E8E1(M, ECE+RoW) = G60·G70·I20·U06·U10·U11 등, 66129362173 = i3 I01 434MHz(66126805980 대체), 51217127047 = X3 E83 도어·점화 키 — 한국 사양(KO) 번호 적용 차종은 미확인이라 [해외 공용 품번]</t>
         </is>
       </c>
     </row>

--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -188,6 +188,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -2244,7 +2247,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr"/>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -2253,7 +2260,7 @@
       <c r="K25" s="11" t="inlineStr"/>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66129312543[M 스포츠], 66129312524[기본형], 66129312539[럭셔리 라인], 66129312532[스포츠 라인]</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr"/>
@@ -3358,7 +3365,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr"/>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -3820,14 +3831,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr"/>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr"/>
-      <c r="L49" s="11" t="n"/>
+      <c r="L49" s="11" t="inlineStr">
+        <is>
+          <t>66126805997</t>
+        </is>
+      </c>
       <c r="M49" s="11" t="inlineStr"/>
       <c r="N49" s="11" t="inlineStr">
         <is>
@@ -3882,14 +3901,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr"/>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J50" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr"/>
-      <c r="L50" s="11" t="inlineStr"/>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>66126805997</t>
+        </is>
+      </c>
       <c r="M50" s="11" t="inlineStr"/>
       <c r="N50" s="11" t="inlineStr">
         <is>
@@ -4010,14 +4037,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr"/>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J52" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr"/>
-      <c r="L52" s="11" t="inlineStr"/>
+      <c r="L52" s="11" t="inlineStr">
+        <is>
+          <t>66126805997</t>
+        </is>
+      </c>
       <c r="M52" s="11" t="inlineStr"/>
       <c r="N52" s="11" t="inlineStr">
         <is>
@@ -4072,14 +4107,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr"/>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr"/>
-      <c r="L53" s="11" t="inlineStr"/>
+      <c r="L53" s="11" t="inlineStr">
+        <is>
+          <t>66126805997</t>
+        </is>
+      </c>
       <c r="M53" s="11" t="inlineStr"/>
       <c r="N53" s="11" t="inlineStr">
         <is>
@@ -5896,7 +5939,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I81" s="11" t="inlineStr"/>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -5905,7 +5952,7 @@
       <c r="K81" s="11" t="inlineStr"/>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767</t>
+          <t>FCC YGOHUF5767, 66129312543[M 스포츠], 66129312524[기본형], 66129312539[럭셔리 라인], 66129312532[스포츠 라인]</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr"/>
@@ -6226,7 +6273,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I86" s="11" t="inlineStr"/>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -6235,7 +6286,7 @@
       <c r="K86" s="11" t="inlineStr"/>
       <c r="L86" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A[4버튼]</t>
+          <t>FCC N5F-ID21A[4버튼], 66128708356[M 스포츠], 66128708340[기본형], 66128708372[인디비주얼]</t>
         </is>
       </c>
       <c r="M86" s="11" t="inlineStr"/>
@@ -6292,7 +6343,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I87" s="11" t="inlineStr"/>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J87" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -6301,7 +6356,7 @@
       <c r="K87" s="11" t="inlineStr"/>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128708356[M 스포츠], 66128708340[기본형], 66128708372[인디비주얼]</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr"/>
@@ -6820,7 +6875,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I95" s="11" t="inlineStr"/>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J95" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -6886,7 +6945,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I96" s="11" t="inlineStr"/>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -7604,7 +7667,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I107" s="11" t="inlineStr"/>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J107" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -7613,7 +7680,7 @@
       <c r="K107" s="11" t="inlineStr"/>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662[4버튼]</t>
+          <t>FCC YGOHUF5662[4버튼], 66128723582[M 스포츠], 66129254893[기본형], 66129254909[럭셔리 라인], 66129254897[모던 라인], 66129254901[스포츠 라인]</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr"/>
@@ -8656,7 +8723,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I123" s="11" t="inlineStr"/>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J123" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -8722,7 +8793,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I124" s="11" t="inlineStr"/>
+      <c r="I124" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J124" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -8788,7 +8863,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I125" s="11" t="inlineStr"/>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J125" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -9653,7 +9732,11 @@
         </is>
       </c>
       <c r="K138" s="11" t="inlineStr"/>
-      <c r="L138" s="11" t="inlineStr"/>
+      <c r="L138" s="11" t="inlineStr">
+        <is>
+          <t>66126933076</t>
+        </is>
+      </c>
       <c r="M138" s="11" t="inlineStr"/>
       <c r="N138" s="11" t="inlineStr">
         <is>
@@ -9717,7 +9800,7 @@
       <c r="K139" s="11" t="inlineStr"/>
       <c r="L139" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK47[4버튼]</t>
+          <t>FCC KR55WK47[4버튼], 66126933076</t>
         </is>
       </c>
       <c r="M139" s="11" t="inlineStr"/>
@@ -9774,7 +9857,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I140" s="11" t="inlineStr"/>
+      <c r="I140" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J140" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -9783,7 +9870,7 @@
       <c r="K140" s="11" t="inlineStr"/>
       <c r="L140" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK47993</t>
+          <t>FCC KR55WK47993, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M140" s="11" t="inlineStr"/>
@@ -9840,7 +9927,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I141" s="11" t="inlineStr"/>
+      <c r="I141" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J141" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -9849,7 +9940,7 @@
       <c r="K141" s="11" t="inlineStr"/>
       <c r="L141" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK47</t>
+          <t>FCC KR55WK47, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M141" s="11" t="inlineStr"/>
@@ -9906,7 +9997,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I142" s="11" t="n"/>
+      <c r="I142" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J142" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -9915,7 +10010,7 @@
       <c r="K142" s="11" t="n"/>
       <c r="L142" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49123, FCC KR55WK49127[리모컨키]</t>
+          <t>FCC KR55WK49123, FCC KR55WK49127[리모컨키], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M142" s="11" t="n"/>
@@ -9972,7 +10067,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I143" s="11" t="n"/>
+      <c r="I143" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J143" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -9981,7 +10080,7 @@
       <c r="K143" s="11" t="n"/>
       <c r="L143" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49123, FCC KR55WK49127[리모컨키]</t>
+          <t>FCC KR55WK49123, FCC KR55WK49127[리모컨키], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M143" s="11" t="n"/>
@@ -10170,7 +10269,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I146" s="11" t="inlineStr"/>
+      <c r="I146" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J146" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -10179,7 +10282,7 @@
       <c r="K146" s="11" t="inlineStr"/>
       <c r="L146" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[리모컨키], FCC KR55WK49147[컴포트액세스]</t>
+          <t>FCC KR55WK49127[리모컨키], FCC KR55WK49147[컴포트액세스], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M146" s="11" t="inlineStr"/>
@@ -10236,7 +10339,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I147" s="11" t="n"/>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J147" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -10245,7 +10352,7 @@
       <c r="K147" s="11" t="inlineStr"/>
       <c r="L147" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[리모컨키]</t>
+          <t>FCC KR55WK49127[리모컨키], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M147" s="11" t="inlineStr"/>
@@ -10368,7 +10475,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I149" s="11" t="inlineStr"/>
+      <c r="I149" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J149" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -10377,7 +10488,7 @@
       <c r="K149" s="11" t="inlineStr"/>
       <c r="L149" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49863</t>
+          <t>FCC KR55WK49863, 66129284934[럭셔리 라인], 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M149" s="11" t="inlineStr"/>
@@ -10434,7 +10545,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I150" s="11" t="n"/>
+      <c r="I150" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J150" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -10443,7 +10558,7 @@
       <c r="K150" s="11" t="n"/>
       <c r="L150" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49863</t>
+          <t>FCC KR55WK49863, 66129284934[럭셔리 라인], 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M150" s="11" t="n"/>
@@ -10500,7 +10615,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I151" s="11" t="n"/>
+      <c r="I151" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J151" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -10509,7 +10628,7 @@
       <c r="K151" s="11" t="n"/>
       <c r="L151" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49863</t>
+          <t>FCC KR55WK49863, 66129284934[럭셔리 라인], 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M151" s="11" t="n"/>
@@ -10566,7 +10685,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I152" s="11" t="inlineStr"/>
+      <c r="I152" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J152" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -10575,7 +10698,7 @@
       <c r="K152" s="11" t="inlineStr"/>
       <c r="L152" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49863</t>
+          <t>FCC KR55WK49863, 66129284934[럭셔리 라인], 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M152" s="11" t="inlineStr"/>
@@ -10632,7 +10755,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I153" s="11" t="inlineStr"/>
+      <c r="I153" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J153" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -10641,7 +10768,7 @@
       <c r="K153" s="11" t="inlineStr"/>
       <c r="L153" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767[4버튼]</t>
+          <t>FCC YGOHUF5767[4버튼], 66129284934[럭셔리 라인], 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M153" s="11" t="inlineStr"/>
@@ -10698,7 +10825,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I154" s="11" t="inlineStr"/>
+      <c r="I154" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J154" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -10707,7 +10838,7 @@
       <c r="K154" s="11" t="inlineStr"/>
       <c r="L154" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767</t>
+          <t>FCC YGOHUF5767, 66129284934[럭셔리 라인], 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M154" s="11" t="inlineStr"/>
@@ -10764,7 +10895,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I155" s="11" t="inlineStr"/>
+      <c r="I155" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J155" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -10773,7 +10908,7 @@
       <c r="K155" s="11" t="inlineStr"/>
       <c r="L155" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767</t>
+          <t>FCC YGOHUF5767, 66129284934[럭셔리 라인], 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M155" s="11" t="inlineStr"/>
@@ -10830,7 +10965,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I156" s="11" t="inlineStr"/>
+      <c r="I156" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J156" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -10839,7 +10978,7 @@
       <c r="K156" s="11" t="inlineStr"/>
       <c r="L156" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49863, FCC YGOHUF5767</t>
+          <t>FCC KR55WK49863, FCC YGOHUF5767, 66129284934[럭셔리 라인], 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M156" s="11" t="inlineStr"/>
@@ -11028,14 +11167,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I159" s="11" t="n"/>
+      <c r="I159" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J159" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K159" s="11" t="n"/>
-      <c r="L159" s="11" t="n"/>
+      <c r="L159" s="11" t="inlineStr">
+        <is>
+          <t>66129284934[럭셔리 라인], 66129259720[컴포트액세스]</t>
+        </is>
+      </c>
       <c r="M159" s="11" t="n"/>
       <c r="N159" s="11" t="inlineStr">
         <is>
@@ -11090,14 +11237,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I160" s="11" t="n"/>
+      <c r="I160" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J160" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K160" s="11" t="n"/>
-      <c r="L160" s="11" t="n"/>
+      <c r="L160" s="11" t="inlineStr">
+        <is>
+          <t>66129284934[럭셔리 라인], 66129259720[컴포트액세스]</t>
+        </is>
+      </c>
       <c r="M160" s="11" t="n"/>
       <c r="N160" s="11" t="inlineStr">
         <is>
@@ -11284,7 +11439,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I163" s="11" t="inlineStr"/>
+      <c r="I163" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J163" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -11293,7 +11452,7 @@
       <c r="K163" s="11" t="inlineStr"/>
       <c r="L163" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662, FCC KR55WK49863</t>
+          <t>FCC YGOHUF5662, FCC KR55WK49863, 66129284934[럭셔리 라인], 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M163" s="11" t="inlineStr"/>
@@ -11416,7 +11575,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I165" s="11" t="inlineStr"/>
+      <c r="I165" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J165" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -11425,7 +11588,7 @@
       <c r="K165" s="11" t="inlineStr"/>
       <c r="L165" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662</t>
+          <t>FCC YGOHUF5662, 66129284934[럭셔리 라인], 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M165" s="11" t="inlineStr"/>
@@ -11680,7 +11843,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I169" s="11" t="n"/>
+      <c r="I169" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J169" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -11689,7 +11856,7 @@
       <c r="K169" s="11" t="n"/>
       <c r="L169" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717527[M 스포츠], 66128717511[기본형], 66128779008[디스플레이키], 66128717535[인디비주얼]</t>
         </is>
       </c>
       <c r="M169" s="11" t="n"/>
@@ -11746,7 +11913,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I170" s="11" t="n"/>
+      <c r="I170" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J170" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -11755,7 +11926,7 @@
       <c r="K170" s="11" t="n"/>
       <c r="L170" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717527[M 스포츠], 66128717511[기본형], 66128779008[디스플레이키], 66128717535[인디비주얼]</t>
         </is>
       </c>
       <c r="M170" s="11" t="n"/>
@@ -12830,7 +13001,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I186" s="11" t="inlineStr"/>
+      <c r="I186" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J186" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -12839,7 +13014,7 @@
       <c r="K186" s="11" t="inlineStr"/>
       <c r="L186" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK47993[3버튼]</t>
+          <t>FCC KR55WK47993[3버튼], 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M186" s="11" t="inlineStr"/>
@@ -12896,7 +13071,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I187" s="11" t="inlineStr"/>
+      <c r="I187" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J187" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -12905,7 +13084,7 @@
       <c r="K187" s="11" t="inlineStr"/>
       <c r="L187" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK47[4버튼]</t>
+          <t>FCC KR55WK47[4버튼], 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M187" s="11" t="inlineStr"/>
@@ -12962,7 +13141,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I188" s="11" t="n"/>
+      <c r="I188" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J188" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -12971,7 +13154,7 @@
       <c r="K188" s="11" t="n"/>
       <c r="L188" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[리모컨키], FCC KR55WK49147[컴포트액세스]</t>
+          <t>FCC KR55WK49127[리모컨키], FCC KR55WK49147[컴포트액세스], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M188" s="11" t="n"/>
@@ -13028,7 +13211,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I189" s="11" t="n"/>
+      <c r="I189" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J189" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -13037,7 +13224,7 @@
       <c r="K189" s="11" t="n"/>
       <c r="L189" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[리모컨키], FCC KR55WK49147[컴포트액세스]</t>
+          <t>FCC KR55WK49127[리모컨키], FCC KR55WK49147[컴포트액세스], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M189" s="11" t="n"/>
@@ -13094,7 +13281,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I190" s="11" t="n"/>
+      <c r="I190" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J190" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -13103,7 +13294,7 @@
       <c r="K190" s="11" t="n"/>
       <c r="L190" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147[컴포트액세스]</t>
+          <t>FCC KR55WK49147[컴포트액세스], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M190" s="11" t="n"/>
@@ -13160,7 +13351,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I191" s="11" t="n"/>
+      <c r="I191" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J191" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -13169,7 +13364,7 @@
       <c r="K191" s="11" t="n"/>
       <c r="L191" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147[컴포트액세스]</t>
+          <t>FCC KR55WK49147[컴포트액세스], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M191" s="11" t="n"/>
@@ -13226,7 +13421,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I192" s="11" t="inlineStr"/>
+      <c r="I192" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J192" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -13235,7 +13434,7 @@
       <c r="K192" s="11" t="inlineStr"/>
       <c r="L192" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[리모컨키]</t>
+          <t>FCC KR55WK49127[리모컨키], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M192" s="11" t="inlineStr"/>
@@ -13292,7 +13491,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I193" s="11" t="inlineStr"/>
+      <c r="I193" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J193" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -13301,7 +13504,7 @@
       <c r="K193" s="11" t="inlineStr"/>
       <c r="L193" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[리모컨키]</t>
+          <t>FCC KR55WK49127[리모컨키], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M193" s="11" t="inlineStr"/>
@@ -13424,7 +13627,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I195" s="11" t="n"/>
+      <c r="I195" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J195" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -13433,7 +13640,7 @@
       <c r="K195" s="11" t="n"/>
       <c r="L195" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49863, FCC YGOHUF5662</t>
+          <t>FCC KR55WK49863, FCC YGOHUF5662, 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M195" s="11" t="n"/>
@@ -13490,7 +13697,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I196" s="11" t="n"/>
+      <c r="I196" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J196" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -13499,7 +13710,7 @@
       <c r="K196" s="11" t="n"/>
       <c r="L196" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49863, FCC YGOHUF5662</t>
+          <t>FCC KR55WK49863, FCC YGOHUF5662, 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M196" s="11" t="n"/>
@@ -13556,7 +13767,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I197" s="11" t="inlineStr"/>
+      <c r="I197" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J197" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -13565,7 +13780,7 @@
       <c r="K197" s="11" t="inlineStr"/>
       <c r="L197" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767</t>
+          <t>FCC YGOHUF5767, 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M197" s="11" t="inlineStr"/>
@@ -13622,7 +13837,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I198" s="11" t="inlineStr"/>
+      <c r="I198" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J198" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -13631,7 +13850,7 @@
       <c r="K198" s="11" t="inlineStr"/>
       <c r="L198" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767</t>
+          <t>FCC YGOHUF5767, 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M198" s="11" t="inlineStr"/>
@@ -13688,7 +13907,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I199" s="11" t="inlineStr"/>
+      <c r="I199" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J199" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -13697,7 +13920,7 @@
       <c r="K199" s="11" t="inlineStr"/>
       <c r="L199" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767</t>
+          <t>FCC YGOHUF5767, 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M199" s="11" t="inlineStr"/>
@@ -13754,7 +13977,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I200" s="11" t="inlineStr"/>
+      <c r="I200" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J200" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -13763,7 +13990,7 @@
       <c r="K200" s="11" t="inlineStr"/>
       <c r="L200" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767</t>
+          <t>FCC YGOHUF5767, 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M200" s="11" t="inlineStr"/>
@@ -13820,7 +14047,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I201" s="11" t="inlineStr"/>
+      <c r="I201" s="11" t="inlineStr">
+        <is>
+          <t>51217293906[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J201" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -13829,7 +14060,7 @@
       <c r="K201" s="11" t="inlineStr"/>
       <c r="L201" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662, FCC YGOHUF5767</t>
+          <t>FCC YGOHUF5662, FCC YGOHUF5767, 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M201" s="11" t="inlineStr"/>
@@ -14018,7 +14249,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I204" s="11" t="n"/>
+      <c r="I204" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J204" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -14027,7 +14262,7 @@
       <c r="K204" s="11" t="n"/>
       <c r="L204" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717527[M 스포츠], 66128779004[디스플레이키]</t>
         </is>
       </c>
       <c r="M204" s="11" t="n"/>
@@ -14084,7 +14319,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I205" s="11" t="n"/>
+      <c r="I205" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J205" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -14093,7 +14332,7 @@
       <c r="K205" s="11" t="n"/>
       <c r="L205" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717527[M 스포츠], 66128779004[디스플레이키]</t>
         </is>
       </c>
       <c r="M205" s="11" t="n"/>
@@ -14623,7 +14862,11 @@
         </is>
       </c>
       <c r="K213" s="11" t="inlineStr"/>
-      <c r="L213" s="11" t="inlineStr"/>
+      <c r="L213" s="11" t="inlineStr">
+        <is>
+          <t>66126933076</t>
+        </is>
+      </c>
       <c r="M213" s="11" t="inlineStr"/>
       <c r="N213" s="11" t="inlineStr">
         <is>
@@ -14687,7 +14930,7 @@
       <c r="K214" s="11" t="inlineStr"/>
       <c r="L214" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK47[4버튼]</t>
+          <t>FCC KR55WK47[4버튼], 66126933076</t>
         </is>
       </c>
       <c r="M214" s="11" t="inlineStr"/>
@@ -14744,7 +14987,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I215" s="11" t="inlineStr"/>
+      <c r="I215" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J215" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -14753,7 +15000,7 @@
       <c r="K215" s="11" t="inlineStr"/>
       <c r="L215" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK47993</t>
+          <t>FCC KR55WK47993, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M215" s="11" t="inlineStr"/>
@@ -14810,7 +15057,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I216" s="11" t="inlineStr"/>
+      <c r="I216" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J216" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -14819,7 +15070,7 @@
       <c r="K216" s="11" t="inlineStr"/>
       <c r="L216" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK47, FCC LX8FZV</t>
+          <t>FCC KR55WK47, FCC LX8FZV, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M216" s="11" t="inlineStr"/>
@@ -14876,7 +15127,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I217" s="11" t="n"/>
+      <c r="I217" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J217" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -14885,7 +15140,7 @@
       <c r="K217" s="11" t="n"/>
       <c r="L217" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[리모컨키], FCC KR55WK49147[컴포트액세스]</t>
+          <t>FCC KR55WK49127[리모컨키], FCC KR55WK49147[컴포트액세스], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M217" s="11" t="n"/>
@@ -14942,7 +15197,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I218" s="11" t="n"/>
+      <c r="I218" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J218" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -14951,7 +15210,7 @@
       <c r="K218" s="11" t="n"/>
       <c r="L218" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[리모컨키], FCC KR55WK49147[컴포트액세스]</t>
+          <t>FCC KR55WK49127[리모컨키], FCC KR55WK49147[컴포트액세스], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M218" s="11" t="n"/>
@@ -15140,7 +15399,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I221" s="11" t="inlineStr"/>
+      <c r="I221" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J221" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -15149,7 +15412,7 @@
       <c r="K221" s="11" t="inlineStr"/>
       <c r="L221" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[리모컨키]</t>
+          <t>FCC KR55WK49127[리모컨키], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M221" s="11" t="inlineStr"/>
@@ -15206,7 +15469,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I222" s="11" t="inlineStr"/>
+      <c r="I222" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J222" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -15215,7 +15482,7 @@
       <c r="K222" s="11" t="inlineStr"/>
       <c r="L222" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[리모컨키]</t>
+          <t>FCC KR55WK49127[리모컨키], 66126986584, 66129268487[컴포트액세스]</t>
         </is>
       </c>
       <c r="M222" s="11" t="inlineStr"/>
@@ -15272,7 +15539,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I223" s="11" t="inlineStr"/>
+      <c r="I223" s="11" t="inlineStr">
+        <is>
+          <t>51217227123[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J223" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -15281,7 +15552,7 @@
       <c r="K223" s="11" t="inlineStr"/>
       <c r="L223" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49863, FCC YGOHUF5662</t>
+          <t>FCC KR55WK49863, FCC YGOHUF5662, 66129259716[컴포트액세스]</t>
         </is>
       </c>
       <c r="M223" s="11" t="inlineStr"/>
@@ -15338,7 +15609,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I224" s="11" t="n"/>
+      <c r="I224" s="11" t="inlineStr">
+        <is>
+          <t>51217227123[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J224" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -15347,7 +15622,7 @@
       <c r="K224" s="11" t="n"/>
       <c r="L224" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662</t>
+          <t>FCC YGOHUF5662, 66129259716[컴포트액세스]</t>
         </is>
       </c>
       <c r="M224" s="11" t="n"/>
@@ -15404,7 +15679,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I225" s="11" t="n"/>
+      <c r="I225" s="11" t="inlineStr">
+        <is>
+          <t>51217227123[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J225" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -15413,7 +15692,7 @@
       <c r="K225" s="11" t="n"/>
       <c r="L225" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662</t>
+          <t>FCC YGOHUF5662, 66129259716[컴포트액세스]</t>
         </is>
       </c>
       <c r="M225" s="11" t="n"/>
@@ -15998,7 +16277,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I234" s="11" t="inlineStr"/>
+      <c r="I234" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J234" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -16007,7 +16290,7 @@
       <c r="K234" s="11" t="inlineStr"/>
       <c r="L234" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717527[M 스포츠], 66128717511[기본형], 66128779008[디스플레이키]</t>
         </is>
       </c>
       <c r="M234" s="11" t="inlineStr"/>
@@ -16064,7 +16347,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I235" s="11" t="n"/>
+      <c r="I235" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J235" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -16073,7 +16360,7 @@
       <c r="K235" s="11" t="n"/>
       <c r="L235" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717527[M 스포츠], 66128717511[기본형], 66128779008[디스플레이키]</t>
         </is>
       </c>
       <c r="M235" s="11" t="n"/>
@@ -16130,7 +16417,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I236" s="11" t="n"/>
+      <c r="I236" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J236" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -16139,7 +16430,7 @@
       <c r="K236" s="11" t="n"/>
       <c r="L236" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717527[M 스포츠], 66128717511[기본형], 66128779008[디스플레이키]</t>
         </is>
       </c>
       <c r="M236" s="11" t="n"/>
@@ -16390,7 +16681,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I240" s="11" t="inlineStr"/>
+      <c r="I240" s="11" t="inlineStr">
+        <is>
+          <t>51217227123[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J240" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -16399,7 +16694,7 @@
       <c r="K240" s="11" t="inlineStr"/>
       <c r="L240" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49863</t>
+          <t>FCC KR55WK49863, 66129259716[컴포트액세스]</t>
         </is>
       </c>
       <c r="M240" s="11" t="inlineStr"/>
@@ -16456,7 +16751,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I241" s="11" t="n"/>
+      <c r="I241" s="11" t="inlineStr">
+        <is>
+          <t>51217227123[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J241" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -16465,7 +16764,7 @@
       <c r="K241" s="11" t="n"/>
       <c r="L241" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49863, FCC YGOHUF5662</t>
+          <t>FCC KR55WK49863, FCC YGOHUF5662, 66129259716[컴포트액세스]</t>
         </is>
       </c>
       <c r="M241" s="11" t="n"/>
@@ -16522,7 +16821,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I242" s="11" t="n"/>
+      <c r="I242" s="11" t="inlineStr">
+        <is>
+          <t>51217227123[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J242" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -16531,7 +16834,7 @@
       <c r="K242" s="11" t="n"/>
       <c r="L242" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49863, FCC YGOHUF5662</t>
+          <t>FCC KR55WK49863, FCC YGOHUF5662, 66129259716[컴포트액세스]</t>
         </is>
       </c>
       <c r="M242" s="11" t="n"/>
@@ -16588,7 +16891,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I243" s="11" t="inlineStr"/>
+      <c r="I243" s="11" t="inlineStr">
+        <is>
+          <t>51217227123[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J243" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -16597,7 +16904,7 @@
       <c r="K243" s="11" t="inlineStr"/>
       <c r="L243" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767</t>
+          <t>FCC YGOHUF5767, 66129259716[컴포트액세스]</t>
         </is>
       </c>
       <c r="M243" s="11" t="inlineStr"/>
@@ -16654,7 +16961,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I244" s="11" t="inlineStr"/>
+      <c r="I244" s="11" t="inlineStr">
+        <is>
+          <t>51217227123[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J244" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -16663,7 +16974,7 @@
       <c r="K244" s="11" t="inlineStr"/>
       <c r="L244" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662</t>
+          <t>FCC YGOHUF5662, 66129259716[컴포트액세스]</t>
         </is>
       </c>
       <c r="M244" s="11" t="inlineStr"/>
@@ -17190,7 +17501,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I252" s="11" t="inlineStr"/>
+      <c r="I252" s="11" t="inlineStr">
+        <is>
+          <t>51217066345[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J252" s="11" t="inlineStr">
         <is>
           <t>HU92[비상키]</t>
@@ -17199,7 +17514,7 @@
       <c r="K252" s="11" t="inlineStr"/>
       <c r="L252" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8766S</t>
+          <t>FCC LX8766S, 66126959045, 66126959060[컴포트액세스]</t>
         </is>
       </c>
       <c r="M252" s="11" t="inlineStr"/>
@@ -17256,7 +17571,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I253" s="11" t="inlineStr"/>
+      <c r="I253" s="11" t="inlineStr">
+        <is>
+          <t>51217066345[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J253" s="11" t="inlineStr">
         <is>
           <t>HU92[비상키]</t>
@@ -17265,7 +17584,7 @@
       <c r="K253" s="11" t="inlineStr"/>
       <c r="L253" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8766S</t>
+          <t>FCC LX8766S, 66126959045, 66126959060[컴포트액세스]</t>
         </is>
       </c>
       <c r="M253" s="11" t="inlineStr"/>
@@ -17322,7 +17641,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I254" s="11" t="n"/>
+      <c r="I254" s="11" t="inlineStr">
+        <is>
+          <t>51217066345[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J254" s="11" t="inlineStr">
         <is>
           <t>HU92[비상키]</t>
@@ -17331,7 +17654,7 @@
       <c r="K254" s="11" t="n"/>
       <c r="L254" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8766S</t>
+          <t>FCC LX8766S, 66126959045, 66126959060[컴포트액세스]</t>
         </is>
       </c>
       <c r="M254" s="11" t="n"/>
@@ -17388,7 +17711,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I255" s="11" t="n"/>
+      <c r="I255" s="11" t="inlineStr">
+        <is>
+          <t>51217066345[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J255" s="11" t="inlineStr">
         <is>
           <t>HU92[비상키]</t>
@@ -17397,7 +17724,7 @@
       <c r="K255" s="11" t="n"/>
       <c r="L255" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8766S</t>
+          <t>FCC LX8766S, 66126959045, 66126959060[컴포트액세스]</t>
         </is>
       </c>
       <c r="M255" s="11" t="n"/>
@@ -17454,7 +17781,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I256" s="11" t="inlineStr"/>
+      <c r="I256" s="11" t="inlineStr">
+        <is>
+          <t>51217066345[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J256" s="11" t="inlineStr">
         <is>
           <t>HU92[비상키]</t>
@@ -17463,7 +17794,7 @@
       <c r="K256" s="11" t="inlineStr"/>
       <c r="L256" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8766S</t>
+          <t>FCC LX8766S, 66126959045, 66126959060[컴포트액세스]</t>
         </is>
       </c>
       <c r="M256" s="11" t="inlineStr"/>
@@ -17520,7 +17851,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I257" s="11" t="inlineStr"/>
+      <c r="I257" s="11" t="inlineStr">
+        <is>
+          <t>51217066345[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J257" s="11" t="inlineStr">
         <is>
           <t>HU92[비상키]</t>
@@ -17529,7 +17864,7 @@
       <c r="K257" s="11" t="inlineStr"/>
       <c r="L257" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8766S</t>
+          <t>FCC LX8766S, 66126959045, 66126959060[컴포트액세스]</t>
         </is>
       </c>
       <c r="M257" s="11" t="inlineStr"/>
@@ -17586,7 +17921,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I258" s="11" t="inlineStr"/>
+      <c r="I258" s="11" t="inlineStr">
+        <is>
+          <t>51217066345[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J258" s="11" t="inlineStr">
         <is>
           <t>HU92[비상키]</t>
@@ -17595,7 +17934,7 @@
       <c r="K258" s="11" t="inlineStr"/>
       <c r="L258" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8766S</t>
+          <t>FCC LX8766S, 66126959045, 66126959060[컴포트액세스]</t>
         </is>
       </c>
       <c r="M258" s="11" t="inlineStr"/>
@@ -17982,7 +18321,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I264" s="11" t="inlineStr"/>
+      <c r="I264" s="11" t="inlineStr">
+        <is>
+          <t>51217227123[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J264" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -17991,7 +18334,7 @@
       <c r="K264" s="11" t="inlineStr"/>
       <c r="L264" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767</t>
+          <t>FCC YGOHUF5767, 66129259716[컴포트액세스]</t>
         </is>
       </c>
       <c r="M264" s="11" t="inlineStr"/>
@@ -18048,7 +18391,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I265" s="11" t="inlineStr"/>
+      <c r="I265" s="11" t="inlineStr">
+        <is>
+          <t>51217227123[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J265" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -18057,7 +18404,7 @@
       <c r="K265" s="11" t="inlineStr"/>
       <c r="L265" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767</t>
+          <t>FCC YGOHUF5767, 66129259716[컴포트액세스]</t>
         </is>
       </c>
       <c r="M265" s="11" t="inlineStr"/>
@@ -18114,7 +18461,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I266" s="11" t="inlineStr"/>
+      <c r="I266" s="11" t="inlineStr">
+        <is>
+          <t>51217227123[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J266" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -18123,7 +18474,7 @@
       <c r="K266" s="11" t="inlineStr"/>
       <c r="L266" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5767</t>
+          <t>FCC YGOHUF5767, 66129259716[컴포트액세스]</t>
         </is>
       </c>
       <c r="M266" s="11" t="inlineStr"/>
@@ -18378,7 +18729,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I270" s="11" t="inlineStr"/>
+      <c r="I270" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J270" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -18387,7 +18742,7 @@
       <c r="K270" s="11" t="inlineStr"/>
       <c r="L270" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128808897[M 스포츠], 66128808880[기본형], 66128806245[디스플레이키], 66128808905[인디비주얼]</t>
         </is>
       </c>
       <c r="M270" s="11" t="inlineStr"/>
@@ -18444,7 +18799,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I271" s="11" t="n"/>
+      <c r="I271" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J271" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -18453,7 +18812,7 @@
       <c r="K271" s="11" t="n"/>
       <c r="L271" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717527[M 스포츠], 66128717511[기본형], 66128779008[디스플레이키], 66128717535[인디비주얼]</t>
         </is>
       </c>
       <c r="M271" s="11" t="n"/>
@@ -18510,7 +18869,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I272" s="11" t="n"/>
+      <c r="I272" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J272" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -18519,7 +18882,7 @@
       <c r="K272" s="11" t="n"/>
       <c r="L272" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717527[M 스포츠], 66128717511[기본형], 66128779008[디스플레이키], 66128717535[인디비주얼]</t>
         </is>
       </c>
       <c r="M272" s="11" t="n"/>
@@ -18576,7 +18939,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I273" s="11" t="inlineStr"/>
+      <c r="I273" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J273" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -18585,7 +18952,7 @@
       <c r="K273" s="11" t="inlineStr"/>
       <c r="L273" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717527[M 스포츠], 66128717511[기본형], 66128779008[디스플레이키], 66128717535[인디비주얼]</t>
         </is>
       </c>
       <c r="M273" s="11" t="inlineStr"/>
@@ -19500,7 +19867,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I287" s="11" t="inlineStr"/>
+      <c r="I287" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J287" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -19509,7 +19880,7 @@
       <c r="K287" s="11" t="inlineStr"/>
       <c r="L287" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128708348, 66128708364[M 스포츠], 66129855654[디스플레이키], 66128708372[인디비주얼]</t>
         </is>
       </c>
       <c r="M287" s="11" t="inlineStr"/>
@@ -20754,7 +21125,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I306" s="11" t="inlineStr"/>
+      <c r="I306" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J306" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -20763,7 +21138,7 @@
       <c r="K306" s="11" t="inlineStr"/>
       <c r="L306" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[리모컨키]</t>
+          <t>FCC KR55WK49127[리모컨키], 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M306" s="11" t="inlineStr"/>
@@ -20886,7 +21261,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I308" s="11" t="inlineStr"/>
+      <c r="I308" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J308" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -20895,7 +21274,7 @@
       <c r="K308" s="11" t="inlineStr"/>
       <c r="L308" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66126805998[M 스포츠, 해외 공용 품번], 66126805990[기본형, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M308" s="11" t="inlineStr"/>
@@ -20952,7 +21331,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I309" s="11" t="inlineStr"/>
+      <c r="I309" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J309" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -20961,7 +21344,7 @@
       <c r="K309" s="11" t="inlineStr"/>
       <c r="L309" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66126805998[M 스포츠, 해외 공용 품번], 66126805990[기본형, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M309" s="11" t="inlineStr"/>
@@ -21018,7 +21401,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I310" s="11" t="inlineStr"/>
+      <c r="I310" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J310" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -21027,7 +21414,7 @@
       <c r="K310" s="11" t="inlineStr"/>
       <c r="L310" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66126805998[M 스포츠, 해외 공용 품번], 66126805990[기본형, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M310" s="11" t="inlineStr"/>
@@ -21084,14 +21471,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I311" s="11" t="inlineStr"/>
+      <c r="I311" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J311" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K311" s="11" t="inlineStr"/>
-      <c r="L311" s="11" t="n"/>
+      <c r="L311" s="11" t="inlineStr">
+        <is>
+          <t>66126805998[M 스포츠, 해외 공용 품번], 66126805990[기본형, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M311" s="11" t="inlineStr"/>
       <c r="N311" s="11" t="inlineStr">
         <is>
@@ -21146,14 +21541,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I312" s="11" t="inlineStr"/>
+      <c r="I312" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J312" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K312" s="11" t="inlineStr"/>
-      <c r="L312" s="11" t="n"/>
+      <c r="L312" s="11" t="inlineStr">
+        <is>
+          <t>66126805990[기본형, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M312" s="11" t="inlineStr"/>
       <c r="N312" s="11" t="inlineStr">
         <is>
@@ -21876,7 +22279,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I323" s="11" t="inlineStr"/>
+      <c r="I323" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J323" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -21885,7 +22292,7 @@
       <c r="K323" s="11" t="inlineStr"/>
       <c r="L323" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66126805998[M 스포츠, 해외 공용 품번], 66126805990[기본형, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M323" s="11" t="inlineStr"/>
@@ -21942,7 +22349,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I324" s="11" t="inlineStr"/>
+      <c r="I324" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J324" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -21951,7 +22362,7 @@
       <c r="K324" s="11" t="inlineStr"/>
       <c r="L324" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66126805998[M 스포츠, 해외 공용 품번], 66126805990[기본형, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M324" s="11" t="inlineStr"/>
@@ -23014,7 +23425,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I340" s="11" t="inlineStr"/>
+      <c r="I340" s="11" t="inlineStr">
+        <is>
+          <t>51217127047[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J340" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -23023,7 +23438,7 @@
       <c r="K340" s="11" t="inlineStr"/>
       <c r="L340" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번], 51218374933[적외선 리모컨]</t>
         </is>
       </c>
       <c r="M340" s="11" t="inlineStr"/>
@@ -23080,7 +23495,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I341" s="11" t="inlineStr"/>
+      <c r="I341" s="11" t="inlineStr">
+        <is>
+          <t>51217127047[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J341" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -23089,7 +23508,7 @@
       <c r="K341" s="11" t="inlineStr"/>
       <c r="L341" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번], 51218374933[적외선 리모컨]</t>
         </is>
       </c>
       <c r="M341" s="11" t="inlineStr"/>
@@ -23146,14 +23565,22 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I342" s="11" t="inlineStr"/>
+      <c r="I342" s="11" t="inlineStr">
+        <is>
+          <t>51217127047[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J342" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
         </is>
       </c>
       <c r="K342" s="11" t="inlineStr"/>
-      <c r="L342" s="11" t="inlineStr"/>
+      <c r="L342" s="11" t="inlineStr">
+        <is>
+          <t>66126955747[해외 공용 품번], 51218374933[적외선 리모컨]</t>
+        </is>
+      </c>
       <c r="M342" s="11" t="inlineStr"/>
       <c r="N342" s="11" t="inlineStr">
         <is>
@@ -23208,7 +23635,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I343" s="11" t="inlineStr"/>
+      <c r="I343" s="11" t="inlineStr">
+        <is>
+          <t>51217127047[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J343" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -23217,7 +23648,7 @@
       <c r="K343" s="11" t="inlineStr"/>
       <c r="L343" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번], 51218374933[적외선 리모컨]</t>
         </is>
       </c>
       <c r="M343" s="11" t="inlineStr"/>
@@ -23274,14 +23705,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I344" s="11" t="inlineStr"/>
+      <c r="I344" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J344" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
         </is>
       </c>
       <c r="K344" s="11" t="inlineStr"/>
-      <c r="L344" s="11" t="inlineStr"/>
+      <c r="L344" s="11" t="inlineStr">
+        <is>
+          <t>66129259720[컴포트액세스]</t>
+        </is>
+      </c>
       <c r="M344" s="11" t="inlineStr"/>
       <c r="N344" s="11" t="inlineStr">
         <is>
@@ -23336,7 +23775,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I345" s="11" t="n"/>
+      <c r="I345" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J345" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -23345,7 +23788,7 @@
       <c r="K345" s="11" t="n"/>
       <c r="L345" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662</t>
+          <t>FCC YGOHUF5662, 66129254893[기본형], 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M345" s="11" t="n"/>
@@ -23402,7 +23845,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I346" s="11" t="n"/>
+      <c r="I346" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J346" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -23411,7 +23858,7 @@
       <c r="K346" s="11" t="n"/>
       <c r="L346" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662</t>
+          <t>FCC YGOHUF5662, 66129254893[기본형], 66129259720[컴포트액세스]</t>
         </is>
       </c>
       <c r="M346" s="11" t="n"/>
@@ -23600,7 +24047,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I349" s="11" t="n"/>
+      <c r="I349" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J349" s="11" t="inlineStr">
         <is>
           <t>HU100R</t>
@@ -23609,7 +24060,7 @@
       <c r="K349" s="11" t="inlineStr"/>
       <c r="L349" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662, FCC KR55WK49863</t>
+          <t>FCC YGOHUF5662, FCC KR55WK49863, 66129254893[기본형]</t>
         </is>
       </c>
       <c r="M349" s="11" t="inlineStr"/>
@@ -23666,14 +24117,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I350" s="11" t="inlineStr"/>
+      <c r="I350" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J350" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K350" s="11" t="inlineStr"/>
-      <c r="L350" s="11" t="inlineStr"/>
+      <c r="L350" s="11" t="inlineStr">
+        <is>
+          <t>66129254893[기본형]</t>
+        </is>
+      </c>
       <c r="M350" s="11" t="inlineStr"/>
       <c r="N350" s="11" t="inlineStr">
         <is>
@@ -23728,14 +24187,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I351" s="11" t="inlineStr"/>
+      <c r="I351" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J351" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K351" s="11" t="inlineStr"/>
-      <c r="L351" s="11" t="n"/>
+      <c r="L351" s="11" t="inlineStr">
+        <is>
+          <t>66129254893[기본형]</t>
+        </is>
+      </c>
       <c r="M351" s="11" t="inlineStr"/>
       <c r="N351" s="11" t="inlineStr">
         <is>
@@ -23922,7 +24389,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I354" s="11" t="inlineStr"/>
+      <c r="I354" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J354" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -23931,7 +24402,7 @@
       <c r="K354" s="11" t="inlineStr"/>
       <c r="L354" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717515[M 스포츠, 해외 공용 품번], 66128717499[기본형, 해외 공용 품번], 66128779005[디스플레이키, 해외 공용 품번], 66128717531[인디비주얼, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M354" s="11" t="inlineStr"/>
@@ -23988,7 +24459,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I355" s="11" t="inlineStr"/>
+      <c r="I355" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J355" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -23997,7 +24472,7 @@
       <c r="K355" s="11" t="inlineStr"/>
       <c r="L355" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717515[M 스포츠, 해외 공용 품번], 66128717499[기본형, 해외 공용 품번], 66128779005[디스플레이키, 해외 공용 품번], 66128717531[인디비주얼, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="M355" s="11" t="inlineStr"/>
@@ -25056,14 +25531,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I371" s="11" t="inlineStr"/>
+      <c r="I371" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J371" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K371" s="11" t="inlineStr"/>
-      <c r="L371" s="11" t="n"/>
+      <c r="L371" s="11" t="inlineStr">
+        <is>
+          <t>66128723582[M 스포츠], 66129254893[기본형], 66129254909[럭셔리 라인]</t>
+        </is>
+      </c>
       <c r="M371" s="11" t="inlineStr"/>
       <c r="N371" s="11" t="inlineStr">
         <is>
@@ -25184,14 +25667,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I373" s="11" t="inlineStr"/>
+      <c r="I373" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J373" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
         </is>
       </c>
       <c r="K373" s="11" t="inlineStr"/>
-      <c r="L373" s="11" t="inlineStr"/>
+      <c r="L373" s="11" t="inlineStr">
+        <is>
+          <t>66128723582[M 스포츠], 66129254893[기본형], 66129254909[럭셔리 라인]</t>
+        </is>
+      </c>
       <c r="M373" s="11" t="inlineStr"/>
       <c r="N373" s="17" t="inlineStr">
         <is>
@@ -25246,7 +25737,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I374" s="11" t="inlineStr"/>
+      <c r="I374" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J374" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -25255,7 +25750,7 @@
       <c r="K374" s="11" t="inlineStr"/>
       <c r="L374" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662</t>
+          <t>FCC YGOHUF5662, 66128723582[M 스포츠], 66129254893[기본형], 66129254909[럭셔리 라인]</t>
         </is>
       </c>
       <c r="M374" s="11" t="inlineStr"/>
@@ -25312,7 +25807,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I375" s="11" t="inlineStr"/>
+      <c r="I375" s="11" t="inlineStr">
+        <is>
+          <t>51217268293[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J375" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -25321,7 +25820,7 @@
       <c r="K375" s="11" t="inlineStr"/>
       <c r="L375" s="11" t="inlineStr">
         <is>
-          <t>FCC YGOHUF5662</t>
+          <t>FCC YGOHUF5662, 66128723582[M 스포츠], 66129254893[기본형], 66129254909[럭셔리 라인]</t>
         </is>
       </c>
       <c r="M375" s="11" t="inlineStr"/>
@@ -25510,7 +26009,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I378" s="11" t="inlineStr"/>
+      <c r="I378" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J378" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -25519,7 +26022,7 @@
       <c r="K378" s="11" t="inlineStr"/>
       <c r="L378" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128717519[M 스포츠], 66128717503[기본형], 66128779004[디스플레이키], 66128717535[인디비주얼]</t>
         </is>
       </c>
       <c r="M378" s="11" t="inlineStr"/>
@@ -26509,7 +27012,7 @@
       <c r="K393" s="11" t="inlineStr"/>
       <c r="L393" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV[3버튼]</t>
+          <t>FCC LX8FZV[3버튼], 66126955747[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M393" s="11" t="inlineStr"/>
@@ -26575,7 +27078,7 @@
       <c r="K394" s="11" t="inlineStr"/>
       <c r="L394" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M394" s="11" t="inlineStr"/>
@@ -26698,7 +27201,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I396" s="11" t="inlineStr"/>
+      <c r="I396" s="11" t="inlineStr">
+        <is>
+          <t>51217127047[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J396" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -26707,7 +27214,7 @@
       <c r="K396" s="11" t="inlineStr"/>
       <c r="L396" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M396" s="11" t="inlineStr"/>
@@ -26764,7 +27271,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I397" s="11" t="inlineStr"/>
+      <c r="I397" s="11" t="inlineStr">
+        <is>
+          <t>51217127047[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J397" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -26773,7 +27284,7 @@
       <c r="K397" s="11" t="inlineStr"/>
       <c r="L397" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M397" s="11" t="inlineStr"/>
@@ -26830,7 +27341,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I398" s="11" t="inlineStr"/>
+      <c r="I398" s="11" t="inlineStr">
+        <is>
+          <t>51217127047[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J398" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -26839,7 +27354,7 @@
       <c r="K398" s="11" t="inlineStr"/>
       <c r="L398" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M398" s="11" t="inlineStr"/>
@@ -26896,7 +27411,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I399" s="11" t="inlineStr"/>
+      <c r="I399" s="11" t="inlineStr">
+        <is>
+          <t>51217127047[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J399" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -26905,7 +27424,7 @@
       <c r="K399" s="11" t="inlineStr"/>
       <c r="L399" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M399" s="11" t="inlineStr"/>
@@ -26962,14 +27481,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I400" s="11" t="inlineStr"/>
+      <c r="I400" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J400" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K400" s="11" t="inlineStr"/>
-      <c r="L400" s="11" t="inlineStr"/>
+      <c r="L400" s="11" t="inlineStr">
+        <is>
+          <t>66126986584, 66129268487[컴포트액세스]</t>
+        </is>
+      </c>
       <c r="M400" s="11" t="inlineStr"/>
       <c r="N400" s="11" t="inlineStr">
         <is>
@@ -27288,14 +27815,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I405" s="11" t="inlineStr"/>
+      <c r="I405" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J405" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
         </is>
       </c>
       <c r="K405" s="11" t="inlineStr"/>
-      <c r="L405" s="11" t="inlineStr"/>
+      <c r="L405" s="11" t="inlineStr">
+        <is>
+          <t>66126986584, 66126986580[컴포트액세스]</t>
+        </is>
+      </c>
       <c r="M405" s="11" t="inlineStr"/>
       <c r="N405" s="11" t="inlineStr">
         <is>
@@ -27350,7 +27885,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I406" s="11" t="inlineStr"/>
+      <c r="I406" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J406" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
@@ -27359,7 +27898,7 @@
       <c r="K406" s="11" t="inlineStr"/>
       <c r="L406" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127</t>
+          <t>FCC KR55WK49127, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M406" s="11" t="inlineStr"/>
@@ -27416,7 +27955,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I407" s="11" t="inlineStr"/>
+      <c r="I407" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J407" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -27425,7 +27968,7 @@
       <c r="K407" s="11" t="inlineStr"/>
       <c r="L407" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49123</t>
+          <t>FCC KR55WK49123, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M407" s="11" t="inlineStr"/>
@@ -27482,7 +28025,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I408" s="11" t="inlineStr"/>
+      <c r="I408" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J408" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -27491,7 +28038,7 @@
       <c r="K408" s="11" t="inlineStr"/>
       <c r="L408" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49123, FCC KR55WK49127</t>
+          <t>FCC KR55WK49123, FCC KR55WK49127, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M408" s="11" t="inlineStr"/>
@@ -27548,7 +28095,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I409" s="11" t="inlineStr"/>
+      <c r="I409" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J409" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -27614,7 +28165,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I410" s="11" t="inlineStr"/>
+      <c r="I410" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J410" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -27944,7 +28499,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I415" s="11" t="inlineStr"/>
+      <c r="I415" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J415" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -27953,7 +28512,7 @@
       <c r="K415" s="11" t="inlineStr"/>
       <c r="L415" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128708348, 66128708364[M 스포츠], 66128708340[기본형], 66129855654[디스플레이키], 66128708372[인디비주얼]</t>
         </is>
       </c>
       <c r="M415" s="11" t="inlineStr"/>
@@ -28010,7 +28569,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I416" s="11" t="inlineStr"/>
+      <c r="I416" s="11" t="inlineStr">
+        <is>
+          <t>51217444576[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J416" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -28019,7 +28582,7 @@
       <c r="K416" s="11" t="inlineStr"/>
       <c r="L416" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128708348, 66128708364[M 스포츠], 66128708340[기본형], 66129855654[디스플레이키], 66128708372[인디비주얼]</t>
         </is>
       </c>
       <c r="M416" s="11" t="inlineStr"/>
@@ -28608,7 +29171,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I425" s="11" t="inlineStr"/>
+      <c r="I425" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J425" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -28617,7 +29184,7 @@
       <c r="K425" s="11" t="inlineStr"/>
       <c r="L425" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID2A</t>
+          <t>FCC N5F-ID2A, 66126805997</t>
         </is>
       </c>
       <c r="M425" s="11" t="inlineStr"/>
@@ -28674,7 +29241,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I426" s="11" t="inlineStr"/>
+      <c r="I426" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J426" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -28683,7 +29254,7 @@
       <c r="K426" s="11" t="inlineStr"/>
       <c r="L426" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID2A, FCC NBGIDGNG1</t>
+          <t>FCC N5F-ID2A, FCC NBGIDGNG1, 66126805997</t>
         </is>
       </c>
       <c r="M426" s="11" t="inlineStr"/>
@@ -29198,7 +29769,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I434" s="11" t="n"/>
+      <c r="I434" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J434" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -29207,7 +29782,7 @@
       <c r="K434" s="11" t="n"/>
       <c r="L434" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[3버튼]</t>
+          <t>FCC KR55WK49127[3버튼], 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M434" s="11" t="n"/>
@@ -29264,7 +29839,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I435" s="11" t="n"/>
+      <c r="I435" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J435" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -29273,7 +29852,7 @@
       <c r="K435" s="11" t="n"/>
       <c r="L435" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127[3버튼]</t>
+          <t>FCC KR55WK49127[3버튼], 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M435" s="11" t="n"/>
@@ -29330,7 +29909,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I436" s="11" t="inlineStr"/>
+      <c r="I436" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J436" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -29339,7 +29922,7 @@
       <c r="K436" s="11" t="inlineStr"/>
       <c r="L436" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127</t>
+          <t>FCC KR55WK49127, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M436" s="11" t="inlineStr"/>
@@ -29396,7 +29979,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I437" s="11" t="inlineStr"/>
+      <c r="I437" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J437" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -29405,7 +29992,7 @@
       <c r="K437" s="11" t="inlineStr"/>
       <c r="L437" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147[컴포트액세스], 926886-02[컴포트액세스]</t>
+          <t>FCC KR55WK49147[컴포트액세스], 926886-02[컴포트액세스], 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M437" s="11" t="inlineStr"/>
@@ -29462,7 +30049,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I438" s="11" t="inlineStr"/>
+      <c r="I438" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J438" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -29471,7 +30062,7 @@
       <c r="K438" s="11" t="inlineStr"/>
       <c r="L438" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147, FCC KR55WK49127</t>
+          <t>FCC KR55WK49147, FCC KR55WK49127, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M438" s="11" t="inlineStr"/>
@@ -29528,14 +30119,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I439" s="11" t="inlineStr"/>
+      <c r="I439" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J439" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K439" s="11" t="inlineStr"/>
-      <c r="L439" s="11" t="inlineStr"/>
+      <c r="L439" s="11" t="inlineStr">
+        <is>
+          <t>66126986584, 66126986580[컴포트액세스]</t>
+        </is>
+      </c>
       <c r="M439" s="11" t="inlineStr"/>
       <c r="N439" s="11" t="inlineStr">
         <is>
@@ -29590,7 +30189,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I440" s="11" t="inlineStr"/>
+      <c r="I440" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J440" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -29599,7 +30202,7 @@
       <c r="K440" s="11" t="inlineStr"/>
       <c r="L440" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127, FCC KR55WK49123</t>
+          <t>FCC KR55WK49127, FCC KR55WK49123, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M440" s="11" t="inlineStr"/>
@@ -29656,7 +30259,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I441" s="11" t="inlineStr"/>
+      <c r="I441" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J441" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -29665,7 +30272,7 @@
       <c r="K441" s="11" t="inlineStr"/>
       <c r="L441" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127</t>
+          <t>FCC KR55WK49127, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M441" s="11" t="inlineStr"/>
@@ -29920,7 +30527,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I445" s="11" t="inlineStr"/>
+      <c r="I445" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J445" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -29929,7 +30540,7 @@
       <c r="K445" s="11" t="inlineStr"/>
       <c r="L445" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66126805997</t>
         </is>
       </c>
       <c r="M445" s="11" t="inlineStr"/>
@@ -29986,7 +30597,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I446" s="11" t="inlineStr"/>
+      <c r="I446" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J446" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -29995,7 +30610,7 @@
       <c r="K446" s="11" t="inlineStr"/>
       <c r="L446" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66126805997</t>
         </is>
       </c>
       <c r="M446" s="11" t="inlineStr"/>
@@ -30052,7 +30667,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I447" s="11" t="inlineStr"/>
+      <c r="I447" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J447" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -30061,7 +30680,7 @@
       <c r="K447" s="11" t="inlineStr"/>
       <c r="L447" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66126805997</t>
         </is>
       </c>
       <c r="M447" s="11" t="inlineStr"/>
@@ -30782,7 +31401,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I458" s="11" t="inlineStr"/>
+      <c r="I458" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J458" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -30791,7 +31414,7 @@
       <c r="K458" s="11" t="inlineStr"/>
       <c r="L458" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66126805997</t>
         </is>
       </c>
       <c r="M458" s="11" t="inlineStr"/>
@@ -30848,7 +31471,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I459" s="11" t="inlineStr"/>
+      <c r="I459" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J459" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -30857,7 +31484,7 @@
       <c r="K459" s="11" t="inlineStr"/>
       <c r="L459" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A, FCC NBGIDGNG1</t>
+          <t>FCC N5F-ID21A, FCC NBGIDGNG1, 66126805997</t>
         </is>
       </c>
       <c r="M459" s="11" t="inlineStr"/>
@@ -32199,7 +32826,11 @@
         </is>
       </c>
       <c r="K479" s="11" t="inlineStr"/>
-      <c r="L479" s="11" t="inlineStr"/>
+      <c r="L479" s="11" t="inlineStr">
+        <is>
+          <t>66126955747[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M479" s="11" t="inlineStr"/>
       <c r="N479" s="11" t="inlineStr">
         <is>
@@ -32263,7 +32894,7 @@
       <c r="K480" s="11" t="inlineStr"/>
       <c r="L480" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M480" s="11" t="inlineStr"/>
@@ -32329,7 +32960,7 @@
       <c r="K481" s="11" t="inlineStr"/>
       <c r="L481" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M481" s="11" t="inlineStr"/>
@@ -32395,7 +33026,7 @@
       <c r="K482" s="11" t="inlineStr"/>
       <c r="L482" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M482" s="11" t="inlineStr"/>
@@ -32461,7 +33092,7 @@
       <c r="K483" s="11" t="inlineStr"/>
       <c r="L483" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M483" s="11" t="inlineStr"/>
@@ -32527,7 +33158,7 @@
       <c r="K484" s="11" t="inlineStr"/>
       <c r="L484" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M484" s="11" t="inlineStr"/>
@@ -32593,7 +33224,7 @@
       <c r="K485" s="11" t="inlineStr"/>
       <c r="L485" s="11" t="inlineStr">
         <is>
-          <t>FCC LX8FZV</t>
+          <t>FCC LX8FZV, 66126955747[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M485" s="11" t="inlineStr"/>
@@ -32650,14 +33281,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I486" s="11" t="inlineStr"/>
+      <c r="I486" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J486" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
         </is>
       </c>
       <c r="K486" s="11" t="inlineStr"/>
-      <c r="L486" s="11" t="inlineStr"/>
+      <c r="L486" s="11" t="inlineStr">
+        <is>
+          <t>66126986584, 66126986580[컴포트액세스]</t>
+        </is>
+      </c>
       <c r="M486" s="11" t="inlineStr"/>
       <c r="N486" s="11" t="inlineStr">
         <is>
@@ -32712,7 +33351,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I487" s="11" t="inlineStr"/>
+      <c r="I487" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J487" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -32721,7 +33364,7 @@
       <c r="K487" s="11" t="inlineStr"/>
       <c r="L487" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127</t>
+          <t>FCC KR55WK49127, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M487" s="11" t="inlineStr"/>
@@ -32778,7 +33421,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I488" s="11" t="inlineStr"/>
+      <c r="I488" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J488" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -32787,7 +33434,7 @@
       <c r="K488" s="11" t="inlineStr"/>
       <c r="L488" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49127</t>
+          <t>FCC KR55WK49127, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M488" s="11" t="inlineStr"/>
@@ -32844,7 +33491,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I489" s="11" t="inlineStr"/>
+      <c r="I489" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J489" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -32853,7 +33504,7 @@
       <c r="K489" s="11" t="inlineStr"/>
       <c r="L489" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147[컴포트액세스], FCC KR55WK49127</t>
+          <t>FCC KR55WK49147[컴포트액세스], FCC KR55WK49127, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M489" s="11" t="inlineStr"/>
@@ -32910,7 +33561,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I490" s="11" t="inlineStr"/>
+      <c r="I490" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J490" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -32919,7 +33574,7 @@
       <c r="K490" s="11" t="inlineStr"/>
       <c r="L490" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147, FCC KR55WK49127</t>
+          <t>FCC KR55WK49147, FCC KR55WK49127, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M490" s="11" t="inlineStr"/>
@@ -32976,7 +33631,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I491" s="11" t="inlineStr"/>
+      <c r="I491" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J491" s="11" t="inlineStr">
         <is>
           <t>HU92[세대 기준]</t>
@@ -32985,7 +33644,7 @@
       <c r="K491" s="11" t="inlineStr"/>
       <c r="L491" s="11" t="inlineStr">
         <is>
-          <t>FCC KR55WK49147, FCC KR55WK49127</t>
+          <t>FCC KR55WK49147, FCC KR55WK49127, 66126986584, 66126986580[컴포트액세스]</t>
         </is>
       </c>
       <c r="M491" s="11" t="inlineStr"/>
@@ -33240,7 +33899,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I495" s="11" t="inlineStr"/>
+      <c r="I495" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J495" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -33249,7 +33912,7 @@
       <c r="K495" s="11" t="inlineStr"/>
       <c r="L495" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128708356[M 스포츠], 66128708340[기본형], 66128708372[인디비주얼]</t>
         </is>
       </c>
       <c r="M495" s="11" t="inlineStr"/>
@@ -33306,7 +33969,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I496" s="11" t="inlineStr"/>
+      <c r="I496" s="11" t="inlineStr">
+        <is>
+          <t>51217409076[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J496" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -33315,7 +33982,7 @@
       <c r="K496" s="11" t="inlineStr"/>
       <c r="L496" s="11" t="inlineStr">
         <is>
-          <t>FCC N5F-ID21A</t>
+          <t>FCC N5F-ID21A, 66128708356[M 스포츠], 66128708340[기본형], 66128708372[인디비주얼]</t>
         </is>
       </c>
       <c r="M496" s="11" t="inlineStr"/>
@@ -34098,7 +34765,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I508" s="11" t="inlineStr"/>
+      <c r="I508" s="11" t="inlineStr">
+        <is>
+          <t>51217393289[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J508" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -34107,7 +34778,7 @@
       <c r="K508" s="11" t="inlineStr"/>
       <c r="L508" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66128728010</t>
         </is>
       </c>
       <c r="M508" s="11" t="inlineStr"/>
@@ -34164,7 +34835,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I509" s="11" t="inlineStr"/>
+      <c r="I509" s="11" t="inlineStr">
+        <is>
+          <t>51217393289[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J509" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -34173,7 +34848,7 @@
       <c r="K509" s="11" t="inlineStr"/>
       <c r="L509" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66128728010</t>
         </is>
       </c>
       <c r="M509" s="11" t="inlineStr"/>
@@ -34296,7 +34971,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I511" s="11" t="inlineStr"/>
+      <c r="I511" s="11" t="inlineStr">
+        <is>
+          <t>51217393289[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J511" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -34305,7 +34984,7 @@
       <c r="K511" s="11" t="inlineStr"/>
       <c r="L511" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1[추정]</t>
+          <t>FCC NBGIDGNG1[추정], 66126805981</t>
         </is>
       </c>
       <c r="M511" s="11" t="inlineStr"/>
@@ -34494,7 +35173,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I514" s="11" t="inlineStr"/>
+      <c r="I514" s="11" t="inlineStr">
+        <is>
+          <t>51217393289[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J514" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -34503,7 +35186,7 @@
       <c r="K514" s="11" t="inlineStr"/>
       <c r="L514" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66126805981</t>
         </is>
       </c>
       <c r="M514" s="11" t="inlineStr"/>
@@ -34626,7 +35309,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I516" s="11" t="inlineStr"/>
+      <c r="I516" s="11" t="inlineStr">
+        <is>
+          <t>51217393289[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J516" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -34635,7 +35322,7 @@
       <c r="K516" s="11" t="inlineStr"/>
       <c r="L516" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66128728013</t>
         </is>
       </c>
       <c r="M516" s="11" t="inlineStr"/>
@@ -34692,7 +35379,11 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I517" s="11" t="inlineStr"/>
+      <c r="I517" s="11" t="inlineStr">
+        <is>
+          <t>51217393289[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J517" s="11" t="inlineStr">
         <is>
           <t>HU100R[세대 기준]</t>
@@ -34701,7 +35392,7 @@
       <c r="K517" s="11" t="inlineStr"/>
       <c r="L517" s="11" t="inlineStr">
         <is>
-          <t>FCC NBGIDGNG1</t>
+          <t>FCC NBGIDGNG1, 66128728013</t>
         </is>
       </c>
       <c r="M517" s="11" t="inlineStr"/>
@@ -35934,14 +36625,22 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I536" s="11" t="inlineStr"/>
+      <c r="I536" s="11" t="inlineStr">
+        <is>
+          <t>51217139710[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J536" s="11" t="inlineStr">
         <is>
           <t>HU92</t>
         </is>
       </c>
       <c r="K536" s="11" t="inlineStr"/>
-      <c r="L536" s="11" t="n"/>
+      <c r="L536" s="11" t="inlineStr">
+        <is>
+          <t>66126986584</t>
+        </is>
+      </c>
       <c r="M536" s="11" t="inlineStr"/>
       <c r="N536" s="11" t="inlineStr">
         <is>
@@ -35967,408 +36666,415 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr"/>
+      <c r="A2" s="22" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(1990년대 출시 모델도 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>- 연식이 '현재'인 모델은 2026년식까지, 단종 모델의 마지막 연식은 '2012(단종)' 형식으로 표기했습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템'은 차량 쪽 모듈(EWS3/EWS4, CAS1~CAS4+, FEM, BDC/BDC2/BDC3, BCP)을 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>- '스마트키(부품번호)'에는 BMW 순정 부품번호(66 12 …, 9xxxxxx-xx 등)와 FCC ID(KR55WK…, YGOHUF…, N5F-ID21A, IYZBK1 등)를 함께 적었습니다. CAS1~CAS3의 삽입식 리모컨키도 이 칸에 적고 괄호로 구분했습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>- '키블레이드(부품번호)'는 해당 연식 검색 결과에 직접 나온 경우에만 적었고, 나오지 않은 칸은 공란입니다(기아 파일 규칙과 동일). 카드키·폴딩키는 BMW에 해당 형태가 없어 비워 두었습니다(E65 CAS1 슬롯형 키는 스마트키 칸에 기재).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>- '키블레이드(키웨이)'에 '(세대 기준)'이 붙은 칸은 그 연식 검색에서 키웨이가 직접 확인되지 않아 같은 세대 기준으로 적은 값입니다. '(추정)'은 신형 차종에서 근거가 약한 값입니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 칩 종류 기준으로 기아 파일의 표기 규칙을 그대로 따랐습니다: ID46·ID44 → O/O/O, ID49(Hitag Pro) → X/△/O, ID46·ID49 병기 → △/△/O. (근거: Xhorse 슈퍼칩 비교 — XT27A는 ID49 미지원, XT27B·XT57B는 ID49 지원 표기) 실제 차량 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>- 출처 칸의 사이트명은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 부품몰 원문을 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr"/>
+      <c r="A16" s="22" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가/확인 필요 — 절대 그대로 신뢰해서 작업하지 마세요.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>- 주황색: 출처가 서로 상충하거나 원문으로 직접 확인되지 않은 경우 — 작업 전 VIN/실물 모듈로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>- 전환기(EWS3→EWS4, CAS1→CAS2, CAS2→CAS3, CAS3→CAS3+, CAS4→CAS4+, BDC2→BDC3)는 색 표시 없이 이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr"/>
+      <c r="A21" s="22" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>- CAS4/CAS4+ 키의 칩은 ID49(PCF7953)입니다(Hitag Pro 계열, 이전 초안의 'Hitag2' 표기는 오류였음). 일부 판매처는 이 칩을 'EWS5'로 부르지만 이모빌라이저 이름(EWS)과 헷갈려 쓰지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="21" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>- CAS4+ 도입 시점은 자료마다 다릅니다(2012 중반 이후 생산분 vs 2013년 F10부터) — 2012년식은 주황색.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>- [이모빌라이저 재검증] F20/F22/F30/F32/F80/F82/F87은 LCI 이후에도 FEM(딜러 부품 FEM 61355A7FB57 등) — BDC가 아닙니다. F15/F16/F85/F86/F45/F48/F39/i3/i8은 BDC.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>- BDC2(BDC_G11): G11/G12(~2019.2), G30/G31/G32/F90(~2020.6), G01/G02/F97/F98(~2021.7), G08(~2021.8). 이후 생산분은 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>- BDC3(BDC_G05): G05/G06/G07/G20/G15/G29/F40/F44/G42/G22/G80/G82/G87/F95/F96은 출시부터 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>- BCP: i7/7시리즈 G70·iX(딜러 부품 'Control u.basic computing platform (BCP)' 61355A9A210), U06/U10/U11, G45. G60/i5/G90은 BDC3·BCP 자료 상충(주황색).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>- BDC2 키: N5F-ID21A(9367401-01), 2022년 이후 순정 키: IYZBK1.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>- U섀시(U06/U10/U11)는 BCP 이모빌라이저 + UWB 키(NCF2951/Hitag Pro/ID49, FCC IYZBK1).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>- E65는 2005 LCI 전 CAS1, 이후 CAS2. E60/E61/E63은 2007.3 LCI 전 CAS2, 이후 CAS3. E83은 2006 중 EWS3→EWS4.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="n"/>
+      <c r="A32" s="22" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="21" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="n"/>
+      <c r="A40" s="22" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="A41" s="22" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="21" t="inlineStr">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="22" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="22" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="21" t="n"/>
+      <c r="A49" s="22" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="21" t="inlineStr">
+      <c r="A50" s="22" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="21" t="inlineStr">
+      <c r="A51" s="22" t="inlineStr">
         <is>
           <t>- BMW G60·i5·M5·X7 LCI: 키 프로그래머 업체(Autel·KeyDIY·Xhorse)가 G섀시(G30/G31/G60 2020.7~)를 BDC3, U섀시를 BCP로 구분 — G60은 BDC3 Add Key 대상으로 명시(obdii365·obd2.ltd)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="21" t="inlineStr">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>- BMW XM G09: IYZBK1 키(X5·X6·X7·XM 공용, UWB) — G섀시 BDC3 키 복사·추가 대상(Xhorse G chassis BDC3)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="21" t="inlineStr">
+      <c r="A53" s="22" t="inlineStr">
         <is>
           <t>- BMW X4 F26 2016: 순정 CAS4+ 키 칩은 PCF7953(ID49) — PCF7945P는 "CAS4 modified type" 애프터마켓 키 칩(mk3·vvdi)이라 뺌</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="21" t="inlineStr">
+      <c r="A54" s="22" t="inlineStr">
         <is>
           <t>- BMW E90 CAS3+: 순정 키 칩 PCF7945·PCF7943·PCF7944 모두 ID46(Hitag2) 계열로 병존(bimmerfest·keyecu) — 자료 상충 아님</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="21" t="inlineStr">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>- BMW X3 G45: Lonsdor K518 PRO "2025 BMW X3 UWB에 BCP 키 추가" 절차(U섀시 BCP) 확인 — 이모빌라이저 BCP 확정</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="21" t="inlineStr">
+      <c r="A56" s="22" t="inlineStr">
         <is>
           <t>- BMW X3 F25 2013: CAS4+ 순정 키 칩 PCF7953(ID49) — 같이 적혀 있던 PCF7945P는 중국산 CAS4 호환 키 칩(mr-key·tlkeys 판매품)이라 뺌(X4 F26과 같은 판단)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="21" t="n"/>
+      <c r="A57" s="22" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="21" t="inlineStr">
+      <c r="A58" s="22" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="21" t="inlineStr">
+      <c r="A59" s="22" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="21" t="inlineStr">
+      <c r="A60" s="22" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="21" t="inlineStr">
+      <c r="A61" s="22" t="inlineStr">
         <is>
           <t>- BMW 순정 부품번호(애프터마켓 대체): 비상키 51215A4FBE5 = F40·F44·G20·G22·G26·G42·G80·G82 등 인서트 키(recambiosyaccesoriosbmw), 51215A65D30 = U06·U10·U11·G60·G70·I20 등 인서트 키, 리모컨 66125A473F4(M 스포츠, ECE+RoW+US) = F40·F44·F9x·G01·G42·G87·G80·G82(hubauer·딜러몰), 66125A47402(기본, ECE+RoW) = G01·G02·G08·G11·G12·G30(schmiedmann), 66125A56076(기본, ECE+RoW) = F15·F16·F39·F45·F46·F48(hubauer), 66128708328(기본, ECE+RoW+US) = F40·G29(hubauer), 66125B3E8E1(M, ECE+RoW) = G60·G70·I20·U06·U10·U11 등, 66129362173 = i3 I01 434MHz(66126805980 대체), 51217127047 = X3 E83 도어·점화 키 — 한국 사양(KO) 번호 적용 차종은 미확인이라 [해외 공용 품번]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>- BMW ETK(etkbmw.cc, 카탈로그 03.2019) 키 부품: 한국 사양(L802A National version Korea) 조건 번호가 있으면 그대로(태그 없음), 없으면 국가 제한 없는 번호를 [해외 공용 품번]으로 기재. 한국 사양 CAS 리모컨은 315MHz 저출력 전용 품번(예: 66126986584 = E60·E63·E70·E71·E84·E89 등, 2005.9 이전 E60·E63은 66126933076), E83 X3 한국 사양은 적외선 리모컨 51218374933도 등재. 트림 태그(기본형·스포츠 라인·럭셔리 라인·M 스포츠 등)는 ETK 키 디자인 구분, M 모델은 M·M 스포츠·디스플레이키·컴포트액세스만. 2021년식 이후와 E38·E39는 카탈로그 범위 밖이라 미기재</t>
         </is>
       </c>
     </row>

--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -188,6 +188,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -36673,408 +36676,408 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>이 표는 락스미스(자동차 키 제작/프로그래밍) 참고용입니다.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr"/>
+      <c r="A2" s="23" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>※ 구성</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>- 맨 앞 '브랜드' 컬럼에 브랜드명을 적었습니다(검색 프로그램에서 '기아 K5'처럼 브랜드와 모델명을 함께 검색 가능).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>- '키종류'는 그 연식에 나온 키 형태(막대키·폴딩키·스마트키·카드키)를 모두 적었습니다. 트림별로 다른 경우 함께 적었습니다(예: 폴딩키,스마트키).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>- 키 부품번호는 국내 사양(433/434MHz)만 적었습니다. 미국(315MHz)·유럽(868MHz) 사양 키는 뺐습니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>- '비고'에는 주황색·빨간색 칸의 이유만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>- 컬럼은 '기아_트랜스폰더_칩코드_DBnew.xlsx'와 동일합니다. 모델마다 연식별로 한 행씩, 2000년식부터 기록했습니다(1990년대 출시 모델도 2000년식부터).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>- 연식이 '현재'인 모델은 2026년식까지, 단종 모델의 마지막 연식은 '2012(단종)' 형식으로 표기했습니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>- '이모빌라이저 시스템'은 차량 쪽 모듈(EWS3/EWS4, CAS1~CAS4+, FEM, BDC/BDC2/BDC3, BCP)을 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>- '스마트키(부품번호)'에는 BMW 순정 부품번호(66 12 …, 9xxxxxx-xx 등)와 FCC ID(KR55WK…, YGOHUF…, N5F-ID21A, IYZBK1 등)를 함께 적었습니다. CAS1~CAS3의 삽입식 리모컨키도 이 칸에 적고 괄호로 구분했습니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>- '키블레이드(부품번호)'는 해당 연식 검색 결과에 직접 나온 경우에만 적었고, 나오지 않은 칸은 공란입니다(기아 파일 규칙과 동일). 카드키·폴딩키는 BMW에 해당 형태가 없어 비워 두었습니다(E65 CAS1 슬롯형 키는 스마트키 칸에 기재).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>- '키블레이드(키웨이)'에 '(세대 기준)'이 붙은 칸은 그 연식 검색에서 키웨이가 직접 확인되지 않아 같은 세대 기준으로 적은 값입니다. '(추정)'은 신형 차종에서 근거가 약한 값입니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>- 'XT27A/A66·XT27B·XT57B 호환'은 칩 종류 기준으로 기아 파일의 표기 규칙을 그대로 따랐습니다: ID46·ID44 → O/O/O, ID49(Hitag Pro) → X/△/O, ID46·ID49 병기 → △/△/O. (근거: Xhorse 슈퍼칩 비교 — XT27A는 ID49 미지원, XT27B·XT57B는 ID49 지원 표기) 실제 차량 적용 전 장비로 재확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>- 출처 칸의 사이트명은 해당 연식 검색에서 근거로 쓴 페이지입니다. 이 환경에서는 부품몰 원문을 직접 열 수 없어 검색 결과 요약을 근거로 했습니다.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr"/>
+      <c r="A16" s="23" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>※ 색상</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>- 빨간색: 확인 불가/확인 필요 — 절대 그대로 신뢰해서 작업하지 마세요.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>- 주황색: 출처가 서로 상충하거나 원문으로 직접 확인되지 않은 경우 — 작업 전 VIN/실물 모듈로 재확인.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>- 전환기(EWS3→EWS4, CAS1→CAS2, CAS2→CAS3, CAS3→CAS3+, CAS4→CAS4+, BDC2→BDC3)는 색 표시 없이 이모빌라이저 칸에 전환 전·후를 함께 적었습니다(예: CAS3(2008 중반 이전 생산) / CAS3+(2008 중반 이후 생산)).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr"/>
+      <c r="A21" s="23" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>※ 조사하며 확인된 주요 사항</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>- CAS4/CAS4+ 키의 칩은 ID49(PCF7953)입니다(Hitag Pro 계열, 이전 초안의 'Hitag2' 표기는 오류였음). 일부 판매처는 이 칩을 'EWS5'로 부르지만 이모빌라이저 이름(EWS)과 헷갈려 쓰지 않았습니다.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>- CAS4+ 도입 시점은 자료마다 다릅니다(2012 중반 이후 생산분 vs 2013년 F10부터) — 2012년식은 주황색.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>- [이모빌라이저 재검증] F20/F22/F30/F32/F80/F82/F87은 LCI 이후에도 FEM(딜러 부품 FEM 61355A7FB57 등) — BDC가 아닙니다. F15/F16/F85/F86/F45/F48/F39/i3/i8은 BDC.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>- BDC2(BDC_G11): G11/G12(~2019.2), G30/G31/G32/F90(~2020.6), G01/G02/F97/F98(~2021.7), G08(~2021.8). 이후 생산분은 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>- BDC3(BDC_G05): G05/G06/G07/G20/G15/G29/F40/F44/G42/G22/G80/G82/G87/F95/F96은 출시부터 BDC3.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>- BCP: i7/7시리즈 G70·iX(딜러 부품 'Control u.basic computing platform (BCP)' 61355A9A210), U06/U10/U11, G45. G60/i5/G90은 BDC3·BCP 자료 상충(주황색).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>- BDC2 키: N5F-ID21A(9367401-01), 2022년 이후 순정 키: IYZBK1.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>- U섀시(U06/U10/U11)는 BCP 이모빌라이저 + UWB 키(NCF2951/Hitag Pro/ID49, FCC IYZBK1).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>- E65는 2005 LCI 전 CAS1, 이후 CAS2. E60/E61/E63은 2007.3 LCI 전 CAS2, 이후 CAS3. E83은 2006 중 EWS3→EWS4.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="n"/>
+      <c r="A32" s="23" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="n"/>
+      <c r="A40" s="23" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="inlineStr">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="inlineStr">
+      <c r="A46" s="23" t="inlineStr">
         <is>
           <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="inlineStr">
+      <c r="A47" s="23" t="inlineStr">
         <is>
           <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="A48" s="23" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="n"/>
+      <c r="A49" s="23" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="inlineStr">
+      <c r="A50" s="23" t="inlineStr">
         <is>
           <t>※ 재조사로 확인한 근거 (색을 지운 행)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="inlineStr">
+      <c r="A51" s="23" t="inlineStr">
         <is>
           <t>- BMW G60·i5·M5·X7 LCI: 키 프로그래머 업체(Autel·KeyDIY·Xhorse)가 G섀시(G30/G31/G60 2020.7~)를 BDC3, U섀시를 BCP로 구분 — G60은 BDC3 Add Key 대상으로 명시(obdii365·obd2.ltd)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="23" t="inlineStr">
         <is>
           <t>- BMW XM G09: IYZBK1 키(X5·X6·X7·XM 공용, UWB) — G섀시 BDC3 키 복사·추가 대상(Xhorse G chassis BDC3)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t>- BMW X4 F26 2016: 순정 CAS4+ 키 칩은 PCF7953(ID49) — PCF7945P는 "CAS4 modified type" 애프터마켓 키 칩(mk3·vvdi)이라 뺌</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="A54" s="23" t="inlineStr">
         <is>
           <t>- BMW E90 CAS3+: 순정 키 칩 PCF7945·PCF7943·PCF7944 모두 ID46(Hitag2) 계열로 병존(bimmerfest·keyecu) — 자료 상충 아님</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="inlineStr">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t>- BMW X3 G45: Lonsdor K518 PRO "2025 BMW X3 UWB에 BCP 키 추가" 절차(U섀시 BCP) 확인 — 이모빌라이저 BCP 확정</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="inlineStr">
+      <c r="A56" s="23" t="inlineStr">
         <is>
           <t>- BMW X3 F25 2013: CAS4+ 순정 키 칩 PCF7953(ID49) — 같이 적혀 있던 PCF7945P는 중국산 CAS4 호환 키 칩(mr-key·tlkeys 판매품)이라 뺌(X4 F26과 같은 판단)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="n"/>
+      <c r="A57" s="23" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="inlineStr">
+      <c r="A58" s="23" t="inlineStr">
         <is>
           <t>※ 행 구분 규칙</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="22" t="inlineStr">
+      <c r="A59" s="23" t="inlineStr">
         <is>
           <t>- 연식 중간에 칩·이모빌라이저·키가 바뀐 해는 바뀌기 전·후를 따로 행으로 나눔. 세대가 바뀌면 세대별 모델명으로 1행씩, 같은 세대 안의 변경(부분변경·생산 시기·키 변경)은 같은 모델명으로 나누고 칸 안의 [생산 시기]·[세대] 표기로 구분</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="22" t="inlineStr">
+      <c r="A60" s="23" t="inlineStr">
         <is>
           <t>- 같은 연식·모델에 행이 2개인데 칸에 시기 표기가 없으면(예: 벤츠 FBS3 행과 FBS4 행) 전환 시점 자료가 없는 것 — 주황색, 비고의 방법(VIN 등)으로 확인</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="22" t="inlineStr">
+      <c r="A61" s="23" t="inlineStr">
         <is>
           <t>- BMW 순정 부품번호(애프터마켓 대체): 비상키 51215A4FBE5 = F40·F44·G20·G22·G26·G42·G80·G82 등 인서트 키(recambiosyaccesoriosbmw), 51215A65D30 = U06·U10·U11·G60·G70·I20 등 인서트 키, 리모컨 66125A473F4(M 스포츠, ECE+RoW+US) = F40·F44·F9x·G01·G42·G87·G80·G82(hubauer·딜러몰), 66125A47402(기본, ECE+RoW) = G01·G02·G08·G11·G12·G30(schmiedmann), 66125A56076(기본, ECE+RoW) = F15·F16·F39·F45·F46·F48(hubauer), 66128708328(기본, ECE+RoW+US) = F40·G29(hubauer), 66125B3E8E1(M, ECE+RoW) = G60·G70·I20·U06·U10·U11 등, 66129362173 = i3 I01 434MHz(66126805980 대체), 51217127047 = X3 E83 도어·점화 키 — 한국 사양(KO) 번호 적용 차종은 미확인이라 [해외 공용 품번]</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="22" t="inlineStr">
-        <is>
-          <t>- BMW ETK(etkbmw.cc, 카탈로그 03.2019) 키 부품: 한국 사양(L802A National version Korea) 조건 번호가 있으면 그대로(태그 없음), 없으면 국가 제한 없는 번호를 [해외 공용 품번]으로 기재. 한국 사양 CAS 리모컨은 315MHz 저출력 전용 품번(예: 66126986584 = E60·E63·E70·E71·E84·E89 등, 2005.9 이전 E60·E63은 66126933076), E83 X3 한국 사양은 적외선 리모컨 51218374933도 등재. 트림 태그(기본형·스포츠 라인·럭셔리 라인·M 스포츠 등)는 ETK 키 디자인 구분, M 모델은 M·M 스포츠·디스플레이키·컴포트액세스만. 2021년식 이후와 E38·E39는 카탈로그 범위 밖이라 미기재</t>
+      <c r="A62" s="23" t="inlineStr">
+        <is>
+          <t>- BMW ETK(etkbmw.cc, 카탈로그 03.2019) 키 부품: 한국 사양(L802A National version Korea) 조건 번호가 있으면 그대로(태그 없음), 없으면 국가 제한 없는 번호를 [해외 공용 품번]으로 기재. 주파수: F·G·I 계열(2009년경~) 한국 사양 키는 434MHz(ETK 표기 434 MHZ KO·KOREA). 단 E 계열(CAS2·CAS3, 2003~2014년경 E60·E63·E65·E70·E71·E84·E89·E8x·1M)은 ETK에서 한국 사양(L802A 적용) 키가 315MHz 저출력(일본과 공용)으로만 등재되고 434MHz 키(예: 66126933075·66126986582)는 한국 사양 제외(L802A 미적용) 조건이라, 국내 사양 번호로 315MHz 저출력 품번을 기재(예: 66126986584, 2005.9 이전 E60·E63은 66126933076, 컴포트액세스 66126986580·66129268487, E65 66126959045). E83 X3 한국 사양은 적외선 리모컨 51218374933도 등재. 트림 태그(기본형·스포츠 라인·럭셔리 라인·M 스포츠 등)는 ETK 키 디자인 구분, M 모델은 M·M 스포츠·디스플레이키·컴포트액세스만. 2021년식 이후와 E38·E39는 카탈로그 범위 밖이라 미기재</t>
         </is>
       </c>
     </row>

--- a/BMW_코리아_출시모델.xlsx
+++ b/BMW_코리아_출시모델.xlsx
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -188,6 +188,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -2851,7 +2854,11 @@
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
-      <c r="L34" s="11" t="inlineStr"/>
+      <c r="L34" s="11" t="inlineStr">
+        <is>
+          <t>FCC N5F-ID21A</t>
+        </is>
+      </c>
       <c r="M34" s="11" t="inlineStr"/>
       <c r="N34" s="11" t="inlineStr">
         <is>
@@ -2860,7 +2867,7 @@
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>bmwpartsnow.com, instacarkey.com(FEM/BDC), rallyebmw.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>bmwpartsnow.com, instacarkey.com(FEM/BDC), rallyebmw.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표, 같은 세대·같은 칩 앞 연식 스마트키 품번과 동일(BMW ETK 03.2019판 이후 연식이라 이어 씀)</t>
         </is>
       </c>
       <c r="P34" s="11" t="inlineStr"/>
@@ -4187,7 +4194,11 @@
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr"/>
-      <c r="L54" s="11" t="n"/>
+      <c r="L54" s="11" t="inlineStr">
+        <is>
+          <t>66126805997</t>
+        </is>
+      </c>
       <c r="M54" s="11" t="inlineStr"/>
       <c r="N54" s="11" t="inlineStr">
         <is>
@@ -4196,7 +4207,7 @@
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>autokeys247.com(F45 2014-2021 3버튼 키), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>autokeys247.com(F45 2014-2021 3버튼 키), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기, 같은 세대·같은 칩 앞 연식 스마트키 품번과 동일(BMW ETK 03.2019판 이후 연식이라 이어 씀)</t>
         </is>
       </c>
       <c r="P54" s="11" t="inlineStr"/>
@@ -4249,7 +4260,11 @@
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr"/>
-      <c r="L55" s="11" t="inlineStr"/>
+      <c r="L55" s="11" t="inlineStr">
+        <is>
+          <t>66126805997</t>
+        </is>
+      </c>
       <c r="M55" s="11" t="inlineStr"/>
       <c r="N55" s="11" t="inlineStr">
         <is>
@@ -4258,7 +4273,7 @@
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(F45 → U06 교체), go-parts.com(2014-2024 BDC), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기</t>
+          <t>wikipedia(F45 → U06 교체), go-parts.com(2014-2024 BDC), 이모빌라이저 검증: 딜러 부품 카탈로그 BDC(Body Domain Controller) 표기, 같은 세대·같은 칩 앞 연식 스마트키 품번과 동일(BMW ETK 03.2019판 이후 연식이라 이어 씀)</t>
         </is>
       </c>
       <c r="P55" s="11" t="inlineStr"/>
@@ -4901,7 +4916,11 @@
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr"/>
-      <c r="L65" s="11" t="inlineStr"/>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1[추정]</t>
+        </is>
+      </c>
       <c r="M65" s="11" t="inlineStr"/>
       <c r="N65" s="11" t="inlineStr">
         <is>
@@ -4910,7 +4929,7 @@
       </c>
       <c r="O65" s="11" t="inlineStr">
         <is>
-          <t>fcpeuro.com, bmwpartsnow.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>fcpeuro.com, bmwpartsnow.com, 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표, 같은 세대·같은 칩 앞 연식 스마트키 품번과 동일(BMW ETK 03.2019판 이후 연식이라 이어 씀)</t>
         </is>
       </c>
       <c r="P65" s="11" t="inlineStr"/>
@@ -4963,7 +4982,11 @@
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr"/>
-      <c r="L66" s="11" t="n"/>
+      <c r="L66" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1[추정]</t>
+        </is>
+      </c>
       <c r="M66" s="11" t="inlineStr"/>
       <c r="N66" s="11" t="inlineStr">
         <is>
@@ -4972,7 +4995,7 @@
       </c>
       <c r="O66" s="11" t="inlineStr">
         <is>
-          <t>go-parts.com(228i F44: BDC2 기재), ebay.de(F44 2020-2025 순정 리모컨), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표</t>
+          <t>go-parts.com(228i F44: BDC2 기재), ebay.de(F44 2020-2025 순정 리모컨), 이모빌라이저 검증: BDC3=BDC_G05(SP2018 플랫폼, 출시부터 BDC3) — Xhorse/Yanhua BDC 적용표, 같은 세대·같은 칩 앞 연식 스마트키 품번과 동일(BMW ETK 03.2019판 이후 연식이라 이어 씀)</t>
         </is>
       </c>
       <c r="P66" s="11" t="inlineStr"/>
@@ -14803,7 +14826,11 @@
         </is>
       </c>
       <c r="K212" s="11" t="inlineStr"/>
-      <c r="L212" s="11" t="n"/>
+      <c r="L212" s="11" t="inlineStr">
+        <is>
+          <t>FCC IYZBK1</t>
+        </is>
+      </c>
       <c r="M212" s="11" t="inlineStr"/>
       <c r="N212" s="17" t="inlineStr">
         <is>
@@ -14812,7 +14839,7 @@
       </c>
       <c r="O212" s="11" t="inlineStr">
         <is>
-          <t>g90.bimmerpost.com(2026 M5: 키 1개·디지털키 카드·서비스 카드 제공)</t>
+          <t>g90.bimmerpost.com(2026 M5: 키 1개·디지털키 카드·서비스 카드 제공), 같은 세대·같은 칩 앞 연식 스마트키 품번과 동일(BMW ETK 03.2019판 이후 연식이라 이어 씀)</t>
         </is>
       </c>
       <c r="P212" s="17" t="n"/>
@@ -21621,7 +21648,11 @@
         </is>
       </c>
       <c r="K313" s="11" t="inlineStr"/>
-      <c r="L313" s="11" t="inlineStr"/>
+      <c r="L313" s="11" t="inlineStr">
+        <is>
+          <t>66126805990[기본형, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M313" s="11" t="inlineStr"/>
       <c r="N313" s="11" t="inlineStr">
         <is>
@@ -21630,7 +21661,7 @@
       </c>
       <c r="O313" s="11" t="inlineStr">
         <is>
-          <t>kfz-sicherungen.com(X1 F48/F49 2015-2022 BDC 퓨즈), go-parts.com(2014-2024 BDC)</t>
+          <t>kfz-sicherungen.com(X1 F48/F49 2015-2022 BDC 퓨즈), go-parts.com(2014-2024 BDC), 같은 세대·같은 칩 앞 연식 스마트키 품번과 동일(BMW ETK 03.2019판 이후 연식이라 이어 씀)</t>
         </is>
       </c>
       <c r="P313" s="11" t="inlineStr"/>
@@ -21683,7 +21714,11 @@
         </is>
       </c>
       <c r="K314" s="11" t="inlineStr"/>
-      <c r="L314" s="11" t="inlineStr"/>
+      <c r="L314" s="11" t="inlineStr">
+        <is>
+          <t>66126805990[기본형, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M314" s="11" t="inlineStr"/>
       <c r="N314" s="11" t="inlineStr">
         <is>
@@ -21692,7 +21727,7 @@
       </c>
       <c r="O314" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(F48 2015-2022), kfz-sicherungen.com</t>
+          <t>wikipedia(F48 2015-2022), kfz-sicherungen.com, 같은 세대·같은 칩 앞 연식 스마트키 품번과 동일(BMW ETK 03.2019판 이후 연식이라 이어 씀)</t>
         </is>
       </c>
       <c r="P314" s="11" t="inlineStr"/>
@@ -22495,7 +22530,11 @@
         </is>
       </c>
       <c r="K326" s="11" t="inlineStr"/>
-      <c r="L326" s="11" t="n"/>
+      <c r="L326" s="11" t="inlineStr">
+        <is>
+          <t>NBGIDGNG1-08</t>
+        </is>
+      </c>
       <c r="M326" s="11" t="inlineStr"/>
       <c r="N326" s="11" t="inlineStr">
         <is>
@@ -22504,7 +22543,7 @@
       </c>
       <c r="O326" s="11" t="inlineStr">
         <is>
-          <t>ebay(2018-2023 X2 F39 키), fcpeuro.com(X2 키)</t>
+          <t>ebay(2018-2023 X2 F39 키), fcpeuro.com(X2 키), 같은 세대·같은 칩 앞 연식 스마트키 품번과 동일(BMW ETK 03.2019판 이후 연식이라 이어 씀)</t>
         </is>
       </c>
       <c r="P326" s="11" t="inlineStr"/>
@@ -22557,7 +22596,11 @@
         </is>
       </c>
       <c r="K327" s="11" t="inlineStr"/>
-      <c r="L327" s="11" t="n"/>
+      <c r="L327" s="11" t="inlineStr">
+        <is>
+          <t>NBGIDGNG1-08</t>
+        </is>
+      </c>
       <c r="M327" s="11" t="inlineStr"/>
       <c r="N327" s="11" t="inlineStr">
         <is>
@@ -22566,7 +22609,7 @@
       </c>
       <c r="O327" s="11" t="inlineStr">
         <is>
-          <t>ebay(2018-2023 X2 F39 키)</t>
+          <t>ebay(2018-2023 X2 F39 키), 같은 세대·같은 칩 앞 연식 스마트키 품번과 동일(BMW ETK 03.2019판 이후 연식이라 이어 씀)</t>
         </is>
       </c>
       <c r="P327" s="11" t="inlineStr"/>
@@ -22619,7 +22662,11 @@
         </is>
       </c>
       <c r="K328" s="11" t="inlineStr"/>
-      <c r="L328" s="11" t="n"/>
+      <c r="L328" s="11" t="inlineStr">
+        <is>
+          <t>NBGIDGNG1-08</t>
+        </is>
+      </c>
       <c r="M328" s="11" t="inlineStr"/>
       <c r="N328" s="11" t="inlineStr">
         <is>
@@ -22628,7 +22675,7 @@
       </c>
       <c r="O328" s="11" t="inlineStr">
         <is>
-          <t>wikipedia(X2 F39 생산 2023.10.11 종료), ebay(2018-2023)</t>
+          <t>wikipedia(X2 F39 생산 2023.10.11 종료), ebay(2018-2023), 같은 세대·같은 칩 앞 연식 스마트키 품번과 동일(BMW ETK 03.2019판 이후 연식이라 이어 씀)</t>
         </is>
       </c>
       <c r="P328" s="11" t="inlineStr"/>
@@ -36669,7 +36716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A62"/>
+  <dimension ref="A1:A63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -37081,6 +37128,13 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>- 6차 세대별 보완: ETK(03.2019판) 이후 연식 중 칩이 같은 행(BDC3 변형 제외)은 같은 세대 앞 연식 스마트키 품번을 이어 씀</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
